--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8077,6 +8077,4659 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ENG-20260527-163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>hit a valuation / mark</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>/hɪt ə væljuˈeɪʃən / mɑːrk/</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>특정 가치나 목표치에 도달하다, 돌파하다.</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>The startup aims to hit a valuation of $10 billion within five years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ENG-20260527-164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>lift stock prices</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>/lɪft stɑːk praɪsɪz/</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>주가를 끌어올리다, 상승시키다.</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>AI boom lifts South Korean chip stocks</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Positive earnings reports often lift stock prices across the market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ENG-20260527-165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>soar over X percent</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>/sɔːr ˈoʊvər ɛks pərˌsɛnt/</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>(주가, 수치 등이) X퍼센트 이상 급등하다.</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Shares of SK Hynix soared over 11% on Wednesday</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>The company's revenue is expected to soar over 20% this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ENG-20260527-166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>push something above a mark</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>/pʊʃ ˈsʌmθɪŋ əˈbʌv ə mɑːrk/</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>~을 특정 수준/기준점 이상으로 끌어올리다.</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>pushing the South Korean memory-chip maker above the $1 trillion market capitalization mark.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Their innovative product could push the company's profits above its competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ENG-20260527-167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>endorse someone</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>/ɛnˈdɔːrs ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>~를 공개적으로 지지하다.</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>President Donald Trump last week endorsed Texas Attorney General Ken Paxton</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Many celebrities endorsed the candidate, hoping to influence public opinion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ENG-20260527-168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>reignite chatter / speculation</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>/riːɪɡˈnaɪt ˈʧætər / ˌspɛkjuˈleɪʃən/</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>(소문, 추측 등이) 다시 불붙다, 재점화되다.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>SpaceX-Tesla merger chatter reignites</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>The CEO's cryptic remarks reignited speculation about a potential acquisition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ENG-20260527-169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>head for public markets</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>/hɛd fɔːr ˈpʌblɪk ˈmɑːrkɪts/</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>(회사가) 주식 시장에 상장되다, 공모하다.</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>With SpaceX headed for the public markets next month</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>The tech firm announced its plans to head for public markets early next year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ENG-20260527-170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>speculate about something</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>/ˈspɛkjuˌleɪt əˈbaʊt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>~에 대해 추측/짐작하다.</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>industry experts and people close to Elon Musk are speculating about a potential tie-up with Tesla.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Analysts are speculating about the central bank's next move regarding interest rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ENG-20260527-171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>form a tie-up</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>/fɔːrm ə taɪ-ʌp/</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>(회사 간의) 제휴/협력을 맺다.</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>speculating about a potential tie-up with Tesla.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>The two companies decided to form a tie-up to develop new AI technologies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ENG-20260527-172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>top an amount</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>/tɑːp ən əˈmaʊnt/</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>(금액/수치 면에서) ~를 넘어서다, 최고치를 기록하다.</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>the latest companies to top $1 trillion in market capitalization</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>The blockbuster movie topped $1 billion in global box office revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ENG-20260527-173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>resume a rally</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>/rɪˈzuːm ə ˈræli/</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>(주가, 시장 등의) 반등세가 재개되다.</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>as the AI rally resumes.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>After a brief dip, the market is expected to resume a rally next week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ENG-20260527-174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>keep something secret</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>/kiːp ˈsʌmθɪŋ ˈsiːkrɪt/</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>~를 비밀로 유지하다.</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>their name is being kept secret by a disciplinary panel.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>It's important to keep customer data secret to maintain trust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ENG-20260527-175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>hold below an amount</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>/hoʊld bɪˈloʊ ən əˈmaʊnt/</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>(가격 등이) 특정 금액/수준 아래를 유지하다.</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>oil prices hold below $100</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>We hope the cost of raw materials will hold below our projected budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ENG-20260527-176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>assess operations / a situation</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>/əˈsɛs ˌɑpəˈreɪʃənz / ə ˌsɪʧuˈeɪʃən/</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>작전/상황을 평가하다, 검토하다.</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>regional investors assess the latest military operations against Iran.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>The committee will assess the situation and propose a course of action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ENG-20260527-177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>double down on something</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>/ˈdʌbl daʊn ɑn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>~에 더욱 전념하다, 투자를 강화하다.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>European companies double down on China manufacturing</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Despite recent setbacks, the company decided to double down on its renewable energy investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ENG-20260527-178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>de-risk supply chains</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>/diː-rɪsk səˈplaɪ ʧeɪnz/</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>공급망의 위험을 줄이다.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>despite EU de-risking push</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Governments are urging companies to de-risk supply chains by diversifying their suppliers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ENG-20260527-179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>reduce reliance on something</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>/rɪˈduːs rɪˈlaɪəns ɑn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>~에 대한 의존도를 줄이다.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>reduce overseas reliance.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Many countries are trying to reduce reliance on imported oil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ENG-20260527-180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>grow barriers</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>/ɡroʊ ˈbæriərz/</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>(장벽이) 높아지다.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Barriers grow for international students seeking U.S. jobs</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cultural differences can grow barriers to effective communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ENG-20260527-181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>collapse a dream</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>/kəˈlæps ə driːm/</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>(꿈, 희망 등이) 좌절되다, 무너지다.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>The 'American dream ... is collapsing'</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>A sudden illness can unfortunately collapse one's dream of pursuing a career.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ENG-20260527-182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>face a weak hiring market</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>/feɪs ə wiːk ˈhaɪrɪŋ ˈmɑːrkɪt/</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>고용 시장의 침체를 겪다.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>International graduates say a weak hiring market... make it harder</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>New graduates often face a weak hiring market during economic downturns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ENG-20260527-183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>be entrenched in something</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>/biː ɛnˈtrɛnʧt ɪn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>~에 깊이 빠져있다, ~에 뿌리박혀 있다.</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Americans are 'entrenched' in financial stress amid debt and price pressures</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>The company seems to be entrenched in outdated practices, resisting any change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ENG-20260527-184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>grapple with pressures</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>/ˈɡræpl wɪθ ˈprɛʃərz/</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>압력/어려움과 씨름하다, 고심하다.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>amid debt and price pressures</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Businesses often grapple with pressures from rising costs and fierce competition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ENG-20260527-185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>help with debt management</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>/hɛlp wɪð dɛt ˈmænɪʤmənt/</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>채무 관리를 돕다.</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Nonprofits can help with debt mangement.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Financial advisors can help with debt management and create a budget plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ENG-20260527-186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>energy bills rise</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>/ˈɛnərʤi bɪlz raɪz/</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>에너지 요금이 오르다.</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Energy bills to rise for millions as impact of Iran war hits</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>With colder weather approaching, many expect their energy bills to rise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ENG-20260527-187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>the impact of something hit</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>/ði ˈɪmpækt ʌv ˈsʌmθɪŋ hɪt/</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>~의 영향이 미치다.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>as impact of Iran war hits</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>The full impact of the new regulations will hit the industry next quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ENG-20260527-188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>pay X amount more</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>/peɪ ɛks əˈmaʊnt mɔːr/</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>X 금액만큼 더 지불하다.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>A household using a typical amount of energy will pay £221 a year more</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Consumers will have to pay 5% more for imported goods due to new tariffs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ENG-20260527-189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>impose a price cap</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>/ɪmˈpoʊz ə praɪs kæp/</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>가격 상한선을 부과하다/설정하다.</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>under the regulator's new price cap.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>The government decided to impose a price cap on essential food items to help low-income families.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ENG-20260527-190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>exhibit bullying behavior</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>/ɪɡˈzɪbɪt ˈbʊliɪŋ bɪˈheɪvjər/</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>괴롭힘/갑질 행위를 보이다.</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>'Bullying' and 'overbearing' behaviour behind abrupt BP chairman removal</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>The company has a zero-tolerance policy for employees who exhibit bullying behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ENG-20260527-191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>abruptly remove someone</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>/əˈbrʌptli rɪˈmuːv ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>~를 갑작스럽게 해고하다/제거하다.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>abrupt BP chairman removal</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>The board decided to abruptly remove the CEO following the scandal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ENG-20260527-192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>join the list of something</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>/ʤɔɪn ðə lɪst ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>~의 명단에 합류하다.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>SK Hynix and Micron are the latest tech firms to join the growing list of stocks with mega valuations.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>She hopes her novel will join the list of bestsellers this year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ENG-20260527-193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>unveil a product</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>/ʌnˈveɪl ə ˈprɑːdʌkt/</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>신제품을 공개하다, 베일을 벗기다.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>after it unveils first fully electric car</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>The tech giant is set to unveil its new smartphone at a highly anticipated event next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ENG-20260527-194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>face intense pressure from someone</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>/feɪs ɪnˈtɛns ˈprɛʃər frʌm ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>~로부터 강한 압력을 받다.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>despite intense pressure from Chinese EV makers.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>The government is facing intense pressure from environmental groups to implement stricter regulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ENG-20260527-195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>issue a warning</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>/ˈɪʃuː ə ˈwɔːrnɪŋ/</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>경고를 발하다/내놓다.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Farmers' warning as milk prices fall below cost</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>The meteorology office issued a warning for heavy rain and strong winds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ENG-20260527-196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>sell family farms</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>/sɛl ˈfæməli fɑːrmz/</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>가업 농장을 팔다.</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Farmers worry more family farms will be sold unless dairy prices rise quickly.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Many small farmers are struggling and may have to sell family farms to survive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ENG-20260527-197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ads be banned</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>/ædz biː bænd/</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>광고가 금지되다.</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Instagram betting ads featuring Kane and Haaland banned</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Many controversial ads were banned from television during prime time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ENG-20260527-198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>make it harder for someone to do something</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>/meɪk ɪt ˈhɑːrdər fɔːr ˈsʌmwʌn tuː duː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>~가 ~하기 더 어렵게 만들다.</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>AI tools like Mythos will make it harder for people like her to compete.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Lack of funding will make it harder for researchers to complete their projects on time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ENG-20260527-199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>compete fiercely</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>/kəmˈpiːt ˈfɪrsli/</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>치열하게 경쟁하다.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>make competing harder</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>In today's global market, companies must innovate to compete fiercely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ENG-20260527-200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>delay an investigation</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>/dɪˈleɪ ən ɪnˌvɛstɪˈɡeɪʃən/</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>조사를 지연시키다.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Post Office investigation could be delayed by five years</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Unexpected obstacles could delay an investigation into the cause of the accident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ENG-20260527-201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>welcome a move / plan</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>/ˈwɛlkəm ə muːv / plæn/</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>(정부 등의) 조치/계획을 환영하다.</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Campaigners welcome the move but say passengers are mostly worried about train fares and delays.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Environmentalists welcome a new government plan to reduce carbon emissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ENG-20260527-202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>be worried about something</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>/biː ˈwɜːrid əˈbaʊt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>~에 대해 걱정하다, 염려하다.</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>passengers are mostly worried about train fares and delays.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Parents are worried about their children's safety at school.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ENG-20260527-203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>experience a dramatic fall</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>/ɪkˈspɪəriəns ə drəˈmætɪk fɔːl/</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>급격한 하락/감소를 겪다.</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Lord Wolfson warns of 'dramatic' fall in entry-level jobs</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>The tourism industry experienced a dramatic fall in visitors during the pandemic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ENG-20260527-204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>receive a number of applicants</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>/rɪˈsiːv ə ˈnʌmbər ʌv ˈæplɪkənts/</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>~명의 지원자를 받다.</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Next now typically receives double the number of applicants for one role than it did two years ago.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Our internship program received a record number of applicants this year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ENG-20260527-205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>get someone another drink</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmwʌn əˈnʌðər drɪŋk/</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>~에게 술/음료 한 잔 더 가져다주다.</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Can I get you another glass of wine?</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>The waiter asked if he could get us another drink.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ENG-20260527-206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>be drunk</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>/biː drʌŋk/</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>술에 취하다.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>I don't wanna be drunk when I go home alone.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>It's dangerous to drive when you're drunk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ENG-20260527-207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>stand someone up</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>/stænd ˈsʌmwʌn ʌp/</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>~를 바람맞히다, 약속 장소에 나타나지 않다.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Got stood up, huh?</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>I can't believe he stood me up on our first date!</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ENG-20260527-208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>be no big deal</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>/biː noʊ bɪɡ diːl/</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>별일 아니다, 대수롭지 않다.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Yeah, it's no big deal. It's just a blind date.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Don't worry about the spilled coffee; it's no big deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ENG-20260527-209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>go on a blind date</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ɑn ə blaɪnd deɪt/</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>소개팅을 하다.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>It's just a blind date.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>My friend tried to set me up, but I'm hesitant to go on a blind date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ENG-20260527-210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>emerge from somewhere</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>/ɪˈmɜːrdʒ frʌm ˈsʌmˌwɛr/</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>~에서 나오다, 나타나다.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Monica emerges from the bathroom.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>The celebrity emerged from the hotel to a crowd of cheering fans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ENG-20260527-211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>be ovulating</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>/biː ˈɑːvjəleɪtɪŋ/</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>배란 중이다.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>We're okay. I'm still ovulating.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Many women track their cycle to know when they are ovulating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ENG-20260527-212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>as of X time / date</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>/æz ʌv ɛks taɪm / deɪt/</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>X 시점/날짜부로.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>as of four o'clock this afternoon, I am not.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>The new policy will be effective as of January 1st.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ENG-20260527-213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>give it a minute</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>/ɡɪv ɪt ə ˈmɪnɪt/</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>잠깐만 기다려봐, 잠시 시간을 줘.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>I know you're not eighteen anymore, but give it a minute.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>The system is rebooting; just give it a minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ENG-20260527-214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>forget someone is here</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>/fərˈɡɛt ˈsʌmwʌn ɪz hɪr/</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>~가 여기 있다는 것을 잊다.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Oh, sweetie, I forgot you were here.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>I'm sorry, I was so engrossed in my work, I completely forgot you were here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ENG-20260527-215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>leave someone alone</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>/liːv ˈsʌmwʌn əˈloʊn/</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>~를 혼자 내버려두다.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>We can't leave her alone.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Please leave me alone; I need some time to think.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ENG-20260527-216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>be aware of something</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>/biː əˈwɛr ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>~를 인지하다, 인식하다.</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>how much can she even be aware of at this age?</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Are you aware of the potential risks involved in this investment?</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ENG-20260527-217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>start canoodling</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>/stɑːrt kəˈnuːdlɪŋ/</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>(특히 공공장소에서) 애정 행각을 시작하다.</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>She may notice if we start... canoodling in it.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>They started canoodling in the park, much to the amusement of passersby.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ENG-20260527-218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>say something in front of someone</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>/seɪ ˈsʌmθɪŋ ɪn frʌnt ʌv ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>~ 앞에서 ~를 말하다.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>I can't say "hump" or "screw" in front of the B-A-B-Y.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>You shouldn't say such things in front of children.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ENG-20260527-219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>be horrifying / scarring</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>/biː ˈhɔːrəˌfaɪɪŋ / ˈskɑːrɪŋ/</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>소름끼치다 / 트라우마를 남기다.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Horrifying? Scarring?</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>The images of the war were truly horrifying and scarring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ENG-20260527-220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>guess someone is right</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>/ɡɛs ˈsʌmwʌn ɪz raɪt/</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>~의 말이 맞는 것 같다.</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>I guess you're right.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>After reconsidering the facts, I guess you're right about the solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ENG-20260527-221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>stare through something</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>/stɛr θruː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>~를 통해 응시하다.</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>you thought a deer was staring through the window.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>She stared through the rain-streaked window, lost in thought.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ENG-20260527-222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>be out of someone's league</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>/biː aʊt ʌv ˈsʌmwʌnz liːɡ/</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>~의 수준을 훨씬 벗어나다, 넘사벽이다.</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Oh, come on, you're way out of my league.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>He's a famous supermodel; she felt he was completely out of her league.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ENG-20260527-223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>rule out something</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>/ruːl aʊt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>~를 배제하다, 가능성을 제외하다.</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>let's not rule out nervous laughter.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Investigators have not ruled out the possibility of foul play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ENG-20260527-224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>own a business</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>/oʊn ə ˈbɪznɪs/</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>사업체를 소유하다, 운영하다.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Phoebe told me that - that you owned your own restaurant.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>It's always been my dream to own a business and be my own boss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ENG-20260527-225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>lose something to something else</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>/luːz ˈsʌmθɪŋ tuː ˈsʌmθɪŋ ɛls/</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>~때문에 ~를 잃다.</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>I lost it. To drugs.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Many people lose their savings to risky investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ENG-20260527-226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>do something for no money</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>/duː ˈsʌmθɪŋ fɔːr noʊ ˈmʌni/</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>무급으로 ~를 하다, 돈을 받지 않고 ~를 하다.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>It's really fulfilling doing something you hate for no money.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Volunteers often do something for no money simply because they believe in the cause.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ENG-20260527-227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>be infertile</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>/biː ɪnˈfɜːrtaɪl/</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>불임이다.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>I'm pretty sure I'm infertile.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>The couple was heartbroken to learn they were infertile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ENG-20260527-228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>hunt someone down</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>/hʌnt ˈsʌmwʌn daʊn/</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>~를 추적하여 찾아내다.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>I'm going to hunt you down and kill you!</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>The detective vowed to hunt down the culprits and bring them to justice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ENG-20260527-229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>set someone up with someone</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>/sɛt ˈsʌmwʌn ʌp wɪð ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>~를 ~와 소개시켜 주다.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>How could you set me up with this creep?</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>My sister tried to set me up with her colleague, but I politely declined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ENG-20260527-230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>be a nightmare</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>/biː ə ˈnaɪtˌmɛr/</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>(사람/상황이) 정말 지긋지긋하다/끔찍하다.</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>This guy is a nightmare!</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Planning a wedding can sometimes be a nightmare, with all the details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ENG-20260527-231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>get stoned</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>/ɡɛt stoʊnd/</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>마리화나 등에 취하다.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>he gets a little crazy when he's stoned.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Some people experiment with drugs to get stoned, but it's very dangerous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ENG-20260527-232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>go out for something</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>/ɡoʊ aʊt fɔːr ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>~를 하러 나가다.</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Did he go out for a cigarette?</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Let's go out for a quick lunch during our break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ENG-20260527-233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>hang up in disgust</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>/hæŋ ʌp ɪn dɪsˈɡʌst/</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>혐오감에 전화를 끊다.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(Rachel hangs up in disgust.)</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>After listening to his insults, she hung up in disgust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ENG-20260527-234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>have a miserable time</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>/hæv ə ˈmɪzərəbl taɪm/</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>비참한/끔찍한 시간을 보내다.</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Rachel is having a miserable time</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>If the weather is bad, we might have a miserable time at the outdoor concert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ENG-20260527-235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>figure out something</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>/ˈfɪɡjər aʊt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>~를 알아내다, 이해하다, 해결하다.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>By the time anyone's figured out what we've done</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>I'm trying to figure out how to solve this complex math problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ENG-20260527-236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>fall asleep</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>/fɔːl əˈsliːp/</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>잠들다.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Emma has fallen asleep in her playpen, and Chandler has fallen asleep right next to her on the floor.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>I was so tired that I fell asleep as soon as my head hit the pillow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ENG-20260527-237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>suck on something</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>/sʌk ɑn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>~를 빨다.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>He's even sucking on a pacifier.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Babies often suck on their thumbs for comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ENG-20260527-238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>wake up</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>/weɪk ʌp/</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>잠에서 깨다.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Chandler wakes up and looks a bit confused</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>I always wake up early on weekends to enjoy the quiet morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ENG-20260527-239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>make noise</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>/meɪk nɔɪz/</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>소음을 내다.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>And you can't make any noise.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Please try not to make noise when you leave, as the baby is sleeping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ENG-20260527-240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>navigate financial hardship</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>/ˈnævɪɡeɪt faɪˈnænʃəl ˈhɑːrdʃɪp/</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>재정적 어려움을 헤쳐나가다.</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Americans are 'entrenched' in financial stress amid debt and price pressures</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Many families are struggling to navigate financial hardship in the current economy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ENG-20260527-241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>reach mega valuations</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>/riːʧ ˈmɛɡə væljuˈeɪʃənz/</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>엄청난 기업 가치에 도달하다.</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>the growing list of stocks with mega valuations.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Successful tech companies can reach mega valuations within just a few years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ENG-20260527-242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>draw divided opinion</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>/drɔː dɪˈvaɪdɪd əˈpɪnjən/</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>의견을 양분시키다, 상반된 반응을 이끌어내다.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>The new Luce model has divided opinion on social media</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>The art exhibition drew divided opinion from critics, with some praising it and others condemning it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ENG-20260527-243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>secure an entry-level job</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>/sɪˈkjʊr ən ˈɛntri-ˈlɛvl ʤɑːb/</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>신입 일자리를 얻다/확보하다.</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>'dramatic' fall in entry-level jobs</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>It can be challenging for recent graduates to secure an entry-level job without prior experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ENG-20260527-244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>put someone in a tough spot</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌmwʌn ɪn ə tʌf spɑːt/</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>~를 곤란한 상황에 처하게 하다.</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>AI tools like Mythos will make it harder for people like her to compete.</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>His unexpected resignation put the team in a tough spot right before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ENG-20260527-245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>keep someone in the loop</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>/kiːp ˈsʌmwʌn ɪn ðə luːp/</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>~에게 계속해서 상황을 알려주다, 정보 공유를 유지하다.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>their name is being kept secret by a disciplinary panel. (inspired by context of keeping information)</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Make sure to keep me in the loop about any developments on the project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ENG-20260527-246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>raise concerns</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>/reɪz kənˈsɜrnz/</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>우려를 제기하다.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Farmers' warning as milk prices fall below cost</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>The new safety report raised concerns among employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ENG-20260527-247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>take action</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>/teɪk ˈækʃən/</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>조치를 취하다.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>ECB 'will do what is necessary' to tame inflation</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>We need to take action immediately to address the environmental crisis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ENG-20260527-248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>come to light</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>/kʌm tuː laɪt/</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>밝혀지다, 드러나다.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>The commander leading the national police inquiry says the size of the investigation team would need to double</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>More details about the scandal are expected to come to light next week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ENG-20260527-249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>fall short of expectations</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>/fɔːl ʃɔːrt ʌv ˌɛkspɛkˈteɪʃənz/</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>기대에 미치지 못하다.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Ferrari shares slump after it unveils first fully electric car</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>The company's latest product launch fell short of market expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ENG-20260527-250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>gain traction</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>/ɡeɪn ˈtrækʃən/</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>주목/지지를 얻다, 추진력을 얻다.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>AI boom lifts South Korean chip stocks</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>The new political movement is starting to gain traction among young voters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ENG-20260527-251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>be on the verge of something</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>/biː ɑn ðə vɜːrdʒ ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>막 ~하려고 하다, ~의 직전이다.</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>With SpaceX headed for the public markets next month</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>The ancient species is now on the verge of extinction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ENG-20260527-252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>weather the storm</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>/ˈwɛðər ðə stɔːrm/</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>어려움을 헤쳐나가다, 위기를 극복하다.</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Americans are 'entrenched' in financial stress amid debt and price pressures</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Small businesses are struggling to weather the storm of the current economic downturn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ENG-20260527-253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>stay afloat</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>/steɪ əˈfloʊt/</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>경제적으로 허덕이지 않고 꾸려나가다, 파산하지 않다.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Farmers worry more family farms will be sold unless dairy prices rise quickly.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Many companies are cutting costs just to stay afloat during this period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ENG-20260527-254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>push back a deadline</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>/pʊʃ bæk ə ˈdɛdlaɪn/</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>마감 기한을 연기하다.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Post Office investigation could be delayed by five years</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>We had to push back the deadline for project submissions due to unforeseen issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ENG-20260527-255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>brush something off</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>/brʌʃ ˈsʌmθɪŋ ɔːf/</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>(중요하지 않다고 생각하고) ~를 무시하다, 떨쳐버리다.</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Yeah, it's no big deal.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>She tried to brush off the criticism, but it clearly affected her.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ENG-20260527-256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>get cold feet</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>/ɡɛt koʊld fiːt/</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>겁을 먹다, 망설이다.</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Chandler: I - I don't think I can.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>He was planning to propose, but he suddenly got cold feet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ENG-20260527-257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>be on the same page</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>/biː ɑn ðə seɪm peɪʤ/</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>같은 생각을 하다, 의견이 일치하다.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>I guess you're right.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Before we proceed, let's ensure everyone is on the same page regarding the project goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ENG-20260527-258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>read between the lines</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>/riːd bɪˈtwiːn ðə laɪnz/</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>속뜻을 파악하다, 숨겨진 의미를 읽어내다.</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>I lost it. To drugs. (Implied more than said)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Her email was vague, but if you read between the lines, she wasn't happy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ENG-20260527-259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>get a grip</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə ɡrɪp/</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>정신 차리다, 자제하다.</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Now, come on, come on, Steve.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>You're panicking; just get a grip and think clearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ENG-20260527-260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>run into someone</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>/rʌn ˈɪntuː ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>~를 우연히 만나다.</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Ross is just stood up somewhere at a restaurant all alone.</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>I ran into an old friend from high school at the grocery store yesterday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ENG-20260527-261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>be out of one's league</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>/bi aʊt əv wʌnz liːɡ/</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>(연애, 능력, 지위 등이) 너무 뛰어나 감히 넘볼 수 없는/수준이 훨씬 높은</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Oh, come on, you're way out of my league.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>She's so smart and accomplished; I feel like I'm completely out of her league.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I262"/>
+  <dimension ref="A1:I362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12730,6 +12730,4706 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ENG-20260527-262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>hit a milestone</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>/hɪt ə ˈmaɪlˌstoʊn/</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>중요한 이정표나 목표를 달성하다</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks. This company certainly hit a milestone.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Our startup just hit a major milestone by securing Series B funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ENG-20260527-263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>send stocks soaring</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>/sɛnd stɑks ˈsɔrɪŋ/</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>주가를 급등시키다</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>The AI boom lifts South Korean chip stocks, sending them soaring to new heights.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Positive earnings reports sent the company's stocks soaring this morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ENG-20260527-264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>top a record</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>/tɑp ə ˈrɛkərd/</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>기록을 경신하다, 최고치를 넘다</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>South Korea's SK Hynix and U.S. chip firm Micron become the latest companies to top $1 trillion in market capitalization as the AI rally resumes.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>The latest sales figures show that we've topped a record in quarterly revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ENG-20260527-265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>do what it takes</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>/du wʌt ɪt teɪks/</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>필요한 모든 조치를 취하다, 수단과 방법을 가리지 않다</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>ECB 'will do what is necessary' to tame inflation, meaning they will do what it takes.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>We'll do what it takes to meet the project deadline, even if it means working overtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ENG-20260527-266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>dash hopes</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>/dæʃ hoʊps/</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>기대를 좌절시키다, 희망을 꺾다</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Changing immigration rules and a weak hiring market dash hopes for international students seeking U.S. jobs.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>The unexpected downturn in the market dashed the hopes of many aspiring entrepreneurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ENG-20260527-267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>be behind something</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>/bi bɪˈhaɪnd ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>어떤 일의 원인이 되다, 배후에 있다</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>'Bullying' and 'overbearing' behaviour behind abrupt BP chairman removal. That's what was behind his dismissal.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>We need to find out who is really behind these rumors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ENG-20260527-268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>get away</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>/ɡɛt əˈweɪ/</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>도망치다, 빠져나가다</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>The most unbelievable thing has happened. Underdog has just gotten away.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>The suspect managed to get away from the police after a brief chase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ENG-20260527-269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>be all over the news</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>/bi ɔl ˈoʊvər ðə nuːz/</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>뉴스를 도배하다, 온통 뉴스에 나오다</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Of course the balloon. It's all over the news.</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>The celebrity scandal was all over the news for weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ENG-20260527-270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>break free</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>/breɪk friː/</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>탈출하다, 벗어나다</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Right before he reached Macy's, he broke free and was spotted flying over Washington Square Park.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>The wild animal managed to break free from its enclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ENG-20260527-271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>let loose</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>/lɛt luːs/</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>(묶인 것을) 풀다; (감정이나 행동을) 마음껏 발산하다</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Come on. An 80-foot inflatable dog let loose over the city. How often does that happen?</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>After a stressful week, I just want to let loose and dance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ENG-20260527-272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>crouch down</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>/kraʊtʃ daʊn/</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>웅크리다, 쭈그리고 앉다</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Ok, ok, here we go. (he crouches down near her stomach) Ok, where am I talking to, here?</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>The photographer had to crouch down to get a good shot of the flowers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ENG-20260527-273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>aim for</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>/eɪm fɔr/</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>~을 목표로 하다, 겨냥하다</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Just aim for the bump.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Always aim for progress, not perfection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ENG-20260527-274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>here goes</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>/hɪər ɡoʊz/</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>자, 시작한다 (새로운/어려운 일을 시작할 때 쓰는 말)</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Ok, ok, ok, ok, here goes. You know, I, you know, can't do this.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>I'm about to give my presentation. Here goes nothing!</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ENG-20260527-275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>all over the place</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>/ɔl ˈoʊvər ðə pleɪs/</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>여기저기 흩어져 있는; 두서없는, 엉망진창인</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>I loved the moment when you first saw the giant dog shadow all over the park.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>My thoughts were all over the place after hearing the shocking news.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ENG-20260527-276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>shoot down</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>/ʃuːt daʊn/</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>(생각, 제안 등을) 거절하다, 묵살하다</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Yeah, but did they have to shoot him down? I mean, that was just mean.</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>My boss tends to shoot down any new ideas without even considering them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ENG-20260527-277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>right about now</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>/raɪt əˈbaʊt naʊ/</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>바로 지금쯤</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Ok, right about now the turkey should be crispy on the outside, juicy on the inside.</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>The delivery should arrive right about now, so let's get ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ENG-20260527-278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>pick a major</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>/pɪk ə ˈmeɪʤər/</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>전공을 선택하다</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>And everyone's telling me, you gotta pick a major, you gotta pick a major.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>It's difficult for many high school students to pick a major before they even start college.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ENG-20260527-279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>on a dare</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>/ɑn ə dɛr/</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>내기/도전으로, 장난 삼아</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>So, on a dare, I picked paleontology.</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>He ate the entire super spicy chili, just on a dare from his friends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ENG-20260527-280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>have no idea</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>/hæv noʊ aɪˈdiːə/</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>전혀 모르다</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>And you have no idea what I'm saying, because, let's face it, you're a fetus.</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>I have no idea how to fix this computer problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ENG-20260527-281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>let's face it</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>/lɛts feɪs ɪt/</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>솔직히 말해서, 현실을 직시하자면</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>And you have no idea what I'm saying, because, let's face it, you're a fetus.</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Let's face it, we're not going to finish this project by tonight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ENG-20260527-282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>sing to</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>/sɪŋ tuː/</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>~에게 노래를 불러주다</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Look, you don't have to talk to it. You can sing to it if you want.</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>My grandmother used to sing to me every night before bed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ENG-20260527-283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>get looks from</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>/ɡɛt lʊks frʌm/</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>~에게 시선을 받다, 주목받다</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Here we come, walkin' down the street, get the funniest looks from, everyone we meet.</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>She gets a lot of admiring looks from strangers when she wears that dress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ENG-20260527-284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>keep doing something</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>/kiːp ˈduːɪŋ ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>계속 ~하다</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Keep singing! Keep singing!</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>If you keep practicing, you'll definitely improve your skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ENG-20260527-285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>come out</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>/kʌm aʊt/</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>나오다, 드러나다; (영화, 책 등이) 출시되다</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>When you come out I'll buy you a bagel, and then we'll go to the zoo.</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>The results of the election will come out sometime next week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ENG-20260527-286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>do the math</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>/duː ðə mæθ/</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>계산해봐, 따져봐</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Hey, I got one keyhole and about a zillion keys. You do the math.</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>If we only have 30 minutes for five presentations, do the math; each person gets six minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ENG-20260527-287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>for an emergency</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>/fɔr æn ɪˈmɜrʤənsi/</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>비상시를 대비하여</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>(sarcastic) For an emergency just like this.</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Always keep a fully charged power bank for an emergency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ENG-20260527-288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>if it wasn't for</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>/ɪf ɪt wɑzənt fɔr/</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>~가 아니었더라면</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>If it wasn't for you and your stupid balloon, I would be on a plane watching a woman do this right now.</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>If it wasn't for my alarm clock, I would have overslept and missed my flight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ENG-20260527-289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>swear by</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>/swɛər baɪ/</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>~을 맹신하다, ~의 효능/효과를 믿다</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Monica: I swear you said you had the keys. Rachel: No, I didn't. (inspired by 'swear you said')</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>My mom swears by this natural remedy for colds; she says it always works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ENG-20260527-290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>aside from the fact that</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>/əˈsaɪd frʌm ðə fæk ðæt/</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>~라는 사실을 제외하면</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Aside from the fact that you said you had them?</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Aside from the fact that it's raining, it's a perfect day for a picnic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ENG-20260527-291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>hang out</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>/hæŋ aʊt/</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>어울려 놀다, 시간을 보내다</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Ross: Does it always, uh--? (A group of friends often hang out together)</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Do you want to hang out at the coffee shop later?</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ENG-20260527-292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>catch up</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>/kætʃ ʌp/</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>밀린 이야기를 나누다; (지연된 일을) 따라잡다</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Monica: Ok, right about now the turkey should be crispy on the outside. (Friends often catch up on each other's lives)</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Let's grab lunch next week and catch up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ENG-20260527-293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>run into</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>/rʌn ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>우연히 마주치다</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Rachel: I loved the moment when you first saw the giant dog shadow. (It's common to run into people in the city)</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>I ran into my old high school teacher at the grocery store yesterday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ENG-20260527-294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>mess up</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>/mɛs ʌp/</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>망치다, 실수하다</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Phoebe felt like she messed up the potatoes)</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>I really messed up my presentation; I forgot half of what I wanted to say.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ENG-20260527-295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>call off</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>/kɔl ɔf/</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>취소하다</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Chandler: The most unbelievable thing has happened. (Sometimes plans get called off unexpectedly)</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>They had to call off the outdoor concert due to heavy rain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ENG-20260527-296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>turn down</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>/tɜrn daʊn/</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>거절하다; (소리, 불빛 등을) 줄이다</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Carol: So don't do it, it's fine. You don't have to do it just because Susan does it. (Ross wanted to turn down the offer to sing)</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>I had to turn down the job offer because it wasn't a good fit for me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ENG-20260527-297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>go through</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>/ɡoʊ θruː/</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>겪다, 경험하다; (서류 등을) 검토하다</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Ross: And everyone's telling me, you gotta pick a major. (He's going through a lot of pressure)</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>She's going through a difficult time after losing her job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ENG-20260527-298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>pull off</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>/pʊl ɔf/</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>성공적으로 해내다, 해치우다</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Joey: Hey, I got one keyhole and about a zillion keys. You do the math. (Pulling off opening the door with so many keys would be impressive)</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>I can't believe they managed to pull off such a complex event with so little planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ENG-20260527-299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>get over</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>(문제, 어려움, 병 등을) 극복하다; (상대방에 대한 감정을) 잊다</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Phoebe: Yeah, but did they have to shoot him down? I mean, that was just mean. (It's hard to get over mean actions)</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>It took her a long time to get over the breakup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ENG-20260527-300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>look up to</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>/lʊk ʌp tuː/</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>~을 존경하다, 우러러보다</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Susan: I felt it! Ross: (singin) Hey, hey, I'm your daddy. (A child might look up to their father)</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Many young athletes look up to professional sports stars as role models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ENG-20260527-301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>put off</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>/pʊt ɔf/</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>연기하다, 미루다; ~에게 불쾌감을 주다</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Monica: Can you go any faster with that? (Joey was putting off finding the right key)</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Don't put off your homework until the last minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ENG-20260527-302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>deal with</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>/dil wɪð/</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>다루다, 처리하다</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Monica: (panicked) The oven is on. (They needed to deal with the locked door situation)</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>The customer service team is trained to deal with difficult complaints calmly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ENG-20260527-303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>figure out</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>/ˈfɪɡjər aʊt/</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>알아내다, 이해하다; 해결하다</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They needed to figure out who had the keys)</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>I'm trying to figure out how to install this new software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ENG-20260527-304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>come across</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>/kʌm əˈkrɔs/</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>우연히 발견하다; ~라는 인상을 주다</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Monica came across as demanding)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>I came across an old photo album while cleaning the attic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ENG-20260527-305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>fall apart</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>/fɔl əˈpɑrt/</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>허물어지다, 무너지다; 붕괴하다</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (Ross felt like he was falling apart under pressure)</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>After the scandal, the company's reputation started to fall apart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ENG-20260527-306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>patch things up</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>/pætʃ θɪŋz ʌp/</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>관계를 회복하다, 화해하다</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (Monica and Rachel need to patch things up after their argument)</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>After their big fight, John and Sarah decided to patch things up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ENG-20260527-307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>fill someone in</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>/fɪl ˈsʌmˌwʌn ɪn/</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>~에게 소식을 전하다, 상황을 알려주다</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He's filling them in on the news)</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>I missed the meeting, so can you fill me in on what was discussed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ENG-20260527-308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>nod off</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>/nɑd ɔf/</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>꾸벅꾸벅 졸다</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Ross: And you have no idea what I'm saying, because, let's face it, you're a fetus. (A fetus would nod off during a long speech)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>The lecture was so boring that I kept nodding off in my seat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ENG-20260527-309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>brush off</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>/brʌʃ ɔf/</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>묵살하다, 무시하다</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Phoebe: Yeah, but did they have to shoot him down? (The authorities might brush off public complaints)</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>He tried to brush off my concerns, but I insisted on discussing them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ENG-20260527-310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>talk over</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>/tɔk ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>상의하다, ~에 대해 논의하다</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They should talk over the key situation calmly)</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Let's talk over the project details before making any final decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ENG-20260527-311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>butt in</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>/bʌt ɪn/</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>(대화나 일에) 끼어들다, 참견하다</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Phoebe: Ooh, ok, that's it. Enough with the keys. No one say keys. (She butted in to stop the argument)</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>It's rude to butt in when other people are talking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ENG-20260527-312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>bail on</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>/beɪl ɑn/</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>(약속, 책임 등을) 저버리다, 바람맞히다</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Rachel: I can't, I gotta go. (She had to bail on going to the roof)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>He bailed on our dinner plans at the last minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ENG-20260527-313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>chicken out</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>/ˈʧɪkɪn aʊt/</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>겁먹고 포기하다, 꽁무니 빼다</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Ross: Ok, ok, ok, ok, here goes. You know, I, you know, can't do this. Uh, this is too weird. I feel stupid. (Ross almost chickened out of talking to Carol's belly)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>I was going to try skydiving, but I chickened out at the last moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ENG-20260527-314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>fend off</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>/fɛnd ɔf/</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>~을 물리치다, 막아내다</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (Companies need to fend off pressure from EU.)</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>The politician had to fend off tough questions from reporters during the press conference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ENG-20260527-315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>pencil in</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>/ˈpɛnsəl ɪn/</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>임시로 일정을 잡다</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>The Post Office investigation could be delayed by five years, police warn. (They need to pencil in new timelines)</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Let's pencil in a meeting for Tuesday afternoon, and I'll confirm with everyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>ENG-20260527-316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>rule out</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>/rul aʊt/</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>배제하다, ~의 가능성을 없애다</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>The commander leading the national police inquiry needs to rule out other possibilities.</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>The detective couldn't rule out the possibility of foul play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>ENG-20260527-317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>wear off</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>/wɛər ɔf/</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>점점 사라지다, 효과가 없어지다</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Energy bills to rise for millions as impact of Iran war hits. (The relief of lower prices will wear off)</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>The initial excitement of the new job started to wear off after a few months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ENG-20260527-318</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>go back on</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>/ɡoʊ bæk ɑn/</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>(약속, 합의 등을) 어기다, 철회하다</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (EU feels they go back on agreements)</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>He's known for always keeping his word and never going back on a promise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>ENG-20260527-319</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>touch base</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>/tʌtʃ beɪs/</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>간략히 연락하다, 안부를 묻거나 상황을 확인하다</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>With SpaceX headed for the public markets next month, industry experts and people close to Elon Musk are speculating about a potential tie-up with Tesla. (They need to touch base with Musk's team)</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Let's touch base next week to discuss the progress of the project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ENG-20260527-320</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>circle back</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>/ˈsɜrkəl bæk/</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>(나중에) 다시 논의하다, 재론하다</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>The ECB 'will do what is necessary' to tame inflation. (They might need to circle back to their strategies)</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>That's a good point, but let's circle back to it after we've covered the main agenda items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ENG-20260527-321</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>hit a snag</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>/hɪt ə snæɡ/</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>예상치 못한 문제에 부딪히다</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>The Post Office investigation could be delayed by five years, police warn. (The investigation hit a snag)</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Our plans to launch the new product hit a snag when we encountered a supply chain issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ENG-20260527-322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>drive a hard bargain</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>/draɪv ə hɑrd ˈbɑrɡɪn/</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>흥정을 잘하다, 타협하지 않고 유리한 조건을 얻으려 하다</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (China often drives a hard bargain)</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>He's known for being a tough negotiator; he always drives a hard bargain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>ENG-20260527-323</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>take the hit</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>/teɪk ðə hɪt/</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>손해를 감수하다, 비난을 받다</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Energy bills to rise for millions as impact of Iran war hits. (Households will take the hit)</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>The company decided to take the hit on profits rather than raise prices for loyal customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ENG-20260527-324</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>call the shots</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>/kɔl ðə ʃɑts/</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>결정권을 쥐다, 지휘하다</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>President Donald Trump last week endorsed Texas Attorney General Ken Paxton. (He calls the shots in his party)</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>As the project manager, she's the one who calls the shots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>ENG-20260527-325</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>clear the air</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>/klɪər ðɪ ɛər/</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>오해를 풀다, 관계를 명확히 하다</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They need to clear the air after their argument)</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>After their disagreement, they decided to meet for coffee to clear the air.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>ENG-20260527-326</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>give someone a heads-up</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmˌwʌn ə ˈhɛdz ʌp/</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>~에게 미리 알려주다, 경고하다</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He gave them a heads-up about the balloon.)</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Can you give me a heads-up if there are any changes to the schedule?</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>ENG-20260527-327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>pull some strings</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>/pʊl sʌm strɪŋz/</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>배후에서 영향력을 행사하다, (인맥을 동원해) 일을 해결하다</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Joey: We have a copy of your key. (Joey might have to pull some strings to get the key faster.)</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>I had to pull some strings to get us tickets for the sold-out concert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>ENG-20260527-328</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>read the room</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>/rid ðə rum/</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>분위기를 파악하다, 상황을 읽다</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (He couldn't read the room well enough to just relax)</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>A good comedian knows how to read the room and adjust their jokes accordingly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>ENG-20260527-329</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>take something with a grain of salt</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>/teɪk ˈsʌmθɪŋ wɪθ ə ɡreɪn ʌv sɔlt/</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>~을 액면 그대로 믿지 않다, 흘려듣다</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>SpaceX-Tesla merger chatter reignites as Musk pushes rocket company towards Nasdaq. (One should take merger rumors with a grain of salt.)</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>You should take his promises with a grain of salt; he often exaggerates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>ENG-20260527-330</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>buy time</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>/baɪ taɪm/</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>시간을 벌다</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>The Post Office investigation could be delayed by five years. (This delay buys them time.)</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>We need to buy time to prepare a better proposal for the client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>ENG-20260527-331</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>cut corners</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>/kʌt ˈkɔrnərz/</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>절차를 무시하고 대충 하다, 비용이나 노력을 절감하다</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (Some companies cut corners on safety)</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Don't cut corners on quality just to save a little money; it will cost more in the long run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>ENG-20260527-332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>face the music</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>/feɪs ðə ˈmjuːzɪk/</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>잘못에 대한 비난/벌을 받다, 결과를 감수하다</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>BP chairman removed due to 'bullying' behavior. He had to face the music.</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>After neglecting his responsibilities, he finally had to face the music and deal with the consequences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ENG-20260527-333</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>have second thoughts</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>/hæv ˈsɛkənd θɔts/</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>다시 생각하다, 재고하다</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Ross: Ok, ok, ok, ok, here goes. You know, I, you know, can't do this. (He was having second thoughts about talking to the belly.)</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>I'm having second thoughts about accepting that job offer; it seems a bit risky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>ENG-20260527-334</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>make ends meet</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>/meɪk ɛndz mit/</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>수입과 지출의 균형을 맞추다, 겨우 생계를 유지하다</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Americans are 'entrenched' in financial stress amid debt and price pressures. (Many struggle to make ends meet.)</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>It's becoming increasingly difficult for families to make ends meet with the rising cost of living.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>ENG-20260527-335</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>play it by ear</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>/pleɪ ɪt baɪ iər/</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>상황 봐서 즉흥적으로 처리하다</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Rachel: We're waiting for you to open the door. You got the keys. (They might have to play it by ear to get inside.)</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>We don't have a strict plan for the weekend; let's just play it by ear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ENG-20260527-336</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>sleep on it</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>/slip ɑn ɪt/</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>하룻밤 자면서 곰곰이 생각하다 (결정을 미루다)</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Carol: So don't do it, it's fine. You don't have to do it just because Susan does it. (Ross could sleep on it before deciding to sing)</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>That's a big decision, so why don't you sleep on it and tell me your answer tomorrow?</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>ENG-20260527-337</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>take a rain check</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>/teɪk ə reɪn tʃɛk/</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>다음 기회로 미루다, (초대를) 나중에 받아들이다</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Rachel: I can't, I gotta go. (She had to take a rain check on going to the roof.)</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>I'm too busy to go out tonight, but can I take a rain check?</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>ENG-20260527-338</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>miss the boat</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>/mɪs ðə boʊt/</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>기회를 놓치다</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks. (Investors who didn't buy early missed the boat.)</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>If you don't apply for the scholarship soon, you'll miss the boat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ENG-20260527-339</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>pick someone's brain</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>/pɪk ˈsʌmˌwʌnz breɪn/</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>~에게 조언을 구하다, 지식을 얻다</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Chompie, one of the world's tops ethical hackers, says AI like Claude Mythos will make it harder for people like her to compete. (Perhaps others want to pick Chompie's brain.)</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>I'd love to pick your brain sometime about your experience in the tech industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>ENG-20260527-340</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>tighten the belt</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>/ˈtaɪtən ðə bɛlt/</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>허리띠를 졸라매다, 지출을 줄이다</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Americans are 'entrenched' in financial stress amid debt and price pressures. (Many have to tighten their belts.)</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>With rising inflation, many families are having to tighten their belts and cut back on non-essential spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>ENG-20260527-341</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>call it a day</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>/kɔl ɪt ə deɪ/</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>하루 일을 마치다, 끝내다</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Ok, all done. (Phoebe was ready to call it a day on the potatoes)</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>It's getting late; let's call it a day and pick this up tomorrow morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>ENG-20260527-342</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>spill the beans</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>/spɪl ðə binz/</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>비밀을 누설하다, 다 불어버리다</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He's spilling the beans about the event.)</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Don't spill the beans about the surprise party; it's a secret!</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>ENG-20260527-343</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>hit the ground running</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>/hɪt ðə ɡraʊnd ˈrʌnɪŋ/</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>즉시 활발하게 일을 시작하다, 빠른 속도로 진행하다</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Booming AI chip demand helps create two new $1tn club members. (New companies hit the ground running.)</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Our new marketing intern hit the ground running and quickly became an invaluable part of the team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>ENG-20260527-344</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>go with the flow</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>/ɡoʊ wɪθ ðə floʊ/</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>흐름에 따르다, 순리에 맡기다</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Monica doesn't go with the flow easily.)</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>My travel plans are flexible; I'll just go with the flow and see where the journey takes me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>ENG-20260527-345</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>bite the bullet</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>/baɪt ðə ˈbʊlɪt/</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>어려움을 감수하다, 이를 악물고 참다</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Energy bills to rise for millions as impact of Iran war hits. (People will have to bite the bullet.)</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>I really don't want to work extra hours, but I'll have to bite the bullet to finish this project on time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ENG-20260527-346</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>break a leg</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>/breɪk ə lɛɡ/</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>행운을 빌다 (특히 공연 전에)</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Ross: Ok, ok, here we go. (Someone might wish him 'break a leg' before his 'performance' for the baby.)</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>You have your big presentation today? Break a leg!</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ENG-20260527-347</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>cost an arm and a leg</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>/kɔst æn ɑrm ənd ə lɛɡ/</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>매우 비싸다, 엄청난 비용이 들다</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Ferrari shares slump after it unveils first fully electric car. (The new car likely costs an arm and a leg.)</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>I'd love to buy a house in this neighborhood, but it would cost an arm and a leg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>ENG-20260527-348</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>get something off one's chest</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmθɪŋ ɔf wʌnz tʃɛst/</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>마음속의 고민을 털어놓다</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (He wants to get this off his chest.)</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>I've been worried about this for days; I need to get it off my chest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>ENG-20260527-349</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>let the cat out of the bag</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>/lɛt ðə kæt aʊt ʌv ðə bæɡ/</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>비밀을 누설하다, 폭로하다</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He let the cat out of the bag about the balloon incident.)</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>We were planning a surprise party for her, but my brother accidentally let the cat out of the bag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ENG-20260527-350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>lose one's touch</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>/luːz wʌnz tʌtʃ/</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>감각을 잃다, 실력이 떨어지다</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Joey: Hey, I got one keyhole and about a zillion keys. (He might feel like he's losing his touch at picking locks.)</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>The chef felt he was losing his touch when his famous dish didn't turn out well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>ENG-20260527-351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>stab someone in the back</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>/stæb ˈsʌmˌwʌn ɪn ðə bæk/</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>~를 배신하다, 뒤통수치다</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Paxton bests Cornyn in Texas Republican Senate primary after Trump endorsement. (Some might see the endorsement as a stab in the back for Cornyn.)</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>I can't believe he stabbed me in the back by telling my secret to everyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>ENG-20260527-352</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>the ball is in one's court</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>/ðə bɔl ɪz ɪn wʌnz kɔrt/</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>(결정이나 행동의) 책임이 ~에게 있다</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Monica: No I don't. Rachel: Yes, you do. When we left, you said, 'got the keys.' (The ball was in Monica's court to find the keys.)</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>I've made my offer, so now the ball is in your court to accept or decline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ENG-20260527-353</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>throw in the towel</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>/θroʊ ɪn ðə ˈtaʊəl/</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>포기하다, 항복하다</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Farmers' warning as milk prices fall below cost. (Some farmers might be forced to throw in the towel.)</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>After several failed attempts, he was ready to throw in the towel, but his coach encouraged him to keep going.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ENG-20260527-354</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>under the weather</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>/ˈʌndər ðə ˈwɛðər/</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>몸이 안 좋다, 약간 아프다</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Ross: I feel stupid. (He might also feel a bit under the weather from the stress.)</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>I'm feeling a bit under the weather today, so I might go home early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>ENG-20260527-355</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>back to square one</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>/bæk tuː skwɛər wʌn/</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>원점으로 돌아가다, 처음부터 다시 시작하다</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Joey: Nope, not that one. (If none of the keys work, they're back to square one.)</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Our entire experiment failed, so we're back to square one with our research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ENG-20260527-356</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>beat around the bush</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>/bit əˈraʊnd ðə bʊʃ/</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>빙빙 돌려 말하다, 요점을 피하다</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Ross: Ok, where am I talking to, here? I mean, uh, well, there is one way that seems to offer a certain acoustical advantage, but... (Ross is beating around the bush.)</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Stop beating around the bush and just tell me what you want to say.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>ENG-20260527-357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>bless someone's heart</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>/blɛs ˈsʌmˌwʌnz hɑrt/</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>(남을 동정하거나 살짝 비꼬는 의미로) 안쓰럽네, 착한 심성 가진 사람</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Phoebe: Yeah, but did they have to shoot him down? I mean, that was just mean. (She might say 'bless their hearts' to the people who shot down the balloon.)</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Bless her heart, she tried her best, even though she clearly had no idea what she was doing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>ENG-20260527-358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>burn the midnight oil</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>/bɜrn ðə ˈmɪdˌnaɪt ɔɪl/</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>밤늦게까지 일하다, 밤샘하다</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>The Post Office investigation team would need to double in order to meet its current timeline. (They might have to burn the midnight oil.)</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>I had to burn the midnight oil to finish my report before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>ENG-20260527-359</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>can't make heads or tails of</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>/kænt meɪk hɛdz ɔr teɪlz ʌv/</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>~을 도무지 이해할 수 없다</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Ross: And you have no idea what I'm saying, because, let's face it, you're a fetus. (The fetus can't make heads or tails of what Ross is saying.)</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>I've read these instructions three times, but I still can't make heads or tails of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>ENG-20260527-360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>chew someone out</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>/tʃuː ˈsʌmˌwʌn aʊt/</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>~를 호되게 꾸짖다, 야단치다</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Monica: (angry) Joey! (She's about to chew him out for being slow with the keys.)</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>My boss chewed me out for being late to the important meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>ENG-20260527-361</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>come clean</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>/kʌm klin/</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>솔직하게 털어놓다, 고백하다</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (One of them needs to come clean about the keys.)</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>After weeks of hiding it, he finally decided to come clean about breaking the vase.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I362"/>
+  <dimension ref="A1:I462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17430,6 +17430,4706 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>ENG-20260527-362</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>push back against</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>/pʊʃ bæk əˈɡɛnst/</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>반대하거나 저항하다, 반발하다</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Former BP Chairman Albert Manifold has pushed back against accusations over his conduct following his shock departure.</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>The employees decided to push back against the new policy regarding remote work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>ENG-20260527-363</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ink a deal</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>/ɪŋk ə diːl/</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>계약에 서명하다, 거래를 성사시키다</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Everyone is speculating if SpaceX and Tesla will ink a deal for a potential tie-up soon.</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>The startup is close to inking a deal with a major investor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>ENG-20260527-364</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>come out in force</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>/kʌm aʊt ɪn fɔːrs/</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>많은 수가 집결하다, 대거 나타나다</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>After the Trump endorsement, voters were expected to come out in force for Paxton.</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Despite the bad weather, fans came out in force to support their favorite team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>ENG-20260527-365</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>throw one's weight behind</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>/θroʊ wʌnz weɪt bɪˈhaɪnd/</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>누군가나 무언가를 적극적으로 지지하고 영향력을 행사하다</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>President Trump threw his weight behind Texas Attorney General Ken Paxton, impacting the primary results.</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>The CEO decided to throw her weight behind the new sustainability initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>ENG-20260527-366</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>beef up</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>/biːf ʌp/</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>강화하다, 보강하다</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Russia needs to beef up its anti-drone defense systems to counter attacks.</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>The company plans to beef up its cybersecurity measures after a recent data breach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>ENG-20260527-367</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>take a nosedive</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>/teɪk ə ˈnoʊzdaɪv/</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>급락하다, 폭락하다</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Ferrari shares took a nosedive after it unveiled its first fully electric car to a divided public.</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>After the scandal, the politician's approval ratings took a nosedive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>ENG-20260527-368</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>hit a record high</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>/hɪt ə ˈrɛkərd haɪ/</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>최고 기록을 경신하다</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>SK Hynix shares hit a record high, pushing its valuation above $1 trillion.</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Oil prices hit a record high last month, causing concerns for consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>ENG-20260527-369</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>take off</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>/teɪk ɒf/</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>갑자기 성공하다, 인기를 얻다; (주식 등이) 급등하다</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>The AI rally resumed, and many tech stocks started to take off again.</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Her new business really started to take off after a successful marketing campaign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>ENG-20260527-370</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>feel the pinch</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>/fiːl ðə pɪntʃ/</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>재정적 어려움을 느끼다, 궁핍함을 겪다</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Americans are feeling the pinch as inflation and high debt levels continue to cause financial anxiety.</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Many families are starting to feel the pinch with the rising cost of living.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>ENG-20260527-371</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>tighten one's belt</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>/ˈtaɪtn wʌnz bɛlt/</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>허리띠를 졸라매다, 지출을 줄이다</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>With energy bills set to rise, many households will have to tighten their belts.</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Due to the economic downturn, we'll all have to tighten our belts for a while.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>ENG-20260527-372</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>drag on</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>/dræɡ ɒn/</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>지루하게 오래 계속되다, 지연되다</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>The Post Office investigation could drag on for another five years if resources aren't increased.</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>The negotiations have been dragging on for weeks without a clear resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>ENG-20260527-373</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>put on hold</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>/pʊt ɒn hoʊld/</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>보류하다, 연기하다</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>The Post Office investigation might be put on hold due to a lack of resources.</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>We've decided to put the new project on hold until next quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>ENG-20260527-374</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>stay ahead of the curve</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>/steɪ əˈhɛd ɒv ðə kɜːrv/</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>트렌드나 경쟁에서 앞서나가다, 시대를 앞서가다</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Chompie warns that ethical hackers need to stay ahead of the curve as AI tools evolve.</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>To remain competitive, companies must constantly innovate and stay ahead of the curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>ENG-20260527-375</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>up one's game</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>/ʌp wʌnz ɡeɪm/</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>실력을 향상시키다, 더 잘하다</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>The rise of AI tools means human hackers will have to up their game to compete.</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>If you want that promotion, you'll really need to up your game in sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>ENG-20260527-376</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>crack down on</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>/kræk daʊn ɒn/</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>단속하다, 엄격하게 규제하다</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>The advertising watchdog decided to crack down on Instagram betting ads featuring footballers.</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>The government is cracking down on tax evasion to boost revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>ENG-20260527-377</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>iron out</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>/ˈaɪərn aʊt/</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>(문제, 오해 등을) 해결하다, 해소하다</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Before the merger can proceed, both companies need to iron out a few legal details.</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Let's meet tomorrow to iron out the final details of the proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>ENG-20260527-378</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>hammer out</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>/ˈhæmər aʊt/</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>협의나 논의를 거쳐 (합의, 계획 등을) 힘들게 도출해내다</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>The two sides spent all night trying to hammer out a compromise on the budget.</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>They finally hammered out a new contract after weeks of negotiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>ENG-20260527-379</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>call out</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>/kɔːl aʊt/</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>비판하다, 잘못을 지적하다; (도움을 요청하며) 부르다</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>The employee decided to call out the bullying behavior of their superior.</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>It's important to call out discriminatory remarks when you hear them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>ENG-20260527-380</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>opt out of</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>/ɒpt aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>선택하지 않다, ~에서 빠져나가다</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Many students are choosing to opt out of the traditional university system for vocational training.</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Employees can opt out of the company's health insurance plan if they have their own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ENG-20260527-381</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>phase out</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>/feɪz aʊt/</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>단계적으로 중단하다, 폐지하다</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>The company plans to phase out its old product line to make way for new innovations.</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>The government is trying to phase out the use of plastic bags over the next few years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>ENG-20260527-382</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>reel in</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>/riːl ɪn/</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>유인하여 끌어들이다 (특히 고객, 투자자 등)</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>The new marketing campaign aims to reel in more subscribers to our streaming service.</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>They used celebrity endorsements to reel in a younger demographic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>ENG-20260527-383</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>weigh in</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>/weɪ ɪn/</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>논쟁이나 토론에 의견을 보태다, 개입하다</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Several industry experts weighed in on the potential SpaceX-Tesla merger chatter.</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>The CEO decided to weigh in on the controversial decision during the board meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ENG-20260527-384</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>hold off on</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>/hoʊld ɒf ɒn/</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>~을 보류하다, ~을 미루다</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Let's hold off on making a final decision until we have all the information.</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>They decided to hold off on their travel plans until the pandemic situation improves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ENG-20260527-385</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>step down</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>/stɛp daʊn/</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>사임하다, 물러나다</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>The chairman was forced to step down after accusations of misconduct.</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>She announced her decision to step down as CEO at the end of the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ENG-20260527-386</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>step up</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>/stɛp ʌp/</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>더 많은 책임을 맡다, 한 단계 올라서다; (노력 등을) 강화하다</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>In the absence of the manager, someone needs to step up and lead the team.</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>We need to step up our customer service to retain our clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ENG-20260527-387</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>back out of</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>/bæk aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>약속이나 계약을 취소하다, 손을 떼다</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>He tried to back out of the deal at the last minute, but the contract was binding.</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>The investor decided to back out of the agreement due to new market conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>ENG-20260527-388</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>follow through on</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>/ˈfɒloʊ θruː ɒn/</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>약속, 계획 등을 이행하다, 끝까지 실행하다</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>It's important to follow through on your commitments to build trust with clients.</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>She always follows through on her promises, which makes her a reliable leader.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>ENG-20260527-389</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>branch out</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>/bræntʃ aʊt/</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>새로운 분야로 진출하다, 사업을 확장하다</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>The tech company decided to branch out into the clean energy sector.</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>After years in finance, she decided to branch out and start her own consulting firm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ENG-20260527-390</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>map out</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>/mæp aʊt/</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>자세하게 계획을 세우다, 설계하다</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>We need to map out a strategy for dealing with the increased competition.</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Before starting the trip, they mapped out their entire route and planned for all contingencies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>ENG-20260527-391</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>zero in on</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>/ˈzɪəroʊ ɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>~에 집중하다, ~을 목표로 삼다</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>The investigation will zero in on the specific details of the financial transactions.</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>The detective managed to zero in on the key suspect after reviewing all the evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>ENG-20260527-392</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>kick off</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>/kɪk ɒf/</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>시작하다, 개시하다</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>The conference will kick off with a keynote speech from the CEO.</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Let's kick off the meeting by reviewing the agenda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ENG-20260527-393</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>wind down</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>/waɪnd daʊn/</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>서서히 끝나다, 마무리하다; 휴식을 취하다</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>The event will wind down around 5 PM with a networking reception.</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>After a busy day, I like to wind down by reading a book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>ENG-20260527-394</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>burn out</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>/bɜːrn aʊt/</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>(과로 등으로) 기진맥진하다, 소진되다</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Working 80 hours a week can quickly lead to burnout and stress.</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>She decided to take a sabbatical to avoid burning out from her demanding job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>ENG-20260527-395</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>cash in on</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>/kæʃ ɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>~을 이용해 이득을 얻다, ~로 돈을 벌다</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Many companies are trying to cash in on the growing demand for AI technology.</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>They hoped to cash in on the holiday season by offering special discounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>ENG-20260527-396</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>dig in</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>/dɪɡ ɪn/</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>열심히 먹기 시작하다; 굳게 버티다, 고수하다</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>When the food arrived, everyone started to dig in with enthusiasm.</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Despite the opposition, the politician dug in and refused to change his stance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>ENG-20260527-397</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>get ahead</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>/ɡɛt əˈhɛd/</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>성공하다, 앞서나가다</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Many international students find it harder to get ahead in the US job market.</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>To get ahead in this industry, you need to be constantly learning new skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>ENG-20260527-398</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>get by</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>/ɡɛt baɪ/</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>그럭저럭 살아가다, 근근이 생활하다</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>With prices rising, it's becoming harder for families to get by on a single income.</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>I don't earn much, but I manage to get by with careful budgeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ENG-20260527-399</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>give in</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>/ɡɪv ɪn/</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>양보하다, 굴복하다</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>After hours of debate, the opposing party finally gave in and accepted the proposal.</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>My kids kept asking for ice cream until I finally gave in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>ENG-20260527-400</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>give up on</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>/ɡɪv ʌp ɒn/</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>~을 포기하다, ~에 대한 희망을 버리다</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Don't give up on your American dream, even if the job market is tough.</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>We can't give up on finding a solution to this problem, no matter how difficult it seems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>ENG-20260527-401</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>grow on</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>/ɡroʊ ɒn/</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>점점 더 좋아지다, 마음에 들게 되다</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>At first, I didn't like the new office design, but it's starting to grow on me.</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>The new song wasn't my favorite initially, but it really started to grow on me after a few listens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>ENG-20260527-402</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>hand over</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>/hænd ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>넘겨주다, 양도하다</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>The outgoing CEO will hand over his responsibilities to his successor next month.</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>The company decided to hand over its operations to a local partner in the region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>ENG-20260527-403</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>knock off</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>/nɒk ɒf/</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>일을 마치다, 퇴근하다; 가격을 깎다; 빠르게 만들다/생산하다</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>We can probably knock off early if we finish all our tasks by lunchtime.</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Can you knock off 10% from the price if I buy two items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>ENG-20260527-404</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>lay off</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>/leɪ ɒf/</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>(직원을) 해고하다, 일시 해고하다</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Due to decreased demand, the factory had to lay off a significant number of workers.</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>The struggling startup had to lay off a third of its staff to stay afloat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>ENG-20260527-405</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>let down</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>/lɛt daʊn/</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>실망시키다, 저버리다</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>I hope I don't let down my team with my performance in the upcoming presentation.</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>She felt completely let down by her friend who didn't show up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>ENG-20260527-406</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>live up to</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>/lɪv ʌp tuː/</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>(기대, 명성 등에) 부응하다, 부합하다</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>The new product needs to live up to the high expectations set by its marketing campaign.</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>The movie didn't quite live up to the hype, but it was still entertaining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ENG-20260527-407</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>make for</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>/meɪk fɔːr/</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>~쪽으로 가다; ~에 도움이 되다, ~을 야기하다</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>The rising prices will make for increased financial stress for many families.</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>A strong team spirit makes for a productive work environment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>ENG-20260527-408</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>make up for</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>/meɪk ʌp fɔːr/</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>~을 만회하다, 보충하다; ~을 보상하다</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>He tried to make up for his mistake by working extra hours over the weekend.</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>The free dessert didn't really make up for the terrible service we received.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ENG-20260527-409</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>miss out on</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>/mɪs aʊt ɒn/</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>~을 놓치다, ~에 참여하지 못하다</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Don't miss out on the opportunity to invest in these booming AI chip stocks.</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>I'd hate to miss out on the annual company picnic this year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>ENG-20260527-410</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>pass up</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>/pæs ʌp/</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>~을 거절하다, ~을 놓치다</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>She couldn't pass up the chance to work at such a prestigious company.</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>It's a great opportunity, you shouldn't pass it up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>ENG-20260527-411</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>pick up on</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>/pɪk ʌp ɒn/</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>~을 알아채다, 눈치채다</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>He didn't directly say it, but I picked up on the fact that he wasn't happy with the decision.</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>She's very observant and always picks up on subtle changes in people's moods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>ENG-20260527-412</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>point out</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>/pɔɪnt aʊt/</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>지적하다, 언급하다</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>The expert pointed out that the AI rally might not last forever.</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>The teacher pointed out several errors in my essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>ENG-20260527-413</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>read into</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>/riːd ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>(숨겨진 의미를) 지나치게 확대 해석하다</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Don't read too much into his comments; he's probably just tired.</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>She tends to read into every little gesture, looking for hidden meanings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>ENG-20260527-414</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>root for</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>/ruːt fɔːr/</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>~을 응원하다, 지지하다</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>I'm always rooting for the underdog in any competition.</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Our whole family is rooting for you to win the championship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>ENG-20260527-415</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>rub off on</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>/rʌb ɒf ɒn/</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>(특성, 습관 등이) ~에게 전염되다, 영향을 주다</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Her enthusiasm for the project eventually started to rub off on the rest of the team.</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>I hope some of your good study habits rub off on me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>ENG-20260527-416</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>set out</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>/sɛt aʊt/</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>출발하다; (목표를 가지고) 시작하다; 진술하다, 제시하다</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>The new initiative sets out clear guidelines for ethical AI development.</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>They set out to build the most innovative smartphone on the market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>ENG-20260527-417</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>size up</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>/saɪz ʌp/</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>평가하다, 상황을 판단하다</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>The investors are trying to size up the potential risks of the new venture.</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Before making a move, it's always good to size up your opponent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>ENG-20260527-418</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>stand out</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>/stænd aʊt/</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>눈에 띄다, 두드러지다</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Her unique presentation really made her stand out among the other candidates.</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>To get noticed in a crowded market, your product needs to stand out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>ENG-20260527-419</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>stir up</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>/stɜːr ʌp/</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>(문제, 감정 등을) 불러일으키다, 자극하다</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>His controversial comments stirred up a lot of debate on social media.</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Don't stir up trouble by talking about sensitive topics at the family dinner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>ENG-20260527-420</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>string along</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>/strɪŋ əˈlɒŋ/</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>~을 속이다, ~을 희망 고문하다</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>I feel like they're just stringing me along with promises of a promotion.</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>She realized her ex-boyfriend was just stringing her along and never intended to get serious.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>ENG-20260527-421</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>take on</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>/teɪk ɒn/</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>책임을 맡다; (도전, 임무 등을) 받아들이다; (직원을) 고용하다</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>She was hesitant to take on such a challenging role, but she eventually accepted.</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>The company decided to take on five new interns for the summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>ENG-20260527-422</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>talk out of</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>/tɔːk aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>~에게 설득하여 ~을 하지 못하게 하다</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>His friends tried to talk him out of quitting his stable job.</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>I managed to talk her out of buying that expensive dress she didn't need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>ENG-20260527-423</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>tell apart</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>/tɛl əˈpɑːrt/</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>~을 구별하다, 분간하다</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>The twins look so similar; it's hard to tell them apart.</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>The two product models are so similar that only an expert can tell them apart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>ENG-20260527-424</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>throw off</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>/θroʊ ɒf/</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>혼란스럽게 하다, 방해하다; (냄새, 열 등을) 내뿜다</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>The sudden change in the schedule threw off my entire day.</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>The unexpected question completely threw him off during the interview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>ENG-20260527-425</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>touch on</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>/tʌtʃ ɒn/</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>(주제 등을) 간단히 다루다, 언급하다</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>The speaker briefly touched on the economic implications of the new policy.</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>During the meeting, we only had time to touch on the main points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>ENG-20260527-426</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>walk out on</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>/wɔːk aʊt ɒn/</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>~을 버리다, 갑자기 떠나다</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>He walked out on his family without saying a word, leaving them in financial difficulty.</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>It was unprofessional for him to walk out on the project halfway through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>ENG-20260527-427</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>zone out</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>/zoʊn aʊt/</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>멍하니 있다, 집중하지 못하다</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>During the long lecture, I found myself zoning out and thinking about dinner.</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Sometimes I just zone out when I'm tired and need a break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>ENG-20260527-428</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>drum up business</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>/drʌm ʌp ˈbɪznɪs/</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>손님을 모으다, 사업을 활성화하다</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>The new cafe is using social media to drum up business in the neighborhood.</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>We need to come up with new strategies to drum up business during the off-peak season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>ENG-20260527-429</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>go the extra mile</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ðɪ ˈɛkstrə maɪl/</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>특별히 더 노력하다, 최선을 다하다</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Our customer service team always goes the extra mile to ensure customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>To get that promotion, you'll really need to go the extra mile and impress your boss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>ENG-20260527-430</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>put out feelers</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>/pʊt aʊt ˈfiːlərz/</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>탐색하다, 의향을 타진하다</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Before launching the new product, we need to put out feelers to gauge market interest.</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>I'm putting out feelers for a new job, quietly seeing what opportunities are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>ENG-20260527-431</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>keep an eye on</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>/kiːp ən aɪ ɒn/</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>~을 주시하다, ~을 잘 살피다</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Please keep an eye on the market trends while I'm away.</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Can you keep an eye on my bag while I go to the restroom?</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>ENG-20260527-432</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>make a point</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>/meɪk ə pɔɪnt/</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>(특정 사실을) 강조하다, 역설하다</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>She made a point of thanking every member of her team for their hard work.</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>During the presentation, he made a point to highlight the company's achievements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>ENG-20260527-433</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>turn a blind eye</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>/tɜːrn ə blaɪnd aɪ/</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>못 본 척하다, 눈감아주다</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>The management was accused of turning a blind eye to the bullying behavior.</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>You can't just turn a blind eye to the problems in our community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>ENG-20260527-434</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Modern Family</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>pull rank</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>/pʊl ræŋk/</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>직위나 권한을 내세워 지시하다</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Instead of debating, the manager just pulled rank and made a unilateral decision.</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Don't try to pull rank on me; we're all equals in this project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>ENG-20260527-435</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>pay lip service</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>/peɪ lɪp ˈsɜːrvɪs/</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>겉으로만 동의하거나 지지하는 척하다, 입발림을 하다</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Critics argue that the company only pays lip service to environmental protection without real action.</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Many politicians pay lip service to helping the poor but do little in practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>ENG-20260527-436</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>give someone the green light</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˌsʌmwʌn ðə ɡriːn laɪt/</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>~에게 허락하다, 승인하다</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>The board finally gave the team the green light to proceed with the experimental project.</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Once we get the green light from legal, we can start advertising the new service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>ENG-20260527-437</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>give someone the benefit of the doubt</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˌsʌmwʌn ðə ˈbɛnɪfɪt ɒv ðə daʊt/</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>일단 믿어주다, 좋게 봐주다</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Despite the mixed reviews, I decided to give the new restaurant the benefit of the doubt.</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>He's usually very reliable, so I'll give him the benefit of the doubt about being late today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>ENG-20260527-438</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>break the bank</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>/breɪk ðə bæŋk/</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>엄청난 돈을 쓰다, 거액을 지출하다</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Getting better WiFi for hundreds of trains shouldn't break the bank for the government.</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>We want a nice vacation, but we don't want to break the bank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>ENG-20260527-439</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>foot the bill</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>/fʊt ðə bɪl/</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>계산하다, 비용을 부담하다</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>The government will foot the bill for the WiFi upgrade on the trains.</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>My company offered to foot the bill for my further education.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>ENG-20260527-440</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>piece of cake</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>/piːs ɒv keɪk/</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>매우 쉬운 일</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Don't worry about the exam; it'll be a piece of cake if you've studied.</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Learning to use the new software was a piece of cake for him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>ENG-20260527-441</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>back to the drawing board</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>/bæk tuː ðə ˈdrɔːɪŋ bɔːrd/</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>원점으로 돌아가 다시 시작하다</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Our first attempt failed, so it's back to the drawing board for the entire team.</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>The client rejected our proposal, so we're back to the drawing board to come up with new ideas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>ENG-20260527-442</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>jump on the bandwagon</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>/dʒʌmp ɒn ðə ˈbændˌwæɡən/</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>시류에 편승하다, 유행을 따르다</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Many investors are jumping on the AI bandwagon hoping for quick profits.</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>After seeing the success of their competitor, they decided to jump on the bandwagon and offer similar services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>ENG-20260527-443</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>get a handle on</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə ˈhændl ɒn/</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>~을 이해하고 통제하다, 다루는 방법을 알다</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>It took me a while to get a handle on the new software's features.</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>We need to get a handle on our expenses before they get out of control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>ENG-20260527-444</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>have a lot on one's plate</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>/hæv ə lɒt ɒn wʌnz pleɪt/</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>할 일이 많다, 책임이 많다</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>With the upcoming merger and new product launch, the CEO has a lot on her plate.</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>I can't take on any more tasks right now; I already have a lot on my plate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>ENG-20260527-445</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>keep one's head above water</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>/kiːp wʌnz hɛd əˈbʌv ˈwɔːtər/</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>빚지지 않고 겨우 살아가다, 재정적 어려움 속에서 버티다</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Many small businesses are struggling to keep their heads above water during the economic downturn.</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>With rising inflation, it's hard for single parents to keep their heads above water.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>ENG-20260527-446</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>up in the air</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>/ʌp ɪn ðɪ ɛər/</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>미정인, 불확실한</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Our travel plans for the summer are still up in the air due to the uncertain situation.</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>The future of the project is still up in the air, awaiting board approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>ENG-20260527-447</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Modern Family</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>a drop in the bucket</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>/ə drɒp ɪn ðə ˈbʌkɪt/</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>새 발의 피, 극히 일부에 지나지 않는 양</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>The initial investment was just a drop in the bucket compared to the total cost of the project.</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Our contribution to the charity felt like a drop in the bucket, but every bit helps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>ENG-20260527-448</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>actions speak louder than words</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>/ˈækʃənz spiːk ˈlaʊdər ðæn wɜːrdz/</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>말보다 행동이 더 중요하다</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>He keeps promising to change, but actions speak louder than words.</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Instead of just talking about sustainability, the company showed that actions speak louder than words with its new eco-friendly products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ENG-20260527-449</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Modern Family</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>add fuel to the fire</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>/æd fjuːəl tuː ðə ˈfaɪər/</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>불난 집에 부채질하다, 상황을 악화시키다</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>His sarcastic remark only added fuel to the fire during the heated discussion.</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Don't mention the layoffs, you'll just add fuel to the fire of employee discontent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>ENG-20260527-450</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>all in the same boat</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>/ɔːl ɪn ðə seɪm boʊt/</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>모두 같은 처지에 있다, 한 배를 타다</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>With rising inflation, we're all in the same boat, trying to cut down on expenses.</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>During the pandemic, remote workers and office workers were all in the same boat, adapting to new routines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>ENG-20260527-451</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>barking up the wrong tree</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>/ˈbɑːrkɪŋ ʌp ðə rɒŋ triː/</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>엉뚱한 사람을 비난하거나 엉뚱한 방향으로 추측하다</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>If you think I'm responsible for this mistake, you're barking up the wrong tree.</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>The police were barking up the wrong tree until they found new evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>ENG-20260527-452</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>by the book</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>/baɪ ðə bʊk/</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>규칙대로, 원칙대로</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>The auditors always do everything by the book, leaving no room for error.</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>We have to handle this situation strictly by the book to avoid any legal issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>ENG-20260527-453</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Modern Family</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>come hell or high water</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>/kʌm hɛl ɔːr haɪ ˈwɔːtər/</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>어떤 어려움이 있어도, 무슨 수를 써서라도</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Come hell or high water, we will finish this project on time.</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>He promised to be there for her, come hell or high water.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>ENG-20260527-454</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>cross that bridge when we come to it</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>/krɒs ðæt brɪdʒ wɛn wiː kʌm tuː ɪt/</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>닥쳐서 해결하다, 미리 걱정하지 않다</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>I know there might be a problem with funding, but we'll cross that bridge when we come to it.</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>We don't know yet if we'll need extra staff; we'll cross that bridge when we come to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>ENG-20260527-455</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>cut to the chase</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>/kʌt tuː ðə tʃeɪs/</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>바로 본론으로 들어가다</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Let's cut to the chase and discuss the main issue without further delay.</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>I don't have much time, so please just cut to the chase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>ENG-20260527-456</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>don't put all your eggs in one basket</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>/doʊnt pʊt ɔːl jʊər ɛɡz ɪn wʌn ˈbɑːskɪt/</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>모든 것을 한 곳에 집중하지 마라, 분산 투자해라</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>It's wise not to put all your eggs in one basket, especially when investing in volatile stocks.</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>When looking for a job, don't put all your eggs in one basket; apply to multiple companies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>ENG-20260527-457</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>easier said than done</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>/ˈiːziər sɛd ðæn dʌn/</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>말이야 쉽지, 실행은 어렵다</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Saving money during high inflation is easier said than done for many families.</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Quitting smoking is easier said than done for many people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>ENG-20260527-458</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>every cloud has a silver lining</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>/ˈɛvri klaʊd hæz ə ˈsɪlvər ˈlaɪnɪŋ/</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>모든 불행에는 한 줄기 희망이 있다, 전화위복</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Losing that job was tough, but I found a better one. Every cloud has a silver lining.</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Even during difficult times, remember that every cloud has a silver lining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>ENG-20260527-459</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>get a taste of one's own medicine</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə teɪst ɒv wʌnz oʊn ˈmɛdɪsɪn/</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>자신이 남에게 행했던 나쁜 일을 그대로 당하다, 자업자득</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>After constantly criticizing his colleagues, he finally got a taste of his own medicine when his project failed.</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>She was always spreading rumors, and now she's getting a taste of her own medicine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>ENG-20260527-460</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>get out of hand</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>/ɡɛt aʊt ɒv hænd/</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>통제 불능이 되다, 걷잡을 수 없게 되다</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>The party started to get out of hand, so we decided to leave early.</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>If we don't address these small issues now, they might get out of hand later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>ENG-20260527-461</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>get the ball rolling</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>/ɡɛt ðə bɔːl ˈroʊlɪŋ/</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>일을 시작하다, 추진하다</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Let's get the ball rolling on this new marketing campaign right away.</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>We need to get the ball rolling on our preparations for the annual conference.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I462"/>
+  <dimension ref="A1:I559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22130,6 +22130,4565 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>ENG-20260527-462</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>trim losses</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>/trɪm ˈlɒsɪz/</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>손실을 줄이다, 손실 폭을 좁히다</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>U.S. crude oil prices trim losses as traders assess whether U.S. is nearing a deal with Iran.</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>The company implemented aggressive cost-cutting measures to trim losses in the last quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>ENG-20260527-463</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>stare down</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>/stɛər daʊn/</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>(어려움, 위협 등에) 맞서다, 정면으로 응시하다, 위협에 굴하지 않다</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Republicans stare down inflation abyss with midterms fast approaching.</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>The new CEO had to stare down a potential employee strike in her first month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>ENG-20260527-464</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>push for</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>/pʊʃ fɔːr/</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>~을 강력히 요구하다, ~을 추진하다</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>President Trump pushes for funding for a White House ballroom, while Republicans struggle to find a clear message.</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Environmental groups continue to push for stricter regulations on carbon emissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>ENG-20260527-465</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>be on the lookout</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>/bi ɒn ðə ˈlʊkˌaʊt/</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>~을 경계하다, ~을 찾다, ~에 대해 주의를 기울이다</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Jamie Dimon says JPMorgan Chase could spend $20 billion on acquisition: 'We are on the lookout.'</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>We need to be on the lookout for new talent to join our expanding team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>ENG-20260527-466</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>invite scrutiny</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>/ɪnˈvaɪt ˈskruːtəni/</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>정밀 조사/감독을 초래하다, 의혹을 사다</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>A $20 billion deal could invite regulatory scrutiny given its position as the largest U.S. bank.</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Their recent accounting practices are likely to invite scrutiny from the IRS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>ENG-20260527-467</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>pull back</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>/pʊl bæk/</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>물러나다, 손을 떼다, (투자 등을) 회수하다</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Homebuyers also pulled back but were still more active than last year.</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Investors began to pull back from the volatile stock market after the news.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>ENG-20260527-468</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>ramp up</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>/ræmp ʌp/</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>~을 늘리다, 강화하다, 증대시키다</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Boeing CEO says company met requirements to increase 737 Max production to 47 jets per month, essentially to ramp up its production.</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>We need to ramp up our marketing efforts before the product launch next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>ENG-20260527-469</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>meet requirements</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>/miːt rɪˈkwaɪərmənts/</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>요구 사항을 충족시키다</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Boeing CEO says company met requirements to increase 737 Max production.</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>The new software successfully meets all the client's security requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>ENG-20260527-470</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>appeal to</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>/əˈpiːl tuː/</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>~의 흥미/관심을 끌다, ~에게 매력적으로 보이다</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>The advertising watchdog said the adverts featuring top footballers had a strong appeal to under-18s.</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>The vibrant packaging is designed to appeal to younger consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>ENG-20260527-471</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>follow up on</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>/ˈfɒloʊ ʌp ɒn/</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>~에 대해 후속 조치를 취하다, 추가 확인하다</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>I need to follow up on that email I sent to the client last week.</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Please follow up on the status of those overdue invoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>ENG-20260527-472</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>fall through</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>/fɔːl θruː/</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>(계획, 협상 등이) 수포로 돌아가다, 실패하다</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Our plans for the weekend fell through because of the sudden change in weather.</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>The acquisition deal almost fell through due to disagreements over intellectual property rights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>ENG-20260527-473</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>bail out</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>/beɪl aʊt/</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>(어려움에 처한 사람/회사 등을) 돕다, 구제하다</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>The government had to bail out several banks during the financial crisis.</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>We had to bail out our friend who got into trouble overseas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>ENG-20260527-474</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>chew out</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>/tʃuː aʊt/</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>~을 꾸짖다, 심하게 야단치다</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>My boss really chewed me out for missing the deadline.</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>The coach chewed out the players for their poor performance in the first half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>ENG-20260527-475</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>call for</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>/kɔːl fɔːr/</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>~을 요구하다, ~을 필요로 하다</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>The environmental report calls for immediate action to reduce pollution levels.</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>This situation calls for a calm and rational approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>ENG-20260527-476</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>square away</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>/skwɛər əˈweɪ/</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>(일 등을) 정리하다, 마무리하다</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>I need to square away a few things before I can leave for vacation.</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Let's square away the paperwork so we can proceed with the project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>ENG-20260527-477</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>come up with</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>/kʌm ʌp wɪð/</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>~을 생각해내다, 제안하다</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>They had to come up with a new strategy after their initial plan failed.</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Can you come up with some innovative ideas for our next product launch?</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>ENG-20260527-478</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>come down with</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>/kʌm daʊn wɪð/</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>(질병에) 걸리다</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>I think I'm coming down with a cold, I feel a bit under the weather.</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>She couldn't attend the meeting because she came down with the flu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>ENG-20260527-479</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>get across</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>/ɡɛt əˈkrɒs/</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>(의미, 메시지 등을) 전달하다, 이해시키다</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>It was difficult to get my point across during the heated discussion.</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>The speaker struggled to get her complex ideas across to the general audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>ENG-20260527-480</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>get around to</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>/ɡɛt əˈraʊnd tuː/</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>(미뤄왔던 일을) 마침내 하다</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>I still haven't gotten around to organizing my files, but I will soon.</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>I hope to get around to calling my parents this weekend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>ENG-20260527-481</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>zoom in on</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>/zuːm ɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>~에 초점을 맞추다, 집중하다</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>The analyst decided to zoom in on the specific details of the company's financial report.</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>The team needs to zoom in on the most critical customer feedback to improve the product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>ENG-20260527-482</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>go through with</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>/ɡoʊ θruː wɪð/</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>(계획, 약속 등을) 실행하다, 끝까지 해내다</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Despite his doubts, he decided to go through with the difficult surgery.</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Are you really going to go through with selling your house in this market?</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>ENG-20260527-483</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>weigh in on</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>/weɪ ɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>~에 대해 의견을 제시하다, 한마디 거들다</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Everyone wanted to weigh in on the controversial decision during the meeting.</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>The expert was asked to weigh in on the potential impact of the new regulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>ENG-20260527-484</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>fill in for</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>/fɪl ɪn fɔːr/</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>~을 대신하다, 대리하다</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Could you fill in for me at the meeting tomorrow? I'm feeling unwell.</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>The junior analyst had to fill in for her manager who was on paternity leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>ENG-20260527-485</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>push back</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>/pʊʃ bæk/</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>(일정, 마감일 등을) 미루다, 연기하다</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>We had to push back the project deadline by a week due to unforeseen delays.</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Can we push back our meeting to Friday afternoon instead of Thursday morning?</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>ENG-20260527-486</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>get something off the ground</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmθɪŋ ɒf ðə ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>(사업, 프로젝트 등을) 시작하다, 본궤도에 올리다</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>It took a lot of effort to get the startup off the ground, but it's finally profitable.</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>We need more funding to get this innovative research project off the ground.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>ENG-20260527-487</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>lose sleep over</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>/luːz sliːp ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>~때문에 걱정하여 잠을 못 이루다</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Don't lose sleep over that minor mistake; it's easily fixable.</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>I'm not going to lose sleep over the company's financial results; it's out of my control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>ENG-20260527-488</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>put a lid on</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>/pʊt ə lɪd ɒn/</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>~을 억제하다, 통제하다</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>The government tried to put a lid on the rising fuel prices, but it was a challenge.</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>We need to put a lid on office gossip before it affects team morale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>ENG-20260527-489</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>bear fruit</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>/bɛər fruːt/</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>결실을 맺다, 성과를 내다</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>After years of hard work, their research project finally began to bear fruit.</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Our investment in new technology will eventually bear fruit in increased efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>ENG-20260527-490</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>come to terms with</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>/kʌm tə tɜːrmz wɪð/</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>~을 받아들이다, 인정하다 (힘든 현실 등)</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>She's still trying to come to terms with the unexpected job loss.</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>It's hard to come to terms with the fact that the project failed after all our efforts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>ENG-20260527-491</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>have a say</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>/hæv ə seɪ/</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>발언권/결정권을 갖다</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Every employee should have a say in decisions that affect their work environment.</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>We believe that customers should have a say in the development of new products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>ENG-20260527-492</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>throw a curveball</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>/θroʊ ə ˈkɜːrvˌbɔːl/</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>예상치 못한 문제를 제기하다, 허를 찌르다</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Just when we thought we had everything planned, the client threw us a curveball with a last-minute change.</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Life has a way of throwing curveballs when you least expect them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>ENG-20260527-493</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>play hardball</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>/pleɪ ˈhɑːrdˌbɔːl/</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>강경하게 나가다, 강경책을 쓰다</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>During the merger negotiations, our CEO decided to play hardball to get the best terms.</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>If they refuse to compromise, we might have to play hardball in the next round of talks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>ENG-20260527-494</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>lose one's train of thought</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>/luːz wʌnz treɪn əv θɔːt/</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>(하던 이야기나 생각을) 놓치다</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>I was about to tell you something important, but I lost my train of thought.</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>The unexpected question made him lose his train of thought during the presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>ENG-20260527-495</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>put all one's eggs in one basket</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>/pʊt ɔːl wʌnz ɛɡz ɪn wʌn ˈbɑːskɪt/</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>모든 것을 한 가지에 걸다, 위험 분산을 하지 않다</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>It's risky to put all your eggs in one basket when investing; diversify your portfolio.</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>The company decided not to put all its eggs in one basket and explored multiple market segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>ENG-20260527-496</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>pass the buck</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>/pɑːs ðə bʌk/</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>책임을 전가하다, 떠넘기다</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Don't try to pass the buck; you're responsible for this mistake.</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Good leaders don't pass the buck; they take responsibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>ENG-20260527-497</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>talk shop</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>/tɔːk ʃɒp/</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>일/직업 이야기를 하다 (특히 사적인 자리에서)</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>We were at a party, but all they did was talk shop about the latest tech trends.</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>I tried to enjoy my vacation, but my colleagues kept wanting to talk shop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>ENG-20260527-498</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>bend over backwards</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>/bɛnd ˈoʊvər ˈbækˌwɜːrdz/</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>엄청나게 노력하다, 무척 애쓰다</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>We bent over backwards to meet the client's demands, but they were still unhappy.</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Our customer support team will bend over backwards to resolve your issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>ENG-20260527-499</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>go with one's gut</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>/ɡoʊ wɪð wʌnz ɡʌt/</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>직감에 따르다, 본능적으로 행동하다</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>I wasn't sure what to do, but I decided to go with my gut feeling and it paid off.</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Sometimes, in uncertain situations, it's best to go with your gut rather than overthinking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>ENG-20260527-500</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>get one's foot in the door</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>/ɡɛt wʌnz fʊt ɪn ðə dɔːr/</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>(직업, 분야에) 발판을 마련하다, 첫발을 들여놓다</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>He started as an intern, just trying to get his foot in the door at the prestigious firm.</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>An entry-level position is often a good way to get your foot in the door of a competitive industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>ENG-20260527-501</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>off the top of one's head</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>/ɒf ðə tɒp ɒv wʌnz hɛd/</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>즉석에서, 생각나는 대로</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>I can't give you the exact figures off the top of my head, but I can look them up.</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Off the top of my head, I'd say the main issue is communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>ENG-20260527-502</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>hit the nail on the head</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>/hɪt ðə neɪl ɒn ðə hɛd/</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>정확히 핵심을 짚다, 정곡을 찌르다</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Your analysis of the problem really hit the nail on the head.</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>When you said the main challenge was motivation, you really hit the nail on the head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ENG-20260527-503</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>blow off steam</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>/bloʊ ɒf stiːm/</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>스트레스를 풀다, 울분을 터뜨리다</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>After a long week at work, he liked to go to the gym to blow off steam.</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Let's go for a walk to blow off some steam after that tense meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ENG-20260527-504</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>take a toll on</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>/teɪk ə toʊl ɒn/</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>~에 큰 피해를 주다, 악영향을 미치다</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>The stress of the job started to take a toll on his health.</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>The prolonged economic downturn is taking a toll on small businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ENG-20260527-505</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>think outside the box</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>/θɪŋk aʊtˈsaɪd ðə bɒks/</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>고정관념에서 벗어나 사고하다, 창의적으로 생각하다</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>To solve this complex problem, we need to think outside the box and come up with new solutions.</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>The company encourages employees to think outside the box for innovative product ideas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ENG-20260527-506</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>bring to the table</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>/brɪŋ tə ðə ˈteɪbl/</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>제공하다, 기여하다 (논의, 협상 등에서)</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>What new skills can you bring to the table if you join our team?</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Each department will bring their ideas to the table during the strategic planning session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ENG-20260527-507</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>put one's two cents in</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>/pʊt wʌnz tuː sɛnts ɪn/</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>자기 의견을 말하다, 한마디 거들다 (주로 비공식적이고 겸손한 표현)</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>If I may put my two cents in, I think we should reconsider the budget.</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Everyone was discussing the new policy, so I decided to put my two cents in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ENG-20260527-508</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>take the plunge</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>/teɪk ðə plʌndʒ/</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>과감히 시도하다, 중요한 결정을 내리다</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>After months of hesitation, she finally decided to take the plunge and start her own business.</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>I'm nervous about moving to a new city, but it's time to take the plunge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ENG-20260527-509</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>have a change of heart</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>/hæv ə tʃeɪndʒ əv hɑːrt/</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>마음을 바꾸다, 변심하다</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>He was going to sell his car, but he had a change of heart at the last minute.</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>The board had a change of heart and decided to approve the controversial merger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>ENG-20260527-510</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>get one's act together</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>/ɡɛt wʌnz ækt təˈɡɛðər/</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>정신 차리다, 일을 제대로 하다</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>If you don't get your act together, you're going to lose your job.</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>The team needs to get its act together before the final presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>ENG-20260527-511</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>run a tight ship</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>/rʌn ə taɪt ʃɪp/</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>조직/사업을 엄격하고 효율적으로 운영하다</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>The new manager runs a very tight ship, ensuring everything is organized and efficient.</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Our finance department runs a tight ship, which is why we rarely have budget overruns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>ENG-20260527-512</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>pull one's weight</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>/pʊl wʌnz weɪt/</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>자기 몫을 다하다, 책임을 다하다</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Everyone on the team needs to pull their weight for us to succeed.</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>He's not pulling his weight in the group project, which is affecting our progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>ENG-20260527-513</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>rock the boat</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>/rɒk ðə boʊt/</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>평지풍파를 일으키다, 말썽을 일으키다</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>I don't want to rock the boat by bringing up that controversial topic again.</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>The new employee was advised not to rock the boat too much in her first few months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>ENG-20260527-514</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>have one's work cut out for one</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>/hæv wʌnz wɜːrk kʌt aʊt fɔːr wʌn/</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>할 일이 많다, 어려운 과제가 주어지다</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>With all these new regulations, the compliance team really has its work cut out for it.</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>After the merger, the integration team will have their work cut out for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>ENG-20260527-515</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>get the hang of</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>/ɡɛt ðə hæŋ ɒv/</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>~의 요령을 터득하다, 익숙해지다</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>It took me a few tries, but I'm finally getting the hang of this new software.</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Don't worry if it's difficult at first; you'll get the hang of it with practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>ENG-20260527-516</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>talk someone into</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>/tɔːk ˈsʌmwʌn ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>~을 설득하여 ~하게 하다</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>She didn't want to go, but I managed to talk her into joining us for dinner.</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>We need to talk the client into extending the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>ENG-20260527-517</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>talk someone out of</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>/tɔːk ˈsʌmwʌn aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>~을 설득하여 ~하지 못하게 하다</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>I tried to talk him out of quitting his job, but he had already made up his mind.</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Can you talk your boss out of cutting the marketing budget?</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>ENG-20260527-518</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>put someone on the spot</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌmwʌn ɒn ðə spɒt/</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>~를 곤란한 입장에 빠뜨리다, 즉답을 요구하다</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>The reporter's unexpected question put the politician on the spot.</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>I didn't want to put you on the spot, but I need an answer by tomorrow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>ENG-20260527-519</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>have a thick skin</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>/hæv ə θɪk skɪn/</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>남의 비판에 개의치 않다, 맷집이 좋다</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>In this industry, you need to have a thick skin because criticism is frequent.</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>You need to have a thick skin if you're going to work in sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>ENG-20260527-520</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>have a thin skin</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>/hæv ə θɪn skɪn/</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>감성적이다, 상처를 잘 받다</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>She has a thin skin, so be careful with your comments around her.</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>He's a talented artist, but he has a thin skin when it comes to criticism of his work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>ENG-20260527-521</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>make a long story short</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>/meɪk ə lɒŋ stɔːri ʃɔːrt/</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>요약하자면, 간단히 말해서</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>To make a long story short, we ended up missing our flight.</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Long story short, the project was successful but incredibly challenging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>ENG-20260527-522</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>get bent out of shape</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>/ɡɛt bɛnt aʊt əv ʃeɪp/</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>화내다, 몹시 기분 상하다</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Don't get bent out of shape over a minor disagreement; it's not worth it.</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>He got all bent out of shape when I told him the meeting was rescheduled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>ENG-20260527-523</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>take a stand</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>/teɪk ə stænd/</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>입장을 취하다, 태도를 분명히 하다</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>The company decided to take a stand against child labor in their supply chain.</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>It's important to take a stand on ethical issues, even if it's unpopular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>ENG-20260527-524</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>step up to the plate</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>/stɛp ʌp tuː ðə pleɪt/</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>책임을 맡다, 적극적으로 나서다</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>When the team leader quit, John stepped up to the plate and took charge.</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>We need someone who is willing to step up to the plate and lead this initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>ENG-20260527-525</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>pay dividends</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>/peɪ ˈdɪvɪdɛndz/</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>수익을 내다, 이득을 가져다주다</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Investing in employee training always pays dividends in the long run.</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Her dedication and hard work eventually paid dividends with a promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>ENG-20260527-526</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>get a foot in the door</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə fʊt ɪn ðə dɔːr/</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>(특정 직업/조직에) 발판을 마련하다, 첫발을 들여놓다</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>He started as an intern, just trying to get his foot in the door at the prestigious firm.</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>An entry-level position is often a good way to get your foot in the door of a competitive industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>ENG-20260527-527</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>put someone through the wringer</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌmwʌn θruː ðə ˈrɪŋər/</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>몹시 힘들게 하다, 고통을 주다</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>The audit really put our finance department through the wringer last month.</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>The rigorous training program put the new recruits through the wringer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>ENG-20260527-528</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>at the end of the day</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>/æt ðɪ ɛnd əv ðə deɪ/</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>결국에는, 궁극적으로는</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>We can argue about the details, but at the end of the day, we all want the project to succeed.</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>At the end of the day, customer satisfaction is our top priority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>ENG-20260527-529</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>come to a head</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>/kʌm tuː ə hɛd/</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>극에 달하다, 절정에 이르다 (위기나 문제 등)</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>The ongoing tensions between the two departments finally came to a head last week.</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>The dispute over funding came to a head during the board meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>ENG-20260527-530</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>get a grasp of</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə ɡrɑːsp ɒv/</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>~을 이해하다, 파악하다</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>It took him a while to get a good grasp of the complex economic theory.</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>New employees need time to get a full grasp of the company's internal processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>ENG-20260527-531</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>keep tabs on</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>/kiːp tæbz ɒn/</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>~을 주시하다, 감시하다</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>The manager asked me to keep tabs on the new project's progress.</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>It's important to keep tabs on your competitors' strategies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>ENG-20260527-532</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>take a backseat</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>/teɪk ə ˈbækˌsiːt/</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>덜 중요한 역할을 하다, 뒷전으로 물러나다</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>After years of leading, she decided to take a backseat and let younger colleagues take charge.</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Sometimes you need to take a backseat and let others lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>ENG-20260527-533</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>put a spin on</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>/pʊt ə spɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>(정보, 상황 등을) 유리하게 해석/설명하다, (견해를) 가미하다</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>The politician tried to put a positive spin on the negative election results.</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>PR teams often try to put a favorable spin on bad news.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>ENG-20260527-534</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>break the ice</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>/breɪk ðɪ aɪs/</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>딱딱한 분위기를 깨다, 서먹서먹한 관계를 완화하다</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>We played a few games to break the ice at the beginning of the workshop.</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>A funny anecdote is always a good way to break the ice in a presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>ENG-20260527-535</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>put one's money where one's mouth is</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>/pʊt wʌnz ˈmʌni wɛər wʌnz maʊθ ɪz/</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>말뿐이 아니라 행동으로 보여주다, 공언한 대로 돈을 쓰거나 행동하다</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>He keeps saying he'll invest, but he needs to put his money where his mouth is.</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>If the company truly believes in environmental protection, they need to put their money where their mouth is and invest in sustainable practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>ENG-20260527-536</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>on the same wavelength</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>/ɒn ðə seɪm ˈweɪvlɛŋθ/</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>생각이 일치하는, 통하는</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>My colleague and I are always on the same wavelength when it comes to creative ideas.</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>It helps a lot when you're working with someone who's on the same wavelength.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>ENG-20260527-537</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>throw one's weight around</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>/θroʊ wʌnz weɪt əˈraʊnd/</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>권력을 휘두르다, 위세를 부리다</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>The new manager started throwing his weight around, making everyone uncomfortable.</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Don't throw your weight around just because you got a promotion; it's bad for team morale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>ENG-20260527-538</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>cut someone some slack</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>/kʌt ˈsʌmwʌn sʌm slæk/</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>~에게 너그러이 대하다, ~을 봐주다</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>He's been under a lot of stress lately, so cut him some slack.</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>It's her first day, so we should cut her some slack if she makes mistakes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>ENG-20260527-539</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>get off the hook</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>/ɡɛt ɒf ðə hʊk/</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>(어려운 상황, 책임에서) 벗어나다</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>I thought I'd have to work late, but luckily I got off the hook.</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>The company managed to get off the hook for the environmental damage by settling out of court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>ENG-20260527-540</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>give it one's best shot</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>/ɡɪv ɪt wʌnz bɛst ʃɒt/</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>최선을 다하다</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>I might not win, but I'm going to give it my best shot in the competition.</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Even if the odds are against us, we should still give it our best shot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ENG-20260527-541</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>on the fly</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>/ɒn ðə flaɪ/</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>즉석에서, 즉흥적으로</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>We had to make some crucial decisions on the fly during the crisis.</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>The developer had to fix the bug on the fly during the live demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>ENG-20260527-542</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>the last straw</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>/ðə læst strɔː/</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>더 이상 참을 수 없는 한계, 마지막 지푸라기</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>His constant tardiness was annoying, but breaking my laptop was the last straw.</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>The increasing energy bills were the last straw for many low-income households.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>ENG-20260527-543</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>have a stake in</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>/hæv ə steɪk ɪn/</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>~에 이해관계가 있다, ~에 대한 책임/권리가 있다</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>As shareholders, we all have a stake in the company's success.</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Every team member has a stake in the project's outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>ENG-20260527-544</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>lose one's cool</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>/luːz wʌnz kuːl/</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>침착함을 잃다, 화내다</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>He rarely loses his cool, even under immense pressure.</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>It's easy to lose your cool when dealing with difficult customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>ENG-20260527-545</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>take sides</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>/teɪk saɪdz/</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>(논쟁 등에서) 편을 들다</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>In a dispute between friends, it's often best not to take sides.</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>The manager refused to take sides in the argument between the two employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>ENG-20260527-546</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>give every chance to succeed</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈɛvri tʃæns tuː səkˈsiːd/</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>~에게 성공할 모든 기회를 주다</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>U.S. will give Iran talks 'every chance to succeed'</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>The company decided to give the new startup every chance to succeed by providing ample resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>ENG-20260527-547</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>near a deal</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>/nɪər ə diːl/</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>합의에 근접하다</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>traders assess whether U.S. is nearing a deal with Iran</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>After weeks of intense negotiations, both parties finally seem to be nearing a deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>ENG-20260527-548</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>be the right way to go</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>/bi ðə raɪt weɪ tuː ɡoʊ/</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>올바른/최적의 방법이다</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>the automaker's decision to kill its EV to focus on plug-in hybrid electric vehicles was 'the right way to go' for his company.</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Investing in sustainable energy is definitely the right way to go for future economic growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>ENG-20260527-549</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>dilute the vote</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>/daɪˈluːt ðə voʊt/</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>(특정 집단의) 표의 영향력을 약화시키다</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>congressional map that dilutes Black vote</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Critics argued that the new district boundaries would dilute the vote of minority communities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>ENG-20260527-550</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>feel worse off</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>/fiːl wɜːrs ɔːf/</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>형편이 더 나빠졌다고 느끼다</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Americans feel worse off than ever before</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Many low-income families feel worse off due to the rising cost of living.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>ENG-20260527-551</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>when the pinch comes</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>/wɛn ðə pɪntʃ kʌmz/</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>어려움/곤궁이 닥칠 때</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>action now can save money when the pinch comes this winter.</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>It's wise to save some money for a rainy day, especially for when the pinch comes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>ENG-20260527-552</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>return to normal</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>/rɪˈtɜːrn tuː ˈnɔːrməl/</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>정상으로 돌아오다</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Iran could return the passageway to normal traffic flows within a month of a peace deal</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>After the power outage, it took a few hours for services to return to normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>ENG-20260527-553</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>be under intense pressure</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>/bi ˈʌndər ɪnˈtɛns ˈprɛʃər/</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>엄청난 압력을 받다</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>comes despite intense pressure from Chinese EV makers.</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>The CEO was under intense pressure to deliver positive quarterly results after recent setbacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>ENG-20260527-554</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>hit hardest</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>/hɪt ˈhɑːrdɪst/</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>가장 큰 타격을 받다</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Mortgage rates rose to the highest level in nine months, hitting refinance demand hardest.</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Small businesses were hit hardest by the economic downturn and lockdown measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>ENG-20260527-555</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>face a rise in</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>/feɪs ə raɪz ɪn/</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>~의 증가에 직면하다</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Low-income households face ‘remarkable’ rise in food insecurity</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Many countries are expected to face a rise in unemployment due to global economic shifts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>ENG-20260527-556</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>be more active than</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>/bi mɔːr ˈæktɪv ðæn/</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>~보다 더 활발하다/활동적이다</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Homebuyers also pulled back but were still more active than last year.</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Investors are typically more active than usual during periods of market volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>ENG-20260527-557</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>fall more than (X percent)</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>/fɔːl mɔːr ðæn ɛks ˈpɜːrsɛnt/</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>~퍼센트 이상 하락하다</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Oil prices fall more than 4%</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Stock prices are expected to fall more than 5 percent by the end of the trading day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>ENG-20260527-558</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>be open to everyone</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>/bi ˈoʊpən tuː ˈɛvriˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>모두에게 개방되다; 모두에게 열려 있다</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Strait of Hormuz...is 'going to be open to everybody.'</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>The new public library will be open to everyone, regardless of age or background.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I559"/>
+  <dimension ref="A1:I657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26689,6 +26689,4612 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>ENG-20260528-001</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>erase gains</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>/ɪˈreɪs ɡeɪnz/</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>(이전의) 상승분/이득을 지우다</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Oil prices pulled back, erasing earlier gains, on a report that an agreement was reached.</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Unexpected geopolitical events can quickly erase gains made in the market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>ENG-20260528-002</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>reach an agreement</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>/riːtʃ ən əˈɡriːmənt/</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>합의에 도달하다</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>U.S. and Iranian negotiators reached an agreement to extend the ceasefire.</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>After weeks of talks, both sides finally managed to reach an agreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>ENG-20260528-003</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>pull something (from somewhere)</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>/pʊl ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>(서비스, 지원 등을) 철회하다, 중단하다</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>The Trump administration is considering pulling international flight processing in 'sanctuary cities.'</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>The company decided to pull its advertising campaign from social media after negative feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>ENG-20260528-004</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>become the face of something</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>/bɪˈkʌm ðə feɪs ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>~의 상징/대표적인 인물이 되다</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Citadel CEO Ken Griffin became the face of the tax after New York City Mayor Mamdani posted a video in front of Griffin's penthouse apartment.</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Her innovative designs made her become the face of sustainable fashion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>ENG-20260528-005</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>hit an annual rate</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>/hɪt ən ˈænjuəl reɪt/</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>연간 비율/수치에 도달하다</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Core inflation hit an annual rate of 3.3% in April, as expected.</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>The unemployment rate is expected to hit an annual rate of 5% by year-end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>ENG-20260528-006</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>hopes fade for something</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>/hoʊps feɪd fɔːr ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>~에 대한 희망이 사라지다</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Traders' hopes fade for U.S.-Iran nuclear deal this year despite report on potential ceasefire talks.</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>As the hours passed, hopes faded for finding survivors of the accident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>ENG-20260528-007</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>sign someone onto something</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>/saɪn ˈsʌmwʌn ˈɒntuː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>(프로젝트, 협약 등에) ~를 참여시키다, 계약하다</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>IBM has signed Goldman Sachs, Morgan Stanley, JP Morgan and Bank of America onto its open-source cybersecurity effort.</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>They're trying to sign more major corporations onto their new sustainability initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>ENG-20260528-008</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>bid to do something</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>/bɪd tuː duː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>~하려는 시도/노력</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>CFTC bid to vacate order against Winklevoss' crypto exchange 'very unusual.'</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>The city council made a last-minute bid to save the historic building from demolition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>ENG-20260528-009</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>vacate an order</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>/ˈveɪkeɪt ən ˈɔːrdər/</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>(법원) 명령을 취소하다</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>The Commodity Futures Trading Commission is looking to undo a $5 million civil penalty and vacate an order.</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>The judge decided to vacate the previous court order due to new evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>ENG-20260528-010</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>lead to something</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>/liːd tuː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>~로 이어지다, ~을 초래하다</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Ro Khanna is taking his economic message on the road. Will it lead to the White House?</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Poor communication can often lead to misunderstandings in a team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>ENG-20260528-011</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>fall to a level</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>/fɔːl tuː ə ˈlɛvl/</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>(수치, 비율 등이 특정) 수준으로 떨어지다</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Americans’ savings rate falls to lowest level since 2022 as inflation outpaces paychecks.</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>The company's profits unexpectedly fell to its lowest level in five years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>ENG-20260528-012</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>put money aside</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>/pʊt ˈmʌni əˈsaɪd/</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>돈을 따로 모아두다, 저축하다</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Americans have less money to put aside for emergencies and other savings goals.</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>It's important to put money aside regularly for retirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>ENG-20260528-013</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>raid 401(k)</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>/reɪd fɔːr oʊ wʌn keɪ/</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>401(k) 연금 계좌에서 돈을 인출하다 (주로 조기 인출)</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>More workers are raiding their 401(k)s as average balances fall, Fidelity says.</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Facing unexpected medical bills, many individuals are forced to raid their retirement savings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>ENG-20260528-014</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>sink at the start of something</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>/sɪŋk æt ðə stɑːrt ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>(수치 등이) ~ 시작 시점에 하락하다</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Retirement account balances sank at the start of 2026 amid market swings.</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Sales figures often sink at the start of a new quarter before picking up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>ENG-20260528-015</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>tap into something</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>/tæp ˈɪntuː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>(자원, 계좌 등을) 활용하다, 이용하다</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>More savers tapped their accounts for cash, indicating financial strain.</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>The company plans to tap into new markets to expand its customer base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>ENG-20260528-016</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>shrink opportunities</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>/ʃrɪŋk ˌɒpərˈtuːnətiz/</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>기회가 줄어들다</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Opportunities shrinking for too many young people, says major report on 'lost generation.'</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>In a competitive job market, entry-level opportunities often shrink.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>ENG-20260528-017</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>be set to do something</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>/bi sɛt tuː duː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>~할 예정이다, ~하게 될 운명이다</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>The number of 16 to 24-year-olds out of work, education or training is set to rise to 1.25 million by 2031.</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>The new factory is set to open next month, creating hundreds of jobs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>ENG-20260528-018</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>be out of work</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>/bi aʊt ʌv wɜːrk/</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>실직 상태이다, 일자리가 없다</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>A report warns the number of 16 to 24-year-olds out of work is set to rise.</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Many graduates find themselves out of work for several months after finishing university.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>ENG-20260528-019</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>struggle to find work</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>/ˈstrʌɡl tuː faɪnd wɜːrk/</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>일자리를 찾는 데 어려움을 겪다</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>The BBC has been hearing from young people who are struggling to find work.</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>After the economic downturn, many people began to struggle to find work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>ENG-20260528-020</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>tackle a challenge</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>/ˈtækl ə ˈtʃælɪndʒ/</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>난제/도전에 맞서 해결하다</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Young people are facing the job shortage and figuring out how they are tackling the challenge.</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>The government is trying to tackle the challenge of climate change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>ENG-20260528-021</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>fight a lawsuit</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>/faɪt ə ˈlɔːsuːt/</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>소송과 싸우다, 소송에 대응하다</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Drag queen Pattie Gonia fights trademark lawsuit by Patagonia.</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>The company announced it would fight a lawsuit filed by its former employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>ENG-20260528-022</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>hit back at something</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>/hɪt bæk æt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>~에 반격하다, 비난에 맞서다</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Ousted BP chairman hits back at 'lies' about his behaviour.</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>The politician hit back at critics who questioned his integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>ENG-20260528-023</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>hide behind anonymity</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>/haɪd bɪˈhaɪnd ˌænəˈnɪməti/</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>익명 뒤에 숨다</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Albert Manifold said no-one should be 'allowed to hide behind anonymity' when commenting on his time at BP.</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Online trolls often hide behind anonymity to spread hateful comments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>ENG-20260528-024</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>tell a story of something</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>/tɛl ə ˈstɔːri ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>~에 대한 이야기를 말해주다, ~을 보여주다</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>The £5 coffee that tells a story of global economic turmoil.</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>The crumbling ruins tell a story of a once-great civilization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>ENG-20260528-025</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>play the market</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>/pleɪ ðə ˈmɑːrkɪt/</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>시장을 이용하다, 시세 변동을 이용해 이익을 얻다</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Savvy coffee farmers playing the market, writes Faisal Islam.</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Experienced investors know how to play the market during times of volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>ENG-20260528-026</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>out of control</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>/aʊt ʌv kənˈtroʊl/</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>통제 불능인, 걷잡을 수 없는</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Is 'out of control' US tipping culture spreading overseas?</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>The party got completely out of control after midnight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>ENG-20260528-027</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>spread overseas</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>/sprɛd ˌoʊvərˈsiːz/</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>해외로 퍼지다, 확산되다</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Is 'out of control' US tipping culture spreading overseas?</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Many global brands are looking for ways to spread their influence overseas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>ENG-20260528-028</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>take account of something</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>/teɪk əˈkaʊnt ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>~을 고려하다, 참작하다</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>The European Commission says the online retailer failed to take account of risks from illegal products.</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>When making decisions, it's crucial to take account of all potential consequences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>ENG-20260528-029</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>save money on something</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>/seɪv ˈmʌni ɒn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>~에 돈을 절약하다</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>How you can save money on your energy bill.</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Shopping during sales is a good way to save money on clothes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>ENG-20260528-030</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>look into something</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>/lʊk ˈɪntuː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>~을 조사하다, 검토하다</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>New York and New Jersey are looking into the association after fans have reportedly been 'misled.'</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>The police are looking into the cause of the mysterious disappearance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>ENG-20260528-031</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>work on a relationship</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>/wɜːrk ɒn ə rɪˈleɪʃənˌʃɪp/</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>관계를 개선하기 위해 노력하다</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Emily's willing to work on the relationship, but in London.</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Every couple needs to actively work on their relationship to keep it strong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>ENG-20260528-032</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>be up to something</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>/bi ʌp tuː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>~할 준비가 되다, ~에 적합하다</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>I don’t think he's up to meeting everyone yet.</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>After a long flight, I'm not really up to going out tonight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>ENG-20260528-033</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>sneak over</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>/sniːk ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>몰래 가다/넘어가다</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>I snuck over there and raked up all the leaves on his front stoop.</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>We used to sneak over to the neighbor's garden to pick apples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>ENG-20260528-034</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>rake up leaves</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>/reɪk ʌp liːvz/</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>나뭇잎을 갈퀴로 긁어모으다</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>I snuck over there and raked up all the leaves on his front stoop.</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>My weekend chore is to rake up leaves in the backyard every autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>ENG-20260528-035</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>force-feed someone something</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>/fɔːrs fiːd ˈsʌmwʌn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>~에게 억지로 ~을 먹이다</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>He caught me and force-fed me cider and cookies.</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Parents sometimes have to force-feed medicine to their children.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>ENG-20260528-036</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>give birth to something</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>/ɡɪv bɜːrθ tuː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>~을 낳다, ~을 탄생시키다</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>I just gave birth to three children and I will not let them be raised in a world where Joey is right!</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>She gave birth to a healthy baby girl last night.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>ENG-20260528-037</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>be raised in a world</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>/bi reɪzd ɪn ə wɜːrld/</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>(어떤) 세상에서 자라다/양육되다</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>I will not let them be raised in a world where Joey is right!</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Children should be raised in a world that values kindness and equality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>ENG-20260528-038</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>respect someone's privacy</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>/rɪˈspɛkt ˈsʌmwʌnz ˈprɪvəsi/</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>~의 사생활을 존중하다</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>I think I'm gonna respect the privacy of my new secret boyfriend.</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>It's important to respect someone's privacy, especially when they ask for it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>ENG-20260528-039</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>work something out</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>/wɜːrk ˈsʌmθɪŋ aʊt/</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>문제를 해결하다, 상황을 정리하다</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>You have to come here so we can work this out.</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>We need to sit down and work out a solution to this disagreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>ENG-20260528-040</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>drive someone mad</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>/draɪv ˈsʌmwʌn mæd/</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>~를 미치게 하다, ~를 몹시 화나게/짜증 나게 하다</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>It drives me mad just thinking of you being in the same room as her!</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>The constant noise from the construction site is driving me mad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>ENG-20260528-041</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>make something work</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>/meɪk ˈsʌmθɪŋ wɜːrk/</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>~가 성공하도록 만들다, ~를 작동시키다</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>I'll come to New York and we'll try and make this work.</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Despite the challenges, they were determined to make their long-distance relationship work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>ENG-20260528-042</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>run into someone/something</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>/rʌn ˈɪntuː ˈsʌmwʌn/ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>우연히 만나다 / (문제 등에) 부딪히다</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>If you move to London, you might run into someone from your past.</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>I ran into my old high school friend at the supermarket yesterday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>ENG-20260528-043</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>go along with</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>/ɡoʊ əˈlɒŋ wɪð/</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>~에 동의하다, 따르다</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Emily decided to go along with Ross's idea of moving to New York.</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Despite her doubts, she decided to go along with the team's plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>ENG-20260528-044</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>get through to someone</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>/ɡɛt θruː tuː ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>~에게 ~을 이해시키다, 납득시키다</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Joey struggled to get through to the stage director that he was the host, not a phone answerer.</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>I've tried explaining it multiple times, but I just can't seem to get through to him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>ENG-20260528-045</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>buy into</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>/baɪ ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>(생각, 계획 등을) 믿다, 받아들이다</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>It was hard for Emily to buy into Ross's promise after the wedding incident.</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Most employees didn't buy into the CEO's explanation for the layoffs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>ENG-20260528-046</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>settle for</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>/ˈsɛtl fɔːr/</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>~에 만족하다, 차선책을 받아들이다</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>The union refused to settle for anything less than a significant pay raise.</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Don't settle for less than you deserve when negotiating your salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>ENG-20260528-047</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>cave in</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>/keɪv ɪn/</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>(압력에) 굴복하다, 항복하다</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>The Trump administration might cave in to pressure regarding international flights.</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>The government refused to cave in to the protesters' demands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>ENG-20260528-048</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>go sour</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ˈsaʊər/</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>(관계, 상황 등이) 틀어지다, 나빠지다</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Emily was worried her relationship with Ross might go sour again if Rachel was involved.</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Their business partnership started to go sour after a series of disagreements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>ENG-20260528-049</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>hold one's ground</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>/hoʊld wʌnz ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>자기 입장을 고수하다, 물러서지 않다</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>The airline management refused to back down and continued to hold its ground on flight processing.</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Despite intense questioning, the witness held his ground and repeated his testimony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>ENG-20260528-050</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>bear in mind</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>/bɛər ɪn maɪnd/</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>~을 명심하다, 유념하다</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Investors should bear in mind that market fluctuations are common.</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>When planning your trip, bear in mind that the weather can be unpredictable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>ENG-20260528-051</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>shed light on</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>/ʃɛd laɪt ɒn/</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>~을 밝히다, 해명하다</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>New reports could shed light on the truth behind the BP chairman's ousting.</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>The investigation aims to shed light on the causes of the accident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>ENG-20260528-052</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>strike a balance</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>/straɪk ə ˈbæləns/</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>균형을 맞추다, 조화를 이루다</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>The EU struggled to strike a balance between promoting online trade and regulating illegal products.</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>It's often hard to strike a balance between work and personal life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>ENG-20260528-053</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>follow suit</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>/ˈfɒloʊ suːt/</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>따라 하다, 선례를 따르다</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>If US tipping culture spreads, other countries might follow suit.</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>When one company raised its prices, others in the industry quickly followed suit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>ENG-20260528-054</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>pick up the slack</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>/pɪk ʌp ðə slæk/</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>다른 사람의 일을 대신하다, 빈틈을 메우다</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>When Joey was demoted, someone else had to pick up the slack as host.</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>When a team member went on leave, the rest of the team had to pick up the slack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>ENG-20260528-055</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>go hand in hand</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>/ɡoʊ hænd ɪn hænd/</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>밀접하게 연관되다, 함께 가다</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Inflation and falling savings rates often go hand in hand.</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Economic growth and job creation often go hand in hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>ENG-20260528-056</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>bridge the gap</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>/brɪdʒ ðə ɡæp/</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>격차를 줄이다, 연결하다</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Negotiators are trying to bridge the gap between the two countries' positions.</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Technology can help bridge the gap between people living far apart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>ENG-20260528-057</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>set the record straight</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>/sɛt ðə ˈrɛkərd streɪt/</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>오해를 풀다, 정확한 사실을 밝히다</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>The ousted chairman wanted to set the record straight about the 'lies' concerning his behavior.</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Let me set the record straight; I never said anything like that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>ENG-20260528-058</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>come under fire</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>/kʌm ˈʌndər ˈfaɪər/</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>비난/공격받다</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Fifa has come under fire over World Cup ticket prices.</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>The new policy came under fire from consumer advocacy groups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>ENG-20260528-059</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>drum up support</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>/drʌm ʌp səˈpɔːrt/</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>지지/후원을 모으다</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Ro Khanna is on the road to drum up support for his economic message.</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>The charity organization is trying to drum up support for its latest campaign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>ENG-20260528-060</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>lose one's temper</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>/luːz wʌnz ˈtɛmpər/</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>화내다, 이성을 잃다</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Emily came close to losing her temper when thinking about Rachel being with Ross.</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>He tends to lose his temper when he's under a lot of pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>ENG-20260528-061</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>miss the mark</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>/mɪs ðə mɑːrk/</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>목표에 미달하다, 실패하다</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>The initial inflation forecast completely missed the mark, leading to unexpected economic pressures.</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>His speech completely missed the mark and failed to address the audience's concerns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>ENG-20260528-062</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>speak of the devil</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>/spiːk ʌv ðə ˈdɛvl/</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>호랑이도 제 말 하면 온다더니 (때마침 이야기하던 사람이 나타날 때 쓰는 표현)</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Rachel was just talking about Monica's secret boyfriend, and then, speak of the devil, Chandler walked in.</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>We were just talking about John, and speak of the devil, here he comes!</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>ENG-20260528-063</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>have a chip on one's shoulder</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>/hæv ə tʃɪp ɒn wʌnz ˈʃoʊldər/</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>앙심을 품다, 불평이 많다</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>After being fired, the former chairman had a chip on his shoulder about the company.</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>He's always had a chip on his shoulder since he didn't get the promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>ENG-20260528-064</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>pull someone's leg</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>/pʊl ˈsʌmwʌnz lɛɡ/</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>~를 놀리다, 장난치다</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Joey thought Phoebe was just pulling his leg about Santa Claus not existing.</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Don't worry, I'm just pulling your leg; I didn't actually forget your birthday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>ENG-20260528-065</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>walk on eggshells</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>/wɔːk ɒn ˈɛɡʃɛlz/</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>살얼음판을 걷다, 매우 조심스럽게 행동하다</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Ross had to walk on eggshells around Emily after the wedding incident to avoid further upsetting her.</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Ever since their argument, I've been walking on eggshells around my parents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>ENG-20260528-066</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>get a head start</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə hɛd stɑːrt/</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>다른 사람보다 먼저 시작하다, 유리한 출발을 하다</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Taking action now to save money on energy bills allows you to get a head start before winter.</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Students who prepare early for exams get a head start on their peers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>ENG-20260528-067</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>let sleeping dogs lie</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>/lɛt ˈsliːpɪŋ dɔːɡz laɪ/</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>긁어 부스럼 만들지 않다, 가만히 두다</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>After patching things up, it was best to let sleeping dogs lie regarding past mistakes.</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>I think it's better to let sleeping dogs lie and not bring up that old argument again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>ENG-20260528-068</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>bite off more than one can chew</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>/baɪt ɒf mɔːr ðæn wʌn kæn tʃuː/</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>자신이 감당할 수 있는 것보다 더 많은 일을 맡다</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Taking on a huge deal without proper preparation could be biting off more than one can chew.</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>I think I bit off more than I can chew by volunteering for three different committees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>ENG-20260528-069</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>get wind of something</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>/ɡɛt wɪnd ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>~에 대해 소문을 듣다, 눈치채다</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>The traders got wind of the ceasefire report before it was officially announced.</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>The boss got wind of the plan to surprise him, so we had to change it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>ENG-20260528-070</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>in the pipeline</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>/ɪn ðə ˈpaɪplaɪn/</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>진행 중인, 준비 중인</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>There are several new initiatives in the pipeline for IBM's cybersecurity efforts.</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>We have a few exciting new projects in the pipeline for next year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>ENG-20260528-071</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>on the back burner</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>/ɒn ðə bæk ˈbɜːrnər/</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>나중으로 미루어진, 우선순위가 낮은</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>The initial plans for the deal were put on the back burner during the ceasefire negotiations.</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>We had to put the renovation plans on the back burner due to budget constraints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>ENG-20260528-072</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>blow over</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>/bloʊ ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>(문제가) 잠잠해지다, 지나가다</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Emily hoped the awkwardness with Ross and Rachel would eventually blow over.</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Just give them some time; the argument will blow over soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>ENG-20260528-073</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>level with someone</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>/ˈlɛvl wɪð ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>~에게 솔직하게 말하다</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Ross decided to level with Emily about the difficulties of moving to London.</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Can I level with you? I'm not happy with the current situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>ENG-20260528-074</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>keep one's chin up</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>/kiːp wʌnz tʃɪn ʌp/</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>낙담하지 않고 기운을 내다</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Joey's friends always encouraged him to keep his chin up even when facing career setbacks.</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>It's tough right now, but keep your chin up; things will get better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>ENG-20260528-075</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>in the red</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>/ɪn ðə rɛd/</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>적자인, 손실을 보고 있는</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Many businesses found themselves in the red after the global economic turmoil.</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>The company has been in the red for two consecutive quarters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>ENG-20260528-076</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>in the black</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>/ɪn ðə blæk/</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>흑자인, 이익을 내고 있는</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Despite global challenges, some savvy companies managed to stay in the black.</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>After a difficult year, the company is finally back in the black.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>ENG-20260528-077</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>be on the fence</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>/bi ɒn ðə fɛns/</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>결정하지 못하고 망설이다</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Trump was on the fence about approving the ceasefire extension.</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>I'm still on the fence about whether to take the new job offer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>ENG-20260528-078</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>play by the rules</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>/pleɪ baɪ ðə ruːlz/</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>규칙을 따르다, 정정당당하게 하다</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>The EU expects all online retailers to play by the rules regarding product safety.</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>In business, it's essential to play by the rules to maintain your reputation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>ENG-20260528-079</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>be in a bind</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>/bi ɪn ə baɪnd/</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>곤경에 처하다, 난처한 상황에 있다</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Americans are in a bind as inflation outpaces their paychecks.</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>I'm in a bind because I promised to help two different friends at the same time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>ENG-20260528-080</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>turn a profit</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>/tɜːrn ə ˈprɒfɪt/</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>이익을 내다, 흑자를 기록하다</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Many businesses are struggling to turn a profit amidst global economic turmoil.</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>After years of losses, the startup finally managed to turn a profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>ENG-20260528-081</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>at stake</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>/æt steɪk/</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>위험에 처한, 성패가 달린</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Many jobs are at stake if the company fails to adapt to new market conditions.</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>With millions of dollars at stake, investors were keenly watching the market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>ENG-20260528-082</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>on the verge of</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>/ɒn ðə vɜːrdʒ ʌv/</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>~의 직전에, 막 ~하려던 참이다</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>The two countries were on the verge of reaching a ceasefire agreement.</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>The company was on the verge of bankruptcy before the new investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>ENG-20260528-083</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>run its course</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>/rʌn ɪts kɔːrs/</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>수명을 다하다, 자연스럽게 끝나다</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Some analysts believe the current inflation trend will run its course by next year.</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>The dispute has run its course, and it's time to move on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>ENG-20260528-084</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>jump through hoops</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>/dʒʌmp θruː huːps/</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>까다로운 절차를 거치다, 힘든 일을 겪다</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Consumers often have to jump through hoops to get refunds for faulty products.</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>We had to jump through hoops to get all the necessary permits for the event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>ENG-20260528-085</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>go down the drain</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>/ɡoʊ daʊn ðə dreɪn/</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>수포로 돌아가다, 헛수고가 되다</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>All the efforts to save money could go down the drain if inflation isn't controlled.</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>If the project fails, all our hard work will go down the drain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>ENG-20260528-086</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>pull the plug</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>/pʊl ðə plʌɡ/</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>(계획, 사업 등을) 중단시키다</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>The Trump administration threatened to pull the plug on flight processing in certain cities.</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>The investors decided to pull the plug on the struggling startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>ENG-20260528-087</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>be in full swing</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>/bi ɪn fʊl swɪŋ/</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>한창 진행 중이다, 무르익다</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Joey's telethon was supposed to be in full swing by this point, but he was answering phones.</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>The festival was in full swing by early afternoon, with music and food stalls everywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>ENG-20260528-088</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>take the bull by the horns</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>/teɪk ðə bʊl baɪ ðə hɔːrnz/</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>어려운 상황에 정면으로 맞서다</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>The new leader needs to take the bull by the horns and address the economic crisis directly.</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Instead of avoiding the problem, she decided to take the bull by the horns and confront her colleague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>ENG-20260528-089</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>take pledges</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>/teɪk plɛdʒɪz/</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>(기부금 등) 약속을 받다</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>No you answer it and take pledges.</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Volunteers worked tirelessly to take pledges from callers during the charity telethon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>ENG-20260528-090</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>go like this</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>/ɡoʊ laɪk ðɪs/</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>(이렇게) 행동/표현하다 (몸짓 등으로 무언가를 보여줄 때)</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>I mean if this guy was me and it was me who had learned that it was me who was the best you'd ever had, I'd be going like this.</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>To explain the new dance move, she said, 'You go like this,' and demonstrated the steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>ENG-20260528-091</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>keep quiet</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>/kiːp ˈkwaɪət/</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>조용히 하다, 침묵을 지키다</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>He motions for them to keep quiet, including Chandler who is still holding the lamp Ross handed him</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>The librarian asked the students to keep quiet in the study area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>ENG-20260528-092</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>in love</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>/ɪn lʌv/</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>사랑에 빠진 (상태)</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>We're gonna be like-like-like two idiots in love!</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>They've been inseparable since college, clearly still deeply in love.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>ENG-20260528-093</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>be humiliating for someone</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>/bi hjuːˈmɪlieɪtɪŋ fɔːr ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>~에게 굴욕적이다</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Well, you have to understand how humiliating it was for me up on that altar in front of my entire family, all my friends.</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Failing the exam in front of everyone was truly humiliating for him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>ENG-20260528-094</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>be in the same room as someone</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>/bi ɪn ðə seɪm ruːm æz ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>~와 같은 공간/방에 있다 (특히 불편하거나 꺼려지는 상황에서)</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>I mean, I can't-I can't be in the same room as her!</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>After their argument, they found it difficult to be in the same room as each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>ENG-20260528-095</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>nothing between two people</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>/ˈnʌθɪŋ bɪˈtwiːn tuː ˈpiːpl/</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>~사이에 아무 관계도 없다 (특히 연인 관계가 아니라는 뜻)</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Emily, there is nothing between Rachel and me. Okay? I love you.</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Despite the rumors, there's absolutely nothing between Mark and Lisa; they're just good friends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>ENG-20260528-096</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>extend the ceasefire</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>/ɪkˈstɛnd ðə ˈsiːsfaɪər/</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>휴전을 연장하다</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Oil prices pulled back Thursday, erasing earlier gains, on a report that U.S. and Iranian negotiators reached an agreement to extend the ceasefire.</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>Both sides agreed to extend the ceasefire for another 72 hours to allow aid deliveries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>ENG-20260528-097</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>post a video</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>/poʊst ə ˈvɪdioʊ/</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>동영상을 게시하다/올리다</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Citadel CEO Ken Griffin became the face of the tax after New York City Mayor Zohran Mamdani posted a video in front of Griffin's penthouse apartment.</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Many influencers post a video daily to engage with their audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>ENG-20260528-098</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>be expected to do something</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>/bi ɪkˈspɛktɪd tuː duː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>~할 것으로 예상되다</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>The PCE price index for April was expected to show an annual inflation rate of 3.8% for all items and 3.3% for core.</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>The new policy is expected to boost economic growth.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I657"/>
+  <dimension ref="A1:I752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31295,6 +31295,4471 @@
         </is>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>ENG-20260529-001</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>lay out</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>/leɪ aʊt/</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>계획, 요구사항, 사실 등을 명확하게 제시하거나 설명하다</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Trump's Truth Social statement left unclear which of his conditions are already part of a deal that negotiators are working on to pause the U.S.-Iran war. Trump lays out Iran deal demands, says he's about to make 'final determination'.</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>The CEO will lay out the company's new strategy for the next fiscal year at the upcoming board meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>ENG-20260529-002</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>work on</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>/wɜːrk ɒn/</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>무언가를 개선하거나 완성하기 위해 노력하다, 연구하다</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Trump's Truth Social statement left unclear which of his conditions are already part of a deal that negotiators are working on to pause the U.S.-Iran war.</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>We are currently working on a new software update to fix the bugs reported by users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>ENG-20260529-003</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>diverge from</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>/daɪˈvɜːrdʒ frɒm/</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>기존의 계획, 의견, 경로 등에서 벗어나다, 달라지다</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>SpaceX skeptics have added reason for concern after Musk comments diverge from IPO filing.</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>The committee's final recommendations diverged significantly from the initial proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>ENG-20260529-004</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>shut someone out of</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>/ʃʌt ˌsʌmwʌn aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>어떤 기회, 시장, 장소 등에서 누군가를 배제하거나 참여를 막다</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz may be shut out of U.S. market under bill aimed at Chinese automaker ownership.</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>They tried to shut us out of the negotiations, but we found a way to participate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>ENG-20260529-005</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>aim at</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>/eɪm æt/</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>특정 목표나 대상을 향하다, 겨냥하다</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz may be shut out of U.S. market under bill aimed at Chinese automaker ownership.</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>The new marketing campaign is primarily aimed at younger consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>ENG-20260529-006</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>raid savings</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>/reɪd ˈseɪvɪŋz/</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>비상금이나 저축한 돈을 꺼내 쓰다</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Higher energy costs can force consumers to raid their savings and lean more into debt to cover expenses.</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Many families had to raid their savings to cover unexpected medical bills during the pandemic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>ENG-20260529-007</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>lean into debt</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>/liːn ˈɪntuː dɛt/</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>빚을 더 많이 지게 되다, 빚에 의존하게 되다</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Higher energy costs can force consumers to raid their savings and lean more into debt to cover expenses.</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Without a steady income, many small businesses were forced to lean into debt to keep their operations going.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>ENG-20260529-008</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>suffer a setback</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>/ˈsʌfər ə ˈsɛtbæk/</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>차질을 겪다, 좌절을 경험하다</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Jeff Bezos' rocket maker suffered a setback on Thursday as its New Glenn rocket went up in flames.</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>The project suffered a major setback when the lead engineer resigned unexpectedly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>ENG-20260529-009</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>go up in flames</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ʌp ɪn fleɪmz/</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>불에 타다; 계획이나 노력이 완전히 실패하다, 수포로 돌아가다</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Jeff Bezos' rocket maker suffered a setback on Thursday as its New Glenn rocket went up in flames.</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>All their hard work went up in flames when the server crashed and they lost all the data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>ENG-20260529-010</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>return to the public market</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>/rɪˈtɜːrn tuː ðə ˈpʌblɪk ˈmɑːrkɪt/</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>상장 폐지 후 다시 주식시장에 상장하다</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Dell reported its fastest pace of revenue growth since returning to the public market in 2018.</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>After several years of private ownership, the tech giant plans to return to the public market next year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>ENG-20260529-011</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>face criticism</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>/feɪs ˈkrɪtɪˌsɪzəm/</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>비난을 받다, 비판에 직면하다</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>The DOJ has faced strong criticism for the creation of a $1.8 Anti-Weaponization Fund.</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>The government is currently facing strong criticism over its handling of the economic crisis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>ENG-20260529-012</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>launch a review</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>/lɔːntʃ ə rɪˈvjuː/</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>조사나 검토를 시작하다</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Disney said it filed renewals for eight broadcast station licenses 'under protest,' after the FCC launched an early review years ahead of schedule.</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>The university decided to launch an independent review into the allegations of academic misconduct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>ENG-20260529-013</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>ahead of schedule</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>/əˈhɛd ɒv ˈʃɛdʒuːl/</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>예정보다 일찍, 기한보다 빨리</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Disney said it filed renewals for eight broadcast station licenses 'under protest,' after the FCC launched an early review years ahead of schedule.</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>The construction project was completed two weeks ahead of schedule, much to everyone's relief.</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>ENG-20260529-014</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>face a hurdle</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>/feɪs ə ˈhɜːrdl/</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>난관에 부딪히다, 장애물에 직면하다</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Roth IRA owners may face a hurdle to get the money.</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Startups often face many hurdles in their early stages, from funding to market acceptance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>ENG-20260529-015</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>be on track to</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>/bi ɒn træk tuː/</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>순조롭게 진행되어 ~할 것으로 예상되다, ~를 달성할 궤도에 오르다</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Royal Mail says its service is improving and that it is on track to hit the regulator Ofcom's reduced targets.</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>The company is on track to exceed its sales targets for the third quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>ENG-20260529-016</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>ease pressure</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>/iːz ˈprɛʃər/</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>압력, 부담, 긴장 등을 완화시키다</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Tom Kerridge, Yotam Ottolenghi, Ravneet Gill and Simon Rogan told BBC Newsnight VAT should be halved to ease mounting pressure on the hospitality industry.</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>The government implemented new policies to ease pressure on small businesses struggling with rising costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>ENG-20260529-017</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>move to make an exception</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>/muːv tuː meɪk æn ɪkˈsɛpʃən/</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>예외를 두는 조치를 취하다, 예외를 만들려 하다</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Federal law bars printing images of living people on US currency, but Trump allies in Congress are moving to make an exception.</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>The council is considering moving to make an exception for historical buildings in the new zoning laws.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>ENG-20260529-018</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>build on</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>/bɪld ɒn/</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>기존의 성공, 경험, 기반 등을 바탕으로 발전시키다</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>BMW is introducing humanoid robots to a car plant in Europe, building on similar projects in the US.</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>We plan to build on the success of our previous product launch with an even stronger marketing campaign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>ENG-20260529-019</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>retaliate against</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>/rɪˈtæliˌeɪt əˈɡɛnst/</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>~에 대해 보복하거나 앙갚음하다</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Sales of the fruity liqueur popular with Canadian students had plummetted north of the border as provinces retaliated against Trump tariffs.</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>The country vowed to retaliate against any cyberattacks on its critical infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>ENG-20260529-020</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>explode into a ball of flame</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>/ɪkˈsploʊd ˈɪntuː ə bɔːl ɒv fleɪm/</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>커다란 불꽃 덩어리로 폭발하다</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Blue Origin rocket explodes into huge ball of flame on Florida launch pad.</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>The old fireworks factory accidentally exploded into a ball of flame, causing widespread alarm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>ENG-20260529-021</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>fall in love with</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>/fɔːl ɪn lʌv wɪð/</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>~와 사랑에 빠지다</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>But I have to warn you; this may make me a better person and that is not the man you feel in love with!</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>They met at a friend's party and quickly fell in love with each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>ENG-20260529-022</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>lay out the ground rules</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>/leɪ aʊt ðə ɡraʊnd ruːlz/</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>기본 규칙이나 원칙을 명확히 설명하다</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Joey and Ross are laying out the ground rules for the maid of honor auditions to Rachel and Phoebe.</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Before we start the project, let's lay out the ground rules for communication and collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>ENG-20260529-023</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>score on a scale of</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>/skɔːr ɒn ə skeɪl ɒv/</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>~의 척도로 점수를 매기다/평가하다</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>We’re gonna give you hypothetical maid of honor situations and you will be scored on a scale of 1 to 10.</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Participants were asked to score the meal on a scale of 1 to 5, with 5 being excellent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>ENG-20260529-024</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>be up first</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>/bi ʌp fɜːrst/</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>첫 번째 순서이다, 먼저 시작하다</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Okay, Rachel you’re up first.</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Who's up first for the presentation? I think it's Sarah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>ENG-20260529-025</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>run out on</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>/rʌn aʊt ɒn/</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>무책임하게 ~를 버리고 떠나다, ~를 외면하다</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>And also, I ran out on a wedding. You don’t get to keep the gifts.</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>She felt completely abandoned after her business partner ran out on their joint venture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>ENG-20260529-026</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>draw on experience</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>/drɔː ɒn ɪkˈspɪriəns/</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>경험을 활용하다, 경험에서 얻은 지식을 이용하다</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Very good! Drawing on your own experience, I like that!</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>The seasoned negotiator had to draw on years of experience to close the difficult deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>ENG-20260529-027</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>kiss ass</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>/kɪs æs/</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>아첨하다, 아부하다 (매우 비격식적이고 다소 부정적인 의미)</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Ugh, what a kiss ass.</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>He's always complimenting the boss; everyone thinks he's just trying to kiss ass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>ENG-20260529-028</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>make a scene</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>/meɪk ə siːn/</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>공공장소에서 소란을 피우다, 시선을 끄는 행동을 하다</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Wait a minute! She just made a scene in the middle of the ceremony!</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Please don't make a scene in the restaurant; let's discuss this calmly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>ENG-20260529-029</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>give a speech</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>/ɡɪv ə spiːtʃ/</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>연설을 하다</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>It is time for you to give your maid of honor speech.</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>The CEO will give a speech at the annual company dinner next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>ENG-20260529-030</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>never mind</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>/ˈnɛvər maɪnd/</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>신경 쓰지 마세요, 잊어버리세요, 상관 마세요</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Okay!! Forget that! That sucks!! Okay, never mind! Forget it!</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Oh, you found it? Never mind, I already bought a new one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>ENG-20260529-031</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>raise one's glass</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>/reɪz wʌnz ɡlɑːs/</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>건배를 제의하며 잔을 들어 올리다</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>So I would like to raise my glass to Monica and Chandler and the beautiful adventure they are about to embark upon together.</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>At the reception, the best man raised his glass and offered a heartfelt toast to the happy couple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>ENG-20260529-032</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>embark on/upon</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>/ɪmˈbɑːrk ɒn/ /ɪmˈbɑːrk əˈpɒn/</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>새로운 일, 여행, 모험 등을 시작하다</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>So I would like to raise my glass to Monica and Chandler and the beautiful adventure they are about to embark upon together.</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>After graduation, she decided to embark on a round-the-world trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>ENG-20260529-033</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>be back in the game</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>/bi bæk ɪn ðə ɡeɪm/</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>활동이나 경쟁에 다시 참여하다, 회복하여 다시 기회가 생기다</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Joey: And she’s back in the game.</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>After recovering from his injury, the athlete is eager to be back in the game next season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>ENG-20260529-034</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>owe an apology</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>/oʊ æn əˈpɒlədʒi/</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>사과해야 할 의무가 있다, 사과할 일이 있다</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Ah, uh, I owe you a long overdue apology.</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>I realized I was wrong, and I definitely owe him an apology for my behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>ENG-20260529-035</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>demand a recount</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>/dɪˈmænd ə ˈriːkaʊnt/</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>재검표를 요구하다</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Well then I demand a recount!</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>The candidate, losing by a very narrow margin, immediately demanded a recount of the votes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>ENG-20260529-036</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>flip a coin</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>/flɪp ə kɔɪn/</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>동전을 던져 결정하다, 운에 맡기다</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>We’re gonna flip a coin! All right?!</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Since we can't agree, let's just flip a coin to decide who goes first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>ENG-20260529-037</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>grunt in disgust</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>/ɡrʌnt ɪn dɪsˈɡʌst/</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>혐오감이나 불쾌감을 표현하며 끙 소리를 내다</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Looks at the coin and grunts in disgust.</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>He grunted in disgust when he saw the mess his roommates had left in the kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>ENG-20260529-038</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>throw a shower</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>/θroʊ ə ˈʃaʊər/</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>아기나 신부를 위한 파티(베이비샤워/브라이덜샤워)를 열어주다</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>I hope Monica forgives you after you throw her, her vegetarian, voodoo, goddess circley shower!</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Her friends are planning to throw her a surprise baby shower next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>ENG-20260529-039</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>be in the red/black</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>/bi ɪn ðə rɛd/ /bi ɪn ðə blæk/</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>적자이다/흑자이다 (재정 상태를 나타냄)</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>After a difficult quarter, the company is finally in the black, showing a modest profit.</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Many small businesses were in the red for months during the economic downturn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>ENG-20260529-040</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>sign off on</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>/saɪn ɒf ɒn/</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>공식적으로 승인하다, 서명하여 허가하다</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>The manager needs to sign off on all major expenditures before they are processed.</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Before we proceed, we need the client to sign off on the design proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>ENG-20260529-041</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>get buy-in</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈbaɪ ɪn/</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>지지나 동의를 얻다 (특히 중요한 결정이나 프로젝트에 대해)</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>It's crucial to get buy-in from all stakeholders before launching such a large-scale initiative.</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>We need to present a strong case to the team if we want to get their buy-in for this new strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>ENG-20260529-042</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>table a motion/discussion</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>/ˈteɪbl ə ˈmoʊʃən/ /dəˈskʌʃən/</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>논의를 나중으로 미루다 (영국 영어에서는 제안하다는 의미도 있음, 미국 영어에서는 보통 연기하다)</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Due to time constraints, the committee decided to table the discussion until the next meeting.</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>I suggest we table this motion and revisit it after we gather more data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>ENG-20260529-043</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>put something on the back burner</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>/pʊt ˌsʌmθɪŋ ɒn ðə bæk ˈbɜːrnər/</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>덜 중요하거나 시급하지 않은 일로 미루다, 보류하다</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>We had to put the new product development on the back burner to focus on our core business.</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>My personal projects have been put on the back burner while I deal with urgent work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>ENG-20260529-044</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>go public</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ˈpʌblɪk/</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>회사 주식을 공개적으로 발행하여 상장하다</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Many startups dream of the day they can go public and offer shares to the public.</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>After years of growth, the successful tech company decided to go public last month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>ENG-20260529-045</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>crunch numbers</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>/krʌntʃ ˈnʌmbərz/</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>복잡한 계산을 하다, 데이터를 분석하다</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>The finance department is busy crunching numbers to prepare the annual budget report.</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>She spends hours every day crunching numbers to identify market trends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>ENG-20260529-046</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>trim the fat</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>/trɪm ðə fæt/</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>불필요한 비용이나 부분을 줄이다, 낭비를 없애다</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>To improve profitability, the company needs to trim the fat from its operational budget.</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>We're trying to trim the fat from our monthly expenses so we can save more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>ENG-20260529-047</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>be in a pickle</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>/bi ɪn ə ˈpɪkl/</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>곤란한 상황에 처하다, 궁지에 몰리다</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>We're really in a pickle now that we missed the deadline and haven't finished the report.</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>If we don't find a solution soon, we're going to be in a real pickle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>ENG-20260529-048</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>pass with flying colors</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>/pæs wɪð ˈflaɪɪŋ ˈkʌlərz/</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>시험이나 과제를 아주 훌륭하게 통과하다, 성공적으로 해내다</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>She studied diligently for weeks and passed her final exams with flying colors.</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Despite the difficulty, he passed the driving test with flying colors on his first attempt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>ENG-20260529-049</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>pull oneself together</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>/pʊl wʌnˈsɛlf təˈɡɛðər/</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>감정을 추스르다, 마음을 가다듬다</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>After a brief moment of panic, she managed to pull herself together and solve the problem calmly.</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Come on, pull yourself together! We need to focus on finding a solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>ENG-20260529-050</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>get a kick out of</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə kɪk aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>~로부터 큰 즐거움이나 흥분을 느끼다</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>He really gets a kick out of surprising people with unexpected gifts.</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>I always get a kick out of watching old comedy shows like Friends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>ENG-20260529-051</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>be glued to</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>/bi ɡluːd tuː/</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>어떤 것에 시선이나 주의를 고정시키다, 몰두하다</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>Kids nowadays are constantly glued to their screens, whether it's a phone or a tablet.</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>I was glued to the TV, watching the breaking news report about the rocket launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>ENG-20260529-052</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>hang in there</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>/hæŋ ɪn ðɛər/</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>어려운 상황에서도 포기하지 않고 버티다, 힘내다</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>I know things are tough right now, but just hang in there; it'll get better.</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Hang in there, you're almost done with this challenging project!</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>ENG-20260529-053</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>let someone off the hook</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>/lɛt ˌsʌmwʌn ɒf ðə hʊk/</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>누군가를 어려운 상황이나 처벌에서 벗어나게 해주다</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Even though he broke the rules, the teacher decided to let him off the hook this time.</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>I'll let you off the hook for washing dishes tonight since you've had a long day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>ENG-20260529-054</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>ring a bell</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>/rɪŋ ə bɛl/</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>익숙하거나 들어본 적이 있는 것 같다, 기억나게 하다</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>His name rings a bell, but I can't quite remember where I know him from.</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>That song title sounds familiar; it definitely rings a bell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>ENG-20260529-055</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>see eye to eye</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>/siː aɪ tuː aɪ/</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>의견이 일치하다, 동의하다</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>My brother and I rarely see eye to eye on political matters, but we respect each other's opinions.</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>It's difficult to work with him because we just don't see eye to eye on anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>ENG-20260529-056</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>brace oneself</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>/breɪs wʌnˈsɛlf/</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>힘든 일이나 충격에 대비하다, 마음의 준비를 하다</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>Everyone had to brace themselves for the severe storm expected to hit the coast.</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>We need to brace ourselves for a challenging quarter with potentially lower sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>ENG-20260529-057</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>pat oneself on the back</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>/pæt wʌnˈsɛlf ɒn ðə bæk/</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>자신을 칭찬하다, 스스로에게 잘했다고 하다</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>After successfully completing the difficult project, the team could finally pat themselves on the back.</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>You did a fantastic job on that presentation; you should definitely pat yourself on the back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>ENG-20260529-058</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>knock it out of the park</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>/nɒk ɪt aʊt ɒv ðə pɑːrk/</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>기대 이상으로 아주 잘 해내다, 대성공을 거두다 (야구 용어에서 유래)</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Her performance in the play was truly exceptional; she really knocked it out of the park.</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>I'm confident the sales team will knock it out of the park with this new product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>ENG-20260529-059</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>get on board</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>/ɡɛt ɒn bɔːrd/</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>어떤 계획, 아이디어 등에 동의하거나 참여하다</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>It was difficult to get all the team members on board with the radical new proposal.</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>We need everyone to get on board with this new initiative if we want it to succeed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>ENG-20260529-060</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>put one's cards on the table</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>/pʊt wʌnz kɑːrdz ɒn ðə ˈteɪbl/</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>자신의 계획이나 의도를 솔직하게 밝히다</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>During the negotiation, both sides agreed to put their cards on the table to find a fair solution.</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Let's put our cards on the table and discuss our expectations openly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>ENG-20260529-061</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>nip something in the bud</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>/nɪp ˌsʌmθɪŋ ɪn ðə bʌd/</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>문제나 나쁜 상황이 더 커지기 전에 미리 막다</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>It's important to nip bad habits in the bud before they become ingrained.</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>The manager intervened quickly to nip the disagreement in the bud before it escalated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>ENG-20260529-062</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>pay through the nose</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>/peɪ θruː ðə noʊz/</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>터무니없이 비싼 값을 지불하다, 바가지를 쓰다</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>I hate having to pay through the nose for basic necessities like groceries these days.</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>We had to pay through the nose for tickets to the concert because we bought them last minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>ENG-20260529-063</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>word of mouth</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>/wɜːrd ɒv maʊθ/</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>입소문, 구전</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Most of our new customers come to us through word of mouth referrals.</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>The restaurant became popular largely through positive word of mouth from local food bloggers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>ENG-20260529-064</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>keep one's options open</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>/kiːp wʌnz ˈɒpʃənz ˈoʊpən/</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>결정을 내리지 않고 여러 가능성을 열어두다</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>It's wise to keep your options open when you're looking for a new job.</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>I'm applying to several universities to keep my options open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>ENG-20260529-065</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>be up to scratch</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>/bi ʌp tuː skrætʃ/</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>기대에 부응하다, 필요한 수준에 미치다 (주로 부정문에 사용)</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>His recent work hasn't been up to scratch, so he needs to improve.</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>The quality of the product wasn't up to scratch, so we returned it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>ENG-20260529-066</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>blow something out of proportion</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>/bloʊ ˌsʌmθɪŋ aʊt ɒv prəˈpɔːrʃən/</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>사소한 일을 과장하다, 침소봉대하다</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>It was just a minor disagreement, but she blew it out of proportion and made a huge fuss.</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Don't blow this small mistake out of proportion; it's easily fixable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>ENG-20260529-067</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>butter someone up</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>/ˈbʌtər ˌsʌmwʌn ʌp/</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>누군가에게 아첨하다, 환심을 사려고 노력하다</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>He tried to butter up his boss before asking for a raise.</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>She's always buttering up her professors to get better grades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>ENG-20260529-068</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>in the blink of an eye</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>/ɪn ðə blɪŋk ɒv æn aɪ/</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>눈 깜짝할 사이에, 순식간에</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>The entire building was engulfed in flames in the blink of an eye.</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>The car disappeared around the corner in the blink of an eye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>ENG-20260529-069</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>jump to conclusions</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>/dʒʌmp tuː kənˈkluːʒənz/</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>성급하게 결론을 내리다, 속단하다</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>Don't jump to conclusions; let's wait for all the facts before making a judgment.</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>I know you're upset, but try not to jump to conclusions about what happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>ENG-20260529-070</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>live and learn</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>/lɪv ænd lɜːrn/</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>실수를 통해 배우다, 경험을 통해 성장하다</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>I made a big mistake, but I guess you live and learn.</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>I accidentally booked flights for the wrong date, but hey, live and learn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>ENG-20260529-071</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>pull strings</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>/pʊl strɪŋz/</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>뒷배경을 이용하다, 인맥을 동원하다 (주로 부정적 의미)</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>He managed to get that exclusive invitation by pulling some strings with influential people.</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>She had to pull some strings to get her son into that prestigious school.</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>ENG-20260529-072</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>rags to riches</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>/ræɡz tuː ˈrɪtʃɪz/</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>극빈층에서 부유층으로 성공하다, 자수성가하다</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>His rags to riches story is an inspiration to many aspiring entrepreneurs.</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Many successful entrepreneurs have a rags to riches story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>ENG-20260529-073</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>red tape</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>/rɛd teɪp/</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>불필요하게 복잡하고 관료적인 절차, 관료주의</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>It took months to get the permits due to excessive red tape and bureaucratic hurdles.</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Dealing with all the government red tape for a small business loan was frustrating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>ENG-20260529-074</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>up to par</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>/ʌp tuː pɑːr/</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>기대하는 수준에 미치다, 보통 수준에 달하다</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>His performance hasn't been up to par recently, and he needs to improve.</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>The new restaurant's service wasn't quite up to par yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>ENG-20260529-075</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>win-win situation</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>/wɪn wɪn ˌsɪtʃuˈeɪʃən/</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>모두에게 이득이 되는 상황, 상생 관계</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>The new partnership is a win-win situation for both companies involved.</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Working from home is a win-win situation for both employees and employers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>ENG-20260529-076</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>call it a night</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>/kɔːl ɪt ə naɪt/</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>그날 밤의 활동을 끝내다, 귀가하다</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>It's late, so let's call it a night and pick this up tomorrow.</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>After a long evening out, we decided to call it a night.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>ENG-20260529-077</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>come rain or shine</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>/kʌm reɪn ɔːr ʃaɪn/</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>날씨가 어떻든, 어떤 어려움이 있든 상관없이, 무슨 일이 있어도</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>I'll be there for you, come rain or shine, no matter what happens.</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>The outdoor festival will proceed come rain or shine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>ENG-20260529-078</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>down to earth</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>/daʊn tuː ɜːrθ/</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>현실적인, 실용적인, 소탈한</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>Despite her fame, she's very down to earth and easy to talk to.</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>I appreciate his down to earth approach to problem-solving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>ENG-20260529-079</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>easy come, easy go</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>/ˈiːzi kʌm ˈiːzi ɡoʊ/</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>쉽게 얻은 것은 쉽게 사라진다</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>He won a large sum of money but spent it all quickly. Easy come, easy go.</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>I lost my lottery winnings quickly; easy come, easy go, I suppose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>ENG-20260529-080</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>get wind of</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>/ɡɛt wɪnd ɒv/</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>소문을 듣다, ~에 대해 알게 되다</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>The competitors got wind of our new product launch plans.</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>The press got wind of the scandal before the official announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>ENG-20260529-081</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>in a nutshell</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>/ɪn ə ˈnʌtʃɛl/</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>아주 간단히 말해서, 요약하자면</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>In a nutshell, the company is facing financial difficulties due to mismanagement.</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>In a nutshell, we need to increase sales and reduce costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>ENG-20260529-082</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>it's not rocket science</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>/ɪts nɒt ˈrɒkɪt ˈsaɪəns/</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>그리 어려운 일이 아니다 (로켓 과학처럼 복잡하지 않다는 뜻)</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Learning to use this new software is not rocket science; anyone can do it.</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Figuring out how to use the coffee machine is not rocket science.</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>ENG-20260529-083</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>know something like the back of one's hand</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>/noʊ ˌsʌmθɪŋ laɪk ðə bæk ɒv wʌnz hænd/</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>무언가를 아주 잘 알다, 꿰뚫어보다</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>She's lived in this city her whole life, so she knows it like the back of her hand.</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>I've worked in this department for years; I know this system like the back of my hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>ENG-20260529-084</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>on the ball</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>/ɒn ðə bɔːl/</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>유능한, 기민한, 상황을 잘 파악하고 있는</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>You need to be on the ball to succeed in a fast-paced environment like this.</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Our new project manager is really on the ball; nothing gets past her.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>ENG-20260529-085</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>the big picture</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>/ðə bɪɡ ˈpɪktʃər/</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>전체적인 상황, 전체적인 그림</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>Don't get too caught up in the details; try to look at the big picture.</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>He's good at seeing the big picture and understanding how all the parts fit together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>ENG-20260529-086</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>work one's fingers to the bone</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>/wɜːrk wʌnz ˈfɪŋɡərz tuː ðə boʊn/</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>뼈 빠지게 일하다, 매우 열심히 일하다</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>She worked her fingers to the bone to provide for her family.</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>Many entrepreneurs work their fingers to the bone to get their businesses off the ground.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>ENG-20260529-087</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>make a determination</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>/meɪk ə dɪˌtɜːrmɪˈneɪʃən/</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>결정을 내리다, 확정하다</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>Trump lays out Iran deal demands, says he's about to make 'final determination'</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>The committee will make a final determination on the proposal next week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>ENG-20260529-088</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>cover expenses</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>/ˈkʌvər ɪkˈspɛnsɪz/</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>비용을 충당하다</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Higher energy costs can force consumers to raid their savings and lean more into debt to cover expenses.</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Many students work part-time jobs to cover their living expenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>ENG-20260529-089</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>pace of growth</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>/peɪs əv ɡroʊθ/</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>성장 속도</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Dell reported its fastest pace of revenue growth since returning to the public market in 2018, with AI server revenue soaring 757% over last year.</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>The company needs to maintain a high pace of growth to attract investors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>ENG-20260529-090</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>file for renewal</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>/faɪl fɔːr rɪˈnuːəl/</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>갱신 신청을 하다</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>Disney's ABC files early broadcast licenses renewal. FCC Chair vows to 'follow the facts'</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>You must file for renewal of your passport before it expires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>ENG-20260529-091</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>follow the facts</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>/ˈfɑːloʊ ðə fækts/</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>사실에 입각하다, 사실을 따르다</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>Disney's ABC files early broadcast licenses renewal. FCC Chair vows to 'follow the facts'</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>It's crucial for journalists to follow the facts and report objectively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>ENG-20260529-092</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>file under protest</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>/faɪl ˈʌndər ˈproʊtɛst/</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>이의를 제기하며 제출하다</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>Disney said it filed renewals for eight broadcast station licenses 'under protest,' after the FCC launched an early review years ahead of schedule.</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>The company decided to file the tax return under protest, reserving its right to challenge the assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>ENG-20260529-093</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>repay debt</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>/riːˈpeɪ dɛt/</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>빚을 갚다</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>Starting July 1, millions of federal student loan holders will have two new ways to repay their debt.</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>It's wise to create a budget to help you repay your debt more efficiently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>ENG-20260529-094</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>hit targets</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>/hɪt ˈtɑːrɡɪts/</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>목표를 달성하다</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>Royal Mail says its service is improving and that it is on track to hit the regulator Ofcom's reduced targets</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>The sales team worked hard to hit their quarterly targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>ENG-20260529-095</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>mounting pressure</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>/ˈmaʊntɪŋ ˈprɛʃər/</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>가중되는 압력/부담</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>Tom Kerridge, Yotam Ottolenghi, Ravneet Gill and Simon Rogan told BBC Newsnight VAT should be halved to ease mounting pressure on the hospitality industry.</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>She felt mounting pressure to finish the project on time.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I752"/>
+  <dimension ref="A1:I832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35760,6 +35760,3766 @@
         </is>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>ENG-20260529-096</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>shut someone/something out</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>/ʃʌt aʊt/</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>~을 배제하다, 시장 진입을 막다</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz may be shut out of U.S. market under bill</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>The new regulations could shut out smaller companies from competing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>ENG-20260529-097</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>apply to</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>/əˈplaɪ tuː/</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>(규칙, 법 등이) ~에 적용되다, 해당하다</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>exemptions in the legislation would not apply.</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>The new tax rules will apply to all citizens, regardless of income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>ENG-20260529-098</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>lean into</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>/liːn ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>~에 기대다, (어려움에) 적극적으로 맞서다</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>force consumers to raid their savings and lean more into debt</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Instead of avoiding the challenge, you should lean into it and learn from the experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>ENG-20260529-099</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>pose a risk</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>/poʊz ə rɪsk/</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>위험을 제기하다</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>posing a risk the market hasn't priced in.</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Driving without a seatbelt can pose a serious risk to your safety.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>ENG-20260529-100</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>claim a benefit</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>/kleɪm ə ˈbɛnɪfɪt/</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>혜택을 신청하다/받다</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>Roth IRA owners may need a second retirement account to claim the new Saver's Match</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>You might be eligible to claim unemployment benefits if you lose your job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>ENG-20260529-101</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>deliver on time</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>/dɪˈlɪvər ɒn taɪm/</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>정시에 배달하다/이행하다</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>Only three-quarters of first class mail delivered on time</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>It's crucial for us to deliver the project on time and within budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>ENG-20260529-102</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>be set to</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>/biː sɛt tuː/</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>~할 예정이다, ~할 준비가 되어 있다</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>the number of 16 to 24-year-olds out of work, education or training is set to rise</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>The new product is set to launch next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>ENG-20260529-103</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>struggle to do something</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>/ˈstrʌɡl̩ tuː duː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>~하는 데 어려움을 겪다, 고군분투하다</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>young people who are struggling to find work</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>He's struggling to learn a new language while working full-time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>ENG-20260529-104</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>bar someone from doing something</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>/bɑːr ˈsʌmwʌn frɒm ˈduːɪŋ ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>누군가가 ~하는 것을 금지하다</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>Federal law bars printing images of living people on US currency</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>The club decided to bar him from entering after his previous behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>ENG-20260529-105</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>make an exception</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>/meɪk ən ɪkˈsɛpʃn̩/</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>예외를 두다/인정하다</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>Trump allies in Congress are moving to make an exception.</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>We usually don't allow pets, but we can make an exception for service animals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>ENG-20260529-106</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>explode into flames</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>/ɪkˈsploʊd ˈɪntuː fleɪmz/</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>폭발하며 불길에 휩싸이다</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>Blue Origin rocket explodes into huge ball of flame</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>The old factory building suddenly exploded into flames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>ENG-20260529-107</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>have a rough day</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>/hæv ə rʌf deɪ/</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>힘든 하루를 보내다</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>Jeff Bezos, who founded Blue Origin, said it was a 'very rough day'.</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>I had a really rough day at work; everything seemed to go wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>ENG-20260529-108</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>get together</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>/ɡɛt təˈɡɛðər/</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>만나다, 함께하다; (연인 관계가) 시작되다</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>I was always rooting for you two kids to get together.</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Let's get together for coffee sometime next week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>ENG-20260529-109</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>be about the money</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>/biː əˈbaʊt ðə ˈmʌni/</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>돈이 문제다, 돈 때문에 하는 것이다</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>this isn't about the money.</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>For some, success is about passion, but for others, it's just about the money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>ENG-20260529-110</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>on top of</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>/ɒn tɒp ɒv/</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>~뿐만 아니라, ~위에 덧붙여</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>And that's on top of the yearly bonus structure you mentioned earlier?</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>On top of working full-time, she's also studying for her master's degree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>ENG-20260529-111</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>have the wrong guy</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>/hæv ðə rɒŋ ɡaɪ/</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>사람을 잘못 찾았다, 오해하다</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>I'm telling you, you've got the wrong guy!</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>If you think I'm the one who stole your wallet, you've got the wrong guy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>ENG-20260529-112</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>slam down the phone</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>/slæm daʊn ðə foʊn/</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>전화를 쾅 내려놓다</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>(slams the phone down)</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>She was so angry that she slammed down the phone after the argument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>ENG-20260529-113</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>show someone around</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>/ʃoʊ ˈsʌmwʌn əˈraʊnd/</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>~에게 구경시켜주다, 안내하다</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>Chandler's new window office, he is showing Phoebe around.</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>When you visit, I'll show you around the city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>ENG-20260529-114</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>check out</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>/tʃɛk aʊt/</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>~을 확인하다, 조사하다; (무언가를) 보다/경험하다</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>Check this out, look at this.</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>You should check out that new cafe downtown; it's really good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>ENG-20260529-115</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>come in</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>/kʌm ɪn/</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>(방 안으로) 들어오다</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>Helen, could you come in here for a moment?</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>Please come in and make yourself comfortable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>ENG-20260529-116</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>that'll be all</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>/ðætɪl biː ɔːl/</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>그게 다예요, 더 필요 없어요</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>Thank you Helen, that'll be all.</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>I'd like a coffee and a croissant, please. That'll be all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>ENG-20260529-117</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>bail on someone/something</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>/beɪl ɒn/</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>(약속을) 바람맞히다, ~을 저버리다</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>Wendy bailed. I have no waitress.</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>He bailed on our dinner plans at the last minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>ENG-20260529-118</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>make plans</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>/meɪk plænz/</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>계획을 세우다</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>I've made plans to walk around.</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>We should make plans to go hiking this summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>ENG-20260529-119</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>be there for someone</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>/biː ðɛr fɔːr ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>누군가를 위해 곁에 있어주다, 돕다</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>when you ran out of your wedding, I was there for you.</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>She was always there for me during my difficult times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>ENG-20260529-120</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>put a roof over someone's head</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>/pʊt ə ruːf ˈoʊvər ˈsʌmwʌnz hɛd/</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>누군가에게 거처를 마련해주다, 재워주다</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>I put a roof over your head</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>My parents always made sure we had a roof over our heads, no matter what.</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>ENG-20260529-121</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>not buy it</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>/nɒt baɪ ɪt/</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>믿지 않다, 납득하지 않다</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>Rachel isn't buying it</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>He tried to tell me he was sick, but I didn't buy it; he looked perfectly fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>ENG-20260529-122</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>drag someone into a mess</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>/dræɡ ˈsʌmwʌn ˈɪntuː ə mɛs/</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>누군가를 곤란한 상황에 끌어들이다</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>(Phoebe stops her and drags her into the kitchen.)</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>I don't want to drag you into this mess, so I'll handle it myself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>ENG-20260529-123</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>be with someone</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>/biː wɪð ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>(말하는 것을) 이해하다, 동의하다</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>OK, OK. I'm with you, Cheech.</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>I think I'm with you now; that explanation makes more sense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>ENG-20260529-124</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>lose meaning</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>/luːz ˈmiːnɪŋ/</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>의미를 잃다</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>The word has lost all meaning.</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>After hearing it so many times, the phrase started to lose meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>ENG-20260529-125</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>wave off</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>/weɪv ɒf/</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>(생각, 제안 등을) 일축하다, (위험을) 물리치다</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>Monica waves it off as though she doesn't believe it.</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>He tried to offer an excuse, but I just waved it off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>ENG-20260529-126</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>spoil an appetite</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>/spɔɪl ən ˈæpɪtaɪt/</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>식욕을 떨어뜨리다</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>You don't want to spoil your appetite.</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Don't eat too much candy, you'll spoil your appetite for dinner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>ENG-20260529-127</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>bend down</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>/bɛnd daʊn/</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>몸을 숙이다, 허리를 굽히다</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>(When she bends down to pick it up he grabs a package of Gummi-bears)</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>He had to bend down to tie his shoelaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>ENG-20260529-128</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>pick up</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>/pɪk ʌp/</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>~을 집어 들다, (물건을) 줍다</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>she bends down to pick it up</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Could you pick up the dry cleaning on your way home?</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>ENG-20260529-129</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>get something out of the way</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmθɪŋ aʊt əv ðə weɪ/</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>성가신 일을 해치우다, 미리 처리하다</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>I need to get this report out of the way before I can relax.</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Let's get the difficult conversation out of the way first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>ENG-20260529-130</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>go through the roof</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>/ɡoʊ θruː ðə ruːf/</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>(가격, 수치 등이) 최고조에 달하다, 급등하다; (화가 머리끝까지) 치밀어 오르다</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>Demand for the new product has gone through the roof.</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>Rent prices in the city have gone through the roof recently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>ENG-20260529-131</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>level the playing field</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>/ˈlɛvl̩ ðə ˈpleɪɪŋ fiːld/</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>경쟁 환경을 공정하게 만들다, 공평한 기회를 제공하다</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>The new regulations are designed to level the playing field for all businesses.</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Access to education helps level the playing field for children from all backgrounds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>ENG-20260529-132</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>turn around</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>/tɜːrn əˈraʊnd/</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>(상황, 회사 등을) 호전시키다, 개선하다</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>The new CEO was hired to turn around the struggling company.</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>It took a lot of effort to turn around the failing project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>ENG-20260529-133</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>be up against</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>/biː ʌp əˈɡɛnst/</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>(어려움, 경쟁자 등에) 직면하다, 맞서다</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>We're up against a tight deadline, so we need to work efficiently.</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>The new startup is up against some major established companies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>ENG-20260529-134</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>be out of line</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>/biː aʊt ɒv laɪn/</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>도를 넘다, 무례하다, 부적절하다</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>His comments in the meeting were completely out of line.</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>You were out of line asking such personal questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>ENG-20260529-135</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>back out</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>/bæk aʊt/</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>(약속, 계약 등에서) 발을 빼다, 취소하다</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>He promised to help, but he backed out at the last minute.</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Don't back out of the deal now; we've come too far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>ENG-20260529-136</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>bring up</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>/brɪŋ ʌp/</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>(문제, 주제를) 제기하다, 꺼내다</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>I didn't want to bring up the sensitive topic during dinner.</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>She decided to bring up her concerns at the staff meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>ENG-20260529-137</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>end up</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>/ɛnd ʌp/</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>결국 ~하게 되다, ~로 끝나다</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>After all that planning, we ended up staying home anyway.</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>If you don't study, you might end up failing the exam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>ENG-20260529-138</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>hold off</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>/hoʊld ɒf/</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>~을 미루다, 보류하다</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>Let's hold off making a decision until we have all the facts.</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>They decided to hold off on their travel plans due to the bad weather.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>ENG-20260529-139</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>look into</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>/lʊk ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>~을 조사하다, 검토하다</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>The company is looking into the possibility of expanding into new markets.</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>We're looking into the cause of the system error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>ENG-20260529-140</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>set up</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>/sɛt ʌp/</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>~을 설치하다, 마련하다; (사업 등을) 시작하다</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>We need to set up a new meeting room for the presentation.</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>They plan to set up a new branch office in London.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>ENG-20260529-141</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>put up with</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>/pʊt ʌp wɪð/</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>~을 참다, 견디다</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>I don't know how she puts up with his constant complaining.</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>He had to put up with a lot of noise from his neighbors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>ENG-20260529-142</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>count on</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>/kaʊnt ɒn/</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>~을 믿다, 의지하다</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>You can always count on me for support.</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>I'm counting on you to help me with this project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>ENG-20260529-143</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>look forward to</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>/lʊk ˈfɔːrwərd tuː/</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>~을 고대하다, 기대하다</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>I'm really looking forward to seeing you next week.</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>We're looking forward to our summer vacation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>ENG-20260529-144</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>show up</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>/ʃoʊ ʌp/</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>나타나다, 모습을 드러내다</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>He said he would be here at 7, but he never showed up.</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>I hope everyone shows up for the meeting on time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>ENG-20260529-145</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>work out</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>/wɜːrk aʊt/</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>잘 풀리다, 성공하다; 운동하다; (문제를) 해결하다</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>I hope everything works out for you.</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Don't worry, I'm sure it will all work out in the end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>ENG-20260529-146</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>break down</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>/breɪk daʊn/</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>고장 나다; (협상 등이) 결렬되다; (울음을) 터뜨리다</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>The car broke down on the highway, so we had to call for a tow.</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Negotiations between the two countries broke down without an agreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>ENG-20260529-147</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>fill in</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>/fɪl ɪn/</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>(빈칸을) 채우다; (정보를) 알려주다</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>Can you fill me in on what I missed during the meeting?</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>I'll fill you in on the details later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>ENG-20260529-148</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>hold on</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>/hoʊld ɒn/</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>기다리다; 버티다</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>Hold on a minute, I'll be right back.</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Can you hold on for a moment while I check?</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>ENG-20260529-149</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>put down</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>/pʊt daʊn/</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>~을 내려놓다; (누군가를) 비하하다, 폄하하다</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Please put down your phone while we're talking.</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>It's not right to put down other people's ideas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>ENG-20260529-150</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>take apart</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>/teɪk əˈpɑːrt/</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>~을 분해하다; (계획 등을) 철저히 분석하다</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>The engineer took apart the machine to find the fault.</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>We need to take apart the competitor's strategy to understand their success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>ENG-20260529-151</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>turn up</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>/tɜːrn ʌp/</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>나타나다; (소리, 불빛 등을) 높이다; (예상치 않게) 발견되다</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>He finally turned up at the party after midnight.</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Could you please turn up the volume?</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>ENG-20260529-152</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>break up</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>/breɪk ʌp/</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>(관계가) 끝나다, 헤어지다</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>They broke up after dating for five years.</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>It's always sad when a band breaks up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>ENG-20260529-153</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>get away with</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>/ɡɛt əˈweɪ wɪð/</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>(처벌 없이) ~을 모면하다</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>He cheated on the exam and got away with it.</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>You can't just break the rules and expect to get away with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>ENG-20260529-154</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>keep up with</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>/kiːp ʌp wɪð/</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>~에 뒤처지지 않다, ~을 따라잡다</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>It's hard to keep up with all the latest technology.</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>She studies hard to keep up with her classmates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>ENG-20260529-155</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>look out for</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>/lʊk aʊt fɔːr/</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>~을 조심하다; ~을 찾아주다, 보살피다</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>Look out for pickpockets in crowded areas.</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Could you look out for my luggage while I get a coffee?</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>ENG-20260529-156</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>pull through</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>/pʊl θruː/</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>(병, 어려움 등을) 극복하다, 이겨내다</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>We were worried, but she managed to pull through her illness.</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>The company managed to pull through the financial crisis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>ENG-20260529-157</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>run out</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>/rʌn aʊt/</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>(시간, 공급 등이) 다 되다, 소진되다</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>Time is running out, so we need to make a decision soon.</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>We've almost run out of patience with their excuses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>ENG-20260529-158</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>walk out</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>/wɔːk aʊt/</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>떠나다, (시위하며) 퇴장하다</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>The employees threatened to walk out if their demands were not met.</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>She was so angry she just walked out of the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>ENG-20260529-159</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>on track</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>/ɑn træk/</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>순조롭게 진행 중인, 예정대로</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>it is on track to hit the regulator Ofcom's reduced targets</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>The construction project is on track to be completed by next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>ENG-20260529-160</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>face job shortage</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>/feɪs dʒɑb ˈʃɔrtɪdʒ/</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>일자리 부족에 직면하다</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>how young people are facing the job shortage</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>In some rural areas, residents often face job shortage due to limited industries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>ENG-20260529-161</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>north of the border</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>/nɔrθ əv ðə ˈbɔrdər/</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>국경 북쪽에서 (주로 캐나다와 미국 사이에서 쓰임), (비유적으로) 특정 기준 이상</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>had plummetted north of the border</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Many Canadians travel south for shopping, but some prefer to find unique items north of the border.</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>ENG-20260529-162</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>rush to explain</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>/rʌʃ tu ɪkˈspleɪn/</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>급하게 설명하다</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>Ross: (rushing to explain) Funny story!</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>When he realized his mistake, he rushed to explain the situation to his boss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>ENG-20260529-163</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>overhear a conversation</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>/ˌoʊvərˈhɪər ə ˌkɑnvərˈseɪʃən/</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>대화를 엿듣다, 우연히 듣다</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>Rachel walks in and overhears the conversation.</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>I accidentally overheard a conversation between my neighbors about their vacation plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>ENG-20260529-164</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>have a deal</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>/hæv ə dil/</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>합의가 되다, 거래가 성사되다</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Wendy, we had a deal!</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>After weeks of discussion, we finally have a deal on the new contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>ENG-20260529-165</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>hang up</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>/hæŋ ʌp/</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>(전화를) 끊다</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>(hangs up)</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Please don't hang up, I need to tell you something important.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>ENG-20260529-166</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>drag someone into</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>/dræɡ ˈsʌmˌwʌn ˈɪntu/</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>(~을) 강제로 끌어들이다, 억지로 참여시키다</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>Phoebe stops her and drags her into the kitchen.</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>He didn't want to get involved, but his friends dragged him into the argument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>ENG-20260529-167</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>on the way over</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>/ɑn ðə weɪ ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>오는 길에, (어떤 곳으로) 가는 도중에</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>In the cab, on the way over, Steve blazed up a doobie.</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>I'll pick up some snacks on the way over to your place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>ENG-20260529-168</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>blaze up</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>/bleɪz ʌp/</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>(담배, 특히 마리화나를) 피우다</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>Steve blazed up a doobie.</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>He tried to blaze up a cigarette discreetly in the alley.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>ENG-20260529-169</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>light a bone</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>/laɪt ə boʊn/</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>(마리화나) 한 대 피우다 (속어)</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>You know, lit a bone?</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>After a long day, some people might want to light a bone to relax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>ENG-20260529-170</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>bring over</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>/brɪŋ ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>(~을) 가져오다, 데려오다</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>Monica brings over a tray</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Can you bring over the documents I left on my desk?</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>ENG-20260529-171</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>one by one</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>/wʌn baɪ wʌn/</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>하나씩, 차례로</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>Steve starts to eat them one by one, quickly</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>The children opened their presents one by one on Christmas morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>ENG-20260529-172</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>with a touch of</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>/wɪð ə tʌtʃ əv/</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>약간의 (~을 곁들여), 조금의 (~을 더해)</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>with just a touch of mints</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>The dish was perfect, with a touch of garlic and fresh herbs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>ENG-20260529-173</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>get someone's attention</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmˌwʌnz əˈtɛnʃən/</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>(~의) 주의를 끌다</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Rachel tries to get Monica's attention</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>She tried waving her hands to get the waiter's attention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>ENG-20260529-174</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>drag on a joint</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>/dræɡ ɑn ə dʒɔɪnt/</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>(마리화나) 한 모금 피우다 (속어)</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>She pretends to drag on a joint</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>He quietly took a drag on his cigarette before going inside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>ENG-20260529-175</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>give the OK signal</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>/ɡɪv ðɪ oʊˈkeɪ ˈsɪɡnəl/</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>승인 신호를 주다, 괜찮다는 신호를 보내다</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>Monica thinks she's giving her the 'OK' signal.</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>The director gave the OK signal, and the cameras started rolling.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I832"/>
+  <dimension ref="A1:I929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39520,6 +39520,4565 @@
         </is>
       </c>
     </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>ENG-20260531-001</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>fast-track something</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>/ˈfæstˌtræk ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>어떤 일을 신속하게 처리하거나 가속화하다, (절차를) 단축하다</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>President Donald Trump is trying to fast-track research into psychedelics as treatments, creating new opportunities and risks.</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>The government decided to fast-track the new infrastructure project to boost the economy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>ENG-20260531-002</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>reverse course</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>/rɪˈvɜrs kɔrs/</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>방침이나 계획을 바꾸다, 방향을 전환하다</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>Why Trump reversed course to fast-track psychedelic drugs for mental healthcare.</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>After receiving negative feedback, the company decided to reverse course on its new pricing strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>ENG-20260531-003</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>ramp up something</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>/ˈræmp ʌp ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>무언가를 늘리다, 강화하다, 증대시키다</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>Disney is poised to ramp its already booming advertising business. Rita Ferro is behind the push.</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>We need to ramp up our production to meet the increasing customer demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>ENG-20260531-004</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>lead the charge</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>/ˈliːd ðə ˈtʃɑːrdʒ/</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>주도하다, 선두에 서다, 솔선수범하다</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>Global ad president Rita Ferro is leading the charge for Disney's advertising growth.</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Our CEO is leading the charge in developing sustainable business practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>ENG-20260531-005</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>buck the trend</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>/ˈbʌk ðə trɛnd/</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>추세에 역행하다, 대세를 거스르다</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>How a borough in Merseyside is bucking the UK's youth unemployment trend.</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Despite the industry downturn, our company managed to buck the trend and increase its profits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>ENG-20260531-006</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>a thing of the past</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>/ə ˈθɪŋ əv ðə pæst/</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>과거의 일, 더 이상 존재하지 않는 것</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>Why Britain's notoriously bad train wi-fi might soon be a thing of the past.</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Physical newspapers are slowly becoming a thing of the past with the rise of digital media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>ENG-20260531-007</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>fall into a trap</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>/ˈfɔl ˈɪntu ə træp/</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>함정에 빠지다, 덫에 걸리다</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>Could personalised early intervention help prevent under-16s falling into the Neet trap?</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Be careful not to fall into the trap of overspending during holiday sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>ENG-20260531-008</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>tackle an issue</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>/ˈtækəl ən ˈɪʃuː/</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>문제를 다루다, 해결하려고 노력하다</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>Ex-M&amp;S chief to help government tackle youth unemployment.</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>The committee was formed to tackle the urgent issue of climate change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>ENG-20260531-009</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>get someone into work</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmˌwʌn ˈɪntu wɜrk/</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>누군가를 취업시키다</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>Marc Bolland will advise on getting young people into work after a review warned of a 'lost generation'.</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>The new program aims to get long-term unemployed individuals back into work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>ENG-20260531-010</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>build on something</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>/bɪld ɑn ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>무언가를 기반으로 삼다, 발전시키다, ~을 토대로 하다</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>BMW is introducing humanoid robots to a car plant in Europe, building on similar projects in the US.</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>The team plans to build on their initial success by expanding into new markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>ENG-20260531-011</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>be on track to do something</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>/bi ɑn træk tu du ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>~할 예정이다, ~을 순조롭게 진행 중이다</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>Royal Mail says its service is improving and that it is on track to hit the regulator Ofcom's reduced targets.</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>We are on track to complete the project ahead of schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>ENG-20260531-012</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>call for something</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>/kɔl fɔr ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>요구하다, 촉구하다, 필요로 하다</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>Top UK chefs call for cutting VAT for pubs and restaurants to 10%.</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>The opposition party called for the minister's resignation after the scandal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>ENG-20260531-013</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>take on something/someone</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>/teɪk ɑn ˈsʌmˌθɪŋ/ /teɪk ɑn ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>(책임, 일을) 맡다; (도전, 상대와) 겨루다, 맞서다</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Ferrari wanted to take on Chinese EVs with the Luce. Student loan borrowers should proceed with caution when taking on more debt.</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>I've decided to take on the new project despite the heavy workload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>ENG-20260531-014</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>knock 'em dead</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>/nɑk əm dɛd/</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>매우 인상 깊게 하다, 훌륭하게 해내다 (특히 공연이나 발표 등에서)</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>You get to do the presentation, you'll knock 'em dead, no one will ever remember that I worked here.</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Go out there and give your best performance; I'm sure you'll knock 'em dead!</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>ENG-20260531-015</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>cover up something</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>/ˈkʌvər ʌp ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>무언가를 덮다, 가리다; (실수, 범죄 등을) 숨기다, 은폐하다</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>Tomorrow, I'll bring you a hat, cover up the bald?</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>The company tried to cover up the environmental damage caused by its factory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>ENG-20260531-016</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>wait on tables</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>/weɪt ɑn ˈteɪbəlz/</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>식당에서 서빙을 하다, 웨이터/웨이트리스로 일하다</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>Maybe this time you don't hit Drake, you just wait on the tables?</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>She worked hard waiting on tables to pay for her college tuition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>ENG-20260531-017</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>steal focus from someone</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>/stil ˈfoʊkəs frəm ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>누군가에게서 주목을 가로채다</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>I'm so good in this scene that I'm stealing focus from you.</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>His flashy presentation style often steals focus from the actual content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>ENG-20260531-018</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>rise to the challenge</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>/raɪz tu ðə ˈtʃælɪndʒ/</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>도전에 맞서다, 난관을 극복하다</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>Well, rise to the challenge Tribianni 'cause I just raised the bar.</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Despite the unexpected obstacles, the team managed to rise to the challenge and deliver excellent results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>ENG-20260531-019</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>raise the bar</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>/reɪz ðə bɑr/</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>기준을 높이다, 수준을 향상시키다</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>I'm so good in this scene that I'm stealing focus from you. Well, rise to the challenge Tribianni 'cause I just raised the bar.</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>The new software has definitely raised the bar for user experience in this industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>ENG-20260531-020</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>not go easy</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>/nɑt ɡoʊ ˈiːzi/</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>(쉽게) 물러서지 않다, 저항하다</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>Yeah, you can fire her, but I would call security, she won't go easy.</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>The lawyer warned that the opposing party would not go easy in court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>ENG-20260531-021</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>fake it</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>/feɪk ɪt/</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>진실이 아닌 척하다, 속이다, 꾸며내다</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>You faked it? You couldn't have faked it! Guys can fake it? Unbelievable.</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>He had to fake it until he made it, pretending to be confident even when he was nervous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>ENG-20260531-022</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>leave money on the table</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>/liːv ˈmʌni ɑn ðə ˈteɪbəl/</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>얻을 수 있는 이익을 놓치다, 기회를 놓치다</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>Travelers to Europe may be leaving money on the table. Here's why.</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>By not negotiating the salary, you might be leaving money on the table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>ENG-20260531-023</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>take effect</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>/teɪk ɪˈfɛkt/</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>(법, 규정 등이) 발효되다, 효력을 발휘하다</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>Student loan borrowing is 'high stakes' as new rules take effect on July 1.</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>The new policy will take effect at the beginning of next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>ENG-20260531-024</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>proceed with caution</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>/proʊˈsiːd wɪð ˈkɔʃən/</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>조심해서 진행하다, 신중하게 행동하다</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>Experts say that student loan borrowers should proceed with caution when taking on more debt.</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>When investing in volatile markets, it's always best to proceed with caution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>ENG-20260531-025</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>take on debt</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>/teɪk ɑn dɛt/</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>빚을 지다, 채무를 떠맡다</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>Student loan borrowers should proceed with caution when taking on more debt or consolidating after July 1.</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Many young entrepreneurs are hesitant to take on debt to fund their startups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>ENG-20260531-026</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>capitalize on something</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>/ˈkæpɪtəlaɪz ɑn ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>무언가를 활용하다, 기회를 잡다, 십분 이용하다</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>Investors keen on capitalizing on the AI boom can track recommendations from top Wall Street analysts.</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>We should capitalize on this surge in demand by launching a new product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>ENG-20260531-027</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>raise questions</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>/reɪz ˈkwɛstʃənz/</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>의문을 제기하다, 질문을 유발하다</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>Iran's blockade of the Strait of Hormuz has seriously challenged freedom of navigation in the sea lane, raising questions about the future.</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>The sudden resignation of the CEO has raised many questions among employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>ENG-20260531-028</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>make someone uncomfortable</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>/meɪk ˈsʌmˌwʌn ʌnˈkʌmfərtəbəl/</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>누군가를 불편하게 만들다</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>I should tell you that crying women make me very uncomfortable.</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>His inappropriate jokes often make his colleagues uncomfortable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>ENG-20260531-029</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>pick up someone</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>/pɪk ʌp ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>누군가를 태우러 가다</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>I have the baby, and Ross is not gonna pick her up for another hour.</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>Can you pick me up from the airport tomorrow evening?</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>ENG-20260531-030</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Global Business</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>pull off something</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>/pʊl ɔf ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>어려운 일을 해내다, 성공시키다</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>The team tried to fast-track the project, hoping to pull off an early launch despite the tight deadline.</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>I can't believe they managed to pull off such a complex event with so little preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>ENG-20260531-031</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>pencil in something</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>/ˈpɛnsɪl ɪn ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>잠정적으로 ~을 예약하거나 계획하다</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>Former Barclays CEO Jes Staley agrees to July 23 interview. I'll pencil in our next meeting for Tuesday, but I'll confirm later.</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>Let's pencil in a quick chat for next Monday morning, and I'll send you a calendar invite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>ENG-20260531-032</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>fend off something/someone</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>/fɛnd ɔf ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>무언가/누군가를 막아내다, 물리치다</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>Companies are facing mounting pressure and constantly have to fend off competition from new market entrants.</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>The small business struggled to fend off a hostile takeover bid from a larger corporation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>ENG-20260531-033</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Daily English</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>run into something/someone</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>/rʌn ˈɪntu ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>(예상치 못하게) ~와/을 만나다/마주치다; (문제에) 부딪히다</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>The project was on track, but we might run into some budget issues if costs aren't controlled.</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>I ran into an old friend at the grocery store yesterday, which was a pleasant surprise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>ENG-20260531-034</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>iron out something</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>/ˈaɪərn aʊt ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>문제를 해결하다, 원만히 처리하다</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>After negotiations broke down, they needed to iron out the remaining disagreements to reach a deal.</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Let's schedule another meeting to iron out the final details of the contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>ENG-20260531-035</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>come to terms with something</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>/kʌm tu tɜrmz wɪð ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>무언가를 받아들이다, 인정하다 (종종 불쾌한 사실)</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>The company had to come to terms with the fact that its first EV had been heavily criticized.</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>It took him a long time to come to terms with the loss of his job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>ENG-20260531-036</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>learn the ropes</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>/lɜrn ðə roʊps/</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>일을 배우다, 요령을 익히다</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>Chandler is starting a whole new career; he'll need some time to learn the ropes.</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>It takes a few months for new employees to learn the ropes and become fully productive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>ENG-20260531-037</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>be a tough pill to swallow</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>/bi ə tʌf pɪl tu ˈswɑloʊ/</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>받아들이기 힘든 사실이다, 쓰디쓴 약이다</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>The heavy criticism of Ferrari's first EV was a tough pill to swallow for the brand's loyal fans.</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Admitting that you made a mistake can be a tough pill to swallow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>ENG-20260531-038</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>wrap one's head around something</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>/ræp wʌnz hɛd əˈraʊnd ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>무언가를 이해하다, 납득하다 (특히 복잡하거나 어려운 것)</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>The new rules for student loan borrowing are complex. Many might struggle to wrap their heads around the changes.</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>It's hard to wrap my head around how quickly technology is advancing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>ENG-20260531-039</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>pull an all-nighter</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>/pʊl ən ɔl ˈnaɪtər/</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>밤샘하다 (특히 일이나 공부로)</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>Rachel worked really hard for her presentation. She might have pulled an all-nighter to prepare for it.</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>I had to pull an all-nighter to finish my essay before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>ENG-20260531-040</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>turn a blind eye to something</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>/tɜrn ə blaɪnd aɪ tu ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>못 본 척하다, 묵인하다</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>The director might have wanted to fire Phoebe, but Joey asked him not to turn a blind eye to Phoebe's talent.</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>The company was accused of turning a blind eye to the safety violations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>ENG-20260531-041</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>get one's feet wet</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>/ɡɛt wʌnz fit wɛt/</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>새로운 경험을 시작하다, 맛을 보다</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>Chandler is starting a new career; he's just trying to get his feet wet with his new writing job.</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>I'm just interning this summer to get my feet wet in the marketing industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>ENG-20260531-042</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>put one's foot down</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>/pʊt wʌnz fʊt daʊn/</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>단호한 태도를 취하다, 강경하게 나오다</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>Monica wanted a baby soon, but Chandler put his foot down about waiting for a year.</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>My parents put their foot down and said I couldn't stay out past midnight anymore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>ENG-20260531-043</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>keep an eye on something</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>/kip ən aɪ ɑn ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>무언가를 주시하다, 눈여겨보다, 감시하다</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>Investors keen on capitalizing on the AI boom can keep an eye on recommendations from top Wall Street analysts.</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>Could you please keep an eye on my luggage while I go get a coffee?</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>ENG-20260531-044</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>put something into perspective</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌmˌθɪŋ ˈɪntu pərˈspɛktɪv/</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>어떤 것의 중요성이나 의미를 제대로 이해하다, 균형 잡힌 시각으로 보다</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>The report on the 'lost generation' helps put the youth unemployment crisis into perspective.</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Traveling to different countries really puts your own problems into perspective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>ENG-20260531-045</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>come to fruition</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>/kʌm tu fruˈɪʃən/</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>결실을 맺다, 실현되다</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>Research into psychedelics as treatments may eventually come to fruition, offering new opportunities.</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Years of hard work finally came to fruition when the scientist made a breakthrough discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>ENG-20260531-046</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>give the green light</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>/ɡɪv ðə ɡrin laɪt/</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>승인하다, 허락하다, 진행을 허가하다</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>President Trump's decision to fast-track research gave the green light for psychedelic drugs as treatments.</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>The board gave the green light for the construction of the new office building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>ENG-20260531-047</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>take the lead</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>/teɪk ðə lid/</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>선두에 서다, 주도권을 잡다</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>Rita Ferro is leading the charge; she definitely takes the lead in Disney's advertising business.</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Someone needs to take the lead on this project, or nothing will get done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>ENG-20260531-048</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>hold your horses</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>/hoʊld jʊər ˈhɔrsɪz/</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>진정해라, 서두르지 마라</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>Monica asked Chandler if he wanted to wait a year for a baby. He might have told her to hold her horses.</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Hold your horses! Let's think this through before we make any hasty decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>ENG-20260531-049</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>have a say in something</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>/hæv ə seɪ ɪn ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>무언가에 대해 발언권이 있다, 결정에 영향을 미칠 권한이 있다</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>Oklahomans will soon vote on a measure to double the minimum wage, having a say in this election issue.</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>As an employee, I want to have a say in the company's new benefits package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>ENG-20260531-050</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>talk someone into something</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>/tɔk ˈsʌmˌwʌn ˈɪntu ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>누군가를 설득하여 ~하게 하다</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>Joey was just talking to the director, trying to talk him into not firing Phoebe.</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>I tried to talk her into joining the team, but she preferred to work alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>ENG-20260531-051</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>make a big deal out of something</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>/meɪk ə bɪɡ dil aʊt əv ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>무언가를 중요하게 여기다, 과장하다, 호들갑 떨다</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>Monica was making a big deal out of Chandler faking it, as it was 'the one thing that's ours!'.</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>It was just a small mistake, there's no need to make such a big deal out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>ENG-20260531-052</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>weigh in on something</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>/weɪ ɪn ɑn ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>무언가에 대해 의견을 제시하다, 자기 생각을 밝히다</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>Top Wall Street analysts weigh in on the potential of certain stocks with robust growth.</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>During the discussion, several experts weighed in on the proposed policy changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>ENG-20260531-053</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>stay on top of something</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>/steɪ ɑn tɑp əv ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>무언가를 잘 파악하고 통제하다, 최신 정보를 놓치지 않다</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>Investors keen on capitalizing on the AI boom need to stay on top of market trends.</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>It's crucial to stay on top of your emails to ensure no important messages are missed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>ENG-20260531-054</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>be in the cards</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>/bi ɪn ðə kɑrdz/</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>일어날 가능성이 있다, 운명이다</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>Chandler thought it'd probably be more than a year before having a baby; he didn't think it was in the cards soon.</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>After such a successful launch, a major expansion seems to be in the cards for the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>ENG-20260531-055</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Global Business</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>keep up with something</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>/kip ʌp wɪð ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>무언가를 따라잡다, 뒤처지지 않다</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>The pace of technological advancement is rapid, making it hard for businesses to keep up with the changes.</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>I struggle to keep up with all the new features constantly being added to the software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>ENG-20260531-056</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>break new ground</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>/breɪk nu ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>새로운 분야를 개척하다, 전례 없는 일을 하다</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>Research into psychedelics as treatments would break new ground in mental healthcare.</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Her innovative research in genetics is breaking new ground in medical science.</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>ENG-20260531-057</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>get off to a good start</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>/ɡɛt ɔf tu ə ɡʊd stɑrt/</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>순조롭게 출발하다, 좋은 시작을 하다</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>Rachel wanted to knock 'em dead with her presentation, hoping to get off to a good start in her job.</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>The new product got off to a good start with strong initial sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>ENG-20260531-058</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>lose sleep over something</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>/luz slip ˈoʊvər ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>무언가 때문에 전전긍긍하다, 걱정으로 잠을 못 이루다</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>Trump says he's not in a 'hurry', implying he won't lose sleep over the Iran negotiations.</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Don't lose sleep over that small mistake; it's not worth the stress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>ENG-20260531-059</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>have mixed feelings</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>/hæv mɪkst ˈfilɪŋz/</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>상반된 감정을 느끼다, 복잡한 심경이다</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>Ferrari's first EV has been heavily criticised. Some fans likely have mixed feelings about its future.</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>I have mixed feelings about moving to a new city; I'm excited but also nervous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>ENG-20260531-060</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>play a key role</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>/pleɪ ə ki roʊl/</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>핵심적인 역할을 하다</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>Rita Ferro is leading the charge; she plays a key role in Disney's advertising revenue.</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Education plays a key role in a child's development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>ENG-20260531-061</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>be a tough sell</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>/bi ə tʌf sɛl/</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>설득하기 어려운 일이다, 판매하기 어려운 상품이다</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>The heavily criticised Ferrari EV might be a tough sell to traditional brand loyalists.</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Convincing management to approve the new budget was a tough sell, but we managed it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>ENG-20260531-062</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>be in over one's head</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>/bi ɪn ˈoʊvər wʌnz hɛd/</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>감당하기 힘들다, 너무 벅차다</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>Student loan borrowers should proceed with caution to avoid being in over their heads with debt.</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>He took on too many responsibilities at work and quickly found himself in over his head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>ENG-20260531-063</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>take the wind out of someone's sails</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>/teɪk ðə wɪnd aʊt əv ˈsʌmˌwʌnz seɪlz/</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>누군가의 기를 꺾다, 의욕을 상실하게 하다</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>The backlash against the new EV must have taken the wind out of Ferrari's sails.</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>His negative comments really took the wind out of my sails before the presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>ENG-20260531-064</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>come out of nowhere</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>/kʌm aʊt əv ˈnoʊˌwɛr/</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>갑자기 나타나다, 예상치 못하게 발생하다</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>The proposal to fast-track psychedelic drugs seemed to come out of nowhere to many observers.</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>The new competitor came out of nowhere and quickly gained market share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>ENG-20260531-065</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>make a splash</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>/meɪk ə splæʃ/</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>큰 반향을 일으키다, 이목을 끌다</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>Disney is selling ads for major events like the Super Bowl, hoping to make a big splash with their campaigns.</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>The new artist made a splash with her debut album, topping the charts for weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>ENG-20260531-066</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>on the brink of something</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>/ɑn ðə brɪŋk əv ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>막 ~하기 직전인, ~의 벼랑 끝에 있는</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>If negotiations break down, the U.S. and Iran could be on the brink of further military action.</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>The company was on the brink of bankruptcy before the new investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>ENG-20260531-067</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>give someone a break</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmˌwʌn ə breɪk/</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>누군가를 좀 봐주다, 기회를 주다</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>Joey asked the director to give Phoebe a break, saying it was her last chance.</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>I've been working non-stop for weeks; I really need a break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>ENG-20260531-068</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>make a killing</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>/meɪk ə ˈkɪlɪŋ/</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>대박을 터뜨리다, 떼돈을 벌다</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>Investors keen on capitalizing on the AI boom are hoping to make a killing in the stock market.</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>He made a killing in the real estate market during the housing boom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>ENG-20260531-069</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>come full circle</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>/kʌm fʊl ˈsɜrkəl/</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>한 바퀴 돌아 제자리로 오다, 처음으로 돌아오다</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>Trump reversed course on fast-tracking psychedelic drugs, almost bringing the issue full circle.</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>After traveling the world, she came full circle and settled down in her hometown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>ENG-20260531-070</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>put in one's place</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>/pʊt ɪn wʌnz pleɪs/</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>누군가의 버릇을 고쳐주다, 겸손하게 만들다</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>Phoebe thought Joey was threatened and that she was raising the bar, effectively putting him in his place.</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>His arrogant attitude needed to be put in its place by a more experienced colleague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>ENG-20260531-071</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>pull out all the stops</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>/pʊl aʊt ɔl ðə stɑps/</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>모든 노력을 다하다, 총력을 기울이다</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>Disney is selling ads for major events; they will pull out all the stops to maximize revenue.</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>To make the wedding perfect, they pulled out all the stops and spared no expense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>ENG-20260531-072</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>take a bold step</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>/teɪk ə boʊld stɛp/</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>과감한 조치를 취하다, 대담한 발걸음을 내딛다</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>President Trump's decision to fast-track psychedelic drugs was a bold step in mental healthcare.</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>The company took a bold step by investing heavily in renewable energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>ENG-20260531-073</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>stick to one's guns</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>/stɪk tu wʌnz ɡʌnz/</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>자기 주장을 고수하다, 의견을 굽히지 않다</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>Phoebe stuck to her guns about her acting process, refusing to just wait on tables.</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Despite criticism, the CEO stuck to his guns regarding the company's new strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>ENG-20260531-074</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>go downhill</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ˈdaʊnˌhɪl/</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>내리막길을 걷다, 악화되다</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>Britain's notoriously bad train wi-fi was going downhill, making it a thing of the past in a good way.</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>After the management change, the quality of the service started to go downhill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>ENG-20260531-075</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>turn the tide</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>/tɜrn ðə taɪd/</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>형세를 뒤집다, 상황을 역전시키다</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>Experts hope new initiatives will turn the tide on youth unemployment and prevent a 'lost generation'.</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>The new marketing campaign was designed to turn the tide of declining sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>ENG-20260531-076</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>have an axe to grind</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>/hæv ən æks tu ɡraɪnd/</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>앙심을 품다, 개인적인 불만(악감정)이 있다</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>Phoebe accused Joey of being threatened, suggesting he might have an axe to grind with her success.</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>He often criticizes the company, but I think he just has an axe to grind because he was fired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>ENG-20260531-077</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>break the mold</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>/breɪk ðə moʊld/</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>관례를 깨다, 전형을 벗어나다, 독창적으로 행동하다</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>Ferrari wanted to take on Chinese EVs, attempting to break the mold for their traditional brand.</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>The new artist is praised for breaking the mold and creating a unique musical style.</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>ENG-20260531-078</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>be in uncharted waters</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>/bi ɪn ʌnˈtʃɑrtɪd ˈwɔtərz/</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>미지의 영역에 있다, 경험해보지 못한 상황에 처하다</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>Fast-tracking psychedelic drugs could mean mental healthcare is entering uncharted waters.</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>The company is entering uncharted waters with its expansion into the virtual reality market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>ENG-20260531-079</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>have a finger in every pie</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>/hæv ə ˈfɪŋɡər ɪn ˈɛvəri paɪ/</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>여러 일에 간섭하다, 많은 분야에 관여하다</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>Bill Gates is scheduled to be interviewed about Epstein, showing he has a finger in many different pies.</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>She's very busy; she seems to have a finger in every pie in the organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>ENG-20260531-080</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>take the moral high ground</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>/teɪk ðə ˈmɔrəl haɪ ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>도덕적 우위를 점하다</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>The chefs calling for VAT cuts are trying to take the moral high ground for the hospitality industry.</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>During the debate, she tried to take the moral high ground by focusing on ethical issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>ENG-20260531-081</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>be a breeze</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>/bi ə briz/</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>식은 죽 먹기이다, 매우 쉽다</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>Gavin told Rachel he was great with children, implying watching Emma would be a breeze for him.</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>After all that practice, the presentation was a breeze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>ENG-20260531-082</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>on thin ice</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>/ɑn θɪn aɪs/</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>위태로운 상황에 처한, 위험한 상태인</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>Phoebe was told it was her last chance; she was definitely on thin ice with the director.</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>After missing so many deadlines, he's really on thin ice with his boss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>ENG-20260531-083</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>give one's all</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>/ɡɪv wʌnz ɔl/</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>전력을 다하다, 모든 것을 쏟아붓다</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>Rachel worked really hard; she gave her all to prepare for the presentation.</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>To win this championship, every player needs to give their all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>ENG-20260531-084</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>be a game changer</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>/bi ə ɡeɪm ˈtʃeɪndʒər/</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>판도를 바꾸는 결정적인 요소/사건이 되다</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>Fast-tracking psychedelic drugs could be a game changer for mental healthcare.</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>The invention of the internet was a game changer for communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>ENG-20260531-085</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>be in a hurry</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>/bi ɪn ə ˈhʌri/</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>서두르다, 바쁘다</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>Trump says he's not in a 'hurry'</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>I can't talk right now; I'm in a hurry to catch my train.</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>ENG-20260531-086</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>be interviewed about</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>/bi ˈɪntəvjuːd əˈbaʊt/</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>~에 대해 인터뷰하다/질문받다</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>Microsoft co-founder Bill Gates is scheduled to be interviewed about his relationship to the sex offender Jeffrey Epstein in June.</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>The CEO was interviewed about the company's financial performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>ENG-20260531-087</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>booming business</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>/ˈbuːmɪŋ ˈbɪznɪs/</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>호황을 누리는 사업, 번창하는 사업</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>Disney is poised to ramp its already booming advertising business.</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>The tech startup became a booming business within just two years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>ENG-20260531-088</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>vote on a measure</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>/voʊt ɒn ə ˈmeʒər/</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>안건/법안에 대해 투표하다</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>Oklahomans will soon vote on a measure to double the minimum wage</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>The council will vote on a measure to restrict plastic use next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>ENG-20260531-089</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>track recommendations</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>/træk ˌrɛkəmɛnˈdeɪʃənz/</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>추천/권고 사항을 추적하다/주시하다</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>Investors keen on capitalizing on the AI boom can track recommendations from top Wall Street analysts</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>We need to track recommendations from our sales team to improve customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>ENG-20260531-090</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>challenge freedom</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>/ˈtʃælɪndʒ ˈfriːdəm/</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>자유를 위협하다/도전하다</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>Iran's blockade of the Strait of Hormuz has seriously challenged freedom of navigation in the sea lane</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>The new policy could challenge the freedom of speech for citizens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>ENG-20260531-091</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>claim a refund</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>/kleɪm ə ˈriːfʌnd/</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>환불을 요청하다/청구하다</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>Travelers to Europe who buy certain merchandise can claim a refund of the value-added taxes they pay.</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>If you are not satisfied with the product, you can claim a refund within 30 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>ENG-20260531-092</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>be heavily criticized</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>/bi ˈhɛvɪli ˈkrɪtɪsaɪzd/</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>심하게 비난받다, 맹렬히 비판받다</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>The brand's first EV has been heavily criticised, with some saying it has abandoned Ferrari's roots.</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>The government's decision to cut public services was heavily criticized by opposition parties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>ENG-20260531-093</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>reject a bid</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>/rɪˈdʒɛkt ə bɪd/</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>입찰/제안을 거절하다</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>Universal rejects billionaire Bill Ackman's takeover bid</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>The board decided to reject the takeover bid, believing it undervalued the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>ENG-20260531-094</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>be set to rise</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>/bi sɛt tə raɪz/</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>상승할 것으로 예상되다, 증가할 예정이다</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>the number of 16 to 24-year-olds out of work, education or training is set to rise to 1.25 million by 2031.</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>Oil prices are set to rise significantly in the coming months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>ENG-20260531-095</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>leave early</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>/liːv ˈɜːrli/</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>일찍 퇴근하다/떠나다</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>Ralph needs to leave early today.</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>I have a dentist appointment, so I need to leave early from work today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>ENG-20260531-096</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>make faces</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>/meɪk ˈfeɪsɪz/</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>(우스꽝스럽거나 못마땅한) 표정을 짓다</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>You just make the faces and the noises.</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>The children were making faces at each other across the dinner table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>ENG-20260531-097</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>start a new career</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>/stɑːrt ə njuː kəˈrɪər/</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>새로운 직업을 시작하다, 전직하다</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>I'm starting a whole new career now</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>After years in finance, she decided to start a new career as a teacher.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I929"/>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44079,6 +44079,3437 @@
         </is>
       </c>
     </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>ENG-20260601-001</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>break into</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>/breɪk ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>(새로운 시장이나 분야에) 진출하다, 침투하다</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>Nvidia is breaking into the PC market for the first time with its new Arm-based chips.</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>It's hard for new startups to break into the highly competitive EV market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>ENG-20260601-002</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>carve out</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>/kɑːv aʊt/</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>(노력을 통해 영역이나 지위를) 개척하다, 만들어 내다</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>Nvidia has managed to carve out a dominant position in the artificial intelligence sector.</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>She worked hard to carve out a niche for herself in the design industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>ENG-20260601-003</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>dry up</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>/draɪ ʌp/</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>(자금, 공급 등이) 바닥나다, 고갈되다</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>Retailers fear consumer spending will drop when tax refunds dry up.</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>If investment funding dries up, many early-stage startups will go out of business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>ENG-20260601-004</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>fast-track</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>/fɑːst træk/</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>신속히 처리하다, 고속 승진시키다</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>The government is trying to fast-track research into psychedelic drugs for healthcare.</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>They decided to fast-track the approval process for the new life-saving drug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>ENG-20260601-005</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>trail behind</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>/treɪl bɪˈhaɪnd/</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>~보다 뒤처지다, 뒤를 쫓다</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>Berkshire is trailing behind the red-hot S&amp;P 500 by its biggest margin this year.</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Our domestic sales are beginning to trail behind those of our main competitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>ENG-20260601-006</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>paper over the cracks</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>/ˈpeɪpər ˈoʊvər ðə kræks/</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>(문제를 근본적으로 해결하지 않고) 임시변통으로 숨기다</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>The strong Q1 earnings only papered over the cracks of structural consumer weakness.</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>Offering discounts will only paper over the cracks of our poor product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>ENG-20260601-007</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>put someone on a blacklist</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌmwʌn ɒn ə ˈblæklɪst/</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>~를 블랙리스트에 올리다, 차단하다</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>Airlines propose to put abusive passengers on a shared blacklist.</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>The company was put on a blacklist after failing multiple safety inspections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>ENG-20260601-008</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>pivot towards</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>/ˈpɪvət təˈwɔːdz/</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>~로 방향을 틀다, 중심축을 이동하다</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>China is making an ambitious pivot towards green energy despite coal mining issues.</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>Our firm is planning to pivot towards cloud-based software services next year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>ENG-20260601-009</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>abandon one's roots</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>/əˈbændən wʌnz ruːts/</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>초심을 잃다, 자신의 뿌리/정체성을 버리다</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>Critics complained that Ferrari abandoned its roots by launching a silent electric vehicle.</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>As we scale our brand, we must make sure we don't abandon our roots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>ENG-20260601-010</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>surge ahead</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>/sɜːdʒ əˈhed/</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>급격히 앞서 나가다, 급등하다</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>Shares in major software companies surged ahead before Monday's opening bell.</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Tech stocks surged ahead after the Fed hinted at keeping rates steady.</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>ENG-20260601-011</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>lead the pack</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>/liːd ðə pæk/</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>선두를 달리다, 가장 앞서가다</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>Nvidia continues to lead the pack in high-performance AI semiconductors.</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>In terms of customer service, our airline aims to lead the pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>ENG-20260601-012</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>make waves</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>/meɪk weɪvz/</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>풍파를 일으키다, 큰 반향을 일으키다</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>Lidl is making waves in the retail industry with its bizarre proposal to open a pub.</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>The young CEO's unconventional management style is making waves in Wall Street.</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>ENG-20260601-013</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>catch someone off guard</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>/kætʃ ˈsʌmwʌn ɒf gɑːd/</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>~의 허를 찌르다, 무방비 상태에서 당황하게 만들다</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>The scale of the consumer spending decline caught many retail executives off guard.</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>The competitor's sudden price cut caught us completely off guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>ENG-20260601-014</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>gain ground</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>/geɪn graʊnd/</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>우세를 차지하다, 입지를 다지다</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>Arm-based chips are gaining ground in the personal computer market.</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Our competitors are gaining ground in the Asian market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>ENG-20260601-015</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>lose ground</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>/luːz graʊnd/</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>입지를 잃다, 뒤처지다</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>Traditional chip makers are losing ground to newcomers focused on AI architecture.</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>If we do not innovate, we run the risk of losing ground to smaller agile startups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>ENG-20260601-016</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>pave the way</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>/peɪv ðə weɪ/</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>길을 열어주다, 기반을 닦다</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>Nvidia’s PC chip reinvention paves the way for a new era of personal computing.</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>The groundbreaking clinical trial paved the way for a new cancer treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>ENG-20260601-017</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>tread carefully</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>/tred ˈkeəfəli/</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>신중하게 행동하다, 조심조심 처신하다</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>The Federal Reserve must tread carefully to avoid causing public mistrust.</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>We need to tread carefully when negotiating with this high-profile client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>ENG-20260601-018</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>set the stage</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>/set ðə steɪdʒ/</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>장을 마련하다, 판을 깔다</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>SoftBank’s massive AI investments set the stage for a technological revolution.</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>The successful trial results set the stage for our global product launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>ENG-20260601-019</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>fall by the wayside</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>/fɔːl baɪ ðə ˈweɪsaɪd/</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>낙오되다, 무용지물이 되어 잊히다</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>Many pre-ChatGPT startups will fall by the wayside as advanced AI platforms dominate.</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>Without regular updates, older software programs will quickly fall by the wayside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>ENG-20260601-020</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>keep a close eye on</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>/kiːp ə kləʊs aɪ ɒn/</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>~을 예의주시하다, 면밀히 감시하다</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>Wall Street is keeping a close eye on Jerome Powell’s warnings about the White House.</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>We should keep a close eye on our competitors' pricing strategies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>ENG-20260601-021</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>reap the benefits</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>/riːp ðə ˈbenɪfɪts/</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>이득을 보다, 결실을 누리다</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>Early adopters of AI integration are already reaping the benefits of higher productivity.</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Our company is now reaping the benefits of our long-term R&amp;D investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>ENG-20260601-022</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>stem from</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>/stem frɒm/</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>~에서 기인하다, 비롯되다</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>The public trust issue stems from ongoing political pressure on the central bank.</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Many customer complaints stem from a lack of clear communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>ENG-20260601-023</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>take the helm</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>/teɪk ðə helm/</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>실권을 잡다, 지휘봉을 잡다</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>Greg Abel is ready to take the helm at Berkshire Hathaway and lead strategic deals.</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>The new manager is set to take the helm of our marketing department next Monday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>ENG-20260601-024</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>play second fiddle</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>/pleɪ ˈsekənd ˈfɪdəl/</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>조연 역할을 하다, 2인자 자리에 머물다</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>Other chip manufactures do not want to play second fiddle to Nvidia in the AI boom.</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>I'm tired of playing second fiddle to him; I want to lead my own project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>ENG-20260601-025</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>go belly up</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>/gəʊ ˈbeli ʌp/</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>파산하다, 완전히 도산하다</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>Startups that failed to adapt to ChatGPT’s technology went belly up.</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>If the bank refuses our loan application, the business might go belly up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>ENG-20260601-026</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>fall short of</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>/fɔːl ʃɔːt ɒv/</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>~에 미치지 못하다, 기대 이하이다</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>SoftBank's investment profits fell short of market expectations last quarter.</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>The final sales numbers unfortunately fell short of our initial targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>ENG-20260601-027</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>blow out of the water</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>/bləʊ aʊt ɒv ðə ˈwɔːtər/</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>완전히 압도하다, 압승하다, 박살을 내다</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>The performance of the new AI chip blew traditional processors out of the water.</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>Our new pricing strategy will blow the competition out of the water.</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>ENG-20260601-028</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>get the upper hand</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>/get ðə ˈʌpər hænd/</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>우세를 점하다, 주도권을 쥐다</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>Microsoft is trying to get the upper hand on rivals by deploying Arm-based chips.</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>The negotiator used a bold strategy to get the upper hand in the contract talks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>ENG-20260601-029</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>ride the wave</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>/raɪd ðə weɪv/</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>트렌드에 편승하다, 흐름을 타다</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>Startups are trying to ride the wave of the AI boom to secure more funding.</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>Our company has successfully ridden the wave of online fitness trends during the lockdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>ENG-20260601-030</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>clear the hurdle</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>/klɪər ðə ˈhɜːdəl/</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>장애물을 극복하다, 난관을 통과하다</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>The strategic deal must clear regulatory hurdles before it can be finalized.</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>Once we clear this financial hurdle, our cash flow will stabilize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>ENG-20260601-031</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>shore up</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>/ʃɔːr ʌp/</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>강화하다, 지탱하다, 지지대를 대다</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>Jerome Powell aims to shore up public trust in the independence of the Fed.</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>The government announced emergency measures to shore up the struggling housing market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>ENG-20260601-032</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>run amok</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>/rʌn əˈmʌk/</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>통제를 잃고 미쳐 날뛰다, 걷잡을 수 없이 돌아가다</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>Investors fear speculation in adjacent tech stocks might run amok, creating a bubble.</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>Without proper regulation, artificial intelligence could run amok.</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>ENG-20260601-033</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>ring the alarm</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>/rɪŋ ðə əˈlɑːm/</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>경종을 울리다, 경보를 울리다</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>Jerome Powell is ringing the alarm on political pressures that threaten the bank.</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>Economists are ringing the alarm over the rising level of national debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>ENG-20260601-034</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>shake up</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>/ʃeɪk ʌp/</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>대대적으로 개편하다, 뒤흔들다</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>Nvidia’s entry into personal computers is bound to shake up the entire industry.</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>The new manager plans to shake up the sales department to boost efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>ENG-20260601-035</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>stave off</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>/steɪv ɒf/</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>(위기, 재난 등을) 피하다, 모면하다</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>The government is introducing measures to stave off a full-blown economic recession.</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>Drinking plenty of water and resting can help stave off a cold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>ENG-20260601-036</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>put a damper on</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>/pʊt ə ˈdæmpər ɒn/</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>찬물을 끼얹다, 기를 꺾다</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>The potential shortage of peppers put a damper on the hot sauce manufacturers' plans.</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>The sudden downpour of rain put a damper on our outdoor company picnic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>ENG-20260601-037</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>leave someone in the dust</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>/liːv ˈsʌmwʌn ɪn ðə dʌst/</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>상대를 멀찌감치 따돌리다, 큰 격차로 앞서다</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>The rapid pace of the AI boom leaves older startup models in the dust.</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>If we don't upgrade our technology, our competitors will leave us in the dust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>ENG-20260601-038</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>clog up</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>/klɒg ʌp/</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>꽉 막히게 하다, 정체시키다</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>Unrecycled electronic waste and vapes continue to clog up our local landfills.</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>Large spam email attachments can clog up your inbox and slow down the server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>ENG-20260601-039</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>lay the groundwork</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>/leɪ ðə ˈgraʊndwɜːk/</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>기반을 마련하다, 기초 작업을 하다</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>The pilot project laid the groundwork for the brand’s global expansion plans.</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>Years of research and development laid the groundwork for this new medical device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>ENG-20260601-040</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>throw a wrench in the works</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>/θrəʊ ə rentʃ ɪn ðə wɜːks/</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>계획을 방해하다, 찬물을 끼얹어 엉망으로 만들다</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>Unexpected political pressure could throw a wrench in the works of the central bank.</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>The shipping strike threw a wrench in the works for our global supply chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>ENG-20260601-041</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>prop up</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>/prɒp ʌp/</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>지원하다, 떠받치다, 지탱하다</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>High tax refunds were helping to prop up consumer spending in the first quarter.</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>The central bank injected massive funds to prop up the failing banking system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>ENG-20260601-042</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>scale back</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>/skeɪl bæk/</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>규모를 축소하다, 감축하다</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>The airline had to scale back its flight schedule due to the acute staff shortage.</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>We had to scale back our budget for marketing to manage our cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>ENG-20260601-043</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>take a hit</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>/teɪk ə hɪt/</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>타격을 입다, 손실을 보다</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>Retail profit margins are expected to take a hit once tax refunds dry up.</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>The tourism industry took a major hit during the prolonged global travel ban.</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>ENG-20260601-044</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>make a comeback</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>/meɪk ə ˈkʌmbæk/</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>재기하다, 복귀하다, 다시 유행하다</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>Nvidia’s breakthrough is helping Arm-based computer chips make a massive comeback.</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>After a disastrous year, the technology brand is finally making a major comeback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>ENG-20260601-045</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>pave the path</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>/peɪv ðə pɑːθ/</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>길을 닦다, 초석을 놓다</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>The new drug research could pave the path for revolutionary psychiatric treatments.</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>The innovative curriculum is designed to pave the path for future tech leaders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>ENG-20260601-046</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>bring to light</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>/brɪŋ tuː laɪt/</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>(세상에) 밝혀내다, 규명하다, 폭로하다</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>The investigation of the coal mine disaster brought multiple safety violations to light.</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>An internal audit brought several financial discrepancies to light.</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>ENG-20260601-047</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>fall on deaf ears</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>/fɔːl ɒn def ɪəz/</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>완전히 무시되다, 전혀 귀 기울이지 않다</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>Warnings about the rising stock market bubble seemed to fall on deaf ears in May.</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>My suggestions for safety improvements in the factory unfortunately fell on deaf ears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>ENG-20260601-048</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>keep the momentum going</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>/kiːp ðə məʊˈmentəm ˈgəʊɪŋ/</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>기세를 계속 이어나가다, 탄력을 유지하다</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>Nvidia is launching new chips to keep the momentum going in the personal computer rally.</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>We need to run a follow-up ad campaign to keep the momentum going.</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>ENG-20260601-049</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>stand the test of time</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>/stænd ðə test ɒv taɪm/</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>오랜 세월을 견뎌내다, 세월이 흘러도 가치를 유지하다</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>Warren Buffett’s value investing philosophy has stood the test of time.</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>A simple, clean design will always stand the test of time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>ENG-20260601-050</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>draw the line</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>/drɔː ðə laɪn/</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>선을 긋다, 한계를 정하다, 허용 범위를 정하다</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>Airlines must draw the line when it comes to abusive behavior toward cabin crew.</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>I'm happy to help a friend, but I have to draw the line at lending large sums of money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>ENG-20260601-051</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>reap what one sows</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>/riːp wɒt wʌn səʊz/</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>자업자득이다, 뿌린 대로 거두다</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>Startups that ignored the AI boom are now reaping what they sowed as they lose market share.</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>If you don't prepare for the client pitch, you'll eventually reap what you sow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>ENG-20260601-052</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>step up one's game</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>/step ʌp wʌnz geɪm/</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>역량을 강화하다, 한 단계 더 노력하다</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>Traditional chipmakers must step up their game to compete with Nvidia's new AI technology.</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>If we want to win this pitch, we really need to step up our game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>ENG-20260601-053</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>smooth over</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>/smuːð ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>문제를 원만하게 수습하다, 미봉하다</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>Ferrari tried to smooth over the backlash from purists after releasing their EV.</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>The PR team managed to smooth over the misunderstanding with a quick statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>ENG-20260601-054</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>keep a lid on</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>/kiːp ə lɪd ɒn/</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>억제하다, 비밀로 유지하다</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>The central bank is trying hard to keep a lid on rising inflation expectations.</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>We must keep a lid on the merger plans until the contract is officially finalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>ENG-20260601-055</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>run the risk of</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>/rʌn ðə rɪsk ɒv/</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>~의 위험을 감수하다, ~할 위험이 있다</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>Airlines that do not blacklist abusive passengers run the risk of losing public trust.</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>If you don't back up your data regularly, you run the risk of losing important files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>ENG-20260601-056</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>unveil a strategy</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>/ʌnˈveɪl ə ˈstrætədʒi/</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>새로운 전략이나 계획을 공식적으로 발표하다/공개하다</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>Nvidia CEO Jensen Huang unveiled a long-awaited strategy to break into the personal computer market.</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>The tech giant is expected to unveil a strategy for its next-generation artificial intelligence platforms next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>ENG-20260601-057</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>funnel money into</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>/ˈfʌnəl ˈmʌni ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>자금을 특정 분야나 사업에 대량으로 쏟아붓다</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>The AI boom has funneled more than $250 billion into OpenAI and Anthropic.</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>Venture capital firms are choosing to funnel money into clean energy startups rather than traditional tech.</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>ENG-20260601-058</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>leave someone stranded</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>/liːv ˈsʌmwʌn ˈstrændɪd/</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>누군가를 곤경에 빠뜨리거나 무방비 상태로 남겨두다</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>The sudden shifts in AI investment have left hundreds of older startups stranded.</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>The sudden cancellation of the development contract left the small supplier stranded without any source of revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>ENG-20260601-059</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>mask the truth</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>/mæsk ðə truːθ/</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>진실을 가리다, 근본적인 문제를 감추다</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>High tax refunds and buy now, pay later options helped mask underlying consumer weakness.</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>The short-term sales boost only served to mask the truth about the company's declining popularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>ENG-20260601-060</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>take on a competitor</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>/teɪk ɒn ə kəmˈpɛtɪtər/</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>경쟁사나 상대에게 도전장을 내밀고 맞서다</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>Ferrari wanted to take on Chinese electric vehicle manufacturers with their latest concept car.</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>To take on a global competitor, the startup decided to lower its pricing substantially.</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>ENG-20260601-061</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>spark a backlash</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>/spɑːrk ə ˈbækˌlæʃ/</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>대중의 격렬한 반발을 불러일으키다</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>Ferrari wanted to challenge local manufacturers, but then the design sparked a major backlash.</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>The company's new policy on remote work sparked a backlash among employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>ENG-20260601-062</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>bounce back</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>/baʊns bæk/</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>(실패, 타격 등에서) 신속하게 회복하다, 다시 일어서다</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>After a difficult quarter, the retail sector managed to bounce back stronger than ever.</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>Analysts believe that tech stocks will bounce back once interest rates begin to stabilize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>ENG-20260601-063</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>run out of steam</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>/rʌn aʊt əv stiːm/</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>추진력을 잃다, 기운이 빠지다, 흐지부지되다</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>The market rally that started in May seems to have run out of steam due to lack of fresh catalysts.</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>The project started with great enthusiasm but ran out of steam due to a lack of funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>ENG-20260601-064</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>hit a brick wall</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>/hɪt ə brɪk wɔːl/</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>더 이상 나아갈 수 없는 한계에 부딪히다, 장벽에 막히다</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>Our expansion plans in Asia hit a brick wall due to unexpected regulatory challenges.</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>The negotiations hit a brick wall when neither side wanted to compromise on the budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>ENG-20260601-065</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>keep a low profile</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>/kiːp ə loʊ ˈproʊfaɪl/</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>대중의 관심을 피해 저자세를 유지하다, 조용히 처신하다</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>The executive was advised to keep a low profile while the investigation was underway.</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>After the public relations disaster, the company decided to keep a low profile for a few months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>ENG-20260601-066</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>keep cards close to one's chest</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>/kiːp kɑːrdz kloʊs tuː wʌnz tʃɛst/</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>자신의 계획이나 생각을 남에게 숨기고 극비로 하다</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>SoftBank's CEO is keeping his cards close to his chest regarding his next massive AI investment.</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>It is wise to keep your cards close to your chest during the initial phases of negotiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>ENG-20260601-067</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>burn bridges</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>/bɜːrn ˈbrɪdʒɪz/</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>관계를 끊어 배수의 진을 치다, 돌아갈 길을 차단하다</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>Leaving the company abruptly like that might burn bridges with key industry contacts.</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>No matter how frustrated you are, try not to burn bridges when resigning from your job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>ENG-20260601-068</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>blow the whistle</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>/bloʊ ðə ˈwɪsəl/</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>부정이나 비리를 고발하다, 폭로하다</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>An internal auditor decided to blow the whistle on the company's unregistered labor practices.</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>She decided to blow the whistle after discovering that the safety reports had been falsified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>ENG-20260601-069</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>put something on hold</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌmθɪŋ ɒn hoʊld/</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>보류하다, 연기하다</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>With the market downturn, we decided to put our expansion plans on hold.</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>The marketing campaign has been put on hold until we resolve the production issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>ENG-20260601-070</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>iron out the details</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>/ˈaɪərn aʊt ðə ˈdiːteɪlz/</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>세부적인 문제들을 해결하여 타협을 완료하다</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>Both sides met to iron out the details of the $6.8 billion acquisition agreement.</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>We have agreed on the main points, but we still need to iron out the details of the contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>ENG-20260601-071</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>deliver the goods</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>/dɪˈlɪvər ðə ɡʊdz/</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>기대에 부응하다, 약속한 성과를 보여주다</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>Greg Abel needs to deliver the goods after taking over the massive conglomerate from Buffett.</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>The design team promised a complete overhaul by Friday, and they truly delivered the goods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>ENG-20260601-072</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>get down to brass tacks</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>/ɡɛt daʊn tuː bræs tæks/</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>본론으로 들어가다, 핵심 사안을 논의하다</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>Now that the introductions are over, let's get down to brass tacks and discuss the price.</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>After an hour of small talk, the investors finally got down to brass tacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>ENG-20260601-073</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>close the deal</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>/kloʊz ðə diːl/</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>거래를 성사시키다, 계약을 체결하다</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>The Berkshire team worked overtime to close the deal for $6.8 billion.</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>We've been negotiating for weeks, and we are finally ready to close the deal.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1002"/>
+  <dimension ref="A1:I1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47510,6 +47510,4048 @@
         </is>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>ENG-20260602-001</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>rein in</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>/reɪn ɪn/</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>(성장, 지출, 행동 등을) 억제하다, 통제하다</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>House leader laid out Democrats' path to a majority next Congress and plans to rein in President Donald Trump. / China goes after 'ghost kitchens' to rein in cut-throat food delivery apps.</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>The government needs to rein in public spending to avoid a larger budget deficit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>ENG-20260602-002</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>gear up for</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>/ɡɪər ʌp fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>~을 준비하다, 대비하다</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>Goldman Sachs CEO David Solomon's comments come as investors prepare for what will be one of the busiest periods for equity issuance in years.</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>We need to gear up for the upcoming holiday season, as demand is expected to be very high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>ENG-20260602-003</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>hone in on</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>/hoʊn ɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>~에 초점을 맞추다, 집중하다</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>Democrats aren't focused on Trump impeachment 'at this moment'</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>During the brainstorming session, we tried to hone in on the core problem we're trying to solve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>ENG-20260602-004</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>stick with</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>/stɪk wɪð/</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>~을 고수하다, ~을 계속하다</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>'I think you gotta stay in,' says the top BlackRock investing official, as earnings growth and cash to be reinvested in stocks support the AI bull market.</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Despite the challenges, we decided to stick with our original plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>ENG-20260602-005</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>break off</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>/breɪk ɒf/</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>(회담, 관계 등을) 중단하다, 끊다</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>Trump, Rubio say talks with Tehran ongoing despite Iranian media claims otherwise / prospect of Iran ending talks with the U.S.</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>The two countries threatened to break off diplomatic relations after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>ENG-20260602-006</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>walk away from</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>/wɔːk əˈweɪ frɒm/</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>~에서 손을 떼다, ~을 포기하다</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>prospect of Iran ending talks with the U.S.</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>They decided to walk away from the negotiation table as the terms were unfavorable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>ENG-20260602-007</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>pour into</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>/pɔːr ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>~에 (돈, 노력 등을) 쏟아붓다</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>cash to be reinvested in stocks support the AI bull market.</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>The tech giant continues to pour billions of dollars into AI research and development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>ENG-20260602-008</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>burst into</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>/bɜːrst ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>(갑자기) ~로 뛰어들다, 터져 나오다</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>Strange man: (he bounds into the house) I knew you'd be here! / Ross: (he bounds into the lounge room) But you didn't!</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>He burst into the room, out of breath, with urgent news.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>ENG-20260602-009</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>steer clear of</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>/stɪər klɪər ɒv/</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>~을 피하다, 가까이 가지 않다</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>Mike: I asked him to keep me away from you.</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>I try to steer clear of crowded places during peak hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>ENG-20260602-010</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>screw up</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>/skruː ʌp/</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>엉망으로 만들다, 실수하다 (mess up보다 더 구어체)</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>Manny: Oh we blew it. I blame myself.</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Don't screw up this chance; it might be your last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>ENG-20260602-011</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>pass away</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>/pæs əˈweɪ/</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>사망하다, 돌아가시다 (die의 완곡한 표현)</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>Chandler: At least he died doing what he loved... / Kori: I can't believe that Ross is gone. It is just so sad.</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Her grandmother passed away peacefully in her sleep last night.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>ENG-20260602-012</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>listen in on</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>/ˈlɪsən ɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>(남의 대화를) 엿듣다</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>Ross: (they press their ears against the door)</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>I caught my little brother trying to listen in on my phone conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>ENG-20260602-013</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>choke up</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>/tʃoʊk ʌp/</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>(감정이 북받쳐) 목이 메다</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>Chandler: (in a mournful voice) Please, come in.</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>He started to choke up as he talked about his late mentor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>ENG-20260602-014</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>kick out</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>/kɪk aʊt/</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>내쫓다, 해고하다</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>Chandler: (he shoves him out the door) Ok Tommy, that's enough mourning for you! Here we go, bye bye!!</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>The unruly customer was kicked out of the bar by the bouncer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>ENG-20260602-015</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>rave about</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>/reɪv əˈbaʊt/</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>~에 대해 열변을 토하다, 극찬하다</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>Kori: He was such a great guy and he talked so passionately about science. I always remembered him.</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>Everyone who's been to the new restaurant just raves about their pasta dishes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>ENG-20260602-016</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>draw up</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>/drɔː ʌp/</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>(계획, 문서 등을) 작성하다, 만들다</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>AI developers, on a voluntary basis, are asked to collaborate with the government and provide early access to frontier models.</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>The legal team is busy drawing up the terms and conditions for the new service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>ENG-20260602-017</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>mull over</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>/mʌl ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>~을 심사숙고하다, 곰곰이 생각하다</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>Some firms are putting pressure on staff to use AI, but have not thought through their AI rollout.</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>I'll mull over your proposal during the weekend and give you my decision on Monday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>ENG-20260602-018</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>square off against</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>/skwɛər ɒf əˈɡɛnst/</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>~와 대결할 준비를 하다, 맞서다</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>Investors are worried about increased competition for the traditional exchanges that have long dominated on Wall Street.</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>The two tech giants are expected to square off against each other in the lucrative cloud computing market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>ENG-20260602-019</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>taper off</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>/ˈteɪpər ɒf/</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>(양, 강도 등이) 점점 줄어들다, 약해지다</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>Job openings in April surged to 7.6 million, the highest in nearly two years.</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>After a strong start, sales began to taper off towards the end of the quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>ENG-20260602-020</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>run up against</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>/rʌn ʌp əˈɡɛnst/</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>(문제, 반대 등에) 부딪히다</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>Some firms are putting pressure on staff to use AI, but have not thought through their AI rollout.</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>We might run up against some regulatory hurdles when launching the new product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>ENG-20260602-021</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>dwell on</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>/dwɛl ɒn/</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>(과거나 불행한 일에 대해) 곱씹다, 계속 생각하다</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>Ross: I'm dead and no one cares?</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>It's not healthy to dwell on past mistakes; you need to move forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>ENG-20260602-022</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>level with</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>/ˈlɛvəl wɪð/</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>~에게 솔직하게 말하다</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>Ross: I know this is a big surprise for you. It's a long story but the things you just said really made my day!</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>I need you to level with me. Is the project really on schedule?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>ENG-20260602-023</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>clear up</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>/klɪər ʌp/</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>(오해, 문제 등을) 해명하다, 해결하다</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>Instagram AI chatbot tricked by hackers to give access to others' accounts</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>There seems to be a misunderstanding; let me clear up the situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>ENG-20260602-024</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>spark controversy</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>/spɑːrk ˈkɒntrəˌvɜːrsi/</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>논란을 불러일으키다</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>The CFTC has sparked a potential revolution on Wall Street. Exchange stocks are dropping</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>The CEO's recent comments sparked controversy among employees and shareholders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>ENG-20260602-025</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>drive down costs</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>/draɪv daʊn kɒsts/</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>비용을 절감하다</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>Microsoft unveils new AI models to lessen reliance on OpenAI and lower costs for developers</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>Implementing new technologies helped the company drive down production costs significantly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>ENG-20260602-026</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>brace for impact</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>/breɪs fɔːr ˈɪmpækt/</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>(충격, 어려운 상황에) 대비하다</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>investors prepare for what will be one of the busiest periods for equity issuance in years.</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>The company is bracing for impact as new regulations are expected to hit the industry hard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>ENG-20260602-027</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>level an accusation</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>/ˈlɛvəl ən ˌækjʊˈzeɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>혐의를 제기하다, 고발하다</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>Pulte has alleged wrongdoing related to mortgages against Trump's foes</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>It's easy to level an accusation, but proving it is another matter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>ENG-20260602-028</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>breathe a sigh of relief</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>/briːð ə saɪ ɒv rɪˈliːf/</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>안도의 한숨을 쉬다</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>Why BlackRock's Rick Rieder feels 'a bit more relaxed' about AI bull market than dotcom era</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>When the exam results were finally posted, I breathed a sigh of relief that I had passed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>ENG-20260602-029</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>hone skills</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>/hoʊn skɪlz/</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>기술을 연마하다</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>having a job as a teenager can build transferable skills for young workers, according to experts.</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>He spent years honing his coding skills to become a top software engineer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>ENG-20260602-030</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>slap a fine on</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>/slæp ə faɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>~에게 벌금을 부과하다</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>Water firm fined £1.8m over parasite outbreak</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>The city council decided to slap a hefty fine on the company for environmental violations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>ENG-20260602-031</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>launch an investigation</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>/lɔːntʃ ən ɪnˌvɛstɪˈɡeɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>조사를 시작하다</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>student loan inquiry begins / MPs will hear the concerns of graduates</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>The police launched an investigation into the cause of the mysterious disappearance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>ENG-20260602-032</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>address concerns</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>/əˈdrɛs kənˈsɜːrnz/</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>우려를 다루다, 해결하다</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>MPs will hear the concerns of graduates about the size of their student debts, and the interest rates.</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>The manager held a meeting to address the team's concerns about the new workload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>ENG-20260602-033</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>soar in value</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>/sɔːr ɪn ˈvæljuː/</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>가치가 급등하다</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>AI giant Anthropic plans to sell shares in US as valuation nears $1tn</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>Property in the city center has continued to soar in value over the past decade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>ENG-20260602-034</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>botch a rollout</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>/bɒtʃ ə ˈraʊlˌaʊt/</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>(제품/서비스 출시 등을) 망치다, 엉망으로 하다</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>How 'confused' AI rollout hurts firms and baffles staff</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>The company completely botched the rollout of its new software, leading to widespread user frustration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>ENG-20260602-035</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>pay tribute to</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>/peɪ ˈtrɪbjuːt tuː/</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>~에게 경의를 표하다, 추모하다</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>Post Office scandal victim dedicates OBE to 'sub-postmasters we have lost'</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>The ceremony was held to pay tribute to the soldiers who lost their lives in the war.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>ENG-20260602-036</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>come to a standstill</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>/kʌm tuː ə ˈstændstɪl/</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>정지하다, 정체되다</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>London Tube strikes go ahead after talks fail</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>Traffic came to a complete standstill after the major accident on the highway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>ENG-20260602-037</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>rattle nerves</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>/ˈrætəl nɜːrvz/</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>신경을 곤두서게 하다, 불안하게 만들다</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>The thousands of "ghost kitchens" - online shops that don't actually exist - have spooked Chinese consumers.</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>The unexpected market fluctuations rattled investors' nerves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>ENG-20260602-038</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>take the blame</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>/teɪk ðə bleɪm/</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>(실패나 잘못에 대한) 책임을 지다</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Manny: Oh we blew it. I blame myself. / Monica: And I blame you too.</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>The CEO decided to take the blame for the company's financial losses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>ENG-20260602-039</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>make a difference</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>/meɪk ə ˈdɪfərəns/</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>영향을 미치다, 변화를 가져오다</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>Ross: I mean, I went to that school for 4 years, I didn't have an impact on anyone?</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>Even small donations can make a big difference in the lives of those in need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>ENG-20260602-040</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>hold weight</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>/hoʊld weɪt/</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>(의견, 주장이) 영향력이 있다, 중요하다</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Chandler: You had an impact on me, I mean, it's 15 years later and we're still best friends. Doesn't that count for something?</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>The expert's testimony didn't seem to hold much weight with the jury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>ENG-20260602-041</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>turn heads</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>/tɜːrn hɛdz/</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>(매력적이거나 눈에 띄어서) 시선을 사로잡다</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>Chandler: Wow! You look amazing!</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>Her stunning dress at the gala really turned heads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>ENG-20260602-042</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>have a thing for</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>/hæv ə θɪŋ fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>~에게 관심/애정이 있다, ~을 좋아하다</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>Ross: Did you hear that? Kori Weston had a crush on me!!</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>I think he has a thing for our new colleague; he always tries to talk to her.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>ENG-20260602-043</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>miss an opportunity</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>/mɪs ən ˌɒpərˈtuːnɪti/</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>기회를 놓치다</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>Kori: I thought so many times about calling him and asking him out. I guess I really missed my chance.</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Many companies regret missing the opportunity to invest in emerging technologies early on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>ENG-20260602-044</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>drive consensus</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>/draɪv kənˈsɛnsəs/</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>합의를 이끌어내다</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>London Tube strikes go ahead after talks fail / in a row over working hours</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Her main role as a leader is to drive consensus among the diverse team members.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>ENG-20260602-045</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>gauge interest</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>/ɡeɪdʒ ˈɪntrɪst/</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>관심도를 측정하다, 알아보다</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>AI giant Anthropic plans to sell shares in US as valuation nears $1tn / The AI company behind Claude is set to offer the public the chance to buy and sell shares in the firm later this year.</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>We sent out a survey to gauge interest in the potential new product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>ENG-20260602-046</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>mitigate risks</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>/ˈmɪtɪɡeɪt rɪsks/</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>위험을 완화하다</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>Investors are worried about increased competition for the traditional exchanges that have long dominated on Wall Street.</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>The project manager implemented several strategies to mitigate risks before launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>ENG-20260602-047</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>reach a consensus</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>/riːtʃ ə kənˈsɛnsəs/</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>합의에 도달하다</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>London Tube strikes go ahead after talks fail</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>After a long debate, the committee finally managed to reach a consensus on the new policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>ENG-20260602-048</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>table a motion</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>/ˈteɪbəl ə ˈmoʊʃən/</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>안건을 상정하다 (미국식: 논의를 위해 제안하다; 영국식: 논의를 연기하다)</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>House leader laid out Democrats' path to a majority next Congress and plans to rein in President Donald Trump.</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>The representative decided to table a motion to review the previous budget decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>ENG-20260602-049</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>vet a candidate</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>/vɛt ə ˈkændɪdeɪt/</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>후보자를 심사하다, 신원 조회를 하다</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>Trump names housing chief Bill Pulte acting intelligence director, replacing Tulsi Gabbard</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>All candidates for the senior position will be thoroughly vetted before interviews begin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>ENG-20260602-050</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>weigh pros and cons</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>/weɪ proʊz ænd kɒnz/</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>장단점을 비교 검토하다</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>Some firms are putting pressure on staff to use AI, but have not thought through their AI rollout.</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Before making such a big decision, it's crucial to weigh the pros and cons carefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>ENG-20260602-051</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>broker a deal</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>/ˈbroʊkər ə diːl/</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>거래를 중개하다, 성사시키다</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>Chinese firms have been vying to secure deals with big stars as they push to become global brands.</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>The seasoned negotiator was able to broker a deal that satisfied both parties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>ENG-20260602-052</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>command respect</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>/kəˈmænd rɪˈspɛkt/</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>존경을 받다</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>Ross: I mean, I went to that school for 4 years, I didn't have an impact on anyone?</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>His integrity and fairness allowed him to command respect from everyone in the organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>ENG-20260602-053</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>face a backlash</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>/feɪs ə ˈbæklæʃ/</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>강한 반발에 직면하다</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>How 'confused' AI rollout hurts firms and baffles staff</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>The new policy faced a strong backlash from consumers who felt it was unfair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>ENG-20260602-054</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>crack a market</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>/kræk ə ˈmɑːrkɪt/</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>새로운 시장을 뚫다, 시장 공략에 성공하다</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>Microsoft is announcing a series of generative AI models to try and crack a market controlled by OpenAI.</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>It is extremely difficult for small startups to crack the enterprise software market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>ENG-20260602-055</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>could not care less</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>/kʊd nɑːt ker les/</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>조금도 신경 쓰지 않다, 전혀 개의치 않다</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>I really don't care. I couldn't care less when asked about the prospect of Iran ending talks.</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Honestly, I couldn't care less about what they say behind my back as long as we deliver results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>ENG-20260602-056</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>lay out a path</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>/leɪ aʊt ə pæθ/</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>방향이나 계획을 명확히 제시하다</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>In conversation with CNBC's Emily Wilkins, the House leader laid out Democrats' path to a majority next Congress.</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>The strategic planning team needs to lay out a path for our global expansion over the next five years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>ENG-20260602-057</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>put pressure on</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>/pʊt ˈpreʃər ɑːn/</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>~에게 압박을 가하다, 다그치다</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>Some firms are putting pressure on staff to use AI, but have not thought through their AI rollout.</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>The board is putting pressure on the CEO to increase short-term profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>ENG-20260602-058</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>think through</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>/θɪŋk θruː/</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>충분히 생각하다, 다각도로 깊이 검토하다</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>Some firms are putting pressure on staff to use AI, but have not thought through their AI rollout.</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>We need to think through the long-term ethical implications of deploying this algorithm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>ENG-20260602-059</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>secure a deal</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>/sɪˈkjʊr ə diːl/</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>계약을 성사시키다, 딜을 확보하다</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>Chinese firms have been vying to secure deals with big stars as they push to become global brands.</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>Our sales executive managed to secure a multi-million dollar deal with the retail giant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>ENG-20260602-060</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>go after</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ˈæftər/</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>~를 규제하다, 단속하다, 추적하다</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>China goes after 'ghost kitchens' to rein in cut-throat food delivery apps.</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Regulatory bodies are planning to go after companies that violate environmental protection laws.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>ENG-20260602-061</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>keep away from</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>/kiːp əˈweɪ frʌm/</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>~에 가까이 가지 못하게 하다, 멀리하다</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>My friend Manny. I asked him to keep me away from you.</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>You should keep away from highly speculative assets during market volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>ENG-20260602-062</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>blow it</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>/bloʊ ɪt/</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>기회를 날려 버리다, 일을 망치다</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>Oh we blew it. I blame myself.</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>I had a perfect chance to pitch our idea to the lead investor, but I completely blew it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>ENG-20260602-063</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>touch someone's life</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>/tʌtʃ ˈsʌmwʌnz laɪf/</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>누군가의 삶에 깊은 감동이나 영향을 미치다</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>I don't remember him, but then again I touched so many lives.</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>The charity organization has touched thousands of children's lives across the country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>ENG-20260602-064</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>see someone</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>/siː ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>누군가와 사귀다, 연애 중이다</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>Yeah, I came because I heard Chandler's news. D'you know if he's seeing anyone?</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Are you still seeing that designer from the marketing agency?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>ENG-20260602-065</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>have an impact on</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>/hæv ən ˈɪmpækt ɑːn/</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>~에 영향을 주다, 효과를 내다</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>I mean, I went to that school for 4 years, I didn't have an impact on anyone?</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>The rising interest rates are starting to have a visible impact on consumer spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>ENG-20260602-066</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>ask someone out</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>/æsk ˈsʌmwʌn aʊt/</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>데이트를 신청하다</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>I thought so many times about calling him and asking him out.</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>He has been trying to find the right moment to ask her out all week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>ENG-20260602-067</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>make someone's day</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>/meɪk ˈsʌmwʌnz deɪ/</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>하루를 행복하게 만들다, 기분을 최고로 만들어 주다</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>It's a long story but the things you just said really made my day!</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Your kind feedback on my presentation really made my day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>ENG-20260602-068</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>have a crush on</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>/hæv ə krʌʃ ɑːn/</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>~에게 반하다, 남모르게 좋아하다</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>I can't believe I had a crush on you!</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>I used to have a huge crush on the lead programmer when I first joined the team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>ENG-20260602-069</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>stay in the game</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>/steɪ ɪn ðə ɡeɪm/</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>경쟁 대열에 계속 참여하다, 포기하지 않고 버티다</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>'I think you gotta stay in,' says the top BlackRock investing official.</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>Despite the market correction, we must keep investing to stay in the game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>ENG-20260602-070</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>vie for</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>/vaɪ fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>우위를 차지하기 위해 치열하게 경쟁하다</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Chinese firms have been vying to secure deals with big stars as they push to become global brands.</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Tech giants are actively vying for the most talented software engineers in Silicon Valley.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>ENG-20260602-071</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>shove out</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>/ʃʌv aʊt/</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>밖으로 밀쳐내다, 강제로 쫓아내다</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Ok Tommy, that's enough mourning for you! Here we go, bye bye!! (he shoves him out the door)</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>The minority shareholders were shoved out of the decision-making process during the restructuring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>ENG-20260602-072</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>press one's ear against</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>/pres wʌnz ɪr əˈɡenst/</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>~에 귀를 바짝 들이대다, 엿듣다</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>I'm sure he's pressing his ear up against it and listening intently.</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>The reporter pressed his ear against the conference room door to catch any gossip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>ENG-20260602-073</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>face cut-throat competition</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>/feɪs ˈkʌt θroʊt ˌkɑːmpəˈtɪʃn/</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>목을 베는 듯한 치열하고 살벌한 경쟁에 직면하다</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>China goes after 'ghost kitchens' to rein in cut-throat food delivery apps.</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>As local coffee shops face cut-throat competition from franchise chains, many are forced to close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>ENG-20260602-074</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>lessen reliance on</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>/ˈlesn rɪˈlaɪəns ɑːn/</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>~에 대한 의존도를 완화하다</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>Microsoft unveils new AI models to lessen reliance on OpenAI and lower costs for developers.</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>Diversifying our suppliers is the only way to lessen our reliance on a single partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>ENG-20260602-075</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>spark a revolution</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>/spɑːrk ə ˌrevəˈluːʃn/</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>대변혁을 촉발하다, 일대 혁신을 일으키다</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>The CFTC has sparked a potential revolution on Wall Street. Exchange stocks are dropping.</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>This green energy breakthrough has the potential to spark a revolution in manufacturing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>ENG-20260602-076</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>bound into</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>/baʊnd ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>기운차게 깡충깡충 뛰어 들어오다</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>Strange man: (he bounds into the house) I knew you'd be here!</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>The dog bounded into the room, wagging its tail with absolute joy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>ENG-20260602-077</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>be in a bad mood</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>/biː ɪn ə bæd muːd/</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>심사가 뒤틀리다, 기분이 몹시 상해 있다</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>Don't listen to him, he's in a really bad mood!</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>I would avoid talking to the boss right now; she is in a bad mood because of the sales drop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>ENG-20260602-078</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>slam the door</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>/slæm ðə dɔːr/</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>문을 쾅 닫아버리다</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>(she leaves and slams the door behind her)</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>He got so angry during the negotiation that he grabbed his files and slammed the door as he left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>ENG-20260602-079</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>allege wrongdoing</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>/əˈledʒ ˈrɔːŋˌduːɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>비위 또는 불법 행위를 제기하다</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>Pulte has alleged wrongdoing related to mortgages against Trump's foes.</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>The whistleblower stepped forward to allege systemic wrongdoing in corporate auditing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>ENG-20260602-080</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>build transferable skills</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>/bɪld trænsˈfɜːrəbl skɪlz/</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>(이직 등에 활용 가능한) 범용성 높은 기술을 연마하다</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>Babysitting may not be your ultimate career path, but having a job as a teenager can build transferable skills.</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>Volunteering helps you build transferable skills such as leadership and project coordination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>ENG-20260602-081</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>fall back on</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>/fɔːl bæk ɑːn/</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>(최후의 수단으로) ~에 기대다, 의지하다</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>If the rollout gets too confused, many traditional firms will fall back on legacy software models.</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>In times of financial crisis, we can always fall back on our emergency reserves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>ENG-20260602-082</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>drive a wedge between</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>/draɪv ə wedʒ bɪˈtwiːn/</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>~ 사이를 갈라놓다, 반목하게 하다</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>The continuous leaks regarding the post office scandal have driven a wedge between executives.</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>Disagreements over resource allocation can easily drive a wedge between the two sister departments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>ENG-20260602-083</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>keep someone in the dark</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>/kiːp ˈsʌmwʌn ɪn ðə dɑːrk/</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>사정을 알리지 않고 철저히 비밀로 유지하다</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>Sub-postmasters felt the Post Office was deliberately keeping them in the dark about software errors.</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>I hate when management keeps us in the dark about impending organizational changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>ENG-20260602-084</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>stand one's ground</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>/stænd wʌnz ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>압력에 굴하지 않고 주장을 고수하다</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>Members of the RMT union are standing their ground in a row over working hours.</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>Even under intense cross-examination, the witness firmly stood her ground.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>ENG-20260602-085</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>lose face</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>/luːz feɪs/</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>체면을 깎아 먹다, 면을 구기다</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>Neither of the giant brands wanted to lose face by admitting their split was due to financial disputes.</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>Apologizing publicly was hard for the director, but she had to do it to avoid losing face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>ENG-20260602-086</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>back down</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>/bæk daʊn/</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>자신의 주장이나 계획에서 양보하고 한발 물러서다</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>The union refused to back down, leading to the cancellation of several train routes.</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>Faced with fierce public backlash, the government had to back down on the tax proposal.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1088"/>
+  <dimension ref="A1:I1185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51552,6 +51552,4565 @@
         </is>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>ENG-20260603-001</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>pull something off the market</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>/pʊl ˈsʌmˌθɪŋ ɔf ðə ˈmɑːrkɪt/</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>시장에서 (판매용으로 내놓았던) 물건을 회수하다, 철회하다</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>Sellers are pulling homes off the market at the fastest pace since 2020.</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Due to low demand, the company decided to pull their new product line off the market for a redesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>ENG-20260603-002</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>face a key test</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>/feɪs ə kiː tɛst/</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>중요한 시험대에 오르다, 중요한 고비를 맞다</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>Historic stock rally faces key test.</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>The new government policy will face a key test in its first few months of implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>ENG-20260603-003</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>change one's mind</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>/ʧeɪndʒ wʌnz maɪnd/</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>생각을 바꾸다, 변심하다</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>Trump says Iran agreed to not have nuclear weapons, but 'they can change their mind'.</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>I was going to quit my job, but I changed my mind after a long talk with my boss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>ENG-20260603-004</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>wide-ranging interview</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>/waɪdˈreɪnʤɪŋ ˈɪntərˌvjuː/</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>광범위한 주제를 다루는 인터뷰</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>The president was speaking to the New York Post's 'Pod Force One' podcast in a wide-ranging interview.</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>The CEO gave a wide-ranging interview covering everything from company strategy to personal anecdotes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>ENG-20260603-005</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>strip something from something</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>/strɪp ˈsʌmˌθɪŋ frəm ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>어떤 것에서 특정 부분을 제거하다, 박탈하다</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>Senate GOP strips up to $1B for Trump ballroom security from immigration enforcement bill.</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>The committee decided to strip controversial clauses from the proposed legislation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>ENG-20260603-006</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>risk derailing something</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>/rɪsk dɪˈreɪlɪŋ ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>무언가를 망치거나 틀어지게 할 위험을 감수하다</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>GOP leaders reportedly privately concluded that the funding proposal risked derailing the broader immigration bill.</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>His impulsive decision risked derailing the entire project right before its deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>ENG-20260603-007</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>hit new lows/highs</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>/hɪt nuː loʊz/haɪz/</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>최저/최고치를 기록하다</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>Bitcoin's high-conviction holders are turning into sellers as the crypto's price hits new lows.</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>The company's stock price hit new lows after the disappointing earnings report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>ENG-20260603-008</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>yield dividends</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>/jiːld ˈdɪvɪˌdɛndz/</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>이익을 낳다, 배당금을 발생시키다</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>A classic strategy that could yield big dividends.</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>Investing in employee training can yield significant dividends in productivity and loyalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>ENG-20260603-009</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>brick-and-mortar</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>/brɪk ənd ˈmɔːrtər/</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>오프라인 (상점, 사업); 전통적인 (물리적) 사업 형태</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>Packaging Corp of America (PKG) is an old-school, brick-and-mortar industrial business.</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>Many brick-and-mortar stores are struggling to compete with online retailers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>ENG-20260603-010</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>take back power/control</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>/teɪk bæk ˈpaʊər/kənˈtroʊl/</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>권력/통제권을 되찾다</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>Democrats look to take back power in Congress.</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>The opposition party aims to take back power in the next general election.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>ENG-20260603-011</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>press someone over something</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>/prɛs ˈsʌmˌwʌn ˈoʊvər ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>어떤 문제에 대해 누군가를 강하게 추궁하다/압박하다</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>Democrats pressed the Treasury chief over whether other taxpayers affected by the leak would receive similar treatment.</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>Reporters pressed the spokesperson over the sudden change in company policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>ENG-20260603-012</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>strike down a law/ruling</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>/straɪk daʊn ə lɔː/ˈruːlɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>법률/판결을 무효화하다, 폐지하다</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>It comes after the US Supreme Court struck down many of US President Donald Trump's previous duties.</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>The appeals court decided to strike down the lower court's controversial ruling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>ENG-20260603-013</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>in the running for something</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>/ɪn ðə ˈrʌnɪŋ fɔr ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>무언가를 얻기 위한 경쟁에 참여하고 있다</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>The 18 creatures in the running to be on the new banknotes.</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>She's definitely in the running for the promotion, given her impressive sales record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>ENG-20260603-014</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>go towards something</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>/ɡoʊ təˈwɔːrdz ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>어떤 용도로 사용되다, ~에 보태지다</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>The government's contribution is going towards upgrading local infrastructure and transport links.</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>A significant portion of the fundraising will go towards supporting local charities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>ENG-20260603-015</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>put pressure on someone</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>/pʊt ˈprɛʃər ɑn ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>누군가에게 압력을 가하다</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>Some firms are putting pressure on staff to use AI, but have not thought through their AI rollout.</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>The community group is putting pressure on the city council to address the noise pollution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>ENG-20260603-016</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>think something through</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>/θɪŋk ˈsʌmˌθɪŋ θruː/</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>무언가를 철저히 생각하다, 심사숙고하다</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>Some firms are putting pressure on staff to use AI, but have not thought through their AI rollout.</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>Before making such a big decision, you really need to think it through carefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>ENG-20260603-017</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>on behalf of someone</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>/ɑn bɪˈhæf əv ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>누구를 대표하여, 누구를 대신하여</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>Betty Brown says she is accepting the honour on behalf of all the victims of the scandal.</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>I'd like to thank you all on behalf of my colleagues for your hard work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>ENG-20260603-018</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>draw someone out</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>/drɔː ˈsʌmˌwʌn aʊt/</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>누군가가 말하도록 유도하다, 속마음을 털어놓게 하다</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>I think you have to draw him out. And then- when you do- he's a preppy animal.</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>It took some effort, but I managed to draw him out about his feelings on the matter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>ENG-20260603-019</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>go on about something</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ɑn əˈbaʊt ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>무언가에 대해 계속 지루하게 이야기하다</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>Ross is still going on about his first night with Carol.</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>He kept going on about his vacation for hours, and I just wanted him to stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>ENG-20260603-020</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>What's the big deal?</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>/wʌts ðə bɪɡ diːl/</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>뭐가 그렇게 대수야? 뭐가 그렇게 중요해?</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>What is the big deal about today? So you slept with her for the first time, so what?</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>She got upset because I was five minutes late, but what's the big deal?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>ENG-20260603-021</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>a whole bunch of something</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>/ə hoʊl bʌnʧ əv ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>많은 양의 무언가</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>There was a whole bunch of stuff we could've done tonight!</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>We have a whole bunch of ideas for the upcoming marketing campaign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>ENG-20260603-022</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>break up (with someone)</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>/breɪk ʌp (wɪð ˈsʌmˌwʌn)/</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>연인 관계를 끝내다, 헤어지다</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>You'd already broken up.</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>They decided to break up after realizing they wanted different things in life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>ENG-20260603-023</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>big girl</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>/bɪɡ ɡɜrl/</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>다 자란 여성 (때로는 비꼬는 투로 '덩치 큰 여자' 또는 '혼자 잘 하는 여자'를 의미)</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>(To Phoebe) She was a big girl.</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>Come on, be a big girl and stop crying over something so trivial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>ENG-20260603-024</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>pee in one's pants</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>/piː ɪn wʌnz pænts/</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>바지에 오줌을 싸다 (놀라거나 웃겨서)</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>Well, at least 'big girls' don't pee in their pants in seventh grade!</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>The movie was so funny, I almost peed in my pants laughing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>ENG-20260603-025</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>drop the towel</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>/drɑp ðə ˈtaʊəl/</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>수건을 떨어뜨리다 (종종 알몸을 드러내라는 농담조의 표현)</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>Oh, George, baby, drop the towel!</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>The crowd chanted for the performer to drop the towel, but he just laughed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>ENG-20260603-026</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>all things considered</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>/ɔl θɪŋz kənˈsɪdərd/</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>모든 것을 고려하면, 전반적으로 볼 때</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>All things considered, you had fun tonight.</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>All things considered, the event was a huge success despite the bad weather.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>ENG-20260603-027</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Finders keepers, losers weepers</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>/ˈfaɪndərz ˈkiːpərz ˈluːzərz ˈwiːpərz/</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>찾는 사람이 임자, 잃는 사람은 울어야지 (찾은 물건은 내 것이라는 아이들의 표현)</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>I found it. Finders keepers, losers weepers.</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>The kid wouldn't give back the toy, saying, 'Finders keepers, losers weepers!'</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>ENG-20260603-028</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>I'm rubber, you're glue</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>/aɪm ˈrʌbər jʊər ɡluː/</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>나는 고무고 너는 풀이야 (네가 하는 욕은 나에게 튕겨지고 너에게 도로 붙는다는 아이들 표현)</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>Oh yeah? Well, I'm rubber, you're glue, whatever—</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>When the bully called him names, the boy just retorted, 'I'm rubber, you're glue!'</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>ENG-20260603-029</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>give something back</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmˌθɪŋ bæk/</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>무언가를 돌려주다</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>Listen, uh- gimme back my puck.</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>Please give me back my book when you're finished reading it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>ENG-20260603-030</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>knock someone out</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>/nɑk ˈsʌmˌwʌn aʊt/</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>누군가를 기절시키다, KO시키다</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>It files out of his grasp and knocks out the receptionist.</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>The boxer delivered a powerful punch that knocked his opponent out in the first round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>ENG-20260603-031</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>knock on the door</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>/nɑk ɑn ðə dɔːr/</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>문을 두드리다</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>There's a knock on the door.</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>I heard a knock on the door, but when I opened it, no one was there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>ENG-20260603-032</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>hand something back</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>/hænd ˈsʌmˌθɪŋ bæk/</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>무언가를 돌려주다, 건네주다</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>Chandler opens it, and silently hands back the cushion.</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>The librarian asked me to hand back the book after I finished reading it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>ENG-20260603-033</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>pencil someone/something in</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>/ˈpɛnsəl ˈsʌmˌwʌn/ˈsʌmˌθɪŋ ɪn/</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>임시로 ~를 예약하다/일정을 잡다</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>Can we pencil in a meeting for next Tuesday, and I'll confirm the details later?</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>Let's pencil in a quick call for Friday afternoon to discuss the progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>ENG-20260603-034</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>iron out the kinks</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>/ˈaɪərn aʊt ðə kɪŋks/</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>문제점들을 해결하다, 매끄럽게 처리하다</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>We're still trying to iron out the kinks in the new software before its official launch.</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>The team needs another week to iron out the kinks in the project plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>ENG-20260603-035</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>circle back (to someone/something)</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>/ˈsɜrkəl bæk (tə ˈsʌmˌwʌn/ˈsʌmˌθɪŋ)/</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>나중에 다시 논의하다/연락하다</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>I'll need to check with the team, but I'll circle back to you by the end of the day.</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>Let's discuss this further in our next meeting; I'll circle back to this point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>ENG-20260603-036</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>touch base (with someone)</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>/tʌʧ beɪs (wɪð ˈsʌmˌwʌn)/</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>누군가와 잠시 연락하여 소식을 확인하다</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>I'll quickly touch base with our sales team to get an update on the client's feedback.</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>Let's touch base next week to see how the new strategy is working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>ENG-20260603-037</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>bear the brunt of something</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>/bɛər ðə brʌnt əv ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>무언가의 가장 심한 부분/타격을 고스란히 받다</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>Small businesses often bear the brunt of new tariffs and economic sanctions.</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>The coastal communities will bear the brunt of the hurricane's full force.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>ENG-20260603-038</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>smooth things over</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>/smuːð θɪŋz ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>어색하거나 불편한 상황을 완화하다, 관계를 원만하게 하다</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>After the argument, he tried to smooth things over by apologizing profusely.</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>We need to smooth things over with the client after the delivery delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>ENG-20260603-039</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>put a stop to something</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>/pʊt ə stɑp tə ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>무언가를 멈추게 하다, 끝내다</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>The government needs to put a stop to these unfair trade practices.</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>Management has decided to put a stop to unnecessary overtime work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>ENG-20260603-040</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>green light something</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>/ɡriːn laɪt ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>무언가를 승인하다, 허가하다</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>The city council gave the green light to the new park development project.</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>After months of review, the board finally green-lighted the merger proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>ENG-20260603-041</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>get the hang of something</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>/ɡɛt ðə hæŋ əv ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>무언가를 하는 요령을 터득하다, 익숙해지다</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>It took me a while, but I'm finally starting to get the hang of using this new software.</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>Don't worry if it's difficult at first; you'll get the hang of it soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>ENG-20260603-042</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>hold one's own</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>/hoʊld wʌnz oʊn/</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>자기 몫을 다하다, 어려움 속에서도 잘 해내다</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>Despite strong competition, the veteran company continued to hold its own in the market.</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>He's new to the team, but he can definitely hold his own in a debate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>ENG-20260603-043</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>pick up steam</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>/pɪk ʌp stiːm/</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>속도가 붙다, 탄력을 받다</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>The historic stock rally began to pick up steam after strong earnings reports from tech companies.</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>Sales for our new product are starting to pick up steam after the advertising campaign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>ENG-20260603-044</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>run the numbers</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>/rʌn ðə ˈnʌmbərz/</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>수치를 계산하다, 예산을 분석하다</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>Before we make a final decision on the IPO price, we need to run the numbers again.</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>Let's run the numbers to see if we can afford the new equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>ENG-20260603-045</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>go south</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>/ɡoʊ saʊθ/</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>상황이 나빠지다, 잘못되다</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>The whole business deal went south when the main investor pulled out at the last minute.</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>Our vacation plans went south when the airline canceled our flight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>ENG-20260603-046</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>bring something to the table</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>/brɪŋ ˈsʌmˌθɪŋ tə ðə ˈteɪbəl/</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>논의나 협상에 유용한 자질/기술/정보를 제공하다</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>The new hire brings a wealth of experience to the table, which will be invaluable for the team.</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>What unique skills or ideas can you bring to the table for this project?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>ENG-20260603-047</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>be at stake</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>/bi æt steɪk/</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>위태로운 상황에 처하다, 달려 있다</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>The future of the company is at stake with this critical investment decision.</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>Thousands of jobs are at stake if the factory closes down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>ENG-20260603-048</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>let someone down</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>/lɛt ˈsʌmˌwʌn daʊn/</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>누군가를 실망시키다</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>I really hope I don't let my parents down with my exam results.</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>I promised to help him, and I don't want to let him down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>ENG-20260603-049</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>have a crush on someone</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>/hæv ə krʌʃ ɑn ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>누군가를 짝사랑하다</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>Rachel just admitted she had a crush on George after seeing him from the balcony.</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>When I was in high school, I had a huge crush on the captain of the football team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>ENG-20260603-050</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>give someone the cold shoulder</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmˌwʌn ðə koʊld ˈʃoʊldər/</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>누군가를 쌀쌀맞게 대하다, 무시하다</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>After their argument, Monica gave Rachel the cold shoulder for a whole day.</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>I tried to talk to her, but she just gave me the cold shoulder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>ENG-20260603-051</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>have a bone to pick with someone</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>/hæv ə boʊn tə pɪk wɪð ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>누군가에게 따질/불평할 것이 있다</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>I have a bone to pick with you about what you said yesterday.</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>I have a bone to pick with the company about their faulty product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>ENG-20260603-052</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>bury the hatchet</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>/ˈbɛri ðə ˈhæʧɪt/</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>화해하다, 싸움을 끝내다</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>After years of feuding, the two families finally decided to bury the hatchet.</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>It's time for us to bury the hatchet and move past our disagreements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>ENG-20260603-053</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>take it easy</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>/teɪk ɪt ˈiːzi/</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>쉬다, 진정하다, 가볍게 생각하다</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>You've been working hard all week; you should take it easy this weekend.</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>After a long day, all I want to do is go home and take it easy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>ENG-20260603-054</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>back someone up</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>/bæk ˈsʌmˌwʌn ʌp/</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>누군가를 지지하다, 옹호하다, 지원하다</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>Chandler looked at Ross and said, 'You gotta do it, man,' effectively backing him up.</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>Don't worry, I'll back you up if the boss asks about the delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>ENG-20260603-055</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>crack a joke</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>/kræk ə ʤoʊk/</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>농담을 하다</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>Joey often tried to crack a joke to lighten the mood in difficult situations.</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>The speaker cracked a joke to break the ice at the beginning of his presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>ENG-20260603-056</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>lend a hand</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>/lɛnd ə hænd/</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>도움을 주다</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>Whenever someone needed help moving, Joey was always there to lend a hand.</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Could you lend a hand with these heavy boxes?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>ENG-20260603-057</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>make up one's mind</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>/meɪk ʌp wʌnz maɪnd/</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>결정하다, 마음을 정하다</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>It took her a long time to make up her mind about which college to attend.</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>Have you made up your mind about where you want to go for dinner?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>ENG-20260603-058</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>call someone out</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>/kɔl ˈsʌmˌwʌn aʊt/</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>누군가의 잘못을 지적하다, 비판하다</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>Chandler liked to call out Ross for being overly dramatic about his personal life.</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>He decided to call out his colleague for taking credit for his work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>ENG-20260603-059</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>get on someone's nerves</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>/ɡɛt ɑn ˈsʌmˌwʌnz nɜrvz/</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>누군가를 짜증 나게 하다, 신경을 거슬리게 하다</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>Ross's constant complaining about Carol was starting to get on Chandler's nerves.</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>His habit of tapping his pen loudly really gets on my nerves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>ENG-20260603-060</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>hit it off</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>/hɪt ɪt ɔf/</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>죽이 잘 맞다, 금방 친해지다</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>When they first met, they hit it off immediately and talked for hours.</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>I introduced my two friends, and they really hit it off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>ENG-20260603-061</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>look out for someone</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>/lʊk aʊt fɔr ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>누군가를 돌보다, 보호하다</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>As an older brother, he always tried to look out for his younger sister.</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>It's important to have friends who will always look out for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>ENG-20260603-062</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>shake something off</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>/ʃeɪk ˈsʌmˌθɪŋ ɔf/</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>무언가에서 벗어나다, 털어내다 (불쾌한 감정, 병 등)</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>She tried to shake off the feeling of disappointment after losing the competition.</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>It took him a few days to shake off the cold he caught last week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>ENG-20260603-063</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>be over the moon</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>/bi ˈoʊvər ðə muːn/</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>매우 기뻐하다, 너무 행복하다</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>She was over the moon when she found out she got accepted into her dream university.</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>My parents were over the moon when I told them I was getting married.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>ENG-20260603-064</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>give it a shot</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>/ɡɪv ɪt ə ʃɑt/</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>시도해 보다, 한번 해보다</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>I'm not sure if I can do it, but I'm willing to give it a shot.</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>You might not succeed, but it's worth giving it a shot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>ENG-20260603-065</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>save for a rainy day</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>/seɪv fɔr ə ˈreɪni deɪ/</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>만일의 경우에 대비하여 저축하다</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>It's always wise to save some money for a rainy day.</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>I'm putting some money aside every month to save for a rainy day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>ENG-20260603-066</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>get someone's drift</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmˌwʌnz drɪft/</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>누군가의 요점/의도를 이해하다</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>I think I get your drift; you want me to finish this by tomorrow.</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Are you saying you're unhappy? I think I get your drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>ENG-20260603-067</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>hit the road</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>/hɪt ðə roʊd/</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>출발하다, 떠나다</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>It's getting late; we should hit the road if we want to get home before dark.</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>We packed our bags and hit the road early in the morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>ENG-20260603-068</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>target a price/valuation</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>/ˈtɑːrɡɪt ə praɪs/ /ˌvæljuˈeɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>특정 가격이나 가치를 목표로 하다</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>SpaceX targets fixed $135 IPO roadshow price at $1.75 trillion valuation, source says</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>The company plans to target a competitive price for its new product to attract more customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>ENG-20260603-069</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>slam someone</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>/slæm ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>~을 맹렬히 비난하다</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>GOP Sen. Tillis slams Trump intelligence pick Pulte: 'Don't think he has a prayer'</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>The CEO slammed his competitors in the press conference, calling their products inferior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>ENG-20260603-070</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>not have a prayer</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>/nɑːt hæv ə prɛər/</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>가망이 전혀 없다 (특히 성공이나 살아남을 가망)</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>GOP Sen. Tillis slams Trump intelligence pick Pulte: 'Don't think he has a prayer'</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Given the overwhelming evidence, the defense attorney knew his client didn't have a prayer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>ENG-20260603-071</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>be widely viewed as</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>/bi ˈwaɪdli vjuːd æz/</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>~로 널리 간주되다/여겨지다</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>Pulte is widely viewed as a Trump loyalist who has targeted the president's political foes during his tenure leading the housing regulatory agency.</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>The new policy is widely viewed as a positive step towards economic recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>ENG-20260603-072</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>report earnings</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>/rɪˈpɔːrt ˈɜːrnɪŋz/</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>실적을 발표하다</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>Two key tech companies reporting earnings after the bell could determine the next move higher or lower.</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Investors are eagerly waiting for the company to report earnings next quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>ENG-20260603-073</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>after the bell</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>/ˈæftər ðə bɛl/</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>(주식시장이) 마감된 후에</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>Two key tech companies reporting earnings after the bell could determine the next move higher or lower.</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Many companies release their sensitive financial news after the bell to minimize market volatility during trading hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>ENG-20260603-074</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>determine the next move</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>/dɪˈtɜːrmɪn ðə nɛkst muːv/</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>다음 행보를 결정하다</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>Two key tech companies reporting earnings after the bell could determine the next move higher or lower.</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>The board meeting will determine the next move for the struggling startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>ENG-20260603-075</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>turn into</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>/tɜːrn ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>~으로 변하다, ~이 되다</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>Bitcoin's high-conviction holders are turning into sellers as the crypto's price hits new lows</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>What started as a small hobby quickly turned into a profitable business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>ENG-20260603-076</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>old-school</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>/ˈoʊld skuːl/</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>구식의, 전통적인 방식의</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>Packaging Corp of America (PKG) is an old-school, brick-and-mortar industrial business.</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>He's an old-school manager who believes in face-to-face meetings rather than emails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>ENG-20260603-077</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>shape a path</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>/ʃeɪp ə pæθ/</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>(미래의) 방향/경로를 형성하다</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>Josh Turek wins Iowa Democratic Senate primary that could shape Democrats' path to Senate majority</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>Early education plays a crucial role in shaping a child's path to success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>ENG-20260603-078</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>perform duties</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>/pərˈfɔːrm ˈduːtiz/</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>직무를 수행하다</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>Bessent says he is performing IRS commissioner duties amid Trump tax settlement scrutiny</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>As a doctor, she has to perform her duties with utmost care and professionalism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>ENG-20260603-079</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>receive treatment</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>/rɪˈsiːv ˈtriːtmənt/</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>(특정 방식으로) 대우/취급을 받다</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>Democrats pressed the Treasury chief over whether other taxpayers affected by the leak that included Trump's tax returns would receive similar treatment.</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>All customers should receive fair treatment, regardless of their purchase history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>ENG-20260603-080</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>announce tariffs</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>/əˈnaʊns ˈtærɪfs/</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>관세를 발표하다</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>US announces new tariffs over forced labour concerns</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>The government decided to announce tariffs on imported steel to protect domestic industries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>ENG-20260603-081</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>ask the public</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>/æsk ðə ˈpʌblɪk/</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>대중에게 묻다/의견을 구하다</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>The Bank of England is asking the public which animals should appear on future banknotes.</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>The city council decided to ask the public for their input on the new park design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>ENG-20260603-082</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>pledge an amount</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>/plɛdʒ ən əˈmaʊnt/</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>(돈 등을) 약속/서약하다</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>Universal park officially named as government pledges £1.3bn</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>Many countries pledged significant amounts of aid after the natural disaster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>ENG-20260603-083</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>upgrade infrastructure</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>/ˈʌpɡreɪd ˈɪnfrəˌstrʌktʃər/</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>인프라를 개선/업그레이드하다</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>The government's contribution is going towards upgrading local infrastructure and transport links.</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>The city council plans to upgrade the infrastructure to support the growing population.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>ENG-20260603-084</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>have issues with something</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>/hæv ˈɪʃuːz wɪð ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>~에 문제가 있다</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>We're aware some customers are having issues with our app and online banking.</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>I've been having issues with my internet connection all morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>ENG-20260603-085</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>baffle staff</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>/ˈbæfl stæf/</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>직원들을 당황/혼란스럽게 하다</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>How 'confused' AI rollout hurts firms and baffles staff</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>The sudden change in company policy baffled even the most experienced employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>ENG-20260603-086</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>be aimed at someone/something</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>/bi eɪmd æt ˈsʌmˌwʌn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>~을 목표로 하다, ~을 대상으로 하다</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>Microsoft testing wearable AI gadget aimed at office workers</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>This new marketing campaign is specifically aimed at young adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>ENG-20260603-087</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>be in a stronger position</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>/bi ɪn ə ˈstrɔːŋər pəˈzɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>더 유리한 입장에 있다</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>The Competition and Markets Authority says it would put publishers "in a stronger position to negotiate content deals with Google".</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>After acquiring the patent, the company was in a stronger position to compete in the market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>ENG-20260603-088</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>negotiate deals</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>/nɪˈɡoʊʃieɪt diːlz/</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>거래를 협상하다</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>it would put publishers "in a stronger position to negotiate content deals with Google"</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>The sales team is working hard to negotiate deals with potential clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>ENG-20260603-089</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>accept an honour</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>/əkˈsɛpt ən ˈɒnər/</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>영예를 받다, 훈장을 수여받다</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>Betty Brown says she is accepting the honour on behalf of all the victims of the scandal.</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>She felt truly humbled to accept an honour from the Queen for her community work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>ENG-20260603-090</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>be fined over something</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>/bi faɪnd ˈoʊvər ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>~에 대해 벌금을 부과받다</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>Water firm fined £1.8m over parasite outbreak</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>The company was fined over environmental violations by the regulatory agency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>ENG-20260603-091</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>come through</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>/kʌm θruː/</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>(빛, 소리 등이) ~을 뚫고 들어오다</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>I remember the moonlight coming through the window- and her face had the most incredible glow.</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>A faint light started to come through the thick clouds, signaling the end of the storm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>ENG-20260603-092</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>have a glow</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>/hæv ə ɡloʊ/</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>(얼굴, 물체 등이) 빛을 띠다, 윤이 나다</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>her face had the most incredible glow.</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>After a long walk in the cold, her cheeks had a healthy glow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>ENG-20260603-093</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>leave someone (for another)</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>/liːv ˈsʌmˌwʌn (fər əˈnʌðər)/</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>(애인/배우자가) 다른 사람 때문에 ~을 떠나다</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>That she left you? That she likes women? That she left you for another woman that likes women?</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>He was devastated when his girlfriend left him for his best friend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>ENG-20260603-094</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>be in a coma</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>/bi ɪn ə ˈkoʊmə/</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>혼수 상태에 있다</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>I think there's a man on the twelfth floor in a coma that didn't quite hear you...</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>After the accident, the patient was in a coma for several days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>ENG-20260603-095</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>mumble the last part</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>/ˈmʌmbl ðə læst pɑːrt/</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>마지막 부분을 웅얼거리다</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>My first time with Carol was... (He mumbles the last part)</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>He was so nervous during his presentation that he mumbled the last part of his speech.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>ENG-20260603-096</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>get one</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>/ɡɛt wʌn/</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>(농담, 이야기 등을) 하나 생각해내다</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>Okay. Okay, I got one.</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>After a moment of thought, she said, 'I got one! Let me tell you about my crazy trip.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>ENG-20260603-097</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>leave something in one's locker</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>/liːv ˈsʌmθɪŋ ɪn wʌnz ˈlɑːkər/</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>~의 사물함에 무언가를 남겨두다</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>The valentine Tommy Rollerson left in your locker was really from me.</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>I found a note that someone left in my locker this morning.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1185"/>
+  <dimension ref="A1:I1275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56111,6 +56111,4236 @@
         </is>
       </c>
     </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>ENG-20260604-001</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>cap withdrawals</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>/kæp wɪðˈdrɔːəlz/</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>인출을 제한하다, 인출 한도를 설정하다</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>Blackstone capped withdrawals from its $79 billion BCRED fund after redemption requests rose, adding to private market liquidity concerns.</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Due to unforeseen market volatility, the bank had to cap withdrawals from certain investment accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>ENG-20260604-002</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>add to concerns</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>/æd tuː kənˈsɜːrnz/</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>~에 대한 우려를 증폭시키다</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>Blackstone capped withdrawals, adding to private market liquidity concerns.</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>The recent data breach only added to concerns about the company's cybersecurity measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>ENG-20260604-003</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>rear its ugly head</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>/rɪr ɪts ˈʌɡli hɛd/</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>골칫거리가 다시 나타나다, 문제가 재발하다</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>Private asset fears reemerge in the market, as if an old problem had decided to rear its ugly head again.</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Just when we thought the project was running smoothly, budget issues started to rear their ugly head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>ENG-20260604-004</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>have ramifications on</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>/hæv ræmɪfɪˈkeɪʃənz ɑn/</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>~에 광범위한 영향을 미치다, 파급 효과를 주다</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>Long-term unemployment can have ramifications on financial, emotional and family health.</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>The new policy is expected to have significant ramifications on the entire industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>ENG-20260604-005</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>spread like wildfire</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>/sprɛd laɪk ˈwaɪldˌfaɪər/</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>(소문·질병 등이) 들불처럼 퍼지다, 빠르게 확산되다</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>Highly contagious diseases can spread quickly through large, fast-moving crowds, like a rumor spreading like wildfire.</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>News of the unexpected merger spread like wildfire throughout the company before the official announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>ENG-20260604-006</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>spot potential winners</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>/spɑːt pəˈtɛnʃəl ˈwɪnərz/</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>잠재적인 성공 후보를 찾아내다</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>Options volume is surging for Zoetis as traders look for potential stock market winners in light of a screwworm case.</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>Experienced investors know how to spot potential winners in emerging markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>ENG-20260604-007</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>speculate on</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>/ˈspɛkjəˌleɪt ɑn/</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>~에 대해 투기하다, 예측하다</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>Pre-IPO perps give traders the ability to speculate on the value of a private company without owning shares.</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Many analysts continue to speculate on the future direction of interest rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>ENG-20260604-008</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>plead guilty</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>/pliːd ˈɡɪlti/</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>유죄를 인정하다, 죄를 자백하다</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>Ex-Trump advisor John Bolton agrees to plead guilty to retaining classified information.</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Facing overwhelming evidence, the defendant decided to plead guilty to the charges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>ENG-20260604-009</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>retain classified information</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>/rɪˈteɪn ˈklæsɪfaɪd ɪnfərˈmeɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>기밀 정보를 보유하다</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>John Bolton agrees to plead guilty to retaining classified information.</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Former intelligence officials are legally forbidden to retain classified information after leaving their posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>ENG-20260604-010</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>be targeted for</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>/bi ˈtɑːrɡɪtɪd fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>~을 이유로 표적이 되다</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>John Bolton said he was innocent and that he was being targeted because of his public opposition to President Trump.</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>The activist group claimed they were being targeted for their outspoken criticism of the government.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>ENG-20260604-011</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>secure funding</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>/sɪˈkjʊər ˈfʌndɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>자금을 확보하다</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>Database startup Supabase announced a $500 million funding round, effectively securing funding for its next phase of growth.</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Many startups struggle to secure funding in the current economic climate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>ENG-20260604-012</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>value at</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>/ˈvæljuː æt/</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>~로 가치를 평가하다</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>Supabase announced a $500 million funding round that values the company at $10.5 billion, including the fresh capital.</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>The independent appraisal firm valued the property at a much higher price than anticipated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>ENG-20260604-013</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>be poised to</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>/bi pɔɪzd tuː/</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>막 ~하려고 하다, ~할 준비가 되어 있다</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>Elon Musk's net worth poised to sail past $1 trillion in SpaceX IPO.</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>The company is poised to become a leader in renewable energy with its new technological breakthrough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>ENG-20260604-014</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>sail past</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>/seɪl pæst/</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>(예상치를) 훌쩍 넘어서다, (특정 지점을) 빠르게 통과하다</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>Elon Musk's net worth poised to sail past $1 trillion in SpaceX IPO.</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>The company's quarterly profits sailed past all analyst expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>ENG-20260604-015</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>set a target price</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>/sɛt ə ˈtɑːrɡɪt praɪs/</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>목표 가격을 설정하다</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>Elon Musk’s space exploration company set a target share price for buyers earlier than expected.</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>The analysts set a target price of $50 for the stock, indicating strong growth potential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>ENG-20260604-016</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>commit funds to</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>/kəˈmɪt fʌndz tuː/</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>~에 자금을 투입하다, 약속하다</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>The government is committing many millions of pounds to the new theme park planned for Bedfordshire.</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>The board decided to commit significant funds to research and development for the next fiscal year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>ENG-20260604-017</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>be in limbo</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>/bi ɪn ˈlɪmboʊ/</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>불확실한 상태에 놓여 있다, 표류하다</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>'I lost thousands in savings and my partner's money is in limbo,' one customer reported.</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Our travel plans are still in limbo because we haven't received our visas yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>ENG-20260604-018</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>outpace something</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>/aʊtˈpeɪs ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>~보다 앞서가다, 능가하다</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>The number of people withdrawing money from a LISA is outpacing the number using one to buy a home.</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Technological advancements continue to outpace regulatory efforts, creating new challenges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>ENG-20260604-019</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>make one's views known</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>/meɪk wʌnz vjuːz noʊn/</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>자신의 견해를 밝히다, 의견을 표명하다</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>The boss of X, Tesla and SpaceX has used his platform to make his views known on a vast array of topics.</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Employees are encouraged to make their views known during open forum discussions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>ENG-20260604-020</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>by the grace of God</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>/baɪ ðə ɡreɪs əv ɡɑːd/</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>(운이 좋게도) 천우신조로, 하나님의 은혜로</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>'By the grace of God,' miners dig on as lab-grown diamonds change market.</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>By the grace of God, we managed to escape the burning building just in time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>ENG-20260604-021</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>heap pressure on</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>/hiːp ˈprɛʃər ɑn/</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>~에 큰 압력을 가하다</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>The rising popularity of lab-grown diamonds heaps pressure on those hunting for the natural gems.</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>The opposition party continues to heap pressure on the government to address the rising cost of living.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>ENG-20260604-022</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>battle a fire</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>/ˈbætl ə ˈfaɪər/</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>화재와 싸우다, 진화 작업을 벌이다</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>Residents are advised to keep windows and doors closed as crews battle the fire in Port Talbot.</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>Firefighters worked tirelessly through the night to battle a massive wildfire in the national park.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>ENG-20260604-023</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>strengthen the case for</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>/ˈstrɛŋθən ðə keɪs fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>~의 주장을 강화하다, ~의 타당성을 높이다</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>Costly fuel pushes more Indians to buy electric cars but challenges remain. High fuel prices are strengthening the case for EV adoption.</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>New scientific evidence continues to strengthen the case for stricter environmental regulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>ENG-20260604-024</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>break even</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>/breɪk ˈiːvən/</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>손익분기점에 도달하다, 본전치기하다</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>Many new startups struggle for years before they can even break even.</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>After covering all our expenses, we just managed to break even on the charity event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>ENG-20260604-025</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>move out</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>/muːv aʊt/</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>이사 나가다, (집에서) 떠나다</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>Monica: Phoebe moved out. I don’t understand, I mean am I so hard to live (with)?</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>After college, I decided to move out of my parents' house and get my own apartment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>ENG-20260604-026</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>be hard to live with</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>/bi hɑːrd tuː lɪv wɪð/</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>~와 함께 살기 힘들다, 다루기 어렵다</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>Monica: Am I so hard to live (with)? Is this why I don’t have a boyfriend?</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>His constant complaining makes him really hard to live with sometimes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>ENG-20260604-027</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>lock up</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>/lɑːk ʌp/</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>문을 잠그다, 퇴근 시 문을 걸어 잠그다</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>Phoebe: Oh, it’s already closed, Chris gave me the keys to lock up.</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>Don't forget to lock up all the doors and windows before you leave the office.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>ENG-20260604-028</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>be over</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>/bi ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>(관계가) 끝나다, 종료되다</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>Ross: My marriage, I think my marriage is um, is kinda over.</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>After years of trying to make it work, their relationship was finally over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>ENG-20260604-029</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>mix and match</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>/mɪks ænd mætʃ/</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>섞어서 조합하다, 어울리게 하다</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>Ross: Carol’s a lesbian. And, and I’m not one. And apparently it’s not a mix and match situation.</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>You can mix and match different pieces from the collection to create your own unique style.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>ENG-20260604-030</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>see something coming</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>/siː ˈsʌmθɪŋ ˈkʌmɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>어떤 일이 일어날 것을 예상하다, 눈치채다</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>Ross: I’m an idiot. I mean shoulda seen it (coming).</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>Looking back, she admitted she should have seen his resignation coming, given his recent behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>ENG-20260604-031</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>hit one's head</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>/hɪt wʌnz hɛd/</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>머리를 부딪치다</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>Ross follows Phoebe and hits his head on the light hanging over the pool table.</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>Be careful when you go through that low doorway; you might hit your head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>ENG-20260604-032</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>be stuck in</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>/bi stʌk ɪn/</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>~에 끼어 옴짝달싹 못하다, 갇히다</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>Ross: My foot is stuck in the pocket. No, I can’t get it out.</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>I was stuck in traffic for two hours this morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>ENG-20260604-033</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>be in the way</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>/bi ɪn ðə weɪ/</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>방해가 되다, 길을 막다</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>Ross: Ouch! What? Stupid balls are in the way.</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>Could you move that box? It's right in the way of the door.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>ENG-20260604-034</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>sit up</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>/sɪt ʌp/</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>앉아 있던 자세에서 상체를 세우다</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>(They both look at each other and start laughing, and sit up.)</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>He had to sit up straight to get a better view of the stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>ENG-20260604-035</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>have a soft spot for</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>/hæv ə sɑːft spɑːt fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>~를 특별히 좋아하다, ~에게 약하다</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>Even though he's strict, the professor has a soft spot for students who show genuine effort.</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>I've always had a soft spot for classic romantic comedies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>ENG-20260604-036</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>turn someone down</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>/tɜːrn ˈsʌmˌwʌn daʊn/</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>~의 제안/요청을 거절하다</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>It was difficult to turn him down, but I knew his offer wasn't right for my career.</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>She had to turn down a job offer because it required too much travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>ENG-20260604-037</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>fall for someone</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>/fɔːl fɔːr ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>~와 사랑에 빠지다, ~에게 홀딱 반하다</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>He tried to resist, but he couldn't help but fall for her charming personality.</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>They met on vacation and instantly fell for each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>ENG-20260604-038</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>get over someone</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈoʊvər ˈsʌmˌwʌn/</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>~를 극복하다, 잊다 (이별 후)</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>Ross is clearly struggling to get over his wife Carol and their breakup.</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>It took him a long time to get over his ex-girlfriend, but he's finally moving on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>ENG-20260604-039</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>take something to heart</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>/teɪk ˈsʌmθɪŋ tuː hɑːrt/</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>~를 진지하게 받아들이다, 마음에 새기다</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>He took the criticism to heart and worked hard to improve his performance.</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>Don't take his comments to heart; he didn't mean to offend you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>ENG-20260604-040</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>lighten up</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>/ˈlaɪtən ʌp/</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>진지함을 덜다, 긴장을 풀다</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>Come on, Ross, lighten up! Not everything has to be so serious.</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>You're too stressed about this project; you need to lighten up a bit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>ENG-20260604-041</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>give someone a hard time</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmˌwʌn ə hɑːrd taɪm/</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>~를 괴롭히다, 힘들게 하다, 꾸짖다</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>Ross: No, come on don’t start (giving me a hard time).</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>My boss has been giving me a hard time about missing deadlines recently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>ENG-20260604-042</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>cheer someone up</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>/tʃɪər ˈsʌmˌwʌn ʌp/</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>~를 기운 나게 하다, 격려하다</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>Monica went to hug Chandler, and Phoebe kissed Ross, trying to cheer them up.</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>I sent her some flowers to cheer her up after she failed her exam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>ENG-20260604-043</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>vent one's frustration</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>/vɛnt wʌnz frʌˈstreɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>좌절감을 표출하다, 화를 터뜨리다</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>Ross used Phoebe as an outlet to vent his frustration about his failing marriage.</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>After a long and difficult day, she went for a run to vent her frustration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>ENG-20260604-044</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>pick oneself up</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>/pɪk wʌnˈsɛlf ʌp/</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>다시 일어서다, 회복하다</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>After a major setback, it's hard but necessary to pick oneself up and try again.</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>He lost everything in the fire, but he's determined to pick himself up and rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>ENG-20260604-045</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>turn over a new leaf</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>/tɜːrn ˈoʊvər ə nuː liːf/</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>새로운 시작을 하다, 지난 잘못을 뉘우치고 새사람이 되다</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>After their big fight, they decided to turn over a new leaf and improve their communication.</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>He promised his family he would turn over a new leaf and start taking his responsibilities seriously.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>ENG-20260604-046</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>call it quits</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>/kɔːl ɪt kwɪts/</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>(관계·활동 등을) 끝내다, 중단하다</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>Ross and Carol's marriage problems ultimately led them to call it quits.</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>After working together for ten years, the business partners decided to call it quits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>ENG-20260604-047</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>get back on one's feet</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>/ɡɛt bæk ɑn wʌnz fiːt/</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>(재정적으로, 건강상으로) 재기하다, 회복하다</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>After experiencing long-term unemployment, it can be challenging for workers to get back on their feet.</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>He lost his job, but with a lot of support, he's slowly getting back on his feet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>ENG-20260604-048</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>get a feel for</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>/ɡɛt ə fiːl fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>~에 익숙해지다, 감을 잡다</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>It takes some time to get a feel for how the new software works.</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>Before making a decision, I need to get a feel for the company culture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>ENG-20260604-049</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>surge</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>/sɜːrdʒ/</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>급증하다, 치솟다</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>Long-term unemployment is surging in the U.S.</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>Demand for the new product is expected to surge after the holiday season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>ENG-20260604-050</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>re-enter the workforce</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>/ˌriːˈɛntər ðə ˈwɜːrkˌfɔːrs/</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>직업 전선에 복귀하다</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>Long-term unemployment can have ramifications on financial, emotional and family health that linger even after reentry into the workforce.</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>After a long break, many mothers struggle to re-enter the workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>ENG-20260604-051</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>focus on</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>/ˈfoʊkəs ɑːn/</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>~에 집중하다, 초점을 맞추다</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>As the largest World Cup ever kicks off, health officials are focused on more than Ebola.</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>We need to focus on finding a long-term solution, not just a quick fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>ENG-20260604-052</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>in light of</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>/ɪn laɪt əv/</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>~을 고려하여, ~에 비추어</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>Options volume is surging for Zoetis as traders look for potential stock market winners in light of a screwworm case in Texas.</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>In light of the new evidence, the police reopened the investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>ENG-20260604-053</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>express public opposition to</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>/ɪkˈsprɛs ˈpʌblɪk ˌɑːpəˈzɪʃən tuː/</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>~에 대한 공개적인 반대를 표명하다</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>When he was indicted, John Bolton said he was innocent and that he was being targeted because of his public opposition to President Trump.</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>Many citizens expressed public opposition to the new city development plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>ENG-20260604-054</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>enforce quarantine</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>/ɪnˈfɔːrs ˈkwɔːrənˌtiːn/</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>격리를 시행하다</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>The USDA and Texas officials are working to contain New World screwworm from Zavala County, including establishing an infested zone and enforcing quarantine.</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>The authorities had to enforce quarantine measures to prevent the spread of the virus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>ENG-20260604-055</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>make a stock market debut</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>/meɪk ə stɑːk ˈmɑːrkɪt ˈdeɪˌbjuː/</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>주식 시장에 상장하다, 첫선을 보이다</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>Musk's SpaceX share sale: Four things you need to know; SpaceX says it's worth $1.75tn as it targets largest stock market debut.</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>The tech giant is expected to make a stock market debut next year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>ENG-20260604-056</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>sustain damage</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>/səˈsteɪn ˈdæmɪdʒ/</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>손상을 입다, 피해를 입다</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>'Apocalyptic' Tata Steel fire sees 'substantial' damage to production line.</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>The building sustained severe damage during the earthquake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>ENG-20260604-057</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>advise someone to do something</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>/ədˈvaɪz ˈsʌmˌwʌn tuː duː ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>누구에게 무엇을 하라고 조언하다</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>Residents are advised to keep windows and doors closed as crews battle the fire in Port Talbot.</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>My lawyer advised me to sign the contract carefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>ENG-20260604-058</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>push someone to do something</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>/pʊʃ ˈsʌmˌwʌn tuː duː ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>누군가가 무엇을 하도록 몰고 가다, 부추기다</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>Costly fuel pushes more Indians to buy electric cars but challenges remain.</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>The tight deadline pushed the team to work overtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>ENG-20260604-059</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>challenges remain</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>/ˈtʃælɪndʒɪz rɪˈmeɪn/</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>과제가 남아있다</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>Costly fuel pushes more Indians to buy electric cars but challenges remain.</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>Despite the progress, significant challenges remain in achieving gender equality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>ENG-20260604-060</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>help oneself</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>/hɛlp wʌnˈsɛlf/</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>마음껏 가져다 먹다/쓰다</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>Help yourself.</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>Please help yourselves to the snacks and drinks in the kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>ENG-20260604-061</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>be one of someone's favorite people</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>/bi wʌn əv ˈsʌmˌwʌnz ˈfeɪvərɪt ˈpiːpəl/</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>누군가에게 가장 좋아하는 사람 중 한 명이다</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>Listen, you are one of my favourite people and the most beautiful woman I’ve ever known in real life.</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>My niece always says I'm one of her favorite people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>ENG-20260604-062</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>know someone in real life</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>/noʊ ˈsʌmˌwʌn ɪn riːəl laɪf/</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>누군가를 실제로 만나서 알다</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>Listen, you are one of my favourite people and the most beautiful woman I’ve ever known in real life.</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>It's different getting to know someone in real life versus online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>ENG-20260604-063</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>pour oneself a drink</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>/pɔːr wʌnˈsɛlf ə drɪŋk/</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>스스로 술/음료를 따르다</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>Ross: (sets out a bunch of shot glasses and starts to poor himself a drink, many drinks)</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>He came home tired and immediately poured himself a drink.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>ENG-20260604-064</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>get something on sale</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmˌθɪŋ ɑːn seɪl/</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>~을 할인 가격으로 구매하다</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>Yeah! And I got it on sale, too.</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>I always try to get my clothes on sale to save money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>ENG-20260604-065</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>kiss someone on the cheek</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>/kɪs ˈsʌmˌwʌn ɑːn ðə tʃiːk/</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>누군가의 뺨에 키스하다</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>You’re, you’re really, you’re so good. (kisses him on the cheek)</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>It's customary in some cultures to kiss someone on the cheek as a greeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>ENG-20260604-066</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>kiss someone on the lips</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>/kɪs ˈsʌmˌwʌn ɑːn ðə lɪps/</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>누군가의 입술에 키스하다</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>And you’re kind (kisses him on the lips)</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>They kissed each other on the lips after the wedding ceremony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>ENG-20260604-067</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>kiss passionately</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>/kɪs ˈpæʃənətli/</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>열정적으로 키스하다</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>(They pause, and they the start kissing passionately, and taking off each others clothes, and they start to lie down on the pool table.)</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>The couple kissed passionately under the moonlight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>ENG-20260604-068</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>take off clothes</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>/teɪk ɔːf kloʊðz/</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>옷을 벗다</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>(They pause, and they the start kissing passionately, and taking off each others clothes, and they start to lie down on the pool table.)</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>It was so hot that he decided to take off his clothes and jump in the lake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>ENG-20260604-069</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>lie down on</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>/laɪ daʊn ɑːn/</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>~ 위에 눕다</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>(They pause, and they the start kissing passionately, and taking off each others clothes, and they start to lie down on the pool table.)</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>She was so tired she just wanted to lie down on the couch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>ENG-20260604-070</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>clear off</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>/klɪər ɔːf/</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>(표면에서) ~을 치우다, 깨끗이 하다</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>(Ross tries to clear off the pool table by knocking the balls to the other end of the table, but they all bounce back, and he frantically starts to throw them into the pockets.)</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>Please clear off your desk before you leave for the day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>ENG-20260604-071</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>not something one wants to hear</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>/nɑːt ˈsʌmθɪŋ wʌn wɑːnts tə hɪər/</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>듣고 싶지 않은 소리이다</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>Well, that’s not something a girl wants to hear.</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>The doctor's diagnosis was certainly not something I wanted to hear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>ENG-20260604-072</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>hold up</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>/hoʊld ʌp/</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>들어 올리다; (지연시키다)</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>Stupid balls are in the way. (holds up two balls)</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>He held up his hand to signal for a taxi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>ENG-20260604-073</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>have chalk on one's face</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>/hæv tʃɔːk ɑːn wʌnz feɪs/</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>얼굴에 분필 가루가 묻어있다</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>You have chalk on your face.</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>After drawing on the blackboard, the teacher often had chalk on her face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>ENG-20260604-074</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>raise a funding round</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>/reɪz ə ˈfʌndɪŋ raʊnd/</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>투자 유치 라운드를 성공시키다</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>Database startup Supabase announced a $500 million funding round that values the company at $10.5 billion, including the fresh capital.</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>The startup aims to raise a funding round of $10 million by the end of the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>ENG-20260604-075</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>lead a moderate lifestyle</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>/liːd ə ˈmɑːdərət ˈlaɪfˌstaɪl/</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>절제된 생활 방식을 영위하다</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>A newly-published report suggests a moderate lifestyle in retirement costs £32,700 for one person and £45,400 for two.</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>He decided to lead a moderate lifestyle to improve his health.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>ENG-20260604-076</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>go get something</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ɡɛt ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>가서 무엇을 가져오다/구하다</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>Yeah, I’ll go get one.</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>I need to go get some groceries from the store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>ENG-20260604-077</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>redemption requests rise</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>/rɪˈdɛmpʃən rɪˈkwɛsts raɪz/</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>환매 요청이 증가하다</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>Blackstone capped withdrawals from its $79 billion BCRED fund after redemption requests rose from 7.9% to 10%, adding to private market liquidity concerns.</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>If the fund performs poorly, redemption requests might rise significantly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>ENG-20260604-078</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>address liquidity concerns</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>/əˈdrɛs lɪˈkwɪdəti kənˈsɜːrnz/</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>유동성 우려를 해소하다</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>Blackstone capped withdrawals from its $79 billion BCRED fund after redemption requests rose from 7.9% to 10%, adding to private market liquidity concerns.</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>The central bank implemented new policies to address liquidity concerns in the banking sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>ENG-20260604-079</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>experience long-term unemployment</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>/ɪkˈspɪriəns ˌlɔːŋtɜːrm ˌʌnɪmˈplɔɪmənt/</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>장기 실업을 겪다</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>Long-term unemployment is surging in the U.S.</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>Many young graduates experience long-term unemployment in the current job market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>ENG-20260604-080</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>linger even after</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>/ˈlɪŋɡər ˈiːvən ˈæftər/</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>~ 후에도 여전히 남아있다</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>Long-term unemployment can have ramifications on financial, emotional and family health that linger even after reentry into the workforce.</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>The scent of her perfume seemed to linger even after she left the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>ENG-20260604-081</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>options volume surge</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>/ˈɑːpʃənz ˈvɑːljuːm sɜːrdʒ/</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>옵션 거래량이 급증하다</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>Options volume is surging for Zoetis as traders look for potential stock market winners in light of a screwworm case in Texas.</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>Ahead of the earnings report, options volume surged for the tech company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>ENG-20260604-082</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>give someone the ability to do something</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmˌwʌn ðə əˈbɪləti tuː duː ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>누군가에게 무엇을 할 능력을 주다</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>Pre-IPO perps give traders the ability to speculate on the value of a private company without owning shares.</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>This new software will give us the ability to process data much faster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>ENG-20260604-083</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>inject fresh capital</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>/ɪnˈdʒɛkt frɛʃ ˈkæpɪtəl/</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>새로운 자본을 투입하다</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>Database startup Supabase announced a $500 million funding round that values the company at $10.5 billion, including the fresh capital.</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>The government decided to inject fresh capital into struggling industries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>ENG-20260604-084</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>own shares in a company</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>/oʊn ʃɛrz ɪn ə ˈkʌmpəni/</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>회사의 주식을 소유하다</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>Based on SpaceX's updated IPO prospectus, Elon Musk owns shares in the company worth more than $866 billion.</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>Many employees choose to own shares in the company they work for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>ENG-20260604-085</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>provide a constructive solution</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>/prəˈvaɪd ə kənˈstrʌktɪv səˈluːʃən/</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>건설적인 해결책을 제시하다</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>It probably would’ve been the most constructive solution.</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>The committee aimed to provide a constructive solution to the ongoing conflict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>ENG-20260604-086</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>give someone the keys to do something</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmˌwʌn ðə kiːz tuː duː ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>누군가에게 무엇을 할 권한을 주다</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>Oh, it’s already closed, Chris gave me the keys to lock up-what is wrong?</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>The manager gave me the keys to handle the client meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>ENG-20260604-087</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>keep windows and doors closed</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>/kiːp ˈwɪndoʊz ənd dɔːrz kloʊzd/</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>창문과 문을 닫아두다</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>Residents are advised to keep windows and doors closed as crews battle the fire in Port Talbot.</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>During the sandstorm, it's important to keep windows and doors closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>ENG-20260604-088</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>agree to do something</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>/əˈɡriː tuː duː ˈsʌmˌθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>무엇을 하는 것에 동의하다</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>Ex-Trump advisor John Bolton agrees to plead guilty to retaining classified information: MS NOW</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>The two companies agreed to merge their operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>ENG-20260604-089</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>contain screwworm</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>/kənˈteɪn ˈskruːˌwɜːrm/</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>나사파리를 억제하다</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>The USDA and Texas officials are working to contain New World screwworm from Zavala County, including establishing an infested zone and enforcing quarantine.</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>Veterinarians are working hard to contain the spread of the disease among livestock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>ENG-20260604-090</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>get something out</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈsʌmˌθɪŋ aʊt/</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>~을 밖으로 꺼내다; (정보 등을) 밝히다</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>No, I can’t get it out.</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>Could you please get the milk out of the fridge?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1275"/>
+  <dimension ref="A1:I1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60341,6 +60341,4424 @@
         </is>
       </c>
     </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>ENG-20260605-001</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>be in for a reality check</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>/biː ɪn fɔːr ə riˈæləti tʃek/</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>냉혹한 현실을 직시하게 되다, 매서운 현실에 직면하다</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>The stronger-than-expected start this year for job creation could be in for a reality check with the upcoming May jobs report.</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>Many young entrepreneurs think running a startup is glamorous, but they are in for a reality check within the first year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>ENG-20260605-002</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>play a big role in</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>/pleɪ ə bɪɡ roʊl ɪn/</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>~에 중요한 역할을 하다, 큰 영향을 미치다</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>OpenAI's Head of Countries told CNBC that governments have a big role to play in how this technology is used and deployed.</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>We believe continuous learning plays a big role in long-term career success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>ENG-20260605-003</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>get worse before it gets better</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>/ɡet wɜːrs bɪˈfɔːr ɪt ɡets ˈbetər/</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>상황이 호전되기 전에 먼저 한층 더 악화되다</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>Lululemon is expecting its retail situation to get a lot worse before it gets better, as it issued weak guidance.</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>The restructuring process will be painful; things are going to get worse before they get better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>ENG-20260605-004</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>press someone over</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>/pres ˈsʌmwʌn ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>~에 대해 누군가를 강하게 다그치다, 압박하다</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>Sen. Elizabeth Warren is pressing Jensen Huang over Nvidia's export controls and sales to China.</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>The committee decided to press the CEO over the company's continuous failure to protect user data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>ENG-20260605-005</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>make the first move</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>/meɪk ðə fɜːrst muːv/</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>먼저 대시하다, 첫 발을 내딛다, 솔선수범하다</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>Single 20-somethings need AI to make the first move on dating apps because they lack confidence.</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>I was too shy to say hello, so I waited for her to make the first move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>ENG-20260605-006</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>draw criticism</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>/drɔː ˈkrɪtɪsɪzəm/</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>비판을 초래하다, 거센 지탄을 받다</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>Micro dramas have surged in popularity, but they have also drawn criticism for sensationalist content.</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>The CEO's decision to lay off workers while receiving a massive bonus drew intense criticism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>ENG-20260605-007</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>loosen the purse strings</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>/ˈluːsn̩ ðə pɜːrs strɪŋz/</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>돈을 더 많이 쓰다, 지갑 끈을 늦추다</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>You bought your sheets at a flea market? Ross, come on, you gotta loosen the purse strings a little.</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>The company decided to loosen the purse strings for the annual marketing campaign to boost sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>ENG-20260605-008</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>cover up</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>/ˈkʌvər ʌp/</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>숨기다, 은폐하다, (가리개 등으로) 덮다</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>Phoebe is gonna be here any second, she cannot see this! Can we please just cover this up with something?</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>They tried to cover up the accounting error, but the auditors discovered it during the review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>ENG-20260605-009</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>be one of a kind</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>/biː wʌn ɒv ə kaɪnd/</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>독보적이다, 세상에 단 하나뿐이다</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>Ross, she is not weird, she just wants her furniture and stuff to be one of a kind.</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>This antique vase is truly one of a kind; you won't find another one anywhere in the world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>ENG-20260605-010</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>hang out with</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>/hæŋ aʊt wɪð/</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>~와 어울려 놀다, 시간을 보내다</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>Well, she didn't want to hang out with you guys two nights in a row. I'm so sorry.</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>I used to hang out with my college friends every weekend, but now we're all too busy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>ENG-20260605-011</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>do something in a row</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>/duː ˈsʌmθɪŋ ɪn ə roʊ/</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>~을 연속으로 (며칠/몇 번) 계속하다</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>She didn't want to hang out with us two nights in a row, so she made up an excuse.</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>I've been working late three days in a row, and I'm absolutely exhausted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>ENG-20260605-012</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>lie to someone's face</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>/laɪ tuː ˈsʌmwʌnz feɪs/</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>상대방의 얼굴을 똑바로 보며 대놓고 거짓말하다</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>So she was just pretending to have a good time last night? She was lying to our faces?!</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>I knew the truth already, but he still stood there and lied to my face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>ENG-20260605-013</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>be a hoot</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>/biː ə huːt/</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>정말 웃기고 유쾌한 사람/물건이다</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>And I am not blah, I am a hoot! People love having me at parties.</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>You should definitely invite Sarah; she is a total hoot when she starts telling stories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>ENG-20260605-014</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>drop the ball</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>/drɒp ðə bɔːl/</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>중요한 순간에 실수를 저지르다, 책임을 다하지 못하다</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>Our logistics supplier completely dropped the ball on delivering our spring product line.</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>I'm sorry I dropped the ball on following up with the client yesterday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>ENG-20260605-015</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>call a spade a spade</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>/cɔːl ə speɪd ə speɪd/</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>솔직하게 있는 그대로 직설적으로 말하다</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>Let's call a spade a spade: she didn't come to dinner because she thinks we are boring.</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>I like his management style because he always calls a spade a spade without sugarcoating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>ENG-20260605-016</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>chip in</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>/tʃɪp ɪn/</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>돈을 조금씩 각출하다, 의견을 보태다</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>If we all chip in, we can easily buy this expensive apothecary table for the apartment.</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>Everyone in the department chipped in ten dollars to buy a farewell gift for the director.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>ENG-20260605-017</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>do something off the cuff</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>/duː ˈsʌmθɪŋ ɒf ðə kʌf/</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>사전 준비 없이 즉석에서 ~을 하다</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>Rachel made up a story about the days of yore completely off the cuff.</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>I wasn't expecting to speak at the wedding, so I had to deliver a speech off the cuff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>ENG-20260605-018</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>happen out of the blue</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>/ˈhæpən aʊt ɒv ðə bluː/</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>뜬금없이 발생하다, 느닷없이 일어나다</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>Her complaints about us being loud and boring came completely out of the blue.</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>I hadn't heard from my high school friend in ten years, and then he called me out of the blue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>ENG-20260605-019</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>play devil's advocate</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>/pleɪ ˈdevlz ˈædvəkət/</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>(토론이나 검토를 위해) 일부러 반대 의견을 제기하다</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>Let me play devil's advocate: what if OpenAI's compliance delays actually damage its market share?</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>I agree with your proposal, but let me play devil's advocate for a second to test its weaknesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>ENG-20260605-020</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>save face</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>/seɪv feɪs/</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>체면을 차리다, 깎인 위신을 세우다</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>The retail brand is cutting its outlook early to save face before actual poor performance leaks.</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>The manager admitted the mistake quickly to save face and preserve his professional reputation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>ENG-20260605-021</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>slip one's mind</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>/slɪp wʌnz maɪnd/</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>깜빡 잊어버리다, 머릿속에서 지워지다</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>I meant to tell you about the dinner invitation, but it completely slipped my mind.</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>I promised to call the supplier this morning, but it totally slipped my mind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>ENG-20260605-022</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>throw someone under the bus</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>/θroʊ ˈsʌmwʌn ˈʌndər ðə bʌs/</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>위기에서 벗어나려 자신의 책임을 누군가에게 뒤집어씌우다, 희생양 삼다</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>Joey threw Rachel under the bus to cover up his own lies about the dinner plans.</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>During the review, the project lead threw his team members under the bus for the missed deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>ENG-20260605-023</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>be touch and go</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>/biː tʌtʃ ænd ɡoʊ/</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>(상황이 어떻게 될지 모르게) 아슬아슬하다, 매우 불확실하다</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>The situation with the stranded cargo ships in the Strait of Hormuz is highly touch and go.</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>The doctor said his recovery was touch and go for the first forty-eight hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>ENG-20260605-024</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>get up to speed</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>/ɡet ʌp tuː spiːd/</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>최신 정보를 파악하다, 지식을 본궤도에 올리다</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>We need to get up to speed on the new AI export regulations proposed by the government.</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>It took the new hire about two weeks to get up to speed with our software development lifecycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>ENG-20260605-025</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>spread by word of mouth</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>/spred baɪ wɜːrd ɒv maʊθ/</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>입소문을 타고 번지다, 구전되다</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>The popularity of micro dramas spread by word of mouth before they became a global phenomenon.</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>We didn't spend any money on marketing; our product's success spread entirely by word of mouth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>ENG-20260605-026</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>work against the clock</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>/wɜːrk əˈɡenst ðə klɒk/</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>마감 시간을 맞추기 위해 필사적으로 급히 일하다</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>SpaceX engineers are working against the clock to prepare the rocket for its upcoming launch.</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>We are working against the clock to finish this software patch before the system reboot tonight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>ENG-20260605-027</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>wrap one's head around</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>/ræp wʌnz hed əˈraʊnd/</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>복잡하거나 놀라운 사실을 온전히 머리로 이해하다, 받아들이다</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>I just can't wrap my head around the fact that Phoebe genuinely hates mass-produced furniture.</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>I'm trying to wrap my head around these new tax codes, but they are incredibly complicated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>ENG-20260605-028</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>write off</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>/raɪt ɒf/</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>(가치가 없다고 판단하여) 장부에서 지우다, 무시하다, 포기하다</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>Lululemon had to write off some underperforming inventory after their disappointing launch.</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>You shouldn't write him off just because he failed his first sales presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>ENG-20260605-029</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>burn one's bridges</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>/bɜːrn wʌnz ˈbrɪdʒɪz/</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>배수의 진을 치다, 이전 관계로 돌아갈 다리를 끊어버리다</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>When Janine told Monica and Chandler they were boring, she definitely burned her bridges.</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>Even if you dislike your current job, don't burn your bridges when you resign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>ENG-20260605-030</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>cry over spilled milk</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>/kraɪ ˈoʊvər spɪld mɪlk/</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>이미 엎질러진 물을 두고 한탄하다, 후회하다</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>The table is already in the apartment, so there is no use crying over spilled milk.</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>Yes, we lost the client, but let's not cry over spilled milk; let's focus on the next pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>ENG-20260605-031</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>hit the ceiling</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>/hɪt ðə ˈsiːlɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>길길이 뛰며 화를 내다, 극도로 분노하다</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>Monica will hit the ceiling if she finds out Janine was lying about being sick to avoid her.</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>My father hit the ceiling when he saw the dent on his brand new car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>ENG-20260605-032</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>skirt around</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>/skɜːrt əˈraʊnd/</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>(곤란한 질문이나 주제 등을) 교묘히 피해 가다</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>The spokesperson tried to skirt around the questions regarding Trump's AI policy orders.</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>Instead of answering directly, the manager spent ten minutes skirting around the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>ENG-20260605-033</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>test the waters</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>/test ðə ˈwɔːtərz/</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>본격적으로 시작하기 전에 시장 반응을 살피다, 간을 보다</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>Ramp launched its beta software to test the waters before targeting multinational corporate clients.</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>We decided to test the waters by launching a small pilot project in selected cities first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>ENG-20260605-034</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>keep a straight face</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>/kiːp ə streɪt feɪs/</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>정색하며 무표정을 짓다, 웃음을 꾹 참다</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>Rachel tried to keep a straight face while telling Phoebe the table was from the days of yore.</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>The joke was so hilarious that I could barely keep a straight face during the board meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>ENG-20260605-035</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>look at the big picture</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>/lʊk æt ðə bɪɡ ˈpɪktʃər/</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>전체적인 거시적 맥락을 파악하다, 숲을 보다</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>When reining in technology expenses, businesses need to look at the big picture and long-term benefits.</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>Don't get discouraged by this month's low sales; we need to look at the big picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>ENG-20260605-036</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>take someone's word for it</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>/teɪk ˈsʌmwʌnz wɜːrd fɔːr ɪt/</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>별다른 증거 없이 누군가의 말을 그대로 믿다</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>Phoebe took Rachel's word for it when she said the table was a flea market find.</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>You don't have to take my word for it; you can check the transaction history yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>ENG-20260605-037</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>give someone credit</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmwʌn ˈkredɪt/</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>누군가의 노력이나 성과를 인정해 주다</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>You've got to give Monica credit; she always prepares amazing dinners for her guests.</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>We have to give him credit for working late every day to hit the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>ENG-20260605-038</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>put yourself in someone's shoes</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>/pʊt jɔːrˈself ɪn ˈsʌmwʌnz ʃuːz/</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>역지사지하여 상대방의 처지에서 생각해보다</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>Just put yourself in Monica's shoes; how would you feel if someone called you blah and loud?</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>Before criticizing his performance, put yourself in his shoes and consider his heavy workload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>ENG-20260605-039</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>be on the brink of</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>/biː ɒn ðə brɪŋk ɒv/</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>~의 직전이나 기로에 놓여 있다, 직면하다</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>The charity organization was on the brink of closing many of its physical high street shops.</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>The two countries were on the brink of war due to the unresolved border dispute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>ENG-20260605-040</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>make a fuss</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>/meɪk ə fʌs/</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>야단법석을 떨다, 트집 잡으며 유난을 떨다</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>Please don't make a fuss about the table; Phoebe hates mass-produced items.</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>It was just a tiny scratch on the car, but he made a huge fuss over it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>ENG-20260605-041</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>get a raw deal</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>/ɡet ə rɔː diːl/</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>부당한 처우를 받다, 불리한 조건에 처하다</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>Many delivery drivers feel they get a raw deal under the platform's current pricing structure.</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>The employees got a raw deal when they were laid off without proper redundancy pay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>ENG-20260605-042</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>take a heavy toll on</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>/teɪk ə ˈhevi toʊl ɒn/</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>~에 심각한 피해나 타격을 주다</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>The Strait of Hormuz standoff has taken a heavy toll on global energy market sentiment.</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>Working seventy hours a week for two years took a heavy toll on his physical health.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>ENG-20260605-043</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>under the table</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>/ˈʌndər ðə ˈteɪbl̩/</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>비밀리에 불법적으로, 뒷거래로</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>Regulators suspect that some chip sales were made under the table to bypass export controls.</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>He was paid under the table to avoid paying income taxes on his second job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>ENG-20260605-044</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>think on one's feet</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>/θɪŋk ɒn wʌnz fiːt/</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>순발력 있게 판단하고 신속하게 대응하다</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>When Phoebe entered the room unexpectedly, Rachel had to think on her feet.</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>A live TV host must be able to think on their feet when technical glitches occur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>ENG-20260605-045</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>stand your ground</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>/stænd jɔːr ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>의견이나 신념을 굽히지 않고 타협 없이 버티다</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>Ross decided to stand his ground and refuse to hide his Pottery Barn table.</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>Despite intense pressure from the board, the CEO stood her ground on the environmental policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>ENG-20260605-046</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>go down to the wire</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>/ɡoʊ daʊn tuː ðə ˈwaɪər/</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>마지막 순간까지 아슬아슬하게 승부가 가려지지 않다</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>The vote on the coal investment bill went down to the wire in the Senate.</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>The contract negotiations went down to the wire, but we signed it just minutes before midnight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>ENG-20260605-047</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>be on the safe side</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>/biː ɒn ðə seɪf saɪnd/</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>신중을 기하기 위해, 혹시 모를 위험에 대비하다</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>Let's put a sheet over this table just to be on the safe side before she knocks.</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>I think the weather will be fine, but I'll take an umbrella just to be on the safe side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>ENG-20260605-048</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>catch wind of</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>/kætʃ wɪnd ɒv/</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>(비밀 정보를) 눈치채다, 풍문으로 전해 듣다</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>If Phoebe catches wind of our lie about the Pottery Barn table, she'll never trust us again.</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>The competitors caught wind of our product development plan and launched a similar model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>ENG-20260605-049</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>see the light of day</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>/siː ðə laɪt ɒv deɪ/</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>(오랜 지연 끝에) 드디어 햇빛을 보다, 공개되다</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>Some highly advanced AI models may never see the light of day due to strict state reviews.</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>After three years of regulatory hurdles, our health app has finally seen the light of day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>ENG-20260605-050</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>give or take</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>/ɡɪv ɔːr teɪk/</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>대략 정도, 얼마간의 오차가 있겠지만</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>The table was at a flea market, so it was like a dollar and fifty cents, give or take.</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>The project will take about six months to complete, give or take a few weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>ENG-20260605-051</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>leave no stone unturned</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>/liːv noʊ stoʊn ʌnˈtɜːrnd/</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>온갖 방법을 다 동원하여 샅샅이 뒤지다, 백방으로 노력하다</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>The U.S. Navy left no stone unturned in safely coordinating the exit of the stranded ships.</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>We will leave no stone unturned to find the source of this major software bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>ENG-20260605-052</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>be tied to</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>/biː taɪd tuː/</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>~와 긴밀히 얽혀 있다, 관련되다</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>The energy debate is directly tied to the geopolitical standoff in the Strait of Hormuz.</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>The CEO's annual bonus package is directly tied to the company's stock market performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>ENG-20260605-053</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>sound like a broken record</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>/saʊnd laɪk ə ˈbroʊkən ˈrekərd/</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>녹음기 틀어놓은 것처럼 똑같은 소리를 계속 반복하다</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>I know I sound like a broken record, but Pottery Barn furniture is mass-produced and unauthentic!</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>I hate to sound like a broken record, but please remember to back up your files daily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>ENG-20260605-054</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>take matters into one's own hands</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>/teɪk ˈmætərz ˈɪntuː wʌnz oʊn hændz/</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>(남에게 안 맡기고) 스스로 직접 해결에 나서다</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>The ships decided to take matters into their own hands and quietly coordinate with the Navy.</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>Tired of waiting for the repairman, she took matters into her own hands and fixed the sink.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>ENG-20260605-055</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>strike a deal</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>/straɪk ə diːl/</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>계약을 체결하다, 합의를 보다</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>Trump stated he could meet Iran's supreme leader if it was to strike a deal on nuclear policy.</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>After several rounds of negotiation, the two firms finally struck a deal yesterday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>ENG-20260605-056</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>go down that road</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>/ɡoʊ daʊn ðæt roʊd/</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>(특정한 행동 방침이나 생각으로) 나아가다, 그러한 일을 벌이다</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>If you start lying about where you buy your furniture, you don't want to go down that road.</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>We shouldn't go down that road of cutting costs by compromising our core product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>ENG-20260605-057</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>make sense of</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>/meɪk sens ɒv/</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>복잡한 현상을 머리로 온전히 이해하다</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>Economists are trying to make sense of the sudden changes in Bitcoin liquidity and narrative.</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>Can you help me make sense of this legal document? The jargon is too dense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>ENG-20260605-058</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>stand out from the crowd</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>/stænd aʊt frɒm ðə kraʊd/</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>군계일학이다, 다른 평범한 것들 사이에서 눈에 띄다</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>Single people need unique profiles to stand out from the crowd on dating applications.</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>If you want to land this job, you need a portfolio that stands out from the crowd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>ENG-20260605-059</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>be a double-edged sword</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>/biː ə ˈdʌbl̩ edʒd sɔːrd/</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>양날의 검이다, 일장일단이 있다</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>Rapidly developing AI without human feedback could be a double-edged sword.</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>The rise of remote work is a double-edged sword; it offers flexibility but can cause isolation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>ENG-20260605-060</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>push the envelope</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>/pʊʃ ðə ˈenvəloʊp/</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>한계를 뛰어넘다, 혁신을 지향하며 새로운 시도를 하다</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>Elon Musk's SpaceX always pushes the envelope in aerospace engineering and rockets.</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>Our design team always pushes the envelope to create products that surprise our consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>ENG-20260605-061</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>get your act together</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>/ɡet jɔːr ækt təˈɡeðər/</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>정신을 차리다, 행동을 똑바로 바르게 정돈하다</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>You need to get your act together and stop lying to Phoebe about your apartment decor.</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>If you don't get your act together and start studying, you're going to fail the course.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>ENG-20260605-062</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>keep your chin up</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>/kiːp jɔːr tʃɪn ʌp/</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>낙담하지 말고 기운을 내다, 의기소침해하지 마라</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>Keep your chin up, Joey! Your acting career will pick up again soon.</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>I know the rejection is disappointing, but keep your chin up and keep applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>ENG-20260605-063</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>bring something to light</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>/brɪŋ ˈsʌmθɪŋ tuː laɪt/</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>(가려졌던 비밀이나 사실을) 세상에 드러내다, 폭로하다</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>The congressional investigation brought to light several hidden AI chip sales to China.</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>The financial audit brought to light several discrepancies in the company's books.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>ENG-20260605-064</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>keep a tight rein on</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>/kiːp ə taɪt reɪn ɒn/</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>~을 타이트하게 쥐어짜며 철저하게 통제하다</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>Tech companies are keeping a tight rein on AI integration costs to satisfy shareholders.</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>The director keeps a tight rein on the project schedule to prevent any deadline delays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>ENG-20260605-065</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>be written all over one's face</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>/biː ˈrɪtn̩ ɔːl ˈoʊvər wʌnz feɪs/</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>얼굴에 기분이나 감정이 고스란히 다 쓰여 있다, 다 티가 나다</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>Phoebe's excitement for the apothecary table was written all over her face.</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>He said he was fine, but his disappointment was written all over his face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>ENG-20260605-066</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>leave a sour taste in one's mouth</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>/liːv ə ˈsaʊər teɪst ɪn wʌnz maʊθ/</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>씁쓸한 뒷맛을 남기다, 불쾌한 감정을 동반하다</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>The way Janine criticized Monica's personality left a sour taste in Joey's mouth.</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>The customer service representative was rude, which left a sour taste in my mouth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>ENG-20260605-067</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>give someone a run for their money</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmwʌn ə rʌn fɔːr ðeər ˈmʌni/</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>상대방을 바짝 위협할 정도로 선전하다, 만만치 않은 경쟁 상대가 되다</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>Other space startup companies are trying to give SpaceX a run for their money.</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>The local coffee shop is giving the giant chain a serious run for their money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>ENG-20260605-068</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>be out of reach</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>/biː aʊt ɒv riːtʃ/</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>손이 닿지 않다, 손에 넣기 어려울 정도로 능력을 벗어나다</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>Paying $30 to visit a presidential library makes it out of reach for lower-income families.</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>Buying a house in central Seoul has become completely out of reach for average earners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>ENG-20260605-069</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>go down in history</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>/ɡoʊ daʊn ɪn ˈhɪstəri/</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>역사에 길이 남다, 획을 긋다</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>SpaceX's successful private commercial rocket flight will surely go down in history.</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>This medical discovery is so significant that it will go down in history as a major breakthrough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>ENG-20260605-070</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>get on track</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>/ɡet ɒn træk/</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>원하는 정상 궤도에 다시 오르다, 순조롭게 풀리기 시작하다</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>Lululemon issued weak guidance to give itself time to get on track with product design.</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>After a difficult first semester, he finally got on track with his academic studies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>ENG-20260605-071</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>keep one's fingers crossed</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>/kiːp wʌnz ˈfɪŋɡərz krɒst/</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>행운을 빌다, 좋은 결과가 있기를 간절히 원하다</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>We are keeping our fingers crossed that Phoebe never visits Ross's new apartment.</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>I have my interview tomorrow, so please keep your fingers crossed for me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>ENG-20260605-072</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>take pride in</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>/teɪk praɪd ɪn/</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>~에 대단한 자부심을 가지다, 자랑스러워하다</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>Phoebe takes great pride in her unique collection of antique and non-mass-produced things.</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>Our family business takes pride in using only organic ingredients for our bread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>ENG-20260605-073</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>pay the price</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>/peɪ ðə praɪs/</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>(자신의 과오나 무리에 대해) 대가를 톡톡히 치르다</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>If OpenAI ignores government compliance safety rules, they will eventually pay the price.</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>He didn't take care of his health when he was young, and now he is paying the price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>ENG-20260605-074</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>keep track of</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>/kiːp træk ɒv/</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>~을 꼼꼼하게 기록하고 관리하다, 파악하다</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>It is hard to keep track of all the different narratives causing Bitcoin's price fluctuations.</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>The software helps small business owners keep track of their daily inventory and sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>ENG-20260605-075</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>under the radar</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>/ˈʌndər ðə ˈreɪdɑːr/</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>눈에 띄지 않게 비밀리에 은밀하게 행해지는</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>The ships quietly negotiated with the Navy, keeping the escape plans under the radar.</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>The team worked on the secret project under the radar to prevent early rumors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>ENG-20260605-076</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>cost a fortune</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>/cɒst ə ˈfɔːrtʃuːn/</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>값이 거금에 달하다, 엄청나게 비용이 많이 들다</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>Visiting the Obama Presidential Center will cost a fortune compared to other museums.</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>Getting my teeth aligned in this private clinic is going to cost a fortune.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>ENG-20260605-077</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>make a move</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>/meɪk ə muːv/</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>행동을 시작하다, 첫 단추를 끼우다</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>The theme park operators finally decided to make a move on the planned development site.</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>If we want to capture the market before others, we need to make a move right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>ENG-20260605-078</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>stand behind</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>/stænd bɪˈhaɪnd/</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>~을 지지하다, 신뢰를 나타내며 든든히 버텨주다</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>The long-serving employee always stands behind her boss through thick and thin.</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>Our customer service guarantees that we always stand behind our products' quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>ENG-20260605-079</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>throw away</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>/θroʊ əˈweɪ/</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>(쓰레기를) 그냥 버리다, 허투루 낭비하다</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>Instead of throwing away food byproducts, fermentation makes them useful and tasty.</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>Please don't throw away that cardboard box; we can reuse it for shipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>ENG-20260605-080</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>get to the point</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>/ɡet tuː ðə pɔɪnt/</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>요점을 말하다, 대화의 본론에 핵심적으로 접근하다</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>Anthropic's co-founder got straight to the point about human control in advanced AI.</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>Stop beating around the bush and just get to the point of your presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>ENG-20260605-081</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>make a deal</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>/meɪk ə diːl/</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>계약을 타결하다, 거래를 트다, 타협하다</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>Trump stated he is willing to meet the supreme leader of Iran if it is to make a deal.</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>We managed to make a deal with the suppliers to get a ten percent wholesale discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>ENG-20260605-082</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>keep in check</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>/kiːp ɪn tʃek/</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>(지출, 감정 등을) 억제하고 철저하게 관리하다</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>The administration is trying to keep oil prices in check during the global energy standoff.</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>It is crucial to keep your personal spending in check when you transition to freelancing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>ENG-20260605-083</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>clash with</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>/klæʃ wɪð/</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>~와 충돌하다, 맞지 않아 마찰을 빚다</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>Joey's plans for a friendly dinner clashed with Janine's intense dislike of Monica's personality.</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>The marketing schedule clashed with the product development team's testing window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>ENG-20260605-084</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>leave much to be desired</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>/liːv mʌtʃ tuː biː dɪˈzaɪərd/</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>(품질이나 결과 등이) 아쉬움이나 미흡한 점을 많이 남기다</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>Lululemon's product launch left much to be desired, according to initial consumer reviews.</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>While the hotel's location was great, the service left much to be desired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>ENG-20260605-085</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>strike a chord</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>/straɪk ə kɔːrd/</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>심금을 울리다, 깊은 공감을 이끌어내다</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>The message about making dating apps more secure and empathetic struck a chord with Gen Z.</t>
+        </is>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>His speech about overcoming failure struck a chord with everyone in the audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>ENG-20260605-086</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>on a roll</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>/ɒn ə roʊl/</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>기세를 몰아 승승장구하는, 탄력받은</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>SpaceX is on a roll with consecutive successful rocket missions and rising valuations.</t>
+        </is>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>Our sales team is on a roll; we've signed five major corporate clients this week alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>ENG-20260605-087</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>go out of one's way</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>/ɡoʊ aʊt ɒv wʌnz weɪ/</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>일부러 수고스럽게 특별히 호의를 베풀다, 애쓰다</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>Monica went out of her way to welcome Janine, cooking a special multi-course dinner.</t>
+        </is>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>My landlord went out of his way to help me move my heavy furniture into the apartment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>ENG-20260605-088</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>bring about</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>/brɪŋ əˈbaʊt/</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>변화나 사건 등을 야기하다, 초래하다</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>The energy dispute will surely bring about massive policy shifts in European parliaments.</t>
+        </is>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>The introduction of the new software has brought about a significant improvement in efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>ENG-20260605-089</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>fall behind</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>/fɔːl bɪˈhaɪnd/</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>(경쟁이나 진도 등에서) 뒤처지다</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>Traditional retailers run the risk of falling behind if they do not adopt digital systems.</t>
+        </is>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>If we don't start the development phase now, we will fall behind our original schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>ENG-20260605-090</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>get over something</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>/ɡet ˈəʊvə ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>(실망, 충격 등에서) 회복하다, 극복하다, 받아들이고 넘어가다</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>Ross, get over it! It’s not like she hates you.</t>
+        </is>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>It took her a few months to get over the disappointment of losing the major client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>ENG-20260605-091</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>wind up</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>/waɪnd ʌp/</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>결국 (특정 상황이나 처지에) 처하게 되다</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>...nothing is authentic, and everyone winds up having the same stuff.</t>
+        </is>
+      </c>
+      <c r="I1366" t="inlineStr">
+        <is>
+          <t>If you keep spending money like this, you will wind up in serious debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>ENG-20260605-092</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>drive up</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>/draɪv ʌp/</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>(가격, 비용 등을) 급격히 올리다, 상승시키다</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>...the president is directing money into coal as the Iran war drives up energy costs for Americans.</t>
+        </is>
+      </c>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>Speculation in the housing market continues to drive up real estate prices in the metropolitan area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>ENG-20260605-093</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>cut one's outlook</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>/kʌt wʌnz ˈaʊt.lʊk/</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>(향후 실적, 경기 전망 등의) 전망치를 하향 조정하다</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>Lululemon cuts annual outlook, citing 'negative' media commentary...</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>Several major tech companies decided to cut their annual outlook due to supply chain disruptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>ENG-20260605-094</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>make one's debut</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>/meɪk wʌnz deɪˈbjuː/</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>첫선을 보이다, 데뷔하다, 시장에 처음 상장되다</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>SpaceX says it's worth $1.75tn as it targets largest stock market debut.</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>The electric vehicle manufacturer is planning to make its stock market debut early next year.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1369"/>
+  <dimension ref="A1:I1462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64759,6 +64759,4377 @@
         </is>
       </c>
     </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>ENG-20260606-001</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>strengthen one's grip on</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>/ˈstrɛŋθən wʌnz ɡrɪp ɒn/</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>~에 대한 통제력이나 영향력을 강화하다</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>Social media bans on teens risk strengthening Big Tech's grip on the sector, Bluesky exec warns.</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>The new policies are designed to strengthen the government's grip on the financial markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>ENG-20260606-002</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>raise funds</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>/reɪz fʌndz/</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>자금을 모으다, 조달하다</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>Meta's stock sinks on report company could raise tens of billions of dollars to fund AI push.</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>The startup is looking to raise funds for its next big project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>ENG-20260606-003</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>put something to the test</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌmθɪŋ tu ðə tɛst/</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>~을 시험대에 올리다, 능력을 시험하다</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>Earnings put the recent rally to the test.</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>Our new security system will be put to the test when the hackers try to breach it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>ENG-20260606-004</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>give something a boost</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmθɪŋ ə buːst/</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>~에 활력을 불어넣다, 증진시키다</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>Mythos gave the cybersecurity sector a boost, but upbeat earnings weren't enough for investors.</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>The government's new initiative aims to give the local economy a much-needed boost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>ENG-20260606-005</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>in search of</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>/ɪn sɜːrtʃ ɒv/</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>~을 찾아서, ~을 구하러</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>Upbeat earnings weren't enough for investors in search of an AI payoff.</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>Many young people move to the city in search of better job opportunities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>ENG-20260606-006</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>build a career on</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>/bɪld ə kəˈrɪər ɒn/</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>~을 기반으로 경력을 쌓다</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>Warren Buffett disciple Guy Spier built career on value investing.</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>She built her career on a strong foundation of ethical journalism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>ENG-20260606-007</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>get to the point where</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>/ɡɛt tu ðə pɔɪnt wɛər/</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>~할 지경에 이르다, ~하는 단계에 도달하다</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>Jack Clark tells BBC's Newsnight AI could get to the point where it develops without human input.</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>Things got to the point where we had no choice but to sell the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>ENG-20260606-008</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>beat expectations</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>/biːt ˌɛkspɛkˈteɪʃənz/</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>예상치를 뛰어넘다, 기대 이상이다</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>It is the third month in a row US jobs figures have beaten expectations.</t>
+        </is>
+      </c>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>The company's quarterly earnings managed to beat expectations, sending the stock price higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>ENG-20260606-009</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>be ready to burst</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>/bi ˈrɛdi tu bɜːrst/</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>(거품, 상황 등이) 터지기 일보 직전이다</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>Is there an AI stock market bubble, and is it ready to burst?</t>
+        </is>
+      </c>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>The pressure in the old pipe was so high it looked ready to burst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>ENG-20260606-010</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>face a challenging environment</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>/feɪs ə ˈtʃælɪndʒɪŋ ɪnˈvaɪrənmənt/</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>어려운 환경에 직면하다</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>The charity says it is facing 'an exceptionally challenging trading environment'.</t>
+        </is>
+      </c>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>Startups often face a challenging environment in their early years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>ENG-20260606-011</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>lack of confidence</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>/læk ɒv ˈkɒnfɪdəns/</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>자신감 부족</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>Loneliness and lack of confidence were challenges for young adults looking for relationships.</t>
+        </is>
+      </c>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>His lack of confidence often prevents him from speaking up in meetings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>ENG-20260606-012</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>get back to</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>/ɡɛt bæk tu/</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>~으로 돌아가다, ~을 다시 시작하다</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>Well, I gotta get, I gotta get back to the dishes.</t>
+        </is>
+      </c>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>I'll call you later; I need to get back to work now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>ENG-20260606-013</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>come into town</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>/kʌm ˈɪntuː taʊn/</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>(누군가) 마을/도시에 오다</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>In fact Emily’s coming into town this weekend, why don’t you say we all have dinner?</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>My cousin is coming into town next month, so we're planning a party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>ENG-20260606-014</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>have something on hold</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>/hæv ˈsʌmθɪŋ ɒn hoʊld/</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>~을 보류하다, 기다리게 하다, (전화 통화에서) 대기 상태로 두다</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>I’m here to pick up a dress that you have on hold.</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>We have the construction project on hold until we receive final approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>ENG-20260606-015</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>try on</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>/traɪ ɒn/</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>(옷 등을) 입어보다</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>Would you like to try it on Ms. Waltham?</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>I need to try on these shoes to make sure they fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>ENG-20260606-016</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>roll over</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>/roʊl ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>몸을 뒤척이다, 옆으로 굴리다</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>All right buddy, time to roll over.</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>The dog was sleeping on its back, then it rolled over onto its side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>ENG-20260606-017</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>cover one's eyes</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>/ˈkʌvər wʌnz aɪz/</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>눈을 가리다</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>(Covers his eyes) No, no-n-n-n-no!!</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>The child covered her eyes during the scary scene in the movie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>ENG-20260606-018</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>make like</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>/meɪk laɪk/</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>~인 척하다, ~하는 시늉을 하다 (구어체)</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>Monica is now wearing the dress while doing the dishes and is making like she is thanking her guests for coming to her wedding.</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>He's just making like he's busy, but he's actually doing nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>ENG-20260606-019</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>let in</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>/lɛt ɪn/</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>~을 안으로 들여보내다</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>No-no, let me in!</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>Could you please let the cat in? It's cold outside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>ENG-20260606-020</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>bounce in</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>/baʊns ɪn/</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>활기차게/껑충 뛰어 들어오다</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>She goes over and lets Phoebe bounce in wearing her own wedding dress.</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>The kids bounced in, excited about the ice cream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>ENG-20260606-021</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>stay up</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>/steɪ ʌp/</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>자지 않고 깨어 있다</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>I didn’t know I had to stay up all night before I went to this stupid sleep clinic!</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>We stayed up late last night talking and watching movies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>ENG-20260606-022</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>suck</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>/sʌk/</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>형편없다, 정말 나쁘다 (구어체)</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>This sucks! I didn’t know I had to stay up all night before I went to this stupid sleep clinic!</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>My vacation plans fell through; this really sucks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>ENG-20260606-023</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>handle something well</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>/ˈhændəl ˈsʌmθɪŋ wɛl/</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>~을 잘 처리하다, 잘 대응하다</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>Yeah, Rach, I think you’re handling that really well.</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>She handled the difficult client very well and managed to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>ENG-20260606-024</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>nothing to handle</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>/ˈnʌθɪŋ tu ˈhændəl/</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>처리할/대응할 문제가 없다, 걱정할 일이 없다</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>Handling it? What do you mean, handling it? There’s nothing to handle.</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>The situation is completely under control; there's nothing to handle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>ENG-20260606-025</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>have a problem with</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>/hæv ə ˈprɒbləm wɪð/</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>~에 문제가 있다, ~에 대해 불만/이의가 있다</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>Now, maybe I would have a problem with this if it wasn’t for me and Joshua.</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>I have a problem with the way you're speaking to your colleagues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>ENG-20260606-026</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>get married</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈmærid/</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>결혼하다</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>They’re not gonna get married anyway!</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>My sister is planning to get married next summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>ENG-20260606-027</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>rush into something</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>/rʌʃ ˈɪntuː ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>~을 성급하게 시작하다</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>They rushed into this thing so fast it’s ridiculous!</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>Don't rush into a decision; take your time to think it over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>ENG-20260606-028</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>somewhere along the way</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>/ˈsʌmˌwɛər əˈlɒŋ ðə weɪ/</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>어느 시점에, 도중에</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>And somewhere along the way, one of them is gonna realise what they’ve done.</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>I started out with a clear plan, but I think I lost my way somewhere along the way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>ENG-20260606-029</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>realize what one has done</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>/ˈriːəlaɪz wɒt wʌn hæz dʌn/</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>자신이 한 일을 깨닫다, 실수를 인지하다</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>One of them is gonna realise what they’ve done and they’re call the whole thing off.</t>
+        </is>
+      </c>
+      <c r="I1398" t="inlineStr">
+        <is>
+          <t>After a serious argument, he began to realize what he had done to upset her.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>ENG-20260606-030</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>look like</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>/lʊk laɪk/</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>~처럼 보이다</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>Because when I dance, I look like this…</t>
+        </is>
+      </c>
+      <c r="I1399" t="inlineStr">
+        <is>
+          <t>She looks like her mother, but she has her father's eyes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>ENG-20260606-031</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>be right there with someone</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>/bi raɪt ðɛər wɪð ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>(감정적으로) ~과 함께하다, ~의 심정을 이해하다</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>It’s like I’m right there with Joshua. You are right there with Emily.</t>
+        </is>
+      </c>
+      <c r="I1400" t="inlineStr">
+        <is>
+          <t>I know you're feeling frustrated, and I'm right there with you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>ENG-20260606-032</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>it's a tie</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>/ɪts ə taɪ/</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>무승부이다, 동점이다, (경쟁에서) 동률이다</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>And it’s y’know, it’s kinda like…. it’s a tie!</t>
+        </is>
+      </c>
+      <c r="I1401" t="inlineStr">
+        <is>
+          <t>After the final round, the score was 3-3, so it's a tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>ENG-20260606-033</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>it's a date</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>/ɪts ə deɪt/</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>(약속이) 성사되다, 만남이 확정되다</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>Yeah, all right, it’s a date.</t>
+        </is>
+      </c>
+      <c r="I1402" t="inlineStr">
+        <is>
+          <t>Sunday at 7? Perfect, it's a date!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>ENG-20260606-034</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>give someone the raspberry</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌmwʌn ðə ˈræzbɛri/</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>(조롱하거나 불만을 표시하며) 혀를 내밀고 입술을 떨어 '뿌' 소리를 내다</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>You hang in there. (Gives him the raspberry.)</t>
+        </is>
+      </c>
+      <c r="I1403" t="inlineStr">
+        <is>
+          <t>When the referee made a bad call, some fans gave him the raspberry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>ENG-20260606-035</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>go out to dinner</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>/ɡoʊ aʊt tu ˈdɪnər/</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>저녁 식사를 하러 외출하다</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>I hear that you and Joshua are going out to dinner with Ross and Emily.</t>
+        </is>
+      </c>
+      <c r="I1404" t="inlineStr">
+        <is>
+          <t>Let's go out to dinner tonight to celebrate your promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>ENG-20260606-036</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>be engaged for</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>/bi ɪnˈɡeɪdʒd fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>~동안 약혼 상태이다</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>I mean, they’re gonna be engaged for like what? A year?</t>
+        </is>
+      </c>
+      <c r="I1405" t="inlineStr">
+        <is>
+          <t>They were engaged for two years before they finally tied the knot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>ENG-20260606-037</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>stronger-than-expected</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>/ˈstrɒŋər ðæn ɪkˈspɛktɪd/</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>예상보다 강한, 예상을 뛰어넘는</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>The weeklong sell-off was exacerbated after a stronger-than-expected May jobs report.</t>
+        </is>
+      </c>
+      <c r="I1406" t="inlineStr">
+        <is>
+          <t>The company announced stronger-than-expected quarterly results, pleasing investors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>ENG-20260606-038</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>shake Wall Street</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>/ʃeɪk wɔːl striːt/</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>(뉴스, 사건 등이) 월스트리트를 흔들다, 증권 시장에 큰 충격을 주다</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>US stocks slump as fears over Big Tech shake Wall Street.</t>
+        </is>
+      </c>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>The sudden interest rate hike is expected to shake Wall Street and cause market volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>ENG-20260606-039</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>take a break</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>/teɪk ə breɪk/</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>휴식을 취하다</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>Let's take a break for fifteen minutes and then continue our discussion.</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>I've been working for hours; I need to take a break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>ENG-20260606-040</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>lose track of</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>/luːz træk ɒv/</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>~을 놓치다, (시간, 상황 등을) 잊어버리다</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>I lost track of time while reading that fascinating book.</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>It's easy to lose track of expenses when you're traveling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>ENG-20260606-041</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>pay attention to</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>/peɪ əˈtɛnʃən tu/</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>~에 주의를 기울이다</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>It's important to pay attention to details when preparing a report.</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>Please pay attention to the instructions carefully before you start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>ENG-20260606-042</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>take charge of</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>/teɪk tʃɑːrdʒ ɒv/</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>~을 책임지다, 담당하다</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>The manager asked me to take charge of the new project.</t>
+        </is>
+      </c>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>He decided to take charge of his health and started exercising regularly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>ENG-20260606-043</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>have a knack for</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>/hæv ə næk fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>~에 재주/요령이 있다</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>She has a real knack for solving complex puzzles quickly.</t>
+        </is>
+      </c>
+      <c r="I1412" t="inlineStr">
+        <is>
+          <t>My brother has a knack for making people laugh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>ENG-20260606-044</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>the elephant in the room</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>/ði ˈɛlɪfənt ɪn ðə ruːm/</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>(모두 알고 있지만) 아무도 언급하지 않는 불편한 문제</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>The company's declining sales were the elephant in the room during the board meeting.</t>
+        </is>
+      </c>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>Nobody wanted to discuss John's recent outburst; it was the elephant in the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>ENG-20260606-045</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>pay X a month</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>/peɪ ˈsʌmθɪŋ ə mʌnθ/</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>X(금액)를 매달 지불하다</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>Google to pay SpaceX $920 million a month</t>
+        </is>
+      </c>
+      <c r="I1414" t="inlineStr">
+        <is>
+          <t>The company decided to pay employees a bonus a month for their exceptional performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>ENG-20260606-046</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>ahead of X</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>/əˈhɛd ʌv ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>X(특정 시간/사건)에 앞서</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>Ahead of a planned IPO, SpaceX inked a deal</t>
+        </is>
+      </c>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>We need to finalize the presentation ahead of the big meeting next week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>ENG-20260606-047</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>rent capacity</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>/rɛnt kəˈpæsɪti/</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>용량/수용 능력을 빌리다</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>SpaceX inked a deal to rent compute capacity to Google</t>
+        </is>
+      </c>
+      <c r="I1416" t="inlineStr">
+        <is>
+          <t>Many cloud providers allow businesses to rent capacity on their servers as needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>ENG-20260606-048</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>live in a world where</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>/lɪv ɪn ə wɜrld wɛr/</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>~한 세상에 살다 (특정 상황을 묘사할 때)</t>
+        </is>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>We're living in a world where it's almost impossible for smaller entrants to come in</t>
+        </is>
+      </c>
+      <c r="I1417" t="inlineStr">
+        <is>
+          <t>We live in a world where technology is constantly evolving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>ENG-20260606-049</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>stock sink</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>/stɑk sɪŋk/</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>주가가 하락하다</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>Meta's stock sinks on report company could raise tens of billions of dollars</t>
+        </is>
+      </c>
+      <c r="I1418" t="inlineStr">
+        <is>
+          <t>Investors became concerned as the tech stock started to sink after the market opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>ENG-20260606-050</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>shares drop</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>/ʃɛrz drɑp/</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>주식이 떨어지다</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>Meta shares dropped after the Financial Times reported</t>
+        </is>
+      </c>
+      <c r="I1419" t="inlineStr">
+        <is>
+          <t>Company shares dropped significantly following the announcement of poor quarterly results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>ENG-20260606-051</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>crack X (a level/barrier)</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>/kræk ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>X(특정 수준/장벽)를 돌파하다</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>Bitcoin cracks $60,000, sinking to lowest level since October 2024</t>
+        </is>
+      </c>
+      <c r="I1420" t="inlineStr">
+        <is>
+          <t>The company's revenue is expected to crack the billion-dollar mark this year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>ENG-20260606-052</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>sink to lowest level</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>/sɪŋk tu ˈloʊɪst ˈlɛvəl/</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>최저 수준으로 떨어지다</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>Bitcoin cracks $60,000, sinking to lowest level since October 2024</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>After several consecutive losses, the team's ranking sank to its lowest level in years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>ENG-20260606-053</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>send yields higher</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>/sɛnd jildz ˈhaɪər/</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>수익률을 높이다</t>
+        </is>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>Friday sent yields higher and pressured risk assets</t>
+        </is>
+      </c>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>Increased demand for government bonds tends to send yields higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>ENG-20260606-054</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>pressure risk assets</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>/ˈprɛʃər rɪsk ˈæsɛts/</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>위험 자산을 압박하다</t>
+        </is>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>Friday sent yields higher and pressured risk assets.</t>
+        </is>
+      </c>
+      <c r="I1423" t="inlineStr">
+        <is>
+          <t>Rising interest rates are likely to pressure risk assets across the market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>ENG-20260606-055</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>highlight importance</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>/ˈhaɪˌlaɪt ɪmˈpɔrtəns/</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>중요성을 강조하다</t>
+        </is>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>The move highlights the growing importance of the technology sector</t>
+        </is>
+      </c>
+      <c r="I1424" t="inlineStr">
+        <is>
+          <t>The recent data breach highlights the importance of strong cybersecurity measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>ENG-20260606-056</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>rejuvenate sector</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>/rɪˈdʒuːvəˌneɪt ˈsɛktər/</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>해당 분야를 활성화/재생시키다</t>
+        </is>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>Mythos rejuvenated the cybersecurity sector.</t>
+        </is>
+      </c>
+      <c r="I1425" t="inlineStr">
+        <is>
+          <t>New government policies aim to rejuvenate the struggling manufacturing sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>ENG-20260606-057</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>upbeat earnings</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>/ˈʌpbit ˈɜrnɪŋz/</t>
+        </is>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>낙관적인/기분 좋은 실적 발표</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>upbeat earnings weren't enough for investors</t>
+        </is>
+      </c>
+      <c r="I1426" t="inlineStr">
+        <is>
+          <t>Despite upbeat earnings, the company's stock price remained flat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>ENG-20260606-058</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>rethink X (concept)</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>/riːˈθɪŋk ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>X(개념)를 재고하다</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>value investor Guy Spier rethought wealth, time and legacy</t>
+        </is>
+      </c>
+      <c r="I1427" t="inlineStr">
+        <is>
+          <t>After the major setback, the team had to rethink their entire strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>ENG-20260606-059</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>unveil X (product/plan)</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>/ʌnˈveɪl ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>X(제품/계획)를 공개하다</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>Amazon unveils latest warehouse robot as tech giants continue AI layoffs</t>
+        </is>
+      </c>
+      <c r="I1428" t="inlineStr">
+        <is>
+          <t>The CEO will unveil the company's new flagship smartphone at the conference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>ENG-20260606-060</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>drive up X (employment/prices)</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>/draɪv ʌp ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>X(고용/물가 등)를 증가시키다</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>it's actually driven up employment rather than the reverse</t>
+        </is>
+      </c>
+      <c r="I1429" t="inlineStr">
+        <is>
+          <t>Strong consumer demand can often drive up prices for goods and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>ENG-20260606-061</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>rather than X</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>/ˈræðər ðæn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>X 대신에</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>driven up employment rather than the reverse</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>We decided to walk rather than take a taxi, to enjoy the fresh air.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>ENG-20260606-062</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>spike (prices/rates)</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>/spaɪk/</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>(가격/금리가) 급등하다</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>Oil prices would spike if Iran's Houthi allies started attacking ships</t>
+        </is>
+      </c>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>Gasoline prices are expected to spike next week due to supply issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>ENG-20260606-063</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>pass through X (area/stage)</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>/pæs θru ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>X(지역/단계)를 통과하다</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>attacking ships passing through the Bab el-Mandeb Strait.</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>Tourists often pass through this historic district on their way to the museum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>ENG-20260606-064</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>stop X developing</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>/stɑp ˈsʌmθɪŋ dɪˈvɛləpɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>X가 발전하는 것을 막다</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>We need to stop AI developing without humans</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>The new regulations aim to stop harmful software developing undetected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>ENG-20260606-065</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>stocks slump</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>/stɑks slʌmp/</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>주식이 폭락하다</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>US stocks slump as fears over Big Tech shake Wall Street</t>
+        </is>
+      </c>
+      <c r="I1434" t="inlineStr">
+        <is>
+          <t>After the negative news, tech stocks slumped sharply, affecting many investors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>ENG-20260606-066</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>fears over X</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>/fɪrz ˈoʊvər ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>X에 대한 우려/두려움</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>as fears over Big Tech shake Wall Street</t>
+        </is>
+      </c>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>There are growing fears over the economic impact of the global pandemic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>ENG-20260606-067</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>take a stake in X</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>/teɪk ə steɪk ɪn ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>X에 지분을 투자하다</t>
+        </is>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>individual investors can take a stake in Musk's rockets-to-AI company.</t>
+        </is>
+      </c>
+      <c r="I1436" t="inlineStr">
+        <is>
+          <t>Many venture capitalists are looking to take a stake in promising startups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>ENG-20260606-068</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>jobs boom</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>/dʒɑbz bum/</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>일자리 호황</t>
+        </is>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>Hospitality jobs boom as US prepares for World Cup</t>
+        </is>
+      </c>
+      <c r="I1437" t="inlineStr">
+        <is>
+          <t>The construction sector experienced a jobs boom last quarter, creating thousands of new positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>ENG-20260606-069</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>prepare for X (event)</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>/prɪˈpɛr fɔr ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>X(이벤트)를 준비하다</t>
+        </is>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>as US prepares for World Cup</t>
+        </is>
+      </c>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>The athletes are intensely training to prepare for the upcoming Olympics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>ENG-20260606-070</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>month in a row</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>/mʌnθ ɪn ə roʊ/</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>연속적으로 몇 달 동안</t>
+        </is>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>It is the third month in a row US jobs figures have beaten expectations.</t>
+        </is>
+      </c>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>She won the employee of the month award for the second month in a row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>ENG-20260606-071</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>throw away X (items/waste)</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>/θroʊ əˈweɪ ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>X(물건/쓰레기)를 버리다</t>
+        </is>
+      </c>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>Instead of throwing away byproducts of food processing</t>
+        </is>
+      </c>
+      <c r="I1440" t="inlineStr">
+        <is>
+          <t>Please don't throw away these old clothes; they can be donated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>ENG-20260606-072</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>fuel by X (something)</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>/fjuəl baɪ ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>X(무엇)에 의해 추진/촉진되다</t>
+        </is>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>fueled largely by AI.</t>
+        </is>
+      </c>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>The economic recovery was fueled by strong consumer spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>ENG-20260606-073</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>look into X (a matter/issue)</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>/lʊk ˈɪntu ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>X(문제/사안)를 조사하다</t>
+        </is>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>BBC's Samira Hussain looks into whether that bubble will burst.</t>
+        </is>
+      </c>
+      <c r="I1442" t="inlineStr">
+        <is>
+          <t>The police are looking into the cause of the mysterious disappearance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>ENG-20260606-074</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>fire pieces (pottery)</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>/faɪər pisɪz/</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>(도자기를) 굽다</t>
+        </is>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>Final pieces fired at Denby as production ends</t>
+        </is>
+      </c>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>The artist will now fire the clay pieces in a kiln to harden them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>ENG-20260606-075</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>hugely proud</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>/ˈhjuːdʒli praʊd/</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>매우 자랑스러워하는</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>We are so hugely proud of everything this Derbyshire pottery has achieved</t>
+        </is>
+      </c>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>Her parents were hugely proud of her graduation from medical school.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>ENG-20260606-076</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>hear about X (news/event)</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>/hɪər əˈbaʊt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>X(소식/사건)에 대해 듣다</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>I mean maybe you didn’t hear about a serious relationship called me and Joshua?</t>
+        </is>
+      </c>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>Did you hear about the new restaurant that just opened downtown?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>ENG-20260606-077</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>be on X dates</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>/bi ɑn ˈsʌmθɪŋ deɪts/</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>X번의 데이트를 하다</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>Oh, I thought you guys had just been on like four dates</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>They had only been on two dates before deciding they wanted to be exclusive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>ENG-20260606-078</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>get to the dishes</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>/gɛt tu ðə ˈdɪʃɪz/</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>설거지를 시작하다</t>
+        </is>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>Well, I gotta get, I gotta get back to the dishes.</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>After dinner, I always get to the dishes right away so the sink doesn't fill up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>ENG-20260606-079</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>get to work</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>/gɛt tu wɜrk/</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>일을 시작하다</t>
+        </is>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>I gotta get to work.</t>
+        </is>
+      </c>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>The team needs to stop talking and get to work on this urgent project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>ENG-20260606-080</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>say X (as a suggestion)</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>/seɪ ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>X(제안)는 어때?</t>
+        </is>
+      </c>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>why don’t you say we all have dinner? Say, Sunday night?</t>
+        </is>
+      </c>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>How about we go for a hike? Say, early in the morning?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>ENG-20260606-081</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>pick up X (item)</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>/pɪk ʌp ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>X(물건)를 찾아오다/가져오다</t>
+        </is>
+      </c>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>Monica and Phoebe are there to pick up Emily’s dress.</t>
+        </is>
+      </c>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>I need to pick up my dry cleaning before the store closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>ENG-20260606-082</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>end up (doing X)</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>/ɛnd ʌp ˈduɪŋ ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>결국 X하게 되다</t>
+        </is>
+      </c>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>about have of these are gonna end up getting divorced.</t>
+        </is>
+      </c>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>If you keep procrastinating, you'll end up rushing at the last minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>ENG-20260606-083</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>gasp at X (something)</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>/gæsp æt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>X(무엇)에 놀라 숨을 들이키다</t>
+        </is>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>Phoebe and Monica both gasp at the dress.</t>
+        </is>
+      </c>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>The audience gasped at the magician's incredible trick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>ENG-20260606-084</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>stare at X (oneself/something)</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>/stɛr æt ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>X(자신/무엇)을 응시하다</t>
+        </is>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>Monica is wearing the dress and starring at herself in the mirror.</t>
+        </is>
+      </c>
+      <c r="I1453" t="inlineStr">
+        <is>
+          <t>It's rude to stare at people you don't know.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>ENG-20260606-085</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>be closing</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>/bi ˈkloʊzɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>문을 닫으려 하다 (영업이 끝나다)</t>
+        </is>
+      </c>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>We’re closing.</t>
+        </is>
+      </c>
+      <c r="I1454" t="inlineStr">
+        <is>
+          <t>The store announced it was closing in ten minutes, so we hurried our shopping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>ENG-20260606-086</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>take off X (clothing/item)</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>/teɪk ɔf ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>X(옷/물건)를 벗다/떼어내다</t>
+        </is>
+      </c>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>Goes to take off the dress.</t>
+        </is>
+      </c>
+      <c r="I1455" t="inlineStr">
+        <is>
+          <t>Please take off your shoes before entering the house.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>ENG-20260606-087</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>get back X (item)</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>/gɛt bæk ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>X(물건)를 돌려받다/되찾다</t>
+        </is>
+      </c>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>And could I get my ring back?</t>
+        </is>
+      </c>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>I lent him my book last week, and I hope to get it back soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>ENG-20260606-088</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>give back X (item)</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>/gɪv bæk ˈsʌmθɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>X(물건)를 돌려주다</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>She disgustedly takes the ring off and gives it back.</t>
+        </is>
+      </c>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>You should always give back borrowed items promptly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>ENG-20260606-089</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>discover a surprise</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>/dɪˈskʌvər ə sərˈpraɪz/</t>
+        </is>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>놀라운 것을 발견하다</t>
+        </is>
+      </c>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>Rolls him over, and discovers a surprise</t>
+        </is>
+      </c>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>While cleaning the attic, she discovered a surprise: a box of old family photos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>ENG-20260606-090</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>do the dishes</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>/du ðə ˈdɪʃɪz/</t>
+        </is>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>설거지하다</t>
+        </is>
+      </c>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>Monica is doing the dishes.</t>
+        </is>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>It's my turn to do the dishes tonight after dinner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>ENG-20260606-091</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>just a second</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>/dʒʌst ə ˈsɛkənd/</t>
+        </is>
+      </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>잠깐만요</t>
+        </is>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>Uh, just a second!</t>
+        </is>
+      </c>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>Can you hold on for just a second? I need to grab my keys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>ENG-20260606-092</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>hold on (for a minute)</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>/hoʊld ɑn/</t>
+        </is>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>잠시 기다리다</t>
+        </is>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>Can you just hold on for one minute?</t>
+        </is>
+      </c>
+      <c r="I1461" t="inlineStr">
+        <is>
+          <t>Please hold on, I'll connect you to the manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>ENG-20260606-093</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>call X off (plan/event)</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>/kɔl ˈsʌmθɪŋ ɔf/</t>
+        </is>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>X(계획/행사)를 취소하다</t>
+        </is>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>they’re call the whole thing off.</t>
+        </is>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>Due to the heavy rain, they had to call off the outdoor concert.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1462"/>
+  <dimension ref="A1:I1533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69130,6 +69130,3343 @@
         </is>
       </c>
     </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>ENG-20260607-001</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>hang in the balance</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>/hæŋ ɪn ðə ˈbæləns/</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>풍전등화 상태에 있다, 어떻게 될지 모르는 불안한 상황에 처하다</t>
+        </is>
+      </c>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>The conflict is about to reach its 100th day, with peace negotiations hanging in the balance.</t>
+        </is>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>The future of the entire merger hangs in the balance as we wait for the board's decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>ENG-20260607-002</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>hit a wall</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>/hɪt ə wɔːl/</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>진전을 이루지 못하고 한계에 부딪히다, 정체 상태에 빠지다</t>
+        </is>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>The monster rally in semiconductor stocks hit a wall on Friday.</t>
+        </is>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>After working on the software design for ten straight hours, I finally hit a wall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>ENG-20260607-003</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>go one's own way</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>/ɡoʊ wʌnz oʊn weɪ/</t>
+        </is>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>타인의 조언이나 대세를 따르지 않고 독자 노선을 걷다</t>
+        </is>
+      </c>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>Abel goes his own way with new Berkshire investments, including billions for AI.</t>
+        </is>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>Even though everyone told her to get a stable job, she decided to go her own way and start a business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>ENG-20260607-004</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>hear back from</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>/hɪər bæk frɒm/</t>
+        </is>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>~로부터 연락이나 피드백을 받다</t>
+        </is>
+      </c>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>Four people who were not hearing back from job applications shared what they did differently.</t>
+        </is>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>I did the job interview last Tuesday, but I have not heard back from them yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>ENG-20260607-005</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>burst the bubble</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>/bɜːst ðə ˈbʌbəl/</t>
+        </is>
+      </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>거품을 터뜨리다, 환상을 깨뜨리다</t>
+        </is>
+      </c>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>BBC's Samira Hussain looks into whether that AI stock market bubble is ready to burst.</t>
+        </is>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>I hate to burst your bubble, but the boss is not going to approve this budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>ENG-20260607-006</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>make up for lost time</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>/meɪk ʌp fɔːr lɒst taɪm/</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>잃어버린 시간이나 늦어진 것을 만회하다</t>
+        </is>
+      </c>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>Clearly I did not start drinking enough at the start of the meal, so Chandler starts to make up for lost time.</t>
+        </is>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>We have not seen each other in years, so we stayed up all night to make up for lost time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>ENG-20260607-007</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>buy off the rack</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>/baɪ ɒf ðə ræk/</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>맞춤복이 아닌 일반 기성복을 사다</t>
+        </is>
+      </c>
+      <c r="H1469" t="inlineStr">
+        <is>
+          <t>You do not need this custom-made satin gown; you can wear off the rack.</t>
+        </is>
+      </c>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>Since I was on a tight budget, I decided to buy my wedding suit off the rack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>ENG-20260607-008</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>earmark something for</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>/ˈɪəmɑːk ˈsʌmθɪŋ fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>특정 목적을 위해 자금 등을 미리 지정해 두다</t>
+        </is>
+      </c>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>I have been saving this money for six years and I kinda had some of it earmarked for the future.</t>
+        </is>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>Most of our research budget has been earmarked for artificial intelligence development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>ENG-20260607-009</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>put a price on</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>/pʊt ə praɪs ɒn/</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>가치를 돈으로 환산하다, 가격을 매기다</t>
+        </is>
+      </c>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>Which means you had seven years of beach fun and you cannot put a price on that sweetie.</t>
+        </is>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>You cannot put a price on peace of mind, which is why we bought insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>ENG-20260607-010</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>tie the knot</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>/taɪ ðə nɒt/</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>결혼하다, 결실을 맺다</t>
+        </is>
+      </c>
+      <c r="H1472" t="inlineStr">
+        <is>
+          <t>Monica and Chandler were planning to tie the knot soon, but faced financial troubles.</t>
+        </is>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>They finally decided to tie the knot after dating for over eight years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>ENG-20260607-011</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>burn the candle at both ends</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>/bɜːn ðə ˈkændəl æt boʊθ endz/</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>밤낮으로 쉬지 않고 무리하게 일해 건강을 해치다</t>
+        </is>
+      </c>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>The CEO had been burning the candle at both ends before his unexpected diagnosis.</t>
+        </is>
+      </c>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>If you keep burning the candle at both ends, you will experience severe burnout soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>ENG-20260607-012</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>brace for</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>/breɪs fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>위기나 불쾌한 상황에 단단히 대비하다</t>
+        </is>
+      </c>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>Investors are bracing for a volatile trading week after the jobs report.</t>
+        </is>
+      </c>
+      <c r="I1474" t="inlineStr">
+        <is>
+          <t>The coastal towns are bracing for the arrival of the category 4 hurricane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>ENG-20260607-013</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>play catch-up</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>/pleɪ ˈkætʃʌp/</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>선두 주자나 뒤처진 실적을 따라잡기 위해 허덕이다</t>
+        </is>
+      </c>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>Local automakers are playing catch-up with Chinese advanced EV technology.</t>
+        </is>
+      </c>
+      <c r="I1475" t="inlineStr">
+        <is>
+          <t>We spent the entire year playing catch-up after our main competitor launched their new app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>ENG-20260607-014</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>ride high</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>/raɪd haɪ/</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>기세등등하게 잘 나가다, 상위권에 머무르다</t>
+        </is>
+      </c>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>Chip stocks were riding high before hitting a solid wall last Friday.</t>
+        </is>
+      </c>
+      <c r="I1476" t="inlineStr">
+        <is>
+          <t>The tech company is riding high on the success of its new software update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>ENG-20260607-015</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>hedge one's bets</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>/hedʒ wʌnz bets/</t>
+        </is>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>손해에 대비해 여러 곳에 분산 투자를 하거나 대안을 마련하다</t>
+        </is>
+      </c>
+      <c r="H1477" t="inlineStr">
+        <is>
+          <t>Investors are buying gold to hedge their bets against a major market crash.</t>
+        </is>
+      </c>
+      <c r="I1477" t="inlineStr">
+        <is>
+          <t>I applied for several jobs to hedge my bets in case my first choice falls through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>ENG-20260607-016</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>wipe out</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>/waɪp aʊt/</t>
+        </is>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>완전히 쓸어버리다, 파산 상태로 만들다, 형체 없이 지우다</t>
+        </is>
+      </c>
+      <c r="H1478" t="inlineStr">
+        <is>
+          <t>A sudden market correction could wipe out billions of dollars in stock value.</t>
+        </is>
+      </c>
+      <c r="I1478" t="inlineStr">
+        <is>
+          <t>The heavy floods wiped out the entire agricultural harvest in that region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>ENG-20260607-017</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>bottom out</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>/ˈbɒtəm aʊt/</t>
+        </is>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>최저점을 찍고 이제 반등할 국면에 가다</t>
+        </is>
+      </c>
+      <c r="H1479" t="inlineStr">
+        <is>
+          <t>Analysts believe that the falling crypto asset prices are finally about to bottom out.</t>
+        </is>
+      </c>
+      <c r="I1479" t="inlineStr">
+        <is>
+          <t>The housing market seems to have bottomed out, and prices are starting to rise again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>ENG-20260607-018</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>hit a glass ceiling</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>/hɪt ə ɡlɑːs ˈsiːlɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>보이지 않는 장벽(유리천장)에 가로막히다</t>
+        </is>
+      </c>
+      <c r="H1480" t="inlineStr">
+        <is>
+          <t>Young female remote employees often fear hitting a glass ceiling in promotion circles.</t>
+        </is>
+      </c>
+      <c r="I1480" t="inlineStr">
+        <is>
+          <t>She left the corporation after hitting a glass ceiling that prevented her from becoming a VP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>ENG-20260607-019</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>raise a red flag</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>/reɪz ə red flæɡ/</t>
+        </is>
+      </c>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>위험 신호를 보내다, 경고를 표하다</t>
+        </is>
+      </c>
+      <c r="H1481" t="inlineStr">
+        <is>
+          <t>The unexpected soda recall raised a red flag for the manufacturing safety inspectors.</t>
+        </is>
+      </c>
+      <c r="I1481" t="inlineStr">
+        <is>
+          <t>The sudden drop in active users raised a red flag for our product development team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>ENG-20260607-020</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>throw a fit</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>/θroʊ ə fɪt/</t>
+        </is>
+      </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>노발대발하다, 몹시 성을 내다</t>
+        </is>
+      </c>
+      <c r="H1482" t="inlineStr">
+        <is>
+          <t>Monica was about to throw a fit when she found out her wedding fund was spent on a beach house.</t>
+        </is>
+      </c>
+      <c r="I1482" t="inlineStr">
+        <is>
+          <t>The customer threw a fit when he was told that his reservation had been canceled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>ENG-20260607-021</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>count one's blessings</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>/kaʊnt wʌnz ˈblesɪŋz/</t>
+        </is>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>나쁜 와중에도 긍정적으로 감사하게 여기다</t>
+        </is>
+      </c>
+      <c r="H1483" t="inlineStr">
+        <is>
+          <t>Even with her diagnosis, Guy Spier rathers count his blessings and focus on rare disease research.</t>
+        </is>
+      </c>
+      <c r="I1483" t="inlineStr">
+        <is>
+          <t>Instead of complaining about our low salaries, we should count our blessings that we still have jobs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>ENG-20260607-022</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>live paycheck to paycheck</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>/lɪv ˈpeɪtʃek tuː ˈpeɪtʃek/</t>
+        </is>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>그달 벌어 그달 먹고살며 저축할 여유가 없다</t>
+        </is>
+      </c>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>Before starting value investing, many young people live paycheck to paycheck.</t>
+        </is>
+      </c>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>With rising inflation rates, more and more families are forced to live paycheck to paycheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>ENG-20260607-023</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>pencil something in</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>/ˈpensəl ˈsʌmθɪŋ ɪn/</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>나중에 바뀔 수 있으니 일단 일정을 임시로 등록하다</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>Let us pencil in a quick meeting for next Thursday to discuss the AI project.</t>
+        </is>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>I will pencil in the lunch date for next Monday, but let me check my calendar first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>ENG-20260607-024</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>hit the books</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>/hɪt ðə bʊks/</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>코박고 공부에 매진하다, 벼락치기를 하다</t>
+        </is>
+      </c>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>Gen Z workers need to hit the books to master the new technical AI tools.</t>
+        </is>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>I have a big exam tomorrow morning, so I really need to hit the books tonight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>ENG-20260607-025</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>pan out</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>/pæn aʊt/</t>
+        </is>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>일이 특정한 방향으로 잘 전개되다, 잘 진행되다</t>
+        </is>
+      </c>
+      <c r="H1487" t="inlineStr">
+        <is>
+          <t>We will have to see how Greg Abel's long-term AI strategy pans out.</t>
+        </is>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>The plans we made did not pan out the way we originally expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>ENG-20260607-026</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>take something for granted</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>/teɪk ˈsʌmθɪŋ fɔːr ˈɡrɑːntɪd/</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>그 가치나 고마움을 모른 채 당연한 기정사실로 여기다</t>
+        </is>
+      </c>
+      <c r="H1488" t="inlineStr">
+        <is>
+          <t>Monica took her wedding fund for granted until she learned it was spent.</t>
+        </is>
+      </c>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>Do not take your health for granted; make sure to eat well and exercise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>ENG-20260607-027</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>on the rise</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>/ɒn ðə raɪz/</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>증가 추세에 있는, 오르고 있는</t>
+        </is>
+      </c>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>As bitcoin dropped to its lowest price, a new Wall Street crypto hype is on the rise.</t>
+        </is>
+      </c>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>Demand for electric vehicles has been on the rise over the last three quarters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>ENG-20260607-028</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>flock to</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>/flɒk tuː/</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>~로 떼 지어 몰려들다</t>
+        </is>
+      </c>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>As bitcoin dropped, investors flock to a new type of crypto investment.</t>
+        </is>
+      </c>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>Tourists flock to the coastal town every summer to enjoy the beaches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>ENG-20260607-029</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>punch back</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>/pʌntʃ bæk/</t>
+        </is>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>반격하다, 맞서 싸우다</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>Wall Street's fear gauge punches back as the crash up in chip stocks finally reverses.</t>
+        </is>
+      </c>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>The small company decided to punch back with a clever advertising campaign against its giant competitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>ENG-20260607-030</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>narrow down</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>/ˈnærəʊ daʊn/</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>범위를 좁히다</t>
+        </is>
+      </c>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>Four people who had trouble finding jobs shared how they managed to narrow down their target list of employers.</t>
+        </is>
+      </c>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>We need to narrow down our options before we make the final decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>ENG-20260607-031</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>go to hell</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>/ɡəʊ tuː hel/</t>
+        </is>
+      </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>(상황이나 계획 등이) 완전히 망가지다, 나락으로 떨어지다</t>
+        </is>
+      </c>
+      <c r="H1493" t="inlineStr">
+        <is>
+          <t>We started saving again when you were dating Richard and then that went to hell, so we redid the kitchen.</t>
+        </is>
+      </c>
+      <c r="I1493" t="inlineStr">
+        <is>
+          <t>Our travel plans went to hell when the airline canceled all flights due to the blizzard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>ENG-20260607-032</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>be made for each other</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>/biː meɪd fɔːr iːtʃ ˈʌðə/</t>
+        </is>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>천생연분이다, 서로 아주 잘 어울리다</t>
+        </is>
+      </c>
+      <c r="H1494" t="inlineStr">
+        <is>
+          <t>Oh, you guys are so made for each other.</t>
+        </is>
+      </c>
+      <c r="I1494" t="inlineStr">
+        <is>
+          <t>They have the same hobbies and values; they are truly made for each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>ENG-20260607-033</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>blaze a trail</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>/bleɪz ə treɪl/</t>
+        </is>
+      </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>새로운 길을 개척하다, 선구자 역할을 하다</t>
+        </is>
+      </c>
+      <c r="H1495" t="inlineStr">
+        <is>
+          <t>The young entrepreneur wants to blaze a trail in the field of renewable energy.</t>
+        </is>
+      </c>
+      <c r="I1495" t="inlineStr">
+        <is>
+          <t>She blazed a trail for female engineers in the aerospace industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>ENG-20260607-034</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>keep pace with</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>/kiːp peɪs wɪð/</t>
+        </is>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>~와 발맞추어 나아가다, 보조를 맞추다</t>
+        </is>
+      </c>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>Traditional retailers are struggling to keep pace with the rapid growth of e-commerce.</t>
+        </is>
+      </c>
+      <c r="I1496" t="inlineStr">
+        <is>
+          <t>Employees must continuously learn new skills to keep pace with technological advancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>ENG-20260607-035</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>gasp for air</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>/ɡɑːsp fɔːr eə/</t>
+        </is>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>숨을 헐떡이다, (경제적 상황 등에서) 필사적으로 버티다</t>
+        </is>
+      </c>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>Small startups are gasping for air as venture capital funding dries up.</t>
+        </is>
+      </c>
+      <c r="I1497" t="inlineStr">
+        <is>
+          <t>The company was gasping for air under the pressure of mounting debts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>ENG-20260607-036</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>fall through the cracks</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>/fɔːl θruː ðə kræks/</t>
+        </is>
+      </c>
+      <c r="G1498" t="inlineStr">
+        <is>
+          <t>부주의 등으로 관리/관심 대상에서 빠지다, 누락되다</t>
+        </is>
+      </c>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>In a remote work environment, some junior employees feel their training falls through the cracks.</t>
+        </is>
+      </c>
+      <c r="I1498" t="inlineStr">
+        <is>
+          <t>We must double-check the client list to ensure no important account falls through the cracks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>ENG-20260607-037</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>climb the corporate ladder</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>/klaɪm ðə ˈkɔːpərət ˈlædə/</t>
+        </is>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>회사에서 승진 코스를 밟다, 출세하다</t>
+        </is>
+      </c>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>Young workers are often eager to climb the corporate ladder as quickly as possible.</t>
+        </is>
+      </c>
+      <c r="I1499" t="inlineStr">
+        <is>
+          <t>She spent ten years working late nights to climb the corporate ladder to vice president.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>ENG-20260607-038</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>show someone the ropes</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>/ʃəʊ ˈsʌmwʌn ðə rəʊps/</t>
+        </is>
+      </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>업무의 기본 요령을 알려주다, 일하는 방법을 가르쳐 주다</t>
+        </is>
+      </c>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>A senior colleague was assigned to show me the ropes during my first week at the office.</t>
+        </is>
+      </c>
+      <c r="I1500" t="inlineStr">
+        <is>
+          <t>Don't worry about the complex software; the team will show you the ropes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>ENG-20260607-039</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>carve out a niche</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>/kɑːv aʊt ə niːʃ/</t>
+        </is>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>틈새시장을 개척하다, 자신만의 확고한 영역을 구축하다</t>
+        </is>
+      </c>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>The custom baker managed to carve out a niche in the organic gluten-free market.</t>
+        </is>
+      </c>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>Our startup carved out a niche by offering hyper-local delivery services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>ENG-20260607-040</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>strike it rich</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>/straɪk ɪt rɪtʃ/</t>
+        </is>
+      </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>벼락부자가 되다, 갑자기 큰돈을 벌다</t>
+        </is>
+      </c>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>Many early investors in crypto hoped to strike it rich within a few months.</t>
+        </is>
+      </c>
+      <c r="I1502" t="inlineStr">
+        <is>
+          <t>He dreamed of striking it rich by developing a viral smartphone app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>ENG-20260607-041</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>sweep something under the rug</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>/swiːp ˈsʌmθɪŋ ˈʌndə ðə rʌɡ/</t>
+        </is>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>(문제를) 숨기려 하다, 은폐하다</t>
+        </is>
+      </c>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>Instead of solving the accounting discrepancy, they tried to sweep it under the rug.</t>
+        </is>
+      </c>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>You cannot just sweep these customer complaints under the rug and hope they go away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>ENG-20260607-042</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>pop the question</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>/pɒp ðə ˈkwestʃən/</t>
+        </is>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>청혼하다, 프로포즈하다</t>
+        </is>
+      </c>
+      <c r="H1504" t="inlineStr">
+        <is>
+          <t>We did not think Chandler would ever pop the question to Monica.</t>
+        </is>
+      </c>
+      <c r="I1504" t="inlineStr">
+        <is>
+          <t>He planned a romantic dinner by the lake to pop the question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>ENG-20260607-043</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>tighten the purse strings</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>/ˈtaɪtn ðə pɜːs strɪŋz/</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>지갑을 닫다, 지출을 줄이다, 예산을 아끼다</t>
+        </is>
+      </c>
+      <c r="H1505" t="inlineStr">
+        <is>
+          <t>Monica's parents had to tighten the purse strings after they spent the money on the beach house.</t>
+        </is>
+      </c>
+      <c r="I1505" t="inlineStr">
+        <is>
+          <t>The board decided to tighten the purse strings on all travel expenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>ENG-20260607-044</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>live beyond one's means</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>/lɪv bɪˈjɒnd wʌnz miːnz/</t>
+        </is>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>자신의 소득 수준 이상으로 과소비하다, 분수에 넘치게 살다</t>
+        </is>
+      </c>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>Some young professionals live beyond their means to show off on social media.</t>
+        </is>
+      </c>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>If you keep living beyond your means, you will end up with massive credit card debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>ENG-20260607-045</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>bring home the bacon</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>/brɪŋ həʊm ðə ˈbeɪkən/</t>
+        </is>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>생활비를 벌다, 가장 역할을 하다</t>
+        </is>
+      </c>
+      <c r="H1507" t="inlineStr">
+        <is>
+          <t>Now that they are getting married, both of them want to bring home the bacon.</t>
+        </is>
+      </c>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>While my husband takes care of the children, I bring home the bacon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>ENG-20260607-046</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>rule of thumb</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>/ruːl ɒv θʌm/</t>
+        </is>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>경험에서 얻은 대략적인 원칙, 일반 상식</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>As a rule of thumb, you should save at least twenty percent of your monthly income.</t>
+        </is>
+      </c>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>A good rule of thumb is to drink at least eight glasses of water every day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>ENG-20260607-047</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>fend for oneself</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>/fend fɔː wʌnˈself/</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>남의 도움 없이 혼자 힘으로 살아가다</t>
+        </is>
+      </c>
+      <c r="H1509" t="inlineStr">
+        <is>
+          <t>When their parents spent the fund, they expected their children to fend for themselves.</t>
+        </is>
+      </c>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>He had to learn to fend for himself when he moved to New York at eighteen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>ENG-20260607-048</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>keep in the loop</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>/kiːp ɪn ðə luːp/</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>핵심 진행 상황을 계속 알려주다, 정보 공유망에 남겨두다</t>
+        </is>
+      </c>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>Please keep me in the loop regarding the changes to the wedding schedule.</t>
+        </is>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>Make sure to keep the stakeholders in the loop during the software transition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>ENG-20260607-049</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>on the tip of one's tongue</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>/ɒn ðə tɪp ɒv wʌnz tʌŋ/</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>(이름이나 단어가) 생각날 듯 말 듯 입가에 맴돌다</t>
+        </is>
+      </c>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>I can't recall the name of her fourth husband, though it is on the tip of my tongue.</t>
+        </is>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>The answer was on the tip of my tongue, but I couldn't say it in time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>ENG-20260607-050</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>ring true</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>/rɪŋ truː/</t>
+        </is>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>진실인 것처럼 들리다, 큰 공감을 주다</t>
+        </is>
+      </c>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>The professor's warnings about remote work pitfalls ring true for many recent graduates.</t>
+        </is>
+      </c>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>His explanation didn't quite ring true to me, so I decided to verify it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>ENG-20260607-051</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>look on the bright side</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>/lʊk ɒn ðə braɪt saɪd/</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>긍정적인 면을 보다, 낙관적으로 생각하다</t>
+        </is>
+      </c>
+      <c r="H1513" t="inlineStr">
+        <is>
+          <t>If you look on the bright side, at least we don't have to spend money on an expensive band.</t>
+        </is>
+      </c>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>Even though our flight was delayed, we looked on the bright side and spent the day exploring the city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>ENG-20260607-052</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>hit a jackpot</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>/hɪt ə ˈdʒækpɒt/</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>대박이 나다, 엄청난 행운을 얻다</t>
+        </is>
+      </c>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>Investing in the new tech startup was like hitting a jackpot for early backers.</t>
+        </is>
+      </c>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>He hit the jackpot when his video went viral, attracting millions of subscribers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>ENG-20260607-053</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>sell like hotcakes</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>/sel laɪk ˈhɒtkeɪks/</t>
+        </is>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>불티나게 팔리다</t>
+        </is>
+      </c>
+      <c r="H1515" t="inlineStr">
+        <is>
+          <t>The new electric vehicles are selling like hotcakes in the metropolitan areas.</t>
+        </is>
+      </c>
+      <c r="I1515" t="inlineStr">
+        <is>
+          <t>Tickets for the rock concert sold like hotcakes and were gone within five minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>ENG-20260607-054</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>take into account</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>/teɪk ˈɪntuː əˈkaʊnt/</t>
+        </is>
+      </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>고려하다, 참작하다</t>
+        </is>
+      </c>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>We must take into account the rising cost of materials before signing the contract.</t>
+        </is>
+      </c>
+      <c r="I1516" t="inlineStr">
+        <is>
+          <t>When planning the outdoor wedding, you have to take the weather into account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>ENG-20260607-055</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>on the horizon</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>/ɒn ðə həˈraɪzn/</t>
+        </is>
+      </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>가까운 시일 내에 일어날 것 같은, 머지않은</t>
+        </is>
+      </c>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>Economists warning that a minor recession might be on the horizon.</t>
+        </is>
+      </c>
+      <c r="I1517" t="inlineStr">
+        <is>
+          <t>With new product launches on the horizon, the team is working overtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>ENG-20260607-056</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>take for a spin</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>/teɪk fɔːr ə spɪn/</t>
+        </is>
+      </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>(차량 등을) 시험 삼아 몰아보다, 시승하다</t>
+        </is>
+      </c>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>He bought a new electric car and couldn't wait to take it for a spin.</t>
+        </is>
+      </c>
+      <c r="I1518" t="inlineStr">
+        <is>
+          <t>Would you like to take my new bicycle for a spin around the block?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>ENG-20260607-057</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>go the distance</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>/ɡəʊ ðə ˈdɪstəns/</t>
+        </is>
+      </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>끝까지 버텨내다, 끝장을 보다</t>
+        </is>
+      </c>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>Only the strongest startups with deep pockets can go the distance in this competitive market.</t>
+        </is>
+      </c>
+      <c r="I1519" t="inlineStr">
+        <is>
+          <t>It is a tough marathon, but she has trained hard enough to go the distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>ENG-20260607-058</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>keep under wraps</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>/kiːp ˈʌndə ræps/</t>
+        </is>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>비밀로 하다, 대외비로 부치다</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>The company kept the new AI chip design under wraps until the launch event.</t>
+        </is>
+      </c>
+      <c r="I1520" t="inlineStr">
+        <is>
+          <t>We need to keep the surprise party under wraps so she doesn't suspect anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>ENG-20260607-059</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>think highly of</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>/θɪŋk ˈhaɪli ɒv/</t>
+        </is>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>~를 높이 평가하다, 우호적으로 생각하다</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>Warren Buffett always thought highly of his disciple Guy Spier.</t>
+        </is>
+      </c>
+      <c r="I1521" t="inlineStr">
+        <is>
+          <t>The manager thinks highly of your technical skills and work ethic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>ENG-20260607-060</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>make headway</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>/meɪk ˈhedweɪ/</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>진전을 보이다, 나아가다</t>
+        </is>
+      </c>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>The peace negotiators are struggling to make headway in the ongoing conflict.</t>
+        </is>
+      </c>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>After hours of hard work, we are finally making some headway on the project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>ENG-20260607-061</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>back on track</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>/bæk ɒn træk/</t>
+        </is>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>정상 궤도로 복귀한, 다시 순조롭게 진행되는</t>
+        </is>
+      </c>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>We need to get our project budget back on track after the unexpected expenses.</t>
+        </is>
+      </c>
+      <c r="I1523" t="inlineStr">
+        <is>
+          <t>With the new manager on board, the team is finally back on track.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>ENG-20260607-062</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>pull out</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>/pʊl aʊt/</t>
+        </is>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>철수하다, 손을 떼다</t>
+        </is>
+      </c>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>Due to rising geopolitical tensions, several foreign investors decided to pull out of the country.</t>
+        </is>
+      </c>
+      <c r="I1524" t="inlineStr">
+        <is>
+          <t>The major sponsor pulled out of the event at the last minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>ENG-20260607-063</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>cut ties</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>/kʌt taɪz/</t>
+        </is>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>관계를 끊다, 단절하다</t>
+        </is>
+      </c>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>The trade department decided to cut ties with suppliers who violated environmental standards.</t>
+        </is>
+      </c>
+      <c r="I1525" t="inlineStr">
+        <is>
+          <t>She decided to cut ties with her former partner after the disagreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>ENG-20260607-064</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>make a fortune</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>/meɪk ə ˈfɔːtʃuːn/</t>
+        </is>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>큰돈을 벌다, 부자가 되다</t>
+        </is>
+      </c>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>He managed to make a fortune by investing in tech stocks early on.</t>
+        </is>
+      </c>
+      <c r="I1526" t="inlineStr">
+        <is>
+          <t>She made a fortune from her real estate investments in the city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>ENG-20260607-065</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>slip through one's fingers</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>/slɪp θruː wʌnz ˈfɪŋɡəz/</t>
+        </is>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>(기회나 행운 등을) 놓치다</t>
+        </is>
+      </c>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>We cannot let this major business opportunity slip through our fingers.</t>
+        </is>
+      </c>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>The gold medal slipped through his fingers due to a mistake in the final seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>ENG-20260607-066</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>keep at bay</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>/kiːp æt beɪ/</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>(위험이나 나쁜 상황을) 저지하다, 막다</t>
+        </is>
+      </c>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>The central bank raised interest rates to keep rising inflation at bay.</t>
+        </is>
+      </c>
+      <c r="I1528" t="inlineStr">
+        <is>
+          <t>Using insect repellent is a good way to keep mosquitoes at bay during summer camping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>ENG-20260607-067</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>by leaps and bounds</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>/baɪ liːps ænd baʊndz/</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>급속도로, 비약적으로</t>
+        </is>
+      </c>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>The company's AI capabilities have been improving by leaps and bounds.</t>
+        </is>
+      </c>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>Her English conversational skills have progressed by leaps and bounds since she moved to London.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>ENG-20260607-068</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>on the spot</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>/ɒn ðə spɒt/</t>
+        </is>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>현장에서 즉시, 곤경에 처한</t>
+        </is>
+      </c>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>The job applicant was offered the position on the spot after a stellar interview.</t>
+        </is>
+      </c>
+      <c r="I1530" t="inlineStr">
+        <is>
+          <t>I was put on the spot when my boss asked me for the project numbers during the meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>ENG-20260607-069</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>have what it takes</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>/hæv wɒt ɪt teɪks/</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>(성공할 수 있는) 자질이나 자격이 있다</t>
+        </is>
+      </c>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>Do you think the new CEO has what it takes to lead the company during this crisis?</t>
+        </is>
+      </c>
+      <c r="I1531" t="inlineStr">
+        <is>
+          <t>She proved that she has what it takes to manage the entire sales team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>ENG-20260607-070</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>cut short</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>/kʌt ʃɔːt/</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>중단시키다, 예정보다 일찍 끝내다</t>
+        </is>
+      </c>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>They had to cut their honeymoon short due to an emergency at work.</t>
+        </is>
+      </c>
+      <c r="I1532" t="inlineStr">
+        <is>
+          <t>The meeting was cut short because the fire alarm started ringing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>ENG-20260607-071</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>take the credit for</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>/teɪk ðə ˈkredɪt fɔː/</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>~의 공로를 차지하다, 자기 공으로 돌리다</t>
+        </is>
+      </c>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>The manager tried to take the credit for the team's successful presentation.</t>
+        </is>
+      </c>
+      <c r="I1533" t="inlineStr">
+        <is>
+          <t>I don't want to take all the credit for this project; it was a collaborative effort.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1533"/>
+  <dimension ref="A1:I1625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72467,6 +72467,4330 @@
         </is>
       </c>
     </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>ENG-20260608-001</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>spook the market</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>/spuːk ðə ˈmɑːr.kɪt/</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>시장(투자자들)을 불안하게 만들다, 위축시키다</t>
+        </is>
+      </c>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>While the experimental drug met its key targets, the newly released safety data spooked the market, causing a massive sell-off.</t>
+        </is>
+      </c>
+      <c r="I1534" t="inlineStr">
+        <is>
+          <t>Rumors of an impending trade war spooked the market, leading to a massive tech sell-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>ENG-20260608-002</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>storm out of</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>/stɔːrm aʊt ʌv/</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>(화가 나서) 급히 뛰쳐나가다</t>
+        </is>
+      </c>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>The former president decided to storm out of the interview after being aggressively challenged about his controversial claims.</t>
+        </is>
+      </c>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>He lost his temper during the board meeting and stormed out of the conference room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>ENG-20260608-003</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>hold someone's feet to the fire</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>/hoʊld ˈsʌm.wʌnz fiːt tuː ðə faɪər/</t>
+        </is>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>합당한 책임을 지도록 압박하다, 끝까지 추궁하다</t>
+        </is>
+      </c>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>The media continues to hold the politician's feet to the fire regarding the fund's lack of transparency.</t>
+        </is>
+      </c>
+      <c r="I1536" t="inlineStr">
+        <is>
+          <t>The committee is going to hold the CEO's feet to the fire until she provides a clear solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>ENG-20260608-004</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>bring it on</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>/brɪŋ ɪt ɒn/</t>
+        </is>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>덤빌 테면 덤벼 봐 (어려움이나 도전을 자신 있게 받아들이는 태도)</t>
+        </is>
+      </c>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>Delta's executive shrugged and said, 'Bring 'em on,' signaling they are fully prepared for a price war.</t>
+        </is>
+      </c>
+      <c r="I1537" t="inlineStr">
+        <is>
+          <t>If they think they can outperform our team, I say bring it on!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>ENG-20260608-005</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>take someone on</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>/teɪk ˈsʌm.wʌn ɒn/</t>
+        </is>
+      </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>~와 정면 승부를 벌이다, 도전하다</t>
+        </is>
+      </c>
+      <c r="H1538" t="inlineStr">
+        <is>
+          <t>Delta's president openly declared that the carrier wants to take United on in the highly lucrative Pacific market.</t>
+        </is>
+      </c>
+      <c r="I1538" t="inlineStr">
+        <is>
+          <t>Our startup is ready to take on the tech giants with our brand-new software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>ENG-20260608-006</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>cushion the blow</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>/ˈkʊʃ.ən ðə bloʊ/</t>
+        </is>
+      </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>충격(피해)을 완화하다, 덜어주다</t>
+        </is>
+      </c>
+      <c r="H1539" t="inlineStr">
+        <is>
+          <t>China's reduced oil imports have helped to cushion the blow of rising global energy prices.</t>
+        </is>
+      </c>
+      <c r="I1539" t="inlineStr">
+        <is>
+          <t>The government is introducing tax cuts to cushion the blow of inflation on low-income families.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>ENG-20260608-007</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>keep something in check</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>/kiːp ˈsʌm.θɪŋ ɪn tʃek/</t>
+        </is>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>~을 통제하다, 억제하다</t>
+        </is>
+      </c>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>Lower demand from major economies helped keep crude oil prices in check below the $100 mark.</t>
+        </is>
+      </c>
+      <c r="I1540" t="inlineStr">
+        <is>
+          <t>You need to keep your spending in check if you want to save up for a new apartment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>ENG-20260608-008</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>fizzle out</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>/ˈfɪz.əl aʊt/</t>
+        </is>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>흐지부지되다, 서서히 식어 가다</t>
+        </is>
+      </c>
+      <c r="H1541" t="inlineStr">
+        <is>
+          <t>The stock market rally began to fizzle out as geopolitical tensions in the Middle East escalated.</t>
+        </is>
+      </c>
+      <c r="I1541" t="inlineStr">
+        <is>
+          <t>Their protest started with high energy but quickly fizzled out when it began to rain heavily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>ENG-20260608-009</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>stomach the cost</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>/ˈstʌm.ək ðə kɔːst/</t>
+        </is>
+      </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>(부담스러운 가격이나 비용을) 울며 겨자 먹기로 감당하다, 수용하다</t>
+        </is>
+      </c>
+      <c r="H1542" t="inlineStr">
+        <is>
+          <t>The airline industry is wondering just how long travelers will be able to stomach the rising cost of fuel.</t>
+        </is>
+      </c>
+      <c r="I1542" t="inlineStr">
+        <is>
+          <t>Small businesses simply cannot stomach the cost of these new environmental regulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>ENG-20260608-010</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>plan ahead</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>/plæn əˈhed/</t>
+        </is>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>미리 계획을 세우다, 앞날을 대비하다</t>
+        </is>
+      </c>
+      <c r="H1543" t="inlineStr">
+        <is>
+          <t>Since women statistically live longer than men, they must plan ahead for costly health care expenses.</t>
+        </is>
+      </c>
+      <c r="I1543" t="inlineStr">
+        <is>
+          <t>If we want this product launch to succeed, we need to plan ahead for any potential supply chain issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>ENG-20260608-011</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>sweeten the deal</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1544" t="inlineStr">
+        <is>
+          <t>/ˈswiː.tən ðə diːl/</t>
+        </is>
+      </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>(거래나 협상을 성사시키기 위해) 제안 조건을 더 매력적으로 만들다, 혜택을 얹어주다</t>
+        </is>
+      </c>
+      <c r="H1544" t="inlineStr">
+        <is>
+          <t>To win the acquisition battle, the Italian bank might have to sweeten the deal with more cash.</t>
+        </is>
+      </c>
+      <c r="I1544" t="inlineStr">
+        <is>
+          <t>The recruiter sweetened the deal by offering a sign-on bonus and extra vacation days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>ENG-20260608-012</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>throw one's hat in the ring</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>/θroʊ wʌnz hæt ɪn ðə rɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>경쟁(선거, 입찰 등)에 참여할 뜻을 밝히다, 도전장을 던지다</t>
+        </is>
+      </c>
+      <c r="H1545" t="inlineStr">
+        <is>
+          <t>Intesa gatecrashed the BPM acquisition talks, throwing its own hat in the ring with a massive offer.</t>
+        </is>
+      </c>
+      <c r="I1545" t="inlineStr">
+        <is>
+          <t>After working behind the scenes for years, she decided to throw her hat in the ring for the mayoral race.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>ENG-20260608-013</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>clamp down on</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>/klæmp daʊn ɒn/</t>
+        </is>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>(부정행위나 바람직하지 못한 일 등을) 강력히 제재하다, 억누르다</t>
+        </is>
+      </c>
+      <c r="H1546" t="inlineStr">
+        <is>
+          <t>Regulators have vowed to clamp down on platforms that fail to protect underage users from adult material.</t>
+        </is>
+      </c>
+      <c r="I1546" t="inlineStr">
+        <is>
+          <t>The university is trying to clamp down on academic dishonesty by using advanced plagiarism software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>ENG-20260608-014</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>feather one's nest</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>/ˈfeð.ər wʌnz nest/</t>
+        </is>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>(종종 부정한 방법이나 이기적인 방식으로) 사리사욕을 채우다, 부를 축적하다</t>
+        </is>
+      </c>
+      <c r="H1547" t="inlineStr">
+        <is>
+          <t>People who set aside money for retirement aren't just hoarding; they are legitimately trying to feather their nest for the future.</t>
+        </is>
+      </c>
+      <c r="I1547" t="inlineStr">
+        <is>
+          <t>The corrupt politician was accused of using public funds to feather his own nest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>ENG-20260608-015</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>tackle head-on</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>/ˈtæk.əl hed ɒn/</t>
+        </is>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>(어려운 문제에 피하지 않고) 정면으로 맞서다, 정면 돌파하다</t>
+        </is>
+      </c>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>The retail chain launched a new program to tackle the growing youth unemployment problem head-on.</t>
+        </is>
+      </c>
+      <c r="I1548" t="inlineStr">
+        <is>
+          <t>Rather than ignoring the customer complaints, the management team decided to tackle the issue head-on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>ENG-20260608-016</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>grapple with</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>/ˈɡræp.əl wɪð/</t>
+        </is>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>(해결하기 힘든 문제와) 씨름하다, 고심하다</t>
+        </is>
+      </c>
+      <c r="H1549" t="inlineStr">
+        <is>
+          <t>Societies across Europe continue to grapple with high rates of youth who are not in employment or training.</t>
+        </is>
+      </c>
+      <c r="I1549" t="inlineStr">
+        <is>
+          <t>The technology team spent the entire weekend grappling with a critical server issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>ENG-20260608-017</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>rise to the occasion</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>/raɪz tuː ðə əˈkeɪ.ʒən/</t>
+        </is>
+      </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>위기 상황이나 도전에 직면하여 역량을 발휘하다, 훌륭히 대처하다</t>
+        </is>
+      </c>
+      <c r="H1550" t="inlineStr">
+        <is>
+          <t>Faced with high unemployment, Dutch local communities managed to rise to the occasion and design effective mentorships.</t>
+        </is>
+      </c>
+      <c r="I1550" t="inlineStr">
+        <is>
+          <t>It was a high-pressure situation, but our sales team rose to the occasion and closed the deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>ENG-20260608-018</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>hang in limbo</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>/hæŋ ɪn ˈlɪm.boʊ/</t>
+        </is>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>불확실한 상태에 놓이다, 진척 없이 붕 뜨다</t>
+        </is>
+      </c>
+      <c r="H1551" t="inlineStr">
+        <is>
+          <t>With no response from potential employers, many job seekers find themselves hanging in limbo for months.</t>
+        </is>
+      </c>
+      <c r="I1551" t="inlineStr">
+        <is>
+          <t>The merger project is hanging in limbo until we get regulatory approval from the government.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>ENG-20260608-019</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>hit an all-time high</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>/hɪt ən ɔːl taɪm haɪ/</t>
+        </is>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>사상 최고치를 기록하다</t>
+        </is>
+      </c>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>Spain's tourist arrival numbers hit an all-time high as travelers chose to bypass more volatile destinations.</t>
+        </is>
+      </c>
+      <c r="I1552" t="inlineStr">
+        <is>
+          <t>The price of gold hit an all-time high this morning amid economic uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>ENG-20260608-020</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>give something a wide berth</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌm.θɪŋ ə waɪd bɜːθ/</t>
+        </is>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>(위험하거나 골치 아픈 일을) 멀찍이 떨어져서 피하다</t>
+        </is>
+      </c>
+      <c r="H1553" t="inlineStr">
+        <is>
+          <t>Many cruise ships are giving the region a wide berth due to the volatile security situation.</t>
+        </is>
+      </c>
+      <c r="I1553" t="inlineStr">
+        <is>
+          <t>After our massive argument yesterday, I decided to give him a wide berth for a few days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>ENG-20260608-021</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>run into a wall</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>/rʌn ˈɪn.tuː ə wɔːl/</t>
+        </is>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>장벽에 부딪히다, 반대에 직면하다</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>The airport expansion plan ran into a wall when the local assembly raised severe noise concerns.</t>
+        </is>
+      </c>
+      <c r="I1554" t="inlineStr">
+        <is>
+          <t>The design team ran into a wall when the budget was suddenly cut by thirty percent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>ENG-20260608-022</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>draw flak from</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>/drɔː flæk frɒm/</t>
+        </is>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>~로부터 거센 비난을 받다, 공격당하다</t>
+        </is>
+      </c>
+      <c r="H1555" t="inlineStr">
+        <is>
+          <t>The proposed low-altitude flight paths drew heavy flak from the local residents' association.</t>
+        </is>
+      </c>
+      <c r="I1555" t="inlineStr">
+        <is>
+          <t>The CEO's comments about reducing remote work options drew flak from employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>ENG-20260608-023</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>meet with resistance</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>/miːt wɪð rɪˈzɪs.təns/</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>저항이나 반대에 부딪히다</t>
+        </is>
+      </c>
+      <c r="H1556" t="inlineStr">
+        <is>
+          <t>Any new expansion proposals by City Airport are bound to meet with fierce resistance from environmentalists.</t>
+        </is>
+      </c>
+      <c r="I1556" t="inlineStr">
+        <is>
+          <t>Our proposal to change the company logo met with unexpected resistance from senior managers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>ENG-20260608-024</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>ghost someone</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>/ɡoʊst ˈsʌm.wʌn/</t>
+        </is>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>(연락을 끊고) 상대방을 잠수 타다, 연락을 무시하다</t>
+        </is>
+      </c>
+      <c r="H1557" t="inlineStr">
+        <is>
+          <t>I was sending hundreds of resumes, but employers would just ghost me without any feedback.</t>
+        </is>
+      </c>
+      <c r="I1557" t="inlineStr">
+        <is>
+          <t>We had a great first date, but then he completely ghosted me and never texted back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>ENG-20260608-025</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>leave someone hanging</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>/liːv ˈsʌm.wʌn ˈhæŋ.ɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>상대방을 하염없이 기다리게 만들다, 미결정 상태로 방치하다</t>
+        </is>
+      </c>
+      <c r="H1558" t="inlineStr">
+        <is>
+          <t>Instead of leaving applicants hanging, firms should at least send an automated rejection email.</t>
+        </is>
+      </c>
+      <c r="I1558" t="inlineStr">
+        <is>
+          <t>Please don't leave me hanging; tell me whether I got the promotion or not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>ENG-20260608-026</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>hear a pin drop</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>/hɪər ə pɪn drɒp/</t>
+        </is>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>쥐 죽은 듯이 조용하다, 적막이 흐르다</t>
+        </is>
+      </c>
+      <c r="H1559" t="inlineStr">
+        <is>
+          <t>When the candidate finished her presentation, you could hear a pin drop in the interview room.</t>
+        </is>
+      </c>
+      <c r="I1559" t="inlineStr">
+        <is>
+          <t>When the teacher walked into the noisy classroom, you could suddenly hear a pin drop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>ENG-20260608-027</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>gain an edge</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>/ɡeɪn ən edʒ/</t>
+        </is>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>경쟁 우위를 확보하다, 유리한 고지를 점하다</t>
+        </is>
+      </c>
+      <c r="H1560" t="inlineStr">
+        <is>
+          <t>Learning a coding language helped him gain an edge over other applicants in the job market.</t>
+        </is>
+      </c>
+      <c r="I1560" t="inlineStr">
+        <is>
+          <t>Obtaining this professional certification will help you gain an edge in your career.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>ENG-20260608-028</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>fall behind schedule</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>/fɔːl bɪˈhaɪnd ˈʃedj.uːl/</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>일정이 뒤처지다, 예정보다 늦어지다</t>
+        </is>
+      </c>
+      <c r="H1561" t="inlineStr">
+        <is>
+          <t>Due to unexpected electrical setbacks, the installation of the new furnace is going to fall behind schedule.</t>
+        </is>
+      </c>
+      <c r="I1561" t="inlineStr">
+        <is>
+          <t>If we don't hire more developers, the app release will definitely fall behind schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>ENG-20260608-029</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>burst someone's bubble</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>/bɜːst ˈsʌm.wʌnz ˈbʌb.əl/</t>
+        </is>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>~의 환상이나 꿈을 깨뜨리다</t>
+        </is>
+      </c>
+      <c r="H1562" t="inlineStr">
+        <is>
+          <t>I hate to burst your bubble, but local councils are planning to shut down home-based cake cupboards.</t>
+        </is>
+      </c>
+      <c r="I1562" t="inlineStr">
+        <is>
+          <t>I don't want to burst your bubble, but that concert was actually cancelled yesterday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>ENG-20260608-030</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>rain on someone's parade</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>/reɪn ɒn ˈsʌm.wʌnz pəˈreɪd/</t>
+        </is>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>~의 김을 빼다, 다 잘되어 가는 판에 찬물을 끼얹다</t>
+        </is>
+      </c>
+      <c r="H1563" t="inlineStr">
+        <is>
+          <t>Home bakers were making great money, but the safety regulators came in to rain on their parade.</t>
+        </is>
+      </c>
+      <c r="I1563" t="inlineStr">
+        <is>
+          <t>I'm sorry to rain on your parade, but we can't afford to go on vacation this month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>ENG-20260608-031</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>lose touch</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>/luːz tʌtʃ/</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>연락이 끊기다, 서먹해지다 (또는 감을 잃다)</t>
+        </is>
+      </c>
+      <c r="H1564" t="inlineStr">
+        <is>
+          <t>It's been a long time since Joey worked at the studio, and he had completely lost touch with the casting crew.</t>
+        </is>
+      </c>
+      <c r="I1564" t="inlineStr">
+        <is>
+          <t>We were best friends in high school, but we gradually lost touch over the years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>ENG-20260608-032</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>play tricks on someone's eyes</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>/pleɪ trɪks ɒn ˈsʌm.wʌnz aɪz/</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>착시 현상을 일으키다, 헛것이 보이다</t>
+        </is>
+      </c>
+      <c r="H1565" t="inlineStr">
+        <is>
+          <t>Joey felt the hallways looked much smaller, wondering if his memory was playing tricks on his eyes.</t>
+        </is>
+      </c>
+      <c r="I1565" t="inlineStr">
+        <is>
+          <t>I thought I saw a shadow in the corner, but the dim light was just playing tricks on my eyes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>ENG-20260608-033</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>hand something to someone on a silver platter</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>/hænd ˈsʌm.θɪŋ tuː ˈsʌm.wʌn ɒn ə ˈsɪl.vər ˈplæt.ər/</t>
+        </is>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>~에게 노력 없이 거저 주다, 식은 죽 먹기로 손에 쥐어주다</t>
+        </is>
+      </c>
+      <c r="H1566" t="inlineStr">
+        <is>
+          <t>Joey confidently assumed that the producers would just hand the role to him on a silver platter.</t>
+        </is>
+      </c>
+      <c r="I1566" t="inlineStr">
+        <is>
+          <t>Don't expect the promotion to be handed to you on a silver platter; you have to work for it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>ENG-20260608-034</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>put on airs</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>/pʊt ɒn ɛərz/</t>
+        </is>
+      </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>젠체하다, 잘난 척을 하며 거드름 피우다</t>
+        </is>
+      </c>
+      <c r="H1567" t="inlineStr">
+        <is>
+          <t>Joey accused Terry of putting on airs just because he sits in a fancy office in a new building.</t>
+        </is>
+      </c>
+      <c r="I1567" t="inlineStr">
+        <is>
+          <t>Ever since she got promoted to manager, she's been putting on airs around the office.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>ENG-20260608-035</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>laugh in someone's face</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>/lɑːf ɪn ˈsʌm.wʌnz feɪs/</t>
+        </is>
+      </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>코웃음 치다, 면전에서 대놓고 비웃다</t>
+        </is>
+      </c>
+      <c r="H1568" t="inlineStr">
+        <is>
+          <t>Tag was grateful that Rachel didn't laugh in his face when he submitted his highly unqualified resume.</t>
+        </is>
+      </c>
+      <c r="I1568" t="inlineStr">
+        <is>
+          <t>I wanted to pitch my startup idea, but I was terrified they would just laugh in my face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>ENG-20260608-036</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>laugh someone out of court</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>/lɑːf ˈsʌm.wʌn aʊt ʌv kɔːrt/</t>
+        </is>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>터무니없는 소리라고 콧방귀를 뀌며 물리치다</t>
+        </is>
+      </c>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>If Joey had demanded a high salary without auditioning, they would have laughed him out of court.</t>
+        </is>
+      </c>
+      <c r="I1569" t="inlineStr">
+        <is>
+          <t>My suggestion to finish the project in two days was laughed out of court by the developers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>ENG-20260608-037</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>have an eye for</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>/hæv ən aɪ fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>~에 안목이 있다, ~을 잘 알아보다</t>
+        </is>
+      </c>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>Tag admitted he doesn't have an eye for interior design since he failed to notice the giant plant.</t>
+        </is>
+      </c>
+      <c r="I1570" t="inlineStr">
+        <is>
+          <t>She has a real eye for choosing the perfect colors for home interiors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>ENG-20260608-038</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>get the picture</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>/ɡet ðə ˈpɪk.tʃər/</t>
+        </is>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>(설명을 듣고 전체적인 상황을) 이해하다, 파악하다</t>
+        </is>
+      </c>
+      <c r="H1571" t="inlineStr">
+        <is>
+          <t>Tag said 'Gotcha' because he got the picture that someone else must have been hired.</t>
+        </is>
+      </c>
+      <c r="I1571" t="inlineStr">
+        <is>
+          <t>You don't need to explain any further; I get the picture now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>ENG-20260608-039</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>have a craving for</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>/hæv ə ˈkreɪ.vɪŋ fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>~이 미친 듯이 먹고 싶다, 갈망하다</t>
+        </is>
+      </c>
+      <c r="H1572" t="inlineStr">
+        <is>
+          <t>Monica prepared a plate of tacos because she had a sudden, intense craving for them.</t>
+        </is>
+      </c>
+      <c r="I1572" t="inlineStr">
+        <is>
+          <t>Whenever it rains, I always have a strong craving for hot noodle soup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>ENG-20260608-040</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>get the axe</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>/ɡet ðə æks/</t>
+        </is>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>해고당하다, 잘리다</t>
+        </is>
+      </c>
+      <c r="H1573" t="inlineStr">
+        <is>
+          <t>Chandler burst in and jokingly blurted out that poor Nancy Thompson was getting the axe.</t>
+        </is>
+      </c>
+      <c r="I1573" t="inlineStr">
+        <is>
+          <t>Several senior managers got the axe during the company's restructuring phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>ENG-20260608-041</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>go down with</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>/ɡoʊ daʊn wɪð/</t>
+        </is>
+      </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>(질병 등에) 걸리다, 앓아눕다</t>
+        </is>
+      </c>
+      <c r="H1574" t="inlineStr">
+        <is>
+          <t>Ross defended himself by explaining he went down with a severe case of food poisoning after eating tacos.</t>
+        </is>
+      </c>
+      <c r="I1574" t="inlineStr">
+        <is>
+          <t>Almost half of our department went down with the flu last week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>ENG-20260608-042</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>spice things up</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>/spaɪs θɪŋz ʌp/</t>
+        </is>
+      </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>흥미진진하게 만들다, 활기를 불어넣다</t>
+        </is>
+      </c>
+      <c r="H1575" t="inlineStr">
+        <is>
+          <t>Ross sarcastically asked if he got sick just to spice things up and make the ride more exciting.</t>
+        </is>
+      </c>
+      <c r="I1575" t="inlineStr">
+        <is>
+          <t>We decided to add some interactive games to the party to spice things up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>ENG-20260608-043</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>live on the edge</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>/lɪv ɒn ðə edʒ/</t>
+        </is>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>위태롭고 스릴 있는 삶을 즐기다, 위험을 무릅쓰고 살다</t>
+        </is>
+      </c>
+      <c r="H1576" t="inlineStr">
+        <is>
+          <t>Eating street tacos right before a roller coaster ride is definitely one way to live on the edge.</t>
+        </is>
+      </c>
+      <c r="I1576" t="inlineStr">
+        <is>
+          <t>He quit his stable corporate job to travel the world without a plan—he loves living on the edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>ENG-20260608-044</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>roll out the red carpet</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>/roʊl aʊt ðə red ˈkɑː.pɪt/</t>
+        </is>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>(VIP를 대하듯) 아주 융숭하게 대접하다</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>Monica jokingly wondered if she should roll out the red carpet and lay down protective papers for sick Ross.</t>
+        </is>
+      </c>
+      <c r="I1577" t="inlineStr">
+        <is>
+          <t>The hotel rolled out the red carpet for the visiting foreign diplomats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>ENG-20260608-045</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>make eyes at</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>/meɪk aɪz æt/</t>
+        </is>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>~에게 추파를 던지다, 꼬시다</t>
+        </is>
+      </c>
+      <c r="H1578" t="inlineStr">
+        <is>
+          <t>Ross revealed that a gorgeous person at the Atlantic City bar was making eyes at Chandler.</t>
+        </is>
+      </c>
+      <c r="I1578" t="inlineStr">
+        <is>
+          <t>I noticed that the guy sitting at the corner table was making eyes at you all evening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>ENG-20260608-046</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>give someone the eye</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈsʌm.wʌn ðə aɪ/</t>
+        </is>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>~에게 눈길을 주다, 매력적으로 쳐다보다</t>
+        </is>
+      </c>
+      <c r="H1579" t="inlineStr">
+        <is>
+          <t>Chandler couldn't resist going over after realizing that the person was giving him the eye.</t>
+        </is>
+      </c>
+      <c r="I1579" t="inlineStr">
+        <is>
+          <t>She was giving him the eye across the crowded dance floor, hoping he'd approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>ENG-20260608-047</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>make out with</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>/meɪk aʊt wɪð/</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>~와 격렬하게 키스하다, 스킨십을 하다</t>
+        </is>
+      </c>
+      <c r="H1580" t="inlineStr">
+        <is>
+          <t>Monica was shocked to find out that Chandler had actually made out with a guy at the bar.</t>
+        </is>
+      </c>
+      <c r="I1580" t="inlineStr">
+        <is>
+          <t>The high school sweethearts were caught making out with each other behind the gym.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>ENG-20260608-048</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>air one's dirty laundry</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>/ɛər wʌnz ˈdɜː.ti ˈlɔːn.dri/</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>집안의 치부나 개인적인 비밀을 남들 앞에서 들추어내다</t>
+        </is>
+      </c>
+      <c r="H1581" t="inlineStr">
+        <is>
+          <t>Ross and Chandler kept retaliating by air their dirty laundry in front of Monica.</t>
+        </is>
+      </c>
+      <c r="I1581" t="inlineStr">
+        <is>
+          <t>I'd prefer not to air our dirty laundry in public, so let's discuss this matter at home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>ENG-20260608-049</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>play it safe</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>/pleɪ ɪt seɪf/</t>
+        </is>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>위험을 피하고 안전책을 쓰다, 신중히 행동하다</t>
+        </is>
+      </c>
+      <c r="H1582" t="inlineStr">
+        <is>
+          <t>Investors who play it safe are shifting their funds from tech stocks to gold.</t>
+        </is>
+      </c>
+      <c r="I1582" t="inlineStr">
+        <is>
+          <t>Instead of investing in volatile stocks, he chose to play it safe with a fixed deposit account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>ENG-20260608-050</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>spill over into</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>/spɪl ˈoʊ.vər ˈɪn.tuː/</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>(부정적인 여파 등이) ~로 번지다, 파급 효과를 미치다</t>
+        </is>
+      </c>
+      <c r="H1583" t="inlineStr">
+        <is>
+          <t>There are growing concerns that regional conflicts will spill over into neighboring countries.</t>
+        </is>
+      </c>
+      <c r="I1583" t="inlineStr">
+        <is>
+          <t>Our domestic economic crisis might easily spill over into the global financial market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>ENG-20260608-051</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>get to the bottom of</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>/ɡet tuː ðə ˈbɒt.əm ʌv/</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>~의 진짜 원인이나 진상을 규명하다</t>
+        </is>
+      </c>
+      <c r="H1584" t="inlineStr">
+        <is>
+          <t>The technical team worked overnight to get to the bottom of the electrical connection problem.</t>
+        </is>
+      </c>
+      <c r="I1584" t="inlineStr">
+        <is>
+          <t>We need to get to the bottom of this recurring software bug as soon as possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>ENG-20260608-052</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>hit home</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>/hɪt hoʊm/</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>(이야기 등이) 가슴에 와닿다, 뼈저리게 느껴지다</t>
+        </is>
+      </c>
+      <c r="H1585" t="inlineStr">
+        <is>
+          <t>The warning about high long-term care costs really hit home for many retired couples.</t>
+        </is>
+      </c>
+      <c r="I1585" t="inlineStr">
+        <is>
+          <t>Her speech about the struggles of single parents really hit home with the audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>ENG-20260608-053</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>keep an eye out for</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>/kiːp ən aɪ aʊt fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>~을 주의 깊게 살피다, 경계하다</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>Rachel told Tag to keep an eye out for any urgent deliveries while she was away.</t>
+        </is>
+      </c>
+      <c r="I1586" t="inlineStr">
+        <is>
+          <t>Please keep an eye out for the mail carrier; I'm expecting an important document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>ENG-20260608-054</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>skimp on</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>/skɪmp ɒn/</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>~에 지나치게 돈이나 노력을 아끼다</t>
+        </is>
+      </c>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>When planning long-term care, you shouldn't skimp on quality insurance coverage.</t>
+        </is>
+      </c>
+      <c r="I1587" t="inlineStr">
+        <is>
+          <t>Never skimp on safety equipment when you are working on a high-risk construction site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>ENG-20260608-055</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>give credit where credit is due</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>/ɡɪv ˈkred.ɪt wɛər ˈkred.ɪt ɪz djuː/</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>인정할 것은 인정하다, 공로를 인정해주다</t>
+        </is>
+      </c>
+      <c r="H1588" t="inlineStr">
+        <is>
+          <t>We must give credit where credit is due: United has done an amazing job dominating the Pacific routes.</t>
+        </is>
+      </c>
+      <c r="I1588" t="inlineStr">
+        <is>
+          <t>I don't like his attitude, but I must give credit where credit is due—he is a brilliant designer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>ENG-20260608-056</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>throw a tantrum</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>/θroʊ ə ˈtæn.trəm/</t>
+        </is>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>떼를 쓰며 화를 내다, 소란을 피우다</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>Joey threw a tantrum when he realized he wasn't being offered the role directly.</t>
+        </is>
+      </c>
+      <c r="I1589" t="inlineStr">
+        <is>
+          <t>The toddler threw a tantrum in the middle of the supermarket because he couldn't get the toy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>ENG-20260608-057</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>add insult to injury</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>/æd ˈɪn.sʌlt tuː ˈɪn.dʒər.i/</t>
+        </is>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>설상가상으로 상황을 더 악화시키다, 엎친 데 덮친 격이 되다</t>
+        </is>
+      </c>
+      <c r="H1590" t="inlineStr">
+        <is>
+          <t>To add insult to injury, the bank's stock dropped right after they announced the bad financial news.</t>
+        </is>
+      </c>
+      <c r="I1590" t="inlineStr">
+        <is>
+          <t>My flight was delayed for six hours, and to add insult to injury, they lost my luggage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>ENG-20260608-058</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>read someone the riot act</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>/riːd ˈsʌm.wʌn ðə ˈraɪ.ət ækt/</t>
+        </is>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>~에게 엄중히 경고하다, 되게 혼내다</t>
+        </is>
+      </c>
+      <c r="H1591" t="inlineStr">
+        <is>
+          <t>The local council decided to read the home bakers the riot act over safety violations.</t>
+        </is>
+      </c>
+      <c r="I1591" t="inlineStr">
+        <is>
+          <t>My boss read me the riot act after I missed the deadline for the second time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>ENG-20260608-059</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>skate on thin ice</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>/skeɪt ɒn θɪn aɪs/</t>
+        </is>
+      </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>아슬아슬하게 살얼음판을 걷다, 위험한 짓을 하다</t>
+        </is>
+      </c>
+      <c r="H1592" t="inlineStr">
+        <is>
+          <t>Chandler was skating on thin ice by mocking Monica's cooking skills right before dinner.</t>
+        </is>
+      </c>
+      <c r="I1592" t="inlineStr">
+        <is>
+          <t>You are skating on thin ice by coming to work late almost every day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>ENG-20260608-060</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>take with a grain of salt</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>/teɪk wɪð ə ɡreɪn ʌv sɔːlt/</t>
+        </is>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>액면 그대로 믿지 않고 에누리해서 듣다, 걸러 듣다</t>
+        </is>
+      </c>
+      <c r="H1593" t="inlineStr">
+        <is>
+          <t>You should take Joey's claims about his famous TV show with a grain of salt.</t>
+        </is>
+      </c>
+      <c r="I1593" t="inlineStr">
+        <is>
+          <t>She promised to finish the task by tomorrow, but I'm taking it with a grain of salt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>ENG-20260608-061</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>throw under the bus</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>/θroʊ ˈʌnd.ər ðə bʌs/</t>
+        </is>
+      </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>(자신의 이익을 위해 동료나 파트너를) 배신하다, 희생양으로 삼다</t>
+        </is>
+      </c>
+      <c r="H1594" t="inlineStr">
+        <is>
+          <t>Chandler threw Ross under the bus by telling Monica all about the food poisoning incident.</t>
+        </is>
+      </c>
+      <c r="I1594" t="inlineStr">
+        <is>
+          <t>She threw her teammate under the bus during the meeting to avoid taking blame for the mistake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>ENG-20260608-062</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>the benefit of the doubt</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>/ðə ˈben.ɪ.fɪt ʌv ðə daʊt/</t>
+        </is>
+      </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>미심쩍지만 좋은 쪽으로 믿어주다, 무죄 추정해주다</t>
+        </is>
+      </c>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>Rachel decided to give Tag the benefit of the doubt and assume his resume was accurate.</t>
+        </is>
+      </c>
+      <c r="I1595" t="inlineStr">
+        <is>
+          <t>I don't entirely believe his story, but let's give him the benefit of the doubt this time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>ENG-20260608-063</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>on cloud nine</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>/ɒn klaʊd naɪn/</t>
+        </is>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>날아갈 듯이 기쁘다, 행복에 젖어 있다</t>
+        </is>
+      </c>
+      <c r="H1596" t="inlineStr">
+        <is>
+          <t>Tag was on cloud nine after learning that he had been hired by a prestigious fashion line.</t>
+        </is>
+      </c>
+      <c r="I1596" t="inlineStr">
+        <is>
+          <t>She was on cloud nine for weeks after her boyfriend proposed to her.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>ENG-20260608-064</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>hit a sour note</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>/hɪt ə saʊər noʊt/</t>
+        </is>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>어색한 분위기를 만들다, 삐끗해서 분위기를 가라앉히다</t>
+        </is>
+      </c>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>Joey's arrogance during the meeting hit a sour note with the casting team.</t>
+        </is>
+      </c>
+      <c r="I1597" t="inlineStr">
+        <is>
+          <t>The joke he made at the dinner table hit a sour note with her parents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>ENG-20260608-065</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>be in hot water</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>/biː ɪn hɒt ˈwɔː.tər/</t>
+        </is>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>곤경에 처하다, 큰 말썽에 휩싸이다</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>Chandler was in hot water with Monica after Ross revealed what happened in Atlantic City.</t>
+        </is>
+      </c>
+      <c r="I1598" t="inlineStr">
+        <is>
+          <t>The employee is in hot water for leaking confidential company designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>ENG-20260608-066</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>on the tip of the iceberg</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>/ɒn ðə tɪp ʌv ðə ˈaɪs.bɜːɡ/</t>
+        </is>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>빙산의 일각에 불과하다</t>
+        </is>
+      </c>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>The initial cost increase of fuel is just the tip of the iceberg for struggling airlines.</t>
+        </is>
+      </c>
+      <c r="I1599" t="inlineStr">
+        <is>
+          <t>The minor flaws we detected today are just the tip of the iceberg of a poorly designed system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>ENG-20260608-067</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>go down the rabbit hole</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>/ɡoʊ daʊn ðə ˈræb.ɪt hoʊl/</t>
+        </is>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>꼬리에 꼬리를 무는 복잡한 수렁(또는 혼란) 속으로 빠져들다</t>
+        </is>
+      </c>
+      <c r="H1600" t="inlineStr">
+        <is>
+          <t>When Ross and Chandler started arguing, Monica went down the rabbit hole of their past secrets.</t>
+        </is>
+      </c>
+      <c r="I1600" t="inlineStr">
+        <is>
+          <t>I only wanted to check one reference, but I ended up going down the rabbit hole of research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>ENG-20260608-068</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>on the cards</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>/ɒn ðə kɑːrdz/</t>
+        </is>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>실현 가능성이 있는, 예상되는</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>An aggressive acquisition of the Italian bank has been on the cards for quite some time.</t>
+        </is>
+      </c>
+      <c r="I1601" t="inlineStr">
+        <is>
+          <t>With the funding secured, a major expansion of our service is now on the cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>ENG-20260608-069</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>cut to the bone</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>/kʌt tuː ðə boʊn/</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>(비용 등을) 뼈를 깎는 수준으로 최소화하다</t>
+        </is>
+      </c>
+      <c r="H1602" t="inlineStr">
+        <is>
+          <t>To stay profitable, the steel firm had to cut their operational costs to the bone.</t>
+        </is>
+      </c>
+      <c r="I1602" t="inlineStr">
+        <is>
+          <t>We've cut our marketing expenditures to the bone, so we can't afford any more print ads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>ENG-20260608-070</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>take to heart</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>/teɪk tuː hɑːrt/</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>(충고나 조언 등을) 마음에 깊이 새기다, 진지하게 받아들이다</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>Tag took Rachel's advice to heart and immediately went to find Hilda to coordinate tasks.</t>
+        </is>
+      </c>
+      <c r="I1603" t="inlineStr">
+        <is>
+          <t>Don't take her critical comments to heart; she was just having a very bad day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>ENG-20260608-071</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>turn the corner</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>/tɜːn ðə ˈkɔː.nər/</t>
+        </is>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>위기를 넘기다, 고비를 넘겨 호전되다</t>
+        </is>
+      </c>
+      <c r="H1604" t="inlineStr">
+        <is>
+          <t>Analysts hope the domestic tech sector will finally turn the corner next quarter.</t>
+        </is>
+      </c>
+      <c r="I1604" t="inlineStr">
+        <is>
+          <t>The economy has turned the corner, and we are starting to see a decline in unemployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>ENG-20260608-072</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>throw a monkey wrench into</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>/θroʊ ə ˈmʌŋ.ki rentʃ ˈɪn.tuː/</t>
+        </is>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>기존의 계획을 망쳐놓다, 훼방을 놓다</t>
+        </is>
+      </c>
+      <c r="H1605" t="inlineStr">
+        <is>
+          <t>The unsolicited rival offer threw a monkey wrench into BPM's original acquisition plans.</t>
+        </is>
+      </c>
+      <c r="I1605" t="inlineStr">
+        <is>
+          <t>The sudden tax hike threw a monkey wrench into our startup expansion budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>ENG-20260608-073</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>keep one's ear to the ground</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>/kiːp wʌnz ɪər tuː ðə ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>세상 돌아가는 형편이나 소문에 항상 귀를 기울이다</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>Investors should keep their ears to the ground for any policy changes in the energy sector.</t>
+        </is>
+      </c>
+      <c r="I1606" t="inlineStr">
+        <is>
+          <t>As a marketing director, you must keep your ear to the ground to catch new consumer trends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>ENG-20260608-074</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>hit the spot</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>/hɪt ðə spɒt/</t>
+        </is>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>(음식이나 음료 등이) 딱 원하던 맛이다, 아주 만족스럽다</t>
+        </is>
+      </c>
+      <c r="H1607" t="inlineStr">
+        <is>
+          <t>Monica smiled and declared that the spicy ground beef smileys really hit the spot.</t>
+        </is>
+      </c>
+      <c r="I1607" t="inlineStr">
+        <is>
+          <t>That ice-cold glass of lemonade really hit the spot after my long run in the park.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>ENG-20260608-075</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>get on the right track</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>/ɡet ɒn ðə raɪt træk/</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>올바른 방향으로 나아가다, 본 궤도에 오르다</t>
+        </is>
+      </c>
+      <c r="H1608" t="inlineStr">
+        <is>
+          <t>After a series of failed interviews, he finally managed to get on the right track with Tag's tip.</t>
+        </is>
+      </c>
+      <c r="I1608" t="inlineStr">
+        <is>
+          <t>We had a lot of setbacks last month, but our new manager helped us get on the right track.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>ENG-20260608-076</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>trigger an escalation</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>/ˈtrɪɡər ən ˌɛskəˈleɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>갈등·전쟁 등의 단계적 확대(에스컬레이션)를 유발하다, 상황을 악화시키다</t>
+        </is>
+      </c>
+      <c r="H1609" t="inlineStr">
+        <is>
+          <t>Iran warns that further retaliatory strikes in Lebanon could trigger an escalation across the region.</t>
+        </is>
+      </c>
+      <c r="I1609" t="inlineStr">
+        <is>
+          <t>Any sudden changes in interest rates could trigger an escalation in market volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>ENG-20260608-077</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>meet key targets</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>/mit ki ˈtɑːrɡɪts/</t>
+        </is>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>핵심 목표를 달성하다</t>
+        </is>
+      </c>
+      <c r="H1610" t="inlineStr">
+        <is>
+          <t>The pharmaceutical company announced that its weight-loss drug met its key targets in the second phase.</t>
+        </is>
+      </c>
+      <c r="I1610" t="inlineStr">
+        <is>
+          <t>If we want to secure the funding, our team must meet key targets by the end of this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>ENG-20260608-078</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>take the crown</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>/teɪk ðə kraʊn/</t>
+        </is>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>왕좌를 차지하다, 1위 자리를 빼앗다</t>
+        </is>
+      </c>
+      <c r="H1611" t="inlineStr">
+        <is>
+          <t>Delta's CEO made it clear that they intend to take the crown from United in the Pacific market.</t>
+        </is>
+      </c>
+      <c r="I1611" t="inlineStr">
+        <is>
+          <t>With their new software update, the startup is hoping to take the crown from the industry giant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>ENG-20260608-079</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>cap prices</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>/kæp ˈpraɪsɪz/</t>
+        </is>
+      </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>가격에 상한선을 두다, 가격을 제한하다</t>
+        </is>
+      </c>
+      <c r="H1612" t="inlineStr">
+        <is>
+          <t>Increased domestic production helped cap prices of essential goods during the supply crisis.</t>
+        </is>
+      </c>
+      <c r="I1612" t="inlineStr">
+        <is>
+          <t>The government decided to cap prices on utility bills to protect lower-income households.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>ENG-20260608-080</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>spark a bidding war</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>/spɑːrk ə ˈbɪdɪŋ wɔːr/</t>
+        </is>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>인수 경쟁(입찰 경쟁)을 촉발하다</t>
+        </is>
+      </c>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>The rare tech patent is expected to spark a bidding war among the industry’s biggest players.</t>
+        </is>
+      </c>
+      <c r="I1613" t="inlineStr">
+        <is>
+          <t>Putting the prime beachfront property on the market will definitely spark a bidding war.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>ENG-20260608-081</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>warn against</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>/wɔːrn əˈɡɛnst/</t>
+        </is>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>~하지 말라고 경고하다, ~의 위험성을 경고하다</t>
+        </is>
+      </c>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>Financial advisors strongly warn against investing all your savings in a single stock.</t>
+        </is>
+      </c>
+      <c r="I1614" t="inlineStr">
+        <is>
+          <t>Security experts warn against clicking on links from unknown senders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>ENG-20260608-082</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>give up work</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>/ɡɪv ʌp wɜːrk/</t>
+        </is>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>일을 그만두다, 은퇴하다</t>
+        </is>
+      </c>
+      <c r="H1615" t="inlineStr">
+        <is>
+          <t>Many workers hope to give up work early, but they fail to save enough for retirement.</t>
+        </is>
+      </c>
+      <c r="I1615" t="inlineStr">
+        <is>
+          <t>After winning the lottery, he decided to give up work and travel the world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>ENG-20260608-083</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>face opposition</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>/feɪs ˌɒpəˈzɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>반대에 부딪히다, 반대에 직면하다</t>
+        </is>
+      </c>
+      <c r="H1616" t="inlineStr">
+        <is>
+          <t>The local airport expansion project faces strong opposition from environmental groups.</t>
+        </is>
+      </c>
+      <c r="I1616" t="inlineStr">
+        <is>
+          <t>The CEO’s restructuring plan is likely to face opposition from the labor union.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>ENG-20260608-084</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>secure a role</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>/sɪˈkjʊər ə rəʊl/</t>
+        </is>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>일자리(직책)를 얻어내다, 확보하다</t>
+        </is>
+      </c>
+      <c r="H1617" t="inlineStr">
+        <is>
+          <t>With the right interview tips, she managed to secure a role at a top-tier accounting firm.</t>
+        </is>
+      </c>
+      <c r="I1617" t="inlineStr">
+        <is>
+          <t>He spent months networking in order to secure a role in the film industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>ENG-20260608-085</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>capture someone's imagination</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>/ˈkæptʃər ˈsʌmwʌnz ɪˌmædʒɪˈneɪʃən/</t>
+        </is>
+      </c>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>~의 상상력(흥미·관심)을 사로잡다</t>
+        </is>
+      </c>
+      <c r="H1618" t="inlineStr">
+        <is>
+          <t>The cute cake cupboards captured the public's imagination, becoming an overnight sensation.</t>
+        </is>
+      </c>
+      <c r="I1618" t="inlineStr">
+        <is>
+          <t>The new sci-fi novel has captured the imagination of readers worldwide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>ENG-20260608-086</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>come for</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>/kʌm fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>(비난·단속 등을 하기 위해) ~를 찾아오다, 겨냥하다</t>
+        </is>
+      </c>
+      <c r="H1619" t="inlineStr">
+        <is>
+          <t>Small business owners worry that local councils are coming for their roadside stands.</t>
+        </is>
+      </c>
+      <c r="I1619" t="inlineStr">
+        <is>
+          <t>The regulatory body is coming for tech giants that violate user privacy laws.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>ENG-20260608-087</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>pad one's resume</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>/pæd wʌnz ˈrɛzʊmeɪ/</t>
+        </is>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>이력서를 부풀리다, (허위나 과장으로) 이력을 채워 넣다</t>
+        </is>
+      </c>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>I wouldn't advise trying to pad your resume with minor achievements they can easily verify.</t>
+        </is>
+      </c>
+      <c r="I1620" t="inlineStr">
+        <is>
+          <t>Many college students take short online courses just to pad their resumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>ENG-20260608-088</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>take a pass on</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>/teɪk ə pæs ɒn/</t>
+        </is>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>~을 거절하다, 건너뛰다</t>
+        </is>
+      </c>
+      <c r="H1621" t="inlineStr">
+        <is>
+          <t>I think I’m going to take a pass on the dessert; I’m already too full.</t>
+        </is>
+      </c>
+      <c r="I1621" t="inlineStr">
+        <is>
+          <t>The company decided to take a pass on the merger opportunity due to high debts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>ENG-20260608-089</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>keep something from someone</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>/kiːp ˈsʌmθɪŋ frɒm ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>~에게 ~을 숨기다, 비밀로 하다</t>
+        </is>
+      </c>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>You shouldn't keep secrets from your business partner if you want the trust to last.</t>
+        </is>
+      </c>
+      <c r="I1622" t="inlineStr">
+        <is>
+          <t>I knew she was keeping something from me when she refused to show me the letter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>ENG-20260608-090</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>in one's defense</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>/ɪn wʌnz dɪˈfɛns/</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>변명을 하자면, 자기방어를 하자면</t>
+        </is>
+      </c>
+      <c r="H1623" t="inlineStr">
+        <is>
+          <t>In my defense, nobody told me the meeting time had been changed.</t>
+        </is>
+      </c>
+      <c r="I1623" t="inlineStr">
+        <is>
+          <t>In his defense, he was only following the guidelines that were given to him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>ENG-20260608-091</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>throw out</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>/θrəʊ aʊt/</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>(쓸모없는 것을) 버리다, 폐기하다</t>
+        </is>
+      </c>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>Don't throw out those old documents; we might need them for the audit.</t>
+        </is>
+      </c>
+      <c r="I1624" t="inlineStr">
+        <is>
+          <t>I had to throw out the milk because it had already gone bad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>ENG-20260608-092</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>offer a part</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>/ˈɒfər ə pɑːrt/</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>(역할·배역 등을) 제안하다, 주다</t>
+        </is>
+      </c>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>They called her back the next day to offer her the lead part in the play.</t>
+        </is>
+      </c>
+      <c r="I1625" t="inlineStr">
+        <is>
+          <t>After a brilliant audition, the director decided to offer him the part immediately.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1625"/>
+  <dimension ref="A1:I1684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76791,6 +76791,2779 @@
         </is>
       </c>
     </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>ENG-20260609-001</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>the grass is always greener</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>/ðə ɡrɑːs ɪz ˈɔːl.weɪz ˈɡriː.nər/</t>
+        </is>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>남의 떡이 늘 더 커 보인다</t>
+        </is>
+      </c>
+      <c r="H1626" t="inlineStr">
+        <is>
+          <t>Airlines are beginning to realize that the grass isn't always greener with new and unproven engine manufacturers.</t>
+        </is>
+      </c>
+      <c r="I1626" t="inlineStr">
+        <is>
+          <t>He quit his job for a flashy startup, but now he knows the grass isn't always greener.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>ENG-20260609-002</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>come under pressure</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>/kʌm ˈʌndər ˈpreʃər/</t>
+        </is>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>심한 압박을 받다, 하락이나 위기 국면에 처하다</t>
+        </is>
+      </c>
+      <c r="H1627" t="inlineStr">
+        <is>
+          <t>Jim Cramer warned that several key pillars of the bull market have recently come under pressure.</t>
+        </is>
+      </c>
+      <c r="I1627" t="inlineStr">
+        <is>
+          <t>The marketing team has come under pressure to deliver a successful campaign after the previous failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>ENG-20260609-003</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>bolster up</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>/ˈbəʊl.stər ʌp/</t>
+        </is>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>부진한 상황을 개선하기 위해 보강하다, 강화하다</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr">
+        <is>
+          <t>Drugmakers are in a race to acquire rivals to bolster up their weak clinical trial pipelines.</t>
+        </is>
+      </c>
+      <c r="I1628" t="inlineStr">
+        <is>
+          <t>The company hired several top security experts to bolster up their digital defenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>ENG-20260609-004</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>take center stage</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>/teɪk ˈsen.tər steɪdʒ/</t>
+        </is>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>가장 주목을 받다, 화제의 중심이 되다</t>
+        </is>
+      </c>
+      <c r="H1629" t="inlineStr">
+        <is>
+          <t>Apple's new artificial intelligence strategy took center stage at its annual developer conference.</t>
+        </is>
+      </c>
+      <c r="I1629" t="inlineStr">
+        <is>
+          <t>Sustainable energy solutions are expected to take center stage at the upcoming global summit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>ENG-20260609-005</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>put a jinx on</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>/pʊt ə dʒɪŋks ɒn/</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>~에게 불운을 가져다주다, 징크스를 씌우다</t>
+        </is>
+      </c>
+      <c r="H1630" t="inlineStr">
+        <is>
+          <t>Some superstitious fans feared Trump's presence at the game would put a jinx on the Knicks.</t>
+        </is>
+      </c>
+      <c r="I1630" t="inlineStr">
+        <is>
+          <t>Don't say we're going to win yet! You'll put a jinx on the team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>ENG-20260609-006</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>run a risk</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>/rʌn ə rɪsk/</t>
+        </is>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>위험을 자초하다, 리스크를 감수하다</t>
+        </is>
+      </c>
+      <c r="H1631" t="inlineStr">
+        <is>
+          <t>Retirees who strictly limit their spending run a risk of drastically lowering their quality of life.</t>
+        </is>
+      </c>
+      <c r="I1631" t="inlineStr">
+        <is>
+          <t>If you don't back up your computer files, you run a risk of losing years of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>ENG-20260609-007</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>heat up</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>/hiːt ʌp/</t>
+        </is>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>분위기가 한층 뜨거워지다, 격화되다</t>
+        </is>
+      </c>
+      <c r="H1632" t="inlineStr">
+        <is>
+          <t>The race to secure funding among AI startups is beginning to heat up intensely.</t>
+        </is>
+      </c>
+      <c r="I1632" t="inlineStr">
+        <is>
+          <t>The competition between Samsung and Apple is heating up with the release of new models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>ENG-20260609-008</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>lose out on</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>/luːz aʊt ɒn/</t>
+        </is>
+      </c>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>남에게 밀려 좋은 기회를 놓치다</t>
+        </is>
+      </c>
+      <c r="H1633" t="inlineStr">
+        <is>
+          <t>Sid Miller lost out on a fourth term in the Texas Republican primary despite a big endorsement.</t>
+        </is>
+      </c>
+      <c r="I1633" t="inlineStr">
+        <is>
+          <t>If you hesitate too long, you might lose out on this once-in-a-lifetime business deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>ENG-20260609-009</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>tighten the reins</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>/ˈtaɪ.tən ðə reɪnz/</t>
+        </is>
+      </c>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>규제를 강화하다, 고삐를 단단히 죄다</t>
+        </is>
+      </c>
+      <c r="H1634" t="inlineStr">
+        <is>
+          <t>The UK government decided to tighten the reins on driving test booking after massive no-shows.</t>
+        </is>
+      </c>
+      <c r="I1634" t="inlineStr">
+        <is>
+          <t>Management decided to tighten the reins on corporate spending starting next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>ENG-20260609-010</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>blow off</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>/bləʊ ɒf/</t>
+        </is>
+      </c>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>약속을 바람맞히다, 무시하다</t>
+        </is>
+      </c>
+      <c r="H1635" t="inlineStr">
+        <is>
+          <t>Thousands of learner drivers booked tests only to blow them off, forcing a change in the rules.</t>
+        </is>
+      </c>
+      <c r="I1635" t="inlineStr">
+        <is>
+          <t>I can't believe he blew off our weekly sync meeting without telling anyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>ENG-20260609-011</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>take a gamble</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>/teɪk ə ˈɡæm.bəl/</t>
+        </is>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>모험을 걸다, 대담하게 배팅하다</t>
+        </is>
+      </c>
+      <c r="H1636" t="inlineStr">
+        <is>
+          <t>SpaceX's decision to go public could be Elon Musk's biggest gamble in recent years.</t>
+        </is>
+      </c>
+      <c r="I1636" t="inlineStr">
+        <is>
+          <t>It's risky, but we have to take a gamble on this new product line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>ENG-20260609-012</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>blast off</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>/blɑːst ɒf/</t>
+        </is>
+      </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>급등하다, 우주선처럼 솟구쳐 오르다</t>
+        </is>
+      </c>
+      <c r="H1637" t="inlineStr">
+        <is>
+          <t>SpaceX's stock is expected to blast off once the official listing goes live.</t>
+        </is>
+      </c>
+      <c r="I1637" t="inlineStr">
+        <is>
+          <t>Upon launching the viral marketing campaign, our subscription numbers blasted off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>ENG-20260609-013</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>sever ties with</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>/ˈsev.ər taɪz wɪð/</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>~와의 관계나 유대를 끊다, 단절하다</t>
+        </is>
+      </c>
+      <c r="H1638" t="inlineStr">
+        <is>
+          <t>The US Pentagon warned domestic firms to sever ties with businesses connected to the Chinese military.</t>
+        </is>
+      </c>
+      <c r="I1638" t="inlineStr">
+        <is>
+          <t>The company had to sever ties with the supplier after they failed the safety audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>ENG-20260609-014</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>be some way off</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>/biː sʌm weɪ ɒf/</t>
+        </is>
+      </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>아직 갈 길이 멀다, 먼 훗날의 이야기다</t>
+        </is>
+      </c>
+      <c r="H1639" t="inlineStr">
+        <is>
+          <t>While military robots are being tested, their actual deployment on the battlefield is still some way off.</t>
+        </is>
+      </c>
+      <c r="I1639" t="inlineStr">
+        <is>
+          <t>Fully autonomous self-driving cars on chaotic city streets are still some way off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>ENG-20260609-015</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>call on</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>/kɔːl ɒn/</t>
+        </is>
+      </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>(공식적으로 대중이나 단체에) 강력히 요구하다, 요청하다</t>
+        </is>
+      </c>
+      <c r="H1640" t="inlineStr">
+        <is>
+          <t>The government decided to call on major app stores to implement stricter age verification.</t>
+        </is>
+      </c>
+      <c r="I1640" t="inlineStr">
+        <is>
+          <t>The environmental group called on the city council to ban single-use plastics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>ENG-20260609-016</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>fall into the trap of</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>/fɔːl ˈɪn.tuː ðə træp ʌv/</t>
+        </is>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>흔히 저지르는 함정(실수)에 빠지다</t>
+        </is>
+      </c>
+      <c r="H1641" t="inlineStr">
+        <is>
+          <t>Retirees shouldn't fall into the trap of underspending out of irrational fear.</t>
+        </is>
+      </c>
+      <c r="I1641" t="inlineStr">
+        <is>
+          <t>Many young companies fall into the trap of expanding too quickly before finding product-market fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>ENG-20260609-017</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>make money hand over fist</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>/meɪk ˈmʌn.i hænd ˈəʊ.vər fɪst/</t>
+        </is>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>돈을 자루째 긁어모으다, 무서운 기세로 돈을 벌다</t>
+        </is>
+      </c>
+      <c r="H1642" t="inlineStr">
+        <is>
+          <t>Phoebe tells Joey that donating to a fertility study will let him make money hand over fist.</t>
+        </is>
+      </c>
+      <c r="I1642" t="inlineStr">
+        <is>
+          <t>Our online educational platform is currently making money hand over fist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>ENG-20260609-018</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>make a big deal out of</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>/meɪk ə bɪɡ diːl aʊt ʌv/</t>
+        </is>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>대수롭지 않은 일을 크게 만들다, 난리법석을 떨다</t>
+        </is>
+      </c>
+      <c r="H1643" t="inlineStr">
+        <is>
+          <t>Joey reassures his friends that joining the fertility program is not that big a deal.</t>
+        </is>
+      </c>
+      <c r="I1643" t="inlineStr">
+        <is>
+          <t>It was just a small typo; there's no need to make a big deal out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>ENG-20260609-019</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>make a contribution to</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>/meɪk ə ˌkɒn.trɪˈbjuː.ʃən tuː/</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>~에 보탬이 되다, 기부/기여하다</t>
+        </is>
+      </c>
+      <c r="H1644" t="inlineStr">
+        <is>
+          <t>Joey visits the research clinic every other day to make his contribution to the project.</t>
+        </is>
+      </c>
+      <c r="I1644" t="inlineStr">
+        <is>
+          <t>She made a significant contribution to the success of our fundraising drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>ENG-20260609-020</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>have a point</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>/hæv ə pɔɪnt/</t>
+        </is>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>일리가 있다, 하는 말이 맞다</t>
+        </is>
+      </c>
+      <c r="H1645" t="inlineStr">
+        <is>
+          <t>Monica admits that Joey has a point when he explains why he won't tell his girlfriend.</t>
+        </is>
+      </c>
+      <c r="I1645" t="inlineStr">
+        <is>
+          <t>You have a point there. Maybe we should postpone the product release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>ENG-20260609-021</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>move on</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>/muːv ɒn/</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>(미련이나 나쁜 기억을 털고) 앞으로 나아가다, 새 출발을 하다</t>
+        </is>
+      </c>
+      <c r="H1646" t="inlineStr">
+        <is>
+          <t>Joey advises Ross to forget about Rachel, move on with his life, and enjoy his trip to China.</t>
+        </is>
+      </c>
+      <c r="I1646" t="inlineStr">
+        <is>
+          <t>It is hard to accept failures, but we have to learn from them and move on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>ENG-20260609-022</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>every now and then</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>/ˈev.ri naʊ ænd ðen/</t>
+        </is>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>가끔씩, 때때로 한 번씩</t>
+        </is>
+      </c>
+      <c r="H1647" t="inlineStr">
+        <is>
+          <t>Ross asks Monica to show his photo to Ben every now and then so his son won't forget him.</t>
+        </is>
+      </c>
+      <c r="I1647" t="inlineStr">
+        <is>
+          <t>Every now and then, I like to unplug from social media and read a book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>ENG-20260609-023</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>show interest in</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>/ʃəʊ ˈɪn.trest ɪn/</t>
+        </is>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>~에 관심을 보이다, 흥미를 표현하다</t>
+        </is>
+      </c>
+      <c r="H1648" t="inlineStr">
+        <is>
+          <t>Joey jokingly wonders why Rachel is going out with Carl when she hasn't shown interest in Ross.</t>
+        </is>
+      </c>
+      <c r="I1648" t="inlineStr">
+        <is>
+          <t>Several foreign investors have shown interest in our startup's core patent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>ENG-20260609-024</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>put out a fire</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>/pʊt aʊt ə faɪər/</t>
+        </is>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>불을 끄다, 시급한 급한 불(문제)을 해결하다</t>
+        </is>
+      </c>
+      <c r="H1649" t="inlineStr">
+        <is>
+          <t>Chandler and Joey joke about putting out the barbecue fire in a very crude way.</t>
+        </is>
+      </c>
+      <c r="I1649" t="inlineStr">
+        <is>
+          <t>I've been busy all morning trying to put out fires with angry customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>ENG-20260609-025</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>pique someone's interest</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>/piːk ˈsʌm.wʌnz ˈɪn.trest/</t>
+        </is>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>~의 호기심(흥미)을 확 자극하다</t>
+        </is>
+      </c>
+      <c r="H1650" t="inlineStr">
+        <is>
+          <t>When Joey mentions a mysterious study, everyone's interest is piqued immediately.</t>
+        </is>
+      </c>
+      <c r="I1650" t="inlineStr">
+        <is>
+          <t>The mysterious trailer for the new sci-fi film really piqued my interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>ENG-20260609-026</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>take someone's side</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>/teɪk ˈsʌm.wʌnz saɪd/</t>
+        </is>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>~의 편을 들어주다, 옹호하다</t>
+        </is>
+      </c>
+      <c r="H1651" t="inlineStr">
+        <is>
+          <t>In a dispute, Chandler is always careful not to take Ross's side too aggressively.</t>
+        </is>
+      </c>
+      <c r="I1651" t="inlineStr">
+        <is>
+          <t>My manager always takes my side when clients make unreasonable demands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>ENG-20260609-027</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>pencil someone in</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>/ˈpen.səl ˈsʌm.wʌn ɪn/</t>
+        </is>
+      </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>임시로 (나중에 변경할 수 있게) 일정을 잡아두다</t>
+        </is>
+      </c>
+      <c r="H1652" t="inlineStr">
+        <is>
+          <t>The advisor suggested retirees pencil in their holiday trips way in advance.</t>
+        </is>
+      </c>
+      <c r="I1652" t="inlineStr">
+        <is>
+          <t>Let's pencil you in for a meeting next Tuesday at 2 PM, and we can confirm later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>ENG-20260609-028</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>hit a home run</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>/hɪt ə həʊm rʌn/</t>
+        </is>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>초대박을 치다, 대성공을 거두다</t>
+        </is>
+      </c>
+      <c r="H1653" t="inlineStr">
+        <is>
+          <t>With the acquisition of Nuvalent, GSK hopes to hit a home run in cancer therapeutics.</t>
+        </is>
+      </c>
+      <c r="I1653" t="inlineStr">
+        <is>
+          <t>The design team really hit a home run with the new minimalist logo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>ENG-20260609-029</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>bring someone up to speed</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>/brɪŋ ˈsʌm.wʌn ʌp tuː spiːd/</t>
+        </is>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>최신 상황과 정보를 업데이트하여 이해하게 돕다</t>
+        </is>
+      </c>
+      <c r="H1654" t="inlineStr">
+        <is>
+          <t>Joey's friends had to bring Ross up to speed on who Carl actually was.</t>
+        </is>
+      </c>
+      <c r="I1654" t="inlineStr">
+        <is>
+          <t>Could you please bring me up to speed on what was decided during the morning meeting?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>ENG-20260609-030</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>call someone's bluff</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>/kɔːl ˈsʌm.wʌnz blʌf/</t>
+        </is>
+      </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>허세나 으름장에 속지 않고 진위를 시험해 보다</t>
+        </is>
+      </c>
+      <c r="H1655" t="inlineStr">
+        <is>
+          <t>The USDA Secretary decided to call the Texas ag chief's bluff by demanding evidence.</t>
+        </is>
+      </c>
+      <c r="I1655" t="inlineStr">
+        <is>
+          <t>He threatened to resign if he didn't get a raise, so the boss decided to call his bluff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>ENG-20260609-031</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>make head or tail of</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>/meɪk hed ɔː teɪl ʌv/</t>
+        </is>
+      </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>(주로 부정문에서) 도통 갈피를 못 잡다, 갈무리를 못 하다</t>
+        </is>
+      </c>
+      <c r="H1656" t="inlineStr">
+        <is>
+          <t>Ross couldn't make head or tail of why Rachel had suddenly agreed to date Carl.</t>
+        </is>
+      </c>
+      <c r="I1656" t="inlineStr">
+        <is>
+          <t>The instructions are so poorly translated that I can't make head or tail of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>ENG-20260609-032</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>hit bottom</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>/hɪt ˈbɒt.əm/</t>
+        </is>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>바닥을 치다, 최악의 국면에 도달하다</t>
+        </is>
+      </c>
+      <c r="H1657" t="inlineStr">
+        <is>
+          <t>Market indicators show that the crumbling pillars of the bull market have not yet hit bottom.</t>
+        </is>
+      </c>
+      <c r="I1657" t="inlineStr">
+        <is>
+          <t>The company's stock value finally hit bottom before surging back up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>ENG-20260609-033</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>take advantage of</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>/teɪk ədˈvɑːn.tɪd ʌv/</t>
+        </is>
+      </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>기회 등을 십분 활용하다, 이용하다</t>
+        </is>
+      </c>
+      <c r="H1658" t="inlineStr">
+        <is>
+          <t>Tech giants are trying to take advantage of newly buoyant public stock markets.</t>
+        </is>
+      </c>
+      <c r="I1658" t="inlineStr">
+        <is>
+          <t>We should take advantage of this sunny weather and have our team meeting outside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>ENG-20260609-034</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>bear the brunt of</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>/beər ðə brʌnt ʌv/</t>
+        </is>
+      </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>(공격이나 불황 등) 가장 안 좋은 타격을 맨몸으로 감내하다</t>
+        </is>
+      </c>
+      <c r="H1659" t="inlineStr">
+        <is>
+          <t>Small business owners always bear the brunt of rising fuel costs during energy crises.</t>
+        </is>
+      </c>
+      <c r="I1659" t="inlineStr">
+        <is>
+          <t>The customer service team had to bear the brunt of the users' anger after the server crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>ENG-20260609-035</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>keep one's fingers on the pulse</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>/kiːp wʌnz ˈfɪŋ.ɡəz ɒn ðə pʌls/</t>
+        </is>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>최신 트렌드나 흐름을 아주 꿰뚫고 있다</t>
+        </is>
+      </c>
+      <c r="H1660" t="inlineStr">
+        <is>
+          <t>To stay ahead in the AI industry, Apple must keep its fingers on the pulse of Silicon Valley.</t>
+        </is>
+      </c>
+      <c r="I1660" t="inlineStr">
+        <is>
+          <t>As a marketing director, you must keep your fingers on the pulse of pop culture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>ENG-20260609-036</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>get down to business</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>/ɡet daʊn tuː ˈbɪz.nɪs/</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>사담을 멈추고 본격적으로 일(본론)에 착수하다</t>
+        </is>
+      </c>
+      <c r="H1661" t="inlineStr">
+        <is>
+          <t>Once Chandler and Joey entered, the girls decided to stop joking and get down to business.</t>
+        </is>
+      </c>
+      <c r="I1661" t="inlineStr">
+        <is>
+          <t>Now that everyone is finally here, let's get down to business and review the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>ENG-20260609-037</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>give rise to</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>/ɡɪv raɪz tuː/</t>
+        </is>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>새로운 결과나 갈등을 초래하다, 발생시키다</t>
+        </is>
+      </c>
+      <c r="H1662" t="inlineStr">
+        <is>
+          <t>The rapid deployment of humanoid robots could give rise to many ethical concerns.</t>
+        </is>
+      </c>
+      <c r="I1662" t="inlineStr">
+        <is>
+          <t>The sudden introduction of the new tax policy gave rise to widespread protests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>ENG-20260609-038</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>be in safe hands</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>/biː ɪn seɪf hændz/</t>
+        </is>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>믿을 만한(안전한) 사람의 관리를 받아 안심해도 되다</t>
+        </is>
+      </c>
+      <c r="H1663" t="inlineStr">
+        <is>
+          <t>Monica assured Ross that Ben would be in safe hands with Carol.</t>
+        </is>
+      </c>
+      <c r="I1663" t="inlineStr">
+        <is>
+          <t>You don't have to worry about the logistics; the entire event is in safe hands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>ENG-20260609-039</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>take account of</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>/teɪk əˈkaʊnt ʌv/</t>
+        </is>
+      </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>결정을 내릴 때 ~을 충분히 감안하다, 고려하다</t>
+        </is>
+      </c>
+      <c r="H1664" t="inlineStr">
+        <is>
+          <t>Retirees must take account of inflation when setting up their long-term budgets.</t>
+        </is>
+      </c>
+      <c r="I1664" t="inlineStr">
+        <is>
+          <t>When planning outdoor events, you always have to take account of the weather.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>ENG-20260609-040</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>throw light on</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>/θrəʊ laɪt ɒn/</t>
+        </is>
+      </c>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>(수수께끼나 어두운 진실을) 명확히 규명하다, 비추어 밝히다</t>
+        </is>
+      </c>
+      <c r="H1665" t="inlineStr">
+        <is>
+          <t>The court's investigation will hopefully throw light on the missing crypto billions.</t>
+        </is>
+      </c>
+      <c r="I1665" t="inlineStr">
+        <is>
+          <t>This newly discovered document throws light on the causes of the civil war.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>ENG-20260609-041</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>rule with an iron fist</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>/ruːl wɪð ən ˈaɪ.ən fɪst/</t>
+        </is>
+      </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>독재적으로 강하게 철권통치하다, 주물럭거리다</t>
+        </is>
+      </c>
+      <c r="H1666" t="inlineStr">
+        <is>
+          <t>The state ag chief was accused of trying to rule his department with an iron fist.</t>
+        </is>
+      </c>
+      <c r="I1666" t="inlineStr">
+        <is>
+          <t>The CEO is known to rule the corporate headquarters with an iron fist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>ENG-20260609-042</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>fall in line</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>/fɔːl ɪn laɪn/</t>
+        </is>
+      </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>규정이나 짓눌러오는 방침에 수긍하며 순순히 따르다</t>
+        </is>
+      </c>
+      <c r="H1667" t="inlineStr">
+        <is>
+          <t>Many app developer groups were forced to fall in line with Apple's strict standards.</t>
+        </is>
+      </c>
+      <c r="I1667" t="inlineStr">
+        <is>
+          <t>Employees who refuse to fall in line with the new hybrid work policy will be penalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>ENG-20260609-043</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>wear many hats</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>/weər ˈmen.i hæts/</t>
+        </is>
+      </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>한 번에 여러 역할(직무)을 소화하느라 종횡무진하다</t>
+        </is>
+      </c>
+      <c r="H1668" t="inlineStr">
+        <is>
+          <t>In early-stage biotech startups, the CEO often has to wear many hats.</t>
+        </is>
+      </c>
+      <c r="I1668" t="inlineStr">
+        <is>
+          <t>As a co-founder of the agency, I wear many hats, from copywriter to accountant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>ENG-20260609-044</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>make a name for oneself</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>/meɪk ə neɪm fɔːr wʌnˈself/</t>
+        </is>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>업계에서 두각을 나타내어 명성을 쌓다</t>
+        </is>
+      </c>
+      <c r="H1669" t="inlineStr">
+        <is>
+          <t>OpenAI managed to make a name for itself in a very short period of time.</t>
+        </is>
+      </c>
+      <c r="I1669" t="inlineStr">
+        <is>
+          <t>She worked extremely hard to make a name for herself as a criminal defense attorney.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>ENG-20260609-045</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>run out of gas</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>/rʌn aʊt ʌv ɡæs/</t>
+        </is>
+      </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>성장 동력이 바닥나다, 탈진하여 힘이 다 빠지다</t>
+        </is>
+      </c>
+      <c r="H1670" t="inlineStr">
+        <is>
+          <t>Critics warned that the continuous bull market was beginning to run out of gas.</t>
+        </is>
+      </c>
+      <c r="I1670" t="inlineStr">
+        <is>
+          <t>After working seventy hours this week, I've completely run out of gas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>ENG-20260609-046</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>keep a close watch on</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>/kiːp ə kləʊs wɒtʃ ɒn/</t>
+        </is>
+      </c>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>~의 동향을 삼엄하게 주시하다, 감시하다</t>
+        </is>
+      </c>
+      <c r="H1671" t="inlineStr">
+        <is>
+          <t>The SEC is keeping a close watch on all confidential IPO filings this year.</t>
+        </is>
+      </c>
+      <c r="I1671" t="inlineStr">
+        <is>
+          <t>The doctors are keeping a close watch on the patient's heart rate overnight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>ENG-20260609-047</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>bring to a halt</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>/brɪŋ tuː ə hɔːlt/</t>
+        </is>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>가동을 전면 중단(정지)시키다</t>
+        </is>
+      </c>
+      <c r="H1672" t="inlineStr">
+        <is>
+          <t>The engine manufacturing crisis threatened to bring flight schedules to a halt.</t>
+        </is>
+      </c>
+      <c r="I1672" t="inlineStr">
+        <is>
+          <t>A sudden power outage brought the entire production line to a halt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>ENG-20260609-048</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>readily available</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>/ˈred.ɪ.li əˈveɪ.lə.bəl/</t>
+        </is>
+      </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>쉽게 손에 넣거나 즉각 이용할 수 있는</t>
+        </is>
+      </c>
+      <c r="H1673" t="inlineStr">
+        <is>
+          <t>Retirees often assume backup funds are readily available without checking account lockups.</t>
+        </is>
+      </c>
+      <c r="I1673" t="inlineStr">
+        <is>
+          <t>Fresh water and organic produce are readily available in this rural eco-village.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>ENG-20260609-049</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>put an end to</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>/pʊt ən end tuː/</t>
+        </is>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>종지부를 찍다, 완전히 마감하다</t>
+        </is>
+      </c>
+      <c r="H1674" t="inlineStr">
+        <is>
+          <t>The government is determined to put an end to unsafe online content targeting children.</t>
+        </is>
+      </c>
+      <c r="I1674" t="inlineStr">
+        <is>
+          <t>We must implement strict regulations to put an end to illegal financial transactions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>ENG-20260609-050</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>fall into place</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>/fɔːl ˈɪn.tuː pleɪs/</t>
+        </is>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>조각들이 제자리를 찾듯 순리대로 일이 잘 풀리다</t>
+        </is>
+      </c>
+      <c r="H1675" t="inlineStr">
+        <is>
+          <t>Once Apple confirmed Nvidia's involvement, all the pieces of their AI plan fell into place.</t>
+        </is>
+      </c>
+      <c r="I1675" t="inlineStr">
+        <is>
+          <t>After we hired a new designer, everything in our product launch plan fell into place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>ENG-20260609-051</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>pose a threat</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>/poʊz ə θrɛt/</t>
+        </is>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>위협이 되다, 위협을 가하다</t>
+        </is>
+      </c>
+      <c r="H1676" t="inlineStr">
+        <is>
+          <t>USDA Secretary Rollins calls Texas ag chief 'unserious' amid screwworm threat.</t>
+        </is>
+      </c>
+      <c r="I1676" t="inlineStr">
+        <is>
+          <t>The rapid development of unregulated AI could pose a threat to data privacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>ENG-20260609-052</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>serve time</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>/sɜːrv taɪm/</t>
+        </is>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>복역하다, 형기를 채우다</t>
+        </is>
+      </c>
+      <c r="H1677" t="inlineStr">
+        <is>
+          <t>The former leader of crypto platform FTX, currently serving a 25-year sentence, applied to be pardoned.</t>
+        </is>
+      </c>
+      <c r="I1677" t="inlineStr">
+        <is>
+          <t>He is currently serving time for financial fraud after the SEC uncovered his scheme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>ENG-20260609-053</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>pile up</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>/paɪl ʌp/</t>
+        </is>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>(일, 물건 등이) 쌓이다, 수북해지다</t>
+        </is>
+      </c>
+      <c r="H1678" t="inlineStr">
+        <is>
+          <t>No no, this big pile of dishes in my mom's breakfront.</t>
+        </is>
+      </c>
+      <c r="I1678" t="inlineStr">
+        <is>
+          <t>While I was away on vacation, my unread emails kept piling up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>ENG-20260609-054</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>loom on the horizon</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>/luːm ɒn ðə həˈraɪ.zən/</t>
+        </is>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>(불안한 일이) 곧 닥칠 것처럼 보이다</t>
+        </is>
+      </c>
+      <c r="H1679" t="inlineStr">
+        <is>
+          <t>The deal comes at a time of biotech dealmaking frenzy, driven by looming patent cliffs.</t>
+        </is>
+      </c>
+      <c r="I1679" t="inlineStr">
+        <is>
+          <t>With a major recession looming on the horizon, tech firms are cutting down their budgets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>ENG-20260609-055</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>scale up</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>/skeɪl ʌp/</t>
+        </is>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>(규모나 범위를) 확대하다</t>
+        </is>
+      </c>
+      <c r="H1680" t="inlineStr">
+        <is>
+          <t>OpenAI is prepping Wall Street for mega AI debut as it tries to expand operations.</t>
+        </is>
+      </c>
+      <c r="I1680" t="inlineStr">
+        <is>
+          <t>The production line needs to scale up quickly to meet the sudden surge in global demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>ENG-20260609-056</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>sound the alarm</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>/saʊnd ðə əˈlɑːrm/</t>
+        </is>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>경종을 울리다, 경고를 보내다</t>
+        </is>
+      </c>
+      <c r="H1681" t="inlineStr">
+        <is>
+          <t>Jim Cramer warns key pillars of the bull market are beginning to crumble.</t>
+        </is>
+      </c>
+      <c r="I1681" t="inlineStr">
+        <is>
+          <t>Economists are sounding the alarm over the rising levels of corporate debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>ENG-20260609-057</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>run into a brick wall</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>/rʌn ˈɪntuː ə brɪk wɔːl/</t>
+        </is>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>큰 장벽에 부딪히다, 진척을 보지 못하다</t>
+        </is>
+      </c>
+      <c r="H1682" t="inlineStr">
+        <is>
+          <t>81% of respondents said the cost of living is their biggest financial hurdle to achieving the American Dream.</t>
+        </is>
+      </c>
+      <c r="I1682" t="inlineStr">
+        <is>
+          <t>Our R&amp;D team ran into a brick wall trying to solve the battery overheating issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>ENG-20260609-058</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>be on the line</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>/biː ɒn ðə laɪn/</t>
+        </is>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>(커리어, 평판, 목숨 등이) 위태로운 처지에 있다</t>
+        </is>
+      </c>
+      <c r="H1683" t="inlineStr">
+        <is>
+          <t>SpaceX's stock market debut could be Musk's biggest gamble yet.</t>
+        </is>
+      </c>
+      <c r="I1683" t="inlineStr">
+        <is>
+          <t>If this marketing campaign fails, my entire career at this company is on the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>ENG-20260609-059</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>fall flat</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>/fɔːl flæt/</t>
+        </is>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>(의도한 시도나 유머 등이) 반응을 얻지 못하고 실패하다</t>
+        </is>
+      </c>
+      <c r="H1684" t="inlineStr">
+        <is>
+          <t>Alright, this barbecue is gonna be very fun.</t>
+        </is>
+      </c>
+      <c r="I1684" t="inlineStr">
+        <is>
+          <t>His jokes at the presentation fell flat, making the atmosphere in the room very awkward.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1684"/>
+  <dimension ref="A1:I1724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79564,6 +79564,1886 @@
         </is>
       </c>
     </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>ENG-20260610-001</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>due out</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>/duː aʊt/</t>
+        </is>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>출시되거나 발표될 예정이다</t>
+        </is>
+      </c>
+      <c r="H1685" t="inlineStr">
+        <is>
+          <t>The May inflation numbers are due out Wednesday morning.</t>
+        </is>
+      </c>
+      <c r="I1685" t="inlineStr">
+        <is>
+          <t>The final report is due out next week, so please hold off on any decisions until then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>ENG-20260610-002</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>capitalize on</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>/ˈkæpɪtəlaɪz ɒn/</t>
+        </is>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>기회를 활용하여 이득을 보다</t>
+        </is>
+      </c>
+      <c r="H1686" t="inlineStr">
+        <is>
+          <t>GM is expanding efforts to capitalize on the expected growth of energy storage.</t>
+        </is>
+      </c>
+      <c r="I1686" t="inlineStr">
+        <is>
+          <t>We should capitalize on the current market trend to boost our sales figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>ENG-20260610-003</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>tap into</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>/tæp ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>자원이나 자금을 끌어다 쓰다</t>
+        </is>
+      </c>
+      <c r="H1687" t="inlineStr">
+        <is>
+          <t>Super Micro is the latest company to announce that it's tapping the capital markets.</t>
+        </is>
+      </c>
+      <c r="I1687" t="inlineStr">
+        <is>
+          <t>Many startups tap into venture capital to accelerate their initial growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>ENG-20260610-004</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>cause a stir</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>/kɔːz ə stɜːr/</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>소동을 일으키다, 화제가 되다</t>
+        </is>
+      </c>
+      <c r="H1688" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 is an AI program which caused a stir among technology leaders.</t>
+        </is>
+      </c>
+      <c r="I1688" t="inlineStr">
+        <is>
+          <t>The CEO's surprise announcement definitely caused a stir during the board meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>ENG-20260610-005</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>no show</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>/noʊ ʃoʊ/</t>
+        </is>
+      </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>예약해놓고 나타나지 않는 사람(노쇼)</t>
+        </is>
+      </c>
+      <c r="H1689" t="inlineStr">
+        <is>
+          <t>Driving test booking rules tightened after thousands of no shows.</t>
+        </is>
+      </c>
+      <c r="I1689" t="inlineStr">
+        <is>
+          <t>We have a strict policy for no shows, so please let us know if you can't make it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>ENG-20260610-006</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>keep someone on side</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>/kiːp ˈsʌmwʌn ɒn saɪd/</t>
+        </is>
+      </c>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>누군가의 지지를 유지하다, 편을 유지하다</t>
+        </is>
+      </c>
+      <c r="H1690" t="inlineStr">
+        <is>
+          <t>Football fans and bosses share their strategies to keep your boss on side.</t>
+        </is>
+      </c>
+      <c r="I1690" t="inlineStr">
+        <is>
+          <t>You need to keep the stakeholders on side if you want the project to proceed smoothly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>ENG-20260610-007</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>hook up</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>/hʊk ʌp/</t>
+        </is>
+      </c>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>남녀가 만나다/관계를 맺다</t>
+        </is>
+      </c>
+      <c r="H1691" t="inlineStr">
+        <is>
+          <t>Y'know when you two hooked up!</t>
+        </is>
+      </c>
+      <c r="I1691" t="inlineStr">
+        <is>
+          <t>Are they dating or did they just hook up once?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>ENG-20260610-008</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>make out</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>/meɪk aʊt/</t>
+        </is>
+      </c>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>진하게 키스하다/애무하다</t>
+        </is>
+      </c>
+      <c r="H1692" t="inlineStr">
+        <is>
+          <t>You and I just made out!</t>
+        </is>
+      </c>
+      <c r="I1692" t="inlineStr">
+        <is>
+          <t>They were making out in the corner of the room all night.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>ENG-20260610-009</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>live it up</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>/lɪv ɪt ʌp/</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>즐겁게 보내다, 호화롭게 생활하다</t>
+        </is>
+      </c>
+      <c r="H1693" t="inlineStr">
+        <is>
+          <t>You're really livin' it up here in London huh?</t>
+        </is>
+      </c>
+      <c r="I1693" t="inlineStr">
+        <is>
+          <t>We saved all year so we could live it up on our vacation in Paris.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>ENG-20260610-010</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>let something go</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>/lɛt ˈsʌmθɪŋ ɡoʊ/</t>
+        </is>
+      </c>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>잊어버리다, 과거에 연연하지 않다</t>
+        </is>
+      </c>
+      <c r="H1694" t="inlineStr">
+        <is>
+          <t>You've just got to let that go okay?</t>
+        </is>
+      </c>
+      <c r="I1694" t="inlineStr">
+        <is>
+          <t>That argument was weeks ago, you really need to let it go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>ENG-20260610-011</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>get off the ground</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>/ɡɛt ɔːf ðə ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>시작되다, 순조롭게 출발하다</t>
+        </is>
+      </c>
+      <c r="H1695" t="inlineStr">
+        <is>
+          <t>It’s really hard to get a startup off the ground without proper funding.</t>
+        </is>
+      </c>
+      <c r="I1695" t="inlineStr">
+        <is>
+          <t>The project finally got off the ground after months of planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>ENG-20260610-012</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>pull your weight</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>/pʊl jɔːr weɪt/</t>
+        </is>
+      </c>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>자신의 몫을 다하다</t>
+        </is>
+      </c>
+      <c r="H1696" t="inlineStr">
+        <is>
+          <t>If everyone pulls their weight, we can finish this on time.</t>
+        </is>
+      </c>
+      <c r="I1696" t="inlineStr">
+        <is>
+          <t>It feels like some team members aren't pulling their weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>ENG-20260610-013</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>in the long run</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>/ɪn ðə lɔːŋ rʌn/</t>
+        </is>
+      </c>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>길게 보면, 장기적으로는</t>
+        </is>
+      </c>
+      <c r="H1697" t="inlineStr">
+        <is>
+          <t>This investment will be beneficial in the long run.</t>
+        </is>
+      </c>
+      <c r="I1697" t="inlineStr">
+        <is>
+          <t>It might be hard now, but it'll pay off in the long run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>ENG-20260610-014</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>think on your feet</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>/θɪŋk ɒn jɔːr fiːt/</t>
+        </is>
+      </c>
+      <c r="G1698" t="inlineStr">
+        <is>
+          <t>즉각적으로 판단하다</t>
+        </is>
+      </c>
+      <c r="H1698" t="inlineStr">
+        <is>
+          <t>In this business, you need to be able to think on your feet.</t>
+        </is>
+      </c>
+      <c r="I1698" t="inlineStr">
+        <is>
+          <t>The interviewer asked me a tough question, so I had to think on my feet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>ENG-20260610-015</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>up to speed</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>/ʌp tuː spiːd/</t>
+        </is>
+      </c>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>최신 정보를 알고 있는</t>
+        </is>
+      </c>
+      <c r="H1699" t="inlineStr">
+        <is>
+          <t>I need to get you up to speed on the recent changes.</t>
+        </is>
+      </c>
+      <c r="I1699" t="inlineStr">
+        <is>
+          <t>Let me get you up to speed with what happened while you were away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>ENG-20260610-016</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>jump the gun</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>/dʒʌmp ðə ɡʌn/</t>
+        </is>
+      </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>성급하게 행동하다</t>
+        </is>
+      </c>
+      <c r="H1700" t="inlineStr">
+        <is>
+          <t>Don't jump the gun; wait until you have all the facts.</t>
+        </is>
+      </c>
+      <c r="I1700" t="inlineStr">
+        <is>
+          <t>I think we jumped the gun by hiring so many people too quickly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>ENG-20260610-017</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>sit on the fence</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>/sɪt ɒn ðə fɛns/</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>결정을 미루다, 중립을 지키다</t>
+        </is>
+      </c>
+      <c r="H1701" t="inlineStr">
+        <is>
+          <t>You can't just sit on the fence forever; you have to choose a side.</t>
+        </is>
+      </c>
+      <c r="I1701" t="inlineStr">
+        <is>
+          <t>He's sitting on the fence about the proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>ENG-20260610-018</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>get into gear</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>/ɡɛt ˈɪntuː ɡɪər/</t>
+        </is>
+      </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>시동을 걸다, 본격적으로 일을 시작하다</t>
+        </is>
+      </c>
+      <c r="H1702" t="inlineStr">
+        <is>
+          <t>Now that we have the budget, we can finally get into gear.</t>
+        </is>
+      </c>
+      <c r="I1702" t="inlineStr">
+        <is>
+          <t>The team needs to get into gear to finish the project by Friday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>ENG-20260610-019</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>show the ropes</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>/ʃoʊ ðə roʊps/</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>방법을 가르쳐주다, 적응을 돕다</t>
+        </is>
+      </c>
+      <c r="H1703" t="inlineStr">
+        <is>
+          <t>I’ll show you the ropes on your first day.</t>
+        </is>
+      </c>
+      <c r="I1703" t="inlineStr">
+        <is>
+          <t>Thanks for showing me the ropes; it made my first week so much easier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>ENG-20260610-020</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>take for granted</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>/teɪk fɔːr ˈɡræntɪd/</t>
+        </is>
+      </c>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>당연하게 여기다</t>
+        </is>
+      </c>
+      <c r="H1704" t="inlineStr">
+        <is>
+          <t>Don’t take your job for granted; it’s a great opportunity.</t>
+        </is>
+      </c>
+      <c r="I1704" t="inlineStr">
+        <is>
+          <t>We often take simple things like internet access for granted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>ENG-20260610-021</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>give the go-ahead</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>/ɡɪv ðə ˈɡoʊ əhɛd/</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>허가하다, 승인하다</t>
+        </is>
+      </c>
+      <c r="H1705" t="inlineStr">
+        <is>
+          <t>The boss gave us the go-ahead to start the renovation.</t>
+        </is>
+      </c>
+      <c r="I1705" t="inlineStr">
+        <is>
+          <t>We can't start until we get the go-ahead from legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>ENG-20260610-022</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>keep in mind</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>/kiːp ɪn maɪnd/</t>
+        </is>
+      </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>명심하다, 기억하다</t>
+        </is>
+      </c>
+      <c r="H1706" t="inlineStr">
+        <is>
+          <t>Please keep in mind that the deadline is next week.</t>
+        </is>
+      </c>
+      <c r="I1706" t="inlineStr">
+        <is>
+          <t>Keep in mind that this is a long-term goal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>ENG-20260610-023</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>see the light</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>/siː ðə laɪt/</t>
+        </is>
+      </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>이해하게 되다, 깨닫다</t>
+        </is>
+      </c>
+      <c r="H1707" t="inlineStr">
+        <is>
+          <t>He finally saw the light and changed his strategy.</t>
+        </is>
+      </c>
+      <c r="I1707" t="inlineStr">
+        <is>
+          <t>I hope they see the light before the project crashes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>ENG-20260610-024</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>at the eleventh hour</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>/æt ði ɪˈlɛvənθ aʊər/</t>
+        </is>
+      </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>마지막 순간에</t>
+        </is>
+      </c>
+      <c r="H1708" t="inlineStr">
+        <is>
+          <t>The deal was saved at the eleventh hour.</t>
+        </is>
+      </c>
+      <c r="I1708" t="inlineStr">
+        <is>
+          <t>They made a change at the eleventh hour, which caused a panic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>ENG-20260610-025</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>throw out an idea</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>/θroʊ aʊt ən aɪˈdɪə/</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>의견을 제시하다/던져보다</t>
+        </is>
+      </c>
+      <c r="H1709" t="inlineStr">
+        <is>
+          <t>I want to throw out an idea for the new project.</t>
+        </is>
+      </c>
+      <c r="I1709" t="inlineStr">
+        <is>
+          <t>She threw out an idea, and we ended up using it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>ENG-20260610-026</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>Modern Family</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>go out of your way</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>/ɡoʊ aʊt ɒv jɔːr weɪ/</t>
+        </is>
+      </c>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>굳이 애써서 ~하다</t>
+        </is>
+      </c>
+      <c r="H1710" t="inlineStr">
+        <is>
+          <t>She went out of her way to help the new intern.</t>
+        </is>
+      </c>
+      <c r="I1710" t="inlineStr">
+        <is>
+          <t>You didn't have to go out of your way to pick me up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>ENG-20260610-027</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>keep in touch</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>/kiːp ɪn tʌtʃ/</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>계속 연락하며 지내다</t>
+        </is>
+      </c>
+      <c r="H1711" t="inlineStr">
+        <is>
+          <t>It was great meeting you; let’s keep in touch.</t>
+        </is>
+      </c>
+      <c r="I1711" t="inlineStr">
+        <is>
+          <t>I try to keep in touch with my colleagues even after leaving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>ENG-20260610-028</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>get the message</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>/ɡɛt ðə ˈmɛsɪdʒ/</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>의도를 알아차리다</t>
+        </is>
+      </c>
+      <c r="H1712" t="inlineStr">
+        <is>
+          <t>I kept hinting, but he just didn't get the message.</t>
+        </is>
+      </c>
+      <c r="I1712" t="inlineStr">
+        <is>
+          <t>After I stopped inviting him, he finally got the message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>ENG-20260610-029</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>have a head for</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>/hæv ə hɛd fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>~에 재능이 있다, 머리가 좋다</t>
+        </is>
+      </c>
+      <c r="H1713" t="inlineStr">
+        <is>
+          <t>He has a head for business, so he's doing great.</t>
+        </is>
+      </c>
+      <c r="I1713" t="inlineStr">
+        <is>
+          <t>I don't really have a head for numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>ENG-20260610-030</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>in the dark</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>/ɪn ðə dɑːrk/</t>
+        </is>
+      </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>모르는 상태인</t>
+        </is>
+      </c>
+      <c r="H1714" t="inlineStr">
+        <is>
+          <t>The staff were kept in the dark about the takeover.</t>
+        </is>
+      </c>
+      <c r="I1714" t="inlineStr">
+        <is>
+          <t>I've been in the dark about these changes for weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>ENG-20260610-031</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>hold your ground</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>/hoʊld jɔːr ɡraʊnd/</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>물러서지 않다, 버티다</t>
+        </is>
+      </c>
+      <c r="H1715" t="inlineStr">
+        <is>
+          <t>It’s important to hold your ground during salary negotiations.</t>
+        </is>
+      </c>
+      <c r="I1715" t="inlineStr">
+        <is>
+          <t>Don't let them intimidate you; just hold your ground.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>ENG-20260610-032</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>Modern Family</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>give a hand</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>/ɡɪv ə hænd/</t>
+        </is>
+      </c>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>도와주다</t>
+        </is>
+      </c>
+      <c r="H1716" t="inlineStr">
+        <is>
+          <t>Can you give me a hand with this heavy box?</t>
+        </is>
+      </c>
+      <c r="I1716" t="inlineStr">
+        <is>
+          <t>I’ll be glad to give you a hand with that project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>ENG-20260610-033</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>get out of my sight</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>/ɡɛt aʊt ɒv maɪ saɪt/</t>
+        </is>
+      </c>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>내 눈앞에서 사라져라</t>
+        </is>
+      </c>
+      <c r="H1717" t="inlineStr">
+        <is>
+          <t>Just get out of my sight before I say something I regret.</t>
+        </is>
+      </c>
+      <c r="I1717" t="inlineStr">
+        <is>
+          <t>Get out of my sight, I don't want to see you right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>ENG-20260610-034</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>Modern Family</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>put your foot in your mouth</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>/pʊt jɔːr fʊt ɪn jɔːr maʊθ/</t>
+        </is>
+      </c>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>말실수를 하다</t>
+        </is>
+      </c>
+      <c r="H1718" t="inlineStr">
+        <is>
+          <t>I really put my foot in my mouth by asking about his ex-wife.</t>
+        </is>
+      </c>
+      <c r="I1718" t="inlineStr">
+        <is>
+          <t>Every time I talk to her, I seem to put my foot in my mouth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>ENG-20260610-035</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>see the big picture</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>/siː ðə bɪɡ ˈpɪktʃər/</t>
+        </is>
+      </c>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>전체적인 상황을 파악하다</t>
+        </is>
+      </c>
+      <c r="H1719" t="inlineStr">
+        <is>
+          <t>You need to step back and try to see the big picture.</t>
+        </is>
+      </c>
+      <c r="I1719" t="inlineStr">
+        <is>
+          <t>He's too focused on the details; he needs to see the big picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>ENG-20260610-036</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>at your word</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>/æt jɔːr wɜːrd/</t>
+        </is>
+      </c>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>누군가의 말을 액면 그대로 믿다</t>
+        </is>
+      </c>
+      <c r="H1720" t="inlineStr">
+        <is>
+          <t>We should take their promise at their word for now.</t>
+        </is>
+      </c>
+      <c r="I1720" t="inlineStr">
+        <is>
+          <t>I'll take you at your word, so please don't let me down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>ENG-20260610-037</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>go bust</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>/ɡoʊ bʌst/</t>
+        </is>
+      </c>
+      <c r="G1721" t="inlineStr">
+        <is>
+          <t>파산하다</t>
+        </is>
+      </c>
+      <c r="H1721" t="inlineStr">
+        <is>
+          <t>Many small retailers went bust during the recession.</t>
+        </is>
+      </c>
+      <c r="I1721" t="inlineStr">
+        <is>
+          <t>Without a new injection of capital, the startup might go bust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>ENG-20260610-038</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>HBR</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>think big</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>/θɪŋk bɪɡ/</t>
+        </is>
+      </c>
+      <c r="G1722" t="inlineStr">
+        <is>
+          <t>크게 생각하다, 원대한 목표를 갖다</t>
+        </is>
+      </c>
+      <c r="H1722" t="inlineStr">
+        <is>
+          <t>The investors want founders who think big.</t>
+        </is>
+      </c>
+      <c r="I1722" t="inlineStr">
+        <is>
+          <t>It's time to stop worrying about small issues and start thinking big.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>ENG-20260610-039</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>show one's true colors</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>/ʃoʊ wʌnz truː ˈkʌlərz/</t>
+        </is>
+      </c>
+      <c r="G1723" t="inlineStr">
+        <is>
+          <t>본색을 드러내다</t>
+        </is>
+      </c>
+      <c r="H1723" t="inlineStr">
+        <is>
+          <t>He showed his true colors during the negotiation.</t>
+        </is>
+      </c>
+      <c r="I1723" t="inlineStr">
+        <is>
+          <t>After the deal went south, she finally showed her true colors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>ENG-20260610-040</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>corner the market</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>/ˈkɔːrnər ðə ˈmɑːrkɪt/</t>
+        </is>
+      </c>
+      <c r="G1724" t="inlineStr">
+        <is>
+          <t>시장을 독점하다</t>
+        </is>
+      </c>
+      <c r="H1724" t="inlineStr">
+        <is>
+          <t>They managed to corner the market for high-end batteries.</t>
+        </is>
+      </c>
+      <c r="I1724" t="inlineStr">
+        <is>
+          <t>With that patent, they could corner the market within a year.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1724"/>
+  <dimension ref="A1:I1758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81444,6 +81444,1604 @@
         </is>
       </c>
     </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>ENG-20260611-001</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>beat on</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>/biːt ɒn/</t>
+        </is>
+      </c>
+      <c r="G1725" t="inlineStr">
+        <is>
+          <t>예상치(기대치)를 상회하는 실적을 내다</t>
+        </is>
+      </c>
+      <c r="H1725" t="inlineStr">
+        <is>
+          <t>Oracle beats on earnings, but stock drops on plans to raise another $20 billion.</t>
+        </is>
+      </c>
+      <c r="I1725" t="inlineStr">
+        <is>
+          <t>Everyone was worried about the tech sector, but their latest quarterly report really beat on expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>ENG-20260611-002</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>raise capital</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>/reɪz ˈkæp.ɪ.təl/</t>
+        </is>
+      </c>
+      <c r="G1726" t="inlineStr">
+        <is>
+          <t>자금을 조달하다</t>
+        </is>
+      </c>
+      <c r="H1726" t="inlineStr">
+        <is>
+          <t>The company plans to raise more capital for data center projects.</t>
+        </is>
+      </c>
+      <c r="I1726" t="inlineStr">
+        <is>
+          <t>The startup is planning to raise capital through a new round of funding next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>ENG-20260611-003</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>market debut</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>/ˈmɑːr.kɪt deɪ.bjuː/</t>
+        </is>
+      </c>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>주식 시장 상장, 첫 거래 시작</t>
+        </is>
+      </c>
+      <c r="H1727" t="inlineStr">
+        <is>
+          <t>Friday's hotly anticipated SpaceX market debut could prove a defining moment.</t>
+        </is>
+      </c>
+      <c r="I1727" t="inlineStr">
+        <is>
+          <t>Investors are closely watching the tech company's market debut scheduled for this Friday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>ENG-20260611-004</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>bear market</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>/ber ˈmɑːr.kɪt/</t>
+        </is>
+      </c>
+      <c r="G1728" t="inlineStr">
+        <is>
+          <t>하락장, 약세장</t>
+        </is>
+      </c>
+      <c r="H1728" t="inlineStr">
+        <is>
+          <t>Here are the odds of bear markets in each stock index this summer.</t>
+        </is>
+      </c>
+      <c r="I1728" t="inlineStr">
+        <is>
+          <t>Analysts are warning that we might be entering a long-term bear market due to economic uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>ENG-20260611-005</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>downplay the threat</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>/daʊn.pleɪ ðə θret/</t>
+        </is>
+      </c>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>위협을 축소해서 말하다/평가절하하다</t>
+        </is>
+      </c>
+      <c r="H1729" t="inlineStr">
+        <is>
+          <t>The agriculture secretary is downplaying the threat posed by the spreading screwworm.</t>
+        </is>
+      </c>
+      <c r="I1729" t="inlineStr">
+        <is>
+          <t>Don't try to downplay the threat of cyberattacks; we need to invest in better security now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>ENG-20260611-006</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>ailing fortunes</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>/ˈeɪ.lɪŋ ˈfɔːr.tʃuːnz/</t>
+        </is>
+      </c>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>어려움을 겪는 경영 상태</t>
+        </is>
+      </c>
+      <c r="H1730" t="inlineStr">
+        <is>
+          <t>Partnerships can revive the auto industry's ailing fortunes.</t>
+        </is>
+      </c>
+      <c r="I1730" t="inlineStr">
+        <is>
+          <t>The new CEO was hired specifically to turn around the company's ailing fortunes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>ENG-20260611-007</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>sticker price</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>/ˈstɪk.ər praɪs/</t>
+        </is>
+      </c>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>정가(할인 전 명목상 가격)</t>
+        </is>
+      </c>
+      <c r="H1731" t="inlineStr">
+        <is>
+          <t>College sticker prices top $100,000 at 16 schools.</t>
+        </is>
+      </c>
+      <c r="I1731" t="inlineStr">
+        <is>
+          <t>Nobody actually pays the sticker price for that car; you can always negotiate a discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>ENG-20260611-008</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>drive a surge</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>/draɪv ə sɜːrdʒ/</t>
+        </is>
+      </c>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>급증을 유발하다, 견인하다</t>
+        </is>
+      </c>
+      <c r="H1732" t="inlineStr">
+        <is>
+          <t>The expansion of games is set to drive a surge in bets placed.</t>
+        </is>
+      </c>
+      <c r="I1732" t="inlineStr">
+        <is>
+          <t>The new marketing campaign is expected to drive a surge in our website traffic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>ENG-20260611-009</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>veto a deal</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>/ˈviː.təʊ ə diːl/</t>
+        </is>
+      </c>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>거래를 거부하다/막다</t>
+        </is>
+      </c>
+      <c r="H1733" t="inlineStr">
+        <is>
+          <t>I'd have vetoed the foreign sale of the UK tech giant.</t>
+        </is>
+      </c>
+      <c r="I1733" t="inlineStr">
+        <is>
+          <t>The board had the power to veto the merger, and they ultimately decided to stop it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>ENG-20260611-010</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>get into</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>/ɡet ˈɪn.tuː/</t>
+        </is>
+      </c>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>자세히 다루다, 깊게 논의하다</t>
+        </is>
+      </c>
+      <c r="H1734" t="inlineStr">
+        <is>
+          <t>We should probably do it when we could really get into it.</t>
+        </is>
+      </c>
+      <c r="I1734" t="inlineStr">
+        <is>
+          <t>This is a complex issue, so let's get into it properly in our next meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>ENG-20260611-011</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>money in the bank</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>/ˈmʌn.i ɪn ðə bæŋk/</t>
+        </is>
+      </c>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>확실한 것, 믿을 만한 것</t>
+        </is>
+      </c>
+      <c r="H1735" t="inlineStr">
+        <is>
+          <t>Nothing like it in this lifetime, money in the bank.</t>
+        </is>
+      </c>
+      <c r="I1735" t="inlineStr">
+        <is>
+          <t>Don't worry about the promotion; that's money in the bank given your performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>ENG-20260611-012</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>stock up</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>/stɒk ʌp/</t>
+        </is>
+      </c>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>비축하다, 사재기하다</t>
+        </is>
+      </c>
+      <c r="H1736" t="inlineStr">
+        <is>
+          <t>Let’s stock up.</t>
+        </is>
+      </c>
+      <c r="I1736" t="inlineStr">
+        <is>
+          <t>We should stock up on supplies before the storm hits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>ENG-20260611-013</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>be on a break</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>/bi ɒn ə breɪk/</t>
+        </is>
+      </c>
+      <c r="G1737" t="inlineStr">
+        <is>
+          <t>잠시 헤어진 상태이다</t>
+        </is>
+      </c>
+      <c r="H1737" t="inlineStr">
+        <is>
+          <t>We were on a break!</t>
+        </is>
+      </c>
+      <c r="I1737" t="inlineStr">
+        <is>
+          <t>Technically, they were on a break, so dating other people wasn't strictly cheating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>ENG-20260611-014</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>be one to talk</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>/bi wʌn tuː tɔːk/</t>
+        </is>
+      </c>
+      <c r="G1738" t="inlineStr">
+        <is>
+          <t>너나 잘하세요(남 비판할 처지가 아님)</t>
+        </is>
+      </c>
+      <c r="H1738" t="inlineStr">
+        <is>
+          <t>Oh, you-you’re-you’re one to talk.</t>
+        </is>
+      </c>
+      <c r="I1738" t="inlineStr">
+        <is>
+          <t>You're criticizing me for being late? You're one to talk, given you missed the last three meetings!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>ENG-20260611-015</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>Business_Idiom</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>run by</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>/rʌn baɪ/</t>
+        </is>
+      </c>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>의견을 묻다, 검토받다</t>
+        </is>
+      </c>
+      <c r="H1739" t="inlineStr">
+        <is>
+          <t>I need to run this idea by my supervisor before we proceed.</t>
+        </is>
+      </c>
+      <c r="I1739" t="inlineStr">
+        <is>
+          <t>Let me run this proposal by the team and get their feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>ENG-20260611-016</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>Business_Idiom</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>put in place</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>/pʊt ɪn pleɪs/</t>
+        </is>
+      </c>
+      <c r="G1740" t="inlineStr">
+        <is>
+          <t>도입하다, 시행하다</t>
+        </is>
+      </c>
+      <c r="H1740" t="inlineStr">
+        <is>
+          <t>We need to put in place a better security system.</t>
+        </is>
+      </c>
+      <c r="I1740" t="inlineStr">
+        <is>
+          <t>The company has put in place new rules to ensure efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>ENG-20260611-017</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>Business_Idiom</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>hit the mark</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>/hɪt ðə mɑːrk/</t>
+        </is>
+      </c>
+      <c r="G1741" t="inlineStr">
+        <is>
+          <t>목표를 달성하다, 핵심을 찌르다</t>
+        </is>
+      </c>
+      <c r="H1741" t="inlineStr">
+        <is>
+          <t>Their new advertising campaign really hit the mark with consumers.</t>
+        </is>
+      </c>
+      <c r="I1741" t="inlineStr">
+        <is>
+          <t>Your argument hit the mark, and they agreed with you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>ENG-20260611-018</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>get under someone's skin</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>/ɡet ˈʌn.dər ˈsʌm.wʌnz skɪn/</t>
+        </is>
+      </c>
+      <c r="G1742" t="inlineStr">
+        <is>
+          <t>신경 거슬리게 하다</t>
+        </is>
+      </c>
+      <c r="H1742" t="inlineStr">
+        <is>
+          <t>His constant complaining is starting to get under my skin.</t>
+        </is>
+      </c>
+      <c r="I1742" t="inlineStr">
+        <is>
+          <t>Don't let him get under your skin; just ignore his comments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>ENG-20260611-019</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>speak one's mind</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>/spiːk wʌnz maɪnd/</t>
+        </is>
+      </c>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>솔직하게 말하다</t>
+        </is>
+      </c>
+      <c r="H1743" t="inlineStr">
+        <is>
+          <t>She has a reputation for always speaking her mind.</t>
+        </is>
+      </c>
+      <c r="I1743" t="inlineStr">
+        <is>
+          <t>Don't be afraid to speak your mind at the meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>ENG-20260611-020</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>cut through the noise</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>/kʌt θruː ðə nɔɪz/</t>
+        </is>
+      </c>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>불필요한 정보를 제치고 핵심을 파악하다</t>
+        </is>
+      </c>
+      <c r="H1744" t="inlineStr">
+        <is>
+          <t>The Big Apple's sweet shops are expanding.</t>
+        </is>
+      </c>
+      <c r="I1744" t="inlineStr">
+        <is>
+          <t>Our marketing strategy helps cut through the noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>ENG-20260611-021</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>stay the course</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>/steɪ ðə kɔːrs/</t>
+        </is>
+      </c>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>하던 일을 끝까지 고수하다</t>
+        </is>
+      </c>
+      <c r="H1745" t="inlineStr">
+        <is>
+          <t>AI will drive economic growth for years to come</t>
+        </is>
+      </c>
+      <c r="I1745" t="inlineStr">
+        <is>
+          <t>Investors are advised to stay the course despite volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>ENG-20260611-022</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>move the needle</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>/muːv ðə ˈniːdəl/</t>
+        </is>
+      </c>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>눈에 띄는 변화를 만들다</t>
+        </is>
+      </c>
+      <c r="H1746" t="inlineStr">
+        <is>
+          <t>AI will drive economic growth for years to come</t>
+        </is>
+      </c>
+      <c r="I1746" t="inlineStr">
+        <is>
+          <t>This small change won't really move the needle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>ENG-20260611-023</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>have a leg up</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>/hæv ə leɡ ʌp/</t>
+        </is>
+      </c>
+      <c r="G1747" t="inlineStr">
+        <is>
+          <t>유리한 위치에 있다</t>
+        </is>
+      </c>
+      <c r="H1747" t="inlineStr">
+        <is>
+          <t>India's gas purchases from the U.S. have grown steadily</t>
+        </is>
+      </c>
+      <c r="I1747" t="inlineStr">
+        <is>
+          <t>Knowing the language gives him a leg up in the international market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>ENG-20260611-024</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>clear the way</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>/klɪər ðə weɪ/</t>
+        </is>
+      </c>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>길을 트다</t>
+        </is>
+      </c>
+      <c r="H1748" t="inlineStr">
+        <is>
+          <t>government sets out how it would back British technology companies.</t>
+        </is>
+      </c>
+      <c r="I1748" t="inlineStr">
+        <is>
+          <t>The new law clears the way for foreign investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>ENG-20260611-025</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>have a heart of gold</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>/hæv ə hɑːrt ɒv ɡoʊld/</t>
+        </is>
+      </c>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>마음씨가 매우 착하다</t>
+        </is>
+      </c>
+      <c r="H1749" t="inlineStr">
+        <is>
+          <t>Susan will be so pleased.</t>
+        </is>
+      </c>
+      <c r="I1749" t="inlineStr">
+        <is>
+          <t>She has a heart of gold and always helps others.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>ENG-20260611-026</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>beat the clock</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>/biːt ðə klɒk/</t>
+        </is>
+      </c>
+      <c r="G1750" t="inlineStr">
+        <is>
+          <t>시간 내에 처리하다</t>
+        </is>
+      </c>
+      <c r="H1750" t="inlineStr">
+        <is>
+          <t>Friday's hotly anticipated SpaceX market debut</t>
+        </is>
+      </c>
+      <c r="I1750" t="inlineStr">
+        <is>
+          <t>We managed to beat the clock and finish the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>ENG-20260611-027</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>cut it close</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>/kʌt ɪt kloʊz/</t>
+        </is>
+      </c>
+      <c r="G1751" t="inlineStr">
+        <is>
+          <t>아슬아슬하게 하다</t>
+        </is>
+      </c>
+      <c r="H1751" t="inlineStr">
+        <is>
+          <t>Susan’s gonna be home any minute</t>
+        </is>
+      </c>
+      <c r="I1751" t="inlineStr">
+        <is>
+          <t>We are cutting it close with this deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>ENG-20260611-028</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>speak for itself</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>/spiːk fɔːr ɪtˈself/</t>
+        </is>
+      </c>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>따로 설명할 필요가 없다</t>
+        </is>
+      </c>
+      <c r="H1752" t="inlineStr">
+        <is>
+          <t>The record fine comes after around 37.5 million users</t>
+        </is>
+      </c>
+      <c r="I1752" t="inlineStr">
+        <is>
+          <t>The quality of the product speaks for itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>ENG-20260611-029</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>catch up with</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>/kætʃ ʌp wɪð/</t>
+        </is>
+      </c>
+      <c r="G1753" t="inlineStr">
+        <is>
+          <t>밀린 일을 따라잡다</t>
+        </is>
+      </c>
+      <c r="H1753" t="inlineStr">
+        <is>
+          <t>get into it, are you free for dinner tomorrow night?</t>
+        </is>
+      </c>
+      <c r="I1753" t="inlineStr">
+        <is>
+          <t>I need to catch up with my emails after the holiday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>ENG-20260611-030</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>take stock of</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>/teɪk stɒk ɒv/</t>
+        </is>
+      </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>상황을 종합적으로 평가하다</t>
+        </is>
+      </c>
+      <c r="H1754" t="inlineStr">
+        <is>
+          <t>KKR said in its mid-year outlook</t>
+        </is>
+      </c>
+      <c r="I1754" t="inlineStr">
+        <is>
+          <t>We need to take stock of our current resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>ENG-20260611-031</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>get into the swing of things</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>/ɡet ˈɪntuː ðə swɪŋ ɒv θɪŋz/</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>일의 흐름에 익숙해지다</t>
+        </is>
+      </c>
+      <c r="H1755" t="inlineStr">
+        <is>
+          <t>we should probably do it when we could really get into it</t>
+        </is>
+      </c>
+      <c r="I1755" t="inlineStr">
+        <is>
+          <t>It took me a few days to get into the swing of things.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>ENG-20260611-032</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>set in stone</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>/set ɪn stoʊn/</t>
+        </is>
+      </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>바꿀 수 없게 확정된</t>
+        </is>
+      </c>
+      <c r="H1756" t="inlineStr">
+        <is>
+          <t>The final conclusions of the investigation have yet to be published</t>
+        </is>
+      </c>
+      <c r="I1756" t="inlineStr">
+        <is>
+          <t>The schedule isn't set in stone yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>ENG-20260611-033</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>stand on one's own two feet</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>/stænd ɒn wʌnz oʊn tuː fiːt/</t>
+        </is>
+      </c>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>자립하다</t>
+        </is>
+      </c>
+      <c r="H1757" t="inlineStr">
+        <is>
+          <t>the government sets out how it would back British technology companies.</t>
+        </is>
+      </c>
+      <c r="I1757" t="inlineStr">
+        <is>
+          <t>She wants to stand on her own two feet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>ENG-20260611-034</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>be worth one's salt</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>/bi wɜːrθ wʌnz sɔːlt/</t>
+        </is>
+      </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>제값을 하다</t>
+        </is>
+      </c>
+      <c r="H1758" t="inlineStr">
+        <is>
+          <t>referendum on Elon Musk's leadership</t>
+        </is>
+      </c>
+      <c r="I1758" t="inlineStr">
+        <is>
+          <t>Any professional worth their salt would know that.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/01_Database/english_expressions_db.xlsx
+++ b/data/01_Database/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1758"/>
+  <dimension ref="A1:I1805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83042,6 +83042,2215 @@
         </is>
       </c>
     </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>ENG-20260612-001</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>put something off</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>/pʊt ˈsʌm.θɪŋ ɒf/</t>
+        </is>
+      </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>일정을 미루다, 연기하다</t>
+        </is>
+      </c>
+      <c r="H1759" t="inlineStr">
+        <is>
+          <t>Monica suggested that they put the wedding off for a bit until they find a decent place.</t>
+        </is>
+      </c>
+      <c r="I1759" t="inlineStr">
+        <is>
+          <t>We had to put the meeting off because several key stakeholders couldn't make it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>ENG-20260612-002</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>fit right in</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>/fɪt raɪt ɪn/</t>
+        </is>
+      </c>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>주변 분위기나 사람들과 완벽하게 어울리다</t>
+        </is>
+      </c>
+      <c r="H1760" t="inlineStr">
+        <is>
+          <t>The vendor assured Joey that he would fit right in with the tall British hat.</t>
+        </is>
+      </c>
+      <c r="I1760" t="inlineStr">
+        <is>
+          <t>With your outgoing personality, you'll fit right in with the new sales team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>ENG-20260612-003</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>be in the market for</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>/biː ɪn ðə ˈmɑː.kɪt fɔːr/</t>
+        </is>
+      </c>
+      <c r="G1761" t="inlineStr">
+        <is>
+          <t>~을 구매할 의향이나 흥미가 있다</t>
+        </is>
+      </c>
+      <c r="H1761" t="inlineStr">
+        <is>
+          <t>The vendor asked Joey and Chandler what they were in the market for.</t>
+        </is>
+      </c>
+      <c r="I1761" t="inlineStr">
+        <is>
+          <t>If you are in the market for a new electric vehicle, this is the best time to buy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>ENG-20260612-004</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>be out of here</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>/biː aʊt əv hɪər/</t>
+        </is>
+      </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>이 자리를 뜨다 (가버리다)</t>
+        </is>
+      </c>
+      <c r="H1762" t="inlineStr">
+        <is>
+          <t>Chandler got so embarrassed by Joey's hat that he announced, 'I am out of here!'</t>
+        </is>
+      </c>
+      <c r="I1762" t="inlineStr">
+        <is>
+          <t>It's getting late and I have an early meeting tomorrow, so I'm out of here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>ENG-20260612-005</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>take time out of</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>/teɪk taɪm aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>일부러 시간을 쪼개어 내다</t>
+        </is>
+      </c>
+      <c r="H1763" t="inlineStr">
+        <is>
+          <t>Ross was upset that people took time out of their busy lives to fly thousands of miles.</t>
+        </is>
+      </c>
+      <c r="I1763" t="inlineStr">
+        <is>
+          <t>Thank you for taking time out of your busy schedule to meet with us today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>ENG-20260612-006</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>go on the record</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1764" t="inlineStr">
+        <is>
+          <t>/ɡəʊ ɒn ðə rɪˈkɔːd/</t>
+        </is>
+      </c>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>공식적으로 발언을 남기다, 언론에 명확히 밝히다</t>
+        </is>
+      </c>
+      <c r="H1764" t="inlineStr">
+        <is>
+          <t>Phoebe wanted to go on the record that she actually loves Ross before criticizing him.</t>
+        </is>
+      </c>
+      <c r="I1764" t="inlineStr">
+        <is>
+          <t>The CEO refused to go on the record about the potential merger during the interview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>ENG-20260612-007</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>feel like doing something</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>/fiːl laɪk ˈduː.ɪŋ ˈsʌm.θɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>~할 마음이 내키다, ~하고 싶다</t>
+        </is>
+      </c>
+      <c r="H1765" t="inlineStr">
+        <is>
+          <t>Phoebe admitted she just didn't feel like getting up to grab the water and chocolate.</t>
+        </is>
+      </c>
+      <c r="I1765" t="inlineStr">
+        <is>
+          <t>I don't really feel like cooking tonight; shall we order some takeout?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>ENG-20260612-008</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>go out with someone</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>/ɡəʊ aʊt wɪð ˈsʌm.wʌn/</t>
+        </is>
+      </c>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>~와 사귀다, 데이트하다</t>
+        </is>
+      </c>
+      <c r="H1766" t="inlineStr">
+        <is>
+          <t>Rachel recalled that she focused on Ross's flaws when they were going out.</t>
+        </is>
+      </c>
+      <c r="I1766" t="inlineStr">
+        <is>
+          <t>Are you still going out with that guy you met at the conference?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>ENG-20260612-009</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>second in command</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>/ˈsek.ənd ɪn kəˈmɑːnd/</t>
+        </is>
+      </c>
+      <c r="G1767" t="inlineStr">
+        <is>
+          <t>2인자, 부지휘관</t>
+        </is>
+      </c>
+      <c r="H1767" t="inlineStr">
+        <is>
+          <t>Gwynne Shotwell has long served as Elon Musk's second-in-command at SpaceX.</t>
+        </is>
+      </c>
+      <c r="I1767" t="inlineStr">
+        <is>
+          <t>She was appointed as the second-in-command to lead the global expansion project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>ENG-20260612-010</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>dismantle a deal</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>/dɪsˈmæn.təl ə diːl/</t>
+        </is>
+      </c>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>인수합병이나 계약을 해체하여 원점으로 돌리다</t>
+        </is>
+      </c>
+      <c r="H1768" t="inlineStr">
+        <is>
+          <t>Meta has begun dismantling its acquisition deal of the AI startup on Beijing's orders.</t>
+        </is>
+      </c>
+      <c r="I1768" t="inlineStr">
+        <is>
+          <t>Regulatory pressure forced the telecom giants to dismantle their merger deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>ENG-20260612-011</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>comply with</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>/kəmˈplaɪ wɪð/</t>
+        </is>
+      </c>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>규정, 법규, 명령에 따르다 (준수하다)</t>
+        </is>
+      </c>
+      <c r="H1769" t="inlineStr">
+        <is>
+          <t>Tech companies must comply with international privacy standards to expand.</t>
+        </is>
+      </c>
+      <c r="I1769" t="inlineStr">
+        <is>
+          <t>Our startup needs to comply with local financial regulations before launching the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>ENG-20260612-012</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>raise eyebrows</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>/reɪz ˈaɪ.braʊz/</t>
+        </is>
+      </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>사람들의 놀라움이나 우려, 의아함을 자아내다</t>
+        </is>
+      </c>
+      <c r="H1770" t="inlineStr">
+        <is>
+          <t>The rapid growth of the AI model raised eyebrows over its massive energy consumption.</t>
+        </is>
+      </c>
+      <c r="I1770" t="inlineStr">
+        <is>
+          <t>His sudden decision to resign without any notice raised eyebrows in the industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>ENG-20260612-013</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>seek answers</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>/siːk ˈɑːn.səz/</t>
+        </is>
+      </c>
+      <c r="G1771" t="inlineStr">
+        <is>
+          <t>해명이나 답변을 요구하다 (답을 갈구하다)</t>
+        </is>
+      </c>
+      <c r="H1771" t="inlineStr">
+        <is>
+          <t>Senator Warren is seeking answers on changes to index provider waiting periods.</t>
+        </is>
+      </c>
+      <c r="I1771" t="inlineStr">
+        <is>
+          <t>The investors are seeking answers regarding the sudden drop in quarterly profits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>ENG-20260612-014</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>make a debut</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>/meɪk ə deɪˈbjuː/</t>
+        </is>
+      </c>
+      <c r="G1772" t="inlineStr">
+        <is>
+          <t>첫선을 보이다, 데뷔하다 (특히 주식시장 상장)</t>
+        </is>
+      </c>
+      <c r="H1772" t="inlineStr">
+        <is>
+          <t>SpaceX is preparing to make its highly anticipated debut on the stock market.</t>
+        </is>
+      </c>
+      <c r="I1772" t="inlineStr">
+        <is>
+          <t>The newly designed electric SUV is set to make its debut at the auto show next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>ENG-20260612-015</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>split the bill</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>/splɪt ðə bɪl/</t>
+        </is>
+      </c>
+      <c r="G1773" t="inlineStr">
+        <is>
+          <t>식사 비용 등을 각자 똑같이 나누어 내다 (더치페이하다)</t>
+        </is>
+      </c>
+      <c r="H1773" t="inlineStr">
+        <is>
+          <t>Some diners prefer to split the bill equally even if they ordered much cheaper dishes.</t>
+        </is>
+      </c>
+      <c r="I1773" t="inlineStr">
+        <is>
+          <t>Let's just split the bill to make it easier for everyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>ENG-20260612-016</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>speak up</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>/spiːk ʌp/</t>
+        </is>
+      </c>
+      <c r="G1774" t="inlineStr">
+        <is>
+          <t>눈치 보지 않고 소신껏 의견을 밝히다 (크게 말하다)</t>
+        </is>
+      </c>
+      <c r="H1774" t="inlineStr">
+        <is>
+          <t>It can be difficult to speak up when you disagree with your friends about dividing the bill.</t>
+        </is>
+      </c>
+      <c r="I1774" t="inlineStr">
+        <is>
+          <t>If you see something that is unfair, you should speak up and say something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>ENG-20260612-017</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>make a fool of oneself</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>/meɪk ə fuːl ɒv wʌnˈself/</t>
+        </is>
+      </c>
+      <c r="G1775" t="inlineStr">
+        <is>
+          <t>스스로 우스꽝스럽거나 부끄러운 행동을 하다 (망신살이 뻗치다)</t>
+        </is>
+      </c>
+      <c r="H1775" t="inlineStr">
+        <is>
+          <t>Chandler worried that Joey would make a fool of himself in London.</t>
+        </is>
+      </c>
+      <c r="I1775" t="inlineStr">
+        <is>
+          <t>I drank too much at the company party and made a total fool of myself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>ENG-20260612-018</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>pretend otherwise</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>/prɪˈtend ˈʌð.ə.waɪz/</t>
+        </is>
+      </c>
+      <c r="G1776" t="inlineStr">
+        <is>
+          <t>그렇지 않은 척 딴청을 피우다 (내숭을 떨다)</t>
+        </is>
+      </c>
+      <c r="H1776" t="inlineStr">
+        <is>
+          <t>Chandler pretended otherwise as if he didn't know Joey in his ridiculous hat.</t>
+        </is>
+      </c>
+      <c r="I1776" t="inlineStr">
+        <is>
+          <t>Everyone knew the company was failing, but management continued to pretend otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>ENG-20260612-019</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>carry out</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>/ˈkær.i aʊt/</t>
+        </is>
+      </c>
+      <c r="G1777" t="inlineStr">
+        <is>
+          <t>지시나 계획, 조사 등을 차질 없이 수행하다</t>
+        </is>
+      </c>
+      <c r="H1777" t="inlineStr">
+        <is>
+          <t>The regulators carried out a thorough investigation into the startup’s funding.</t>
+        </is>
+      </c>
+      <c r="I1777" t="inlineStr">
+        <is>
+          <t>Our team is fully capable of carrying out this complex system migration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>ENG-20260612-020</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>hold water</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>/həʊld ˈwɔː.tər/</t>
+        </is>
+      </c>
+      <c r="G1778" t="inlineStr">
+        <is>
+          <t>논리나 주장이 타당하다 (앞뒤가 들어맞다)</t>
+        </is>
+      </c>
+      <c r="H1778" t="inlineStr">
+        <is>
+          <t>The attorney's arguments did not hold water in the eyes of the federal judge.</t>
+        </is>
+      </c>
+      <c r="I1778" t="inlineStr">
+        <is>
+          <t>Her excuse about the traffic didn't hold water because she was already late before she left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>ENG-20260612-021</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>take public</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>/teɪk ˈpʌb.lɪk/</t>
+        </is>
+      </c>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>기업을 기업공개(IPO)하여 주식 시장에 상장시키다</t>
+        </is>
+      </c>
+      <c r="H1779" t="inlineStr">
+        <is>
+          <t>Elon Musk is finally taking SpaceX public, raising billions from retail investors.</t>
+        </is>
+      </c>
+      <c r="I1779" t="inlineStr">
+        <is>
+          <t>The founders are planning to take the software startup public within the next eighteen months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>ENG-20260612-022</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>yield results</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>/jiːld rɪˈzʌlts/</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>구체적인 결과나 성과를 낳다</t>
+        </is>
+      </c>
+      <c r="H1780" t="inlineStr">
+        <is>
+          <t>The government's new support program for foster youth has started to yield results.</t>
+        </is>
+      </c>
+      <c r="I1780" t="inlineStr">
+        <is>
+          <t>The design changes we made last month are already beginning to yield positive results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>ENG-20260612-023</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>trip over</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>/trɪp ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G1781" t="inlineStr">
+        <is>
+          <t>~에 발이 걸려 넘어지다</t>
+        </is>
+      </c>
+      <c r="H1781" t="inlineStr">
+        <is>
+          <t>Chandler trips over a box, falls into a flower stand and walks away trying to be cool.</t>
+        </is>
+      </c>
+      <c r="I1781" t="inlineStr">
+        <is>
+          <t>Be careful not to trip over the loose cables on the office floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>ENG-20260612-024</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>zip up</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>/zɪp ʌp/</t>
+        </is>
+      </c>
+      <c r="G1782" t="inlineStr">
+        <is>
+          <t>지퍼를 채우다</t>
+        </is>
+      </c>
+      <c r="H1782" t="inlineStr">
+        <is>
+          <t>Ross was chasing her, trying to zip up his pants.</t>
+        </is>
+      </c>
+      <c r="I1782" t="inlineStr">
+        <is>
+          <t>Zip up your jacket before going out into the freezing wind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>ENG-20260612-025</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>chase after</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>/tʃeɪs ˈæftər/</t>
+        </is>
+      </c>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>~를 뒤쫓다, 추적하다</t>
+        </is>
+      </c>
+      <c r="H1783" t="inlineStr">
+        <is>
+          <t>Ross was chasing after her, trying to zip up his pants.</t>
+        </is>
+      </c>
+      <c r="I1783" t="inlineStr">
+        <is>
+          <t>The firm is chasing after global market share by slashing its prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>ENG-20260612-026</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>stay on</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>/steɪ ɑn/</t>
+        </is>
+      </c>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>남아 있다, 계속 유지되다</t>
+        </is>
+      </c>
+      <c r="H1784" t="inlineStr">
+        <is>
+          <t>Pirro's losses in Fed investigation should stay on the books, judge rules.</t>
+        </is>
+      </c>
+      <c r="I1784" t="inlineStr">
+        <is>
+          <t>Despite the restructuring, she decided to stay on as an advisor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>ENG-20260612-027</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>spin off</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>/spɪn ɔf/</t>
+        </is>
+      </c>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>분사하다, 회사를 분할하여 독립시키다</t>
+        </is>
+      </c>
+      <c r="H1785" t="inlineStr">
+        <is>
+          <t>Speculation grew that SpaceX might spin off its Starlink division before the public launch.</t>
+        </is>
+      </c>
+      <c r="I1785" t="inlineStr">
+        <is>
+          <t>The conglomerate plans to spin off its electric vehicle sector next year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>ENG-20260612-028</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>lock in</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>/lɑːk ɪn/</t>
+        </is>
+      </c>
+      <c r="G1786" t="inlineStr">
+        <is>
+          <t>확정하다, 가격이나 혜택을 고정하다</t>
+        </is>
+      </c>
+      <c r="H1786" t="inlineStr">
+        <is>
+          <t>Waymo launched a subscription model to lock in power users early.</t>
+        </is>
+      </c>
+      <c r="I1786" t="inlineStr">
+        <is>
+          <t>Signing a multi-year lease will lock in a much lower monthly rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>ENG-20260612-029</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>go under</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ˈʌndər/</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr">
+        <is>
+          <t>파산하다, 망하다</t>
+        </is>
+      </c>
+      <c r="H1787" t="inlineStr">
+        <is>
+          <t>Many small suppliers might go under if the economic contraction continues.</t>
+        </is>
+      </c>
+      <c r="I1787" t="inlineStr">
+        <is>
+          <t>Without a cash injection, the startup is likely to go under within weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>ENG-20260612-030</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>play it cool</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>/pleɪ ɪt kuːl/</t>
+        </is>
+      </c>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>침착하게 행동하다, 태연한 척하다</t>
+        </is>
+      </c>
+      <c r="H1788" t="inlineStr">
+        <is>
+          <t>Chandler walks away, trying to play it cool after his embarrassing fall.</t>
+        </is>
+      </c>
+      <c r="I1788" t="inlineStr">
+        <is>
+          <t>Even though I was extremely nervous during the pitch, I tried to play it cool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>ENG-20260612-031</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>now or never</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>/naʊ ɔːr ˈnɛvər/</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>지금 아니면 두 번 다시 없을 기회인</t>
+        </is>
+      </c>
+      <c r="H1789" t="inlineStr">
+        <is>
+          <t>Emily asked, 'So what are you saying? It’s now or never?'</t>
+        </is>
+      </c>
+      <c r="I1789" t="inlineStr">
+        <is>
+          <t>With these low interest rates, it is now or never to buy a house.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>ENG-20260612-032</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>for the record</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>/fɔːr ðə ˈrɛkərd/</t>
+        </is>
+      </c>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>공식적으로, 분명히 말해서</t>
+        </is>
+      </c>
+      <c r="H1790" t="inlineStr">
+        <is>
+          <t>Before we get started, I just want to say for the record that I love Ross.</t>
+        </is>
+      </c>
+      <c r="I1790" t="inlineStr">
+        <is>
+          <t>For the record, I was against this marketing campaign from the very beginning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>ENG-20260612-033</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>be booked solid</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>/biː bʊkt ˈsɑːlɪd/</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>예약이 완전히 차다</t>
+        </is>
+      </c>
+      <c r="H1791" t="inlineStr">
+        <is>
+          <t>Anywhere that’s half-decent would’ve been booked solid months ago.</t>
+        </is>
+      </c>
+      <c r="I1791" t="inlineStr">
+        <is>
+          <t>The conference venue is booked solid for the next three weekends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>ENG-20260612-034</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>sour public sentiment</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>/ˈsaʊər ˈpʌblɪk ˈsɛntɪmənt/</t>
+        </is>
+      </c>
+      <c r="G1792" t="inlineStr">
+        <is>
+          <t>대중적 여론을 악화시키다</t>
+        </is>
+      </c>
+      <c r="H1792" t="inlineStr">
+        <is>
+          <t>Recent safety concerns did not completely sour public sentiment on autonomous driving.</t>
+        </is>
+      </c>
+      <c r="I1792" t="inlineStr">
+        <is>
+          <t>The sudden data leak could severely sour public sentiment toward the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>ENG-20260612-035</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>lift sanctions</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>/lɪft ˈsæŋkʃənz/</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>제재를 해제하다</t>
+        </is>
+      </c>
+      <c r="H1793" t="inlineStr">
+        <is>
+          <t>The proposed deal would reopen the shipping lanes and lift oil sanctions.</t>
+        </is>
+      </c>
+      <c r="I1793" t="inlineStr">
+        <is>
+          <t>The United Nations agreed to lift sanctions once the treaty was verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>ENG-20260612-036</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>live up to the hype</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>/lɪv ʌp tuː ðə haɪp/</t>
+        </is>
+      </c>
+      <c r="G1794" t="inlineStr">
+        <is>
+          <t>기대에 부응하다, 소문만큼 좋다</t>
+        </is>
+      </c>
+      <c r="H1794" t="inlineStr">
+        <is>
+          <t>Investors wonder if SpaceX's IPO will truly live up to the hype.</t>
+        </is>
+      </c>
+      <c r="I1794" t="inlineStr">
+        <is>
+          <t>The newly released smartphone didn't quite live up to the hype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>ENG-20260612-037</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>stay on the books</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>/steɪ ɑn ðə bʊks/</t>
+        </is>
+      </c>
+      <c r="G1795" t="inlineStr">
+        <is>
+          <t>(기록이나 법적 장부상에) 그대로 유지되다</t>
+        </is>
+      </c>
+      <c r="H1795" t="inlineStr">
+        <is>
+          <t>The judge ruled that the losses should stay on the books.</t>
+        </is>
+      </c>
+      <c r="I1795" t="inlineStr">
+        <is>
+          <t>The controversial policy will stay on the books for another fiscal year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>ENG-20260612-038</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>issue a scathing ruling</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>/ˈɪʃuː ə ˈskeɪðɪŋ ˈruːlɪŋ/</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>가혹한 판결을 내리다, 혹평을 담은 판결을 내리다</t>
+        </is>
+      </c>
+      <c r="H1796" t="inlineStr">
+        <is>
+          <t>In a scathing ruling, the district judge denied the request to drop the charges.</t>
+        </is>
+      </c>
+      <c r="I1796" t="inlineStr">
+        <is>
+          <t>The court issued a scathing ruling against the monopoly's pricing strategies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>ENG-20260612-039</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>feel a growing unease</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>/fiːl ə ˈɡroʊɪŋ ʌnˈiːz/</t>
+        </is>
+      </c>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>점점 더 심해지는 불안감을 느끼다</t>
+        </is>
+      </c>
+      <c r="H1797" t="inlineStr">
+        <is>
+          <t>Many consumers feel a growing unease over AI's environmental impact.</t>
+        </is>
+      </c>
+      <c r="I1797" t="inlineStr">
+        <is>
+          <t>Investors feel a growing unease about the company's high debt-to-equity ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>ENG-20260612-040</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>veto a sale</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>/ˈviːtoʊ ə seɪl/</t>
+        </is>
+      </c>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>매각에 대해 거부권을 행사하다</t>
+        </is>
+      </c>
+      <c r="H1798" t="inlineStr">
+        <is>
+          <t>The Secretary of State declared he would have vetoed the foreign sale of the local firm.</t>
+        </is>
+      </c>
+      <c r="I1798" t="inlineStr">
+        <is>
+          <t>The antitrust commission has the authority to veto the sale of the asset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>ENG-20260612-041</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>block a payout</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>/blɑːk ə ˈpeɪaʊt/</t>
+        </is>
+      </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>지급을 중단시키다, 배당금 지급을 차단하다</t>
+        </is>
+      </c>
+      <c r="H1799" t="inlineStr">
+        <is>
+          <t>The government signals it may block the massive payout to foreign owners.</t>
+        </is>
+      </c>
+      <c r="I1799" t="inlineStr">
+        <is>
+          <t>Creditors are attempting to block any payout to the company's executive board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>ENG-20260612-042</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>contract slightly</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>/kənˈtrækt ˈslaɪtli/</t>
+        </is>
+      </c>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>미미하게 수축하다, 소폭 감소하다</t>
+        </is>
+      </c>
+      <c r="H1800" t="inlineStr">
+        <is>
+          <t>The domestic economy contracted slightly in April due to geopolitical events.</t>
+        </is>
+      </c>
+      <c r="I1800" t="inlineStr">
+        <is>
+          <t>The retail market is expected to contract slightly over the winter months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>ENG-20260612-043</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>cope with soaring prices</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>/koʊp wɪð ˈsɔːrɪŋ ˈpraɪsəz/</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>치솟는 물가에 대처하다</t>
+        </is>
+      </c>
+      <c r="H1801" t="inlineStr">
+        <is>
+          <t>Fans find it hard to cope with soaring ticket prices for international events.</t>
+        </is>
+      </c>
+      <c r="I1801" t="inlineStr">
+        <is>
+          <t>Low-income households are struggling to cope with soaring energy prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>ENG-20260612-044</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>run one's hands through</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>/rʌn wʌnz hændz θruː/</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr">
+        <is>
+          <t>손으로 ~을 쓸어 넘기다</t>
+        </is>
+      </c>
+      <c r="H1802" t="inlineStr">
+        <is>
+          <t>Phoebe asked her to imagine running her hands through his hair.</t>
+        </is>
+      </c>
+      <c r="I1802" t="inlineStr">
+        <is>
+          <t>He nervously ran his hands through his hair before presenting the slides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>ENG-20260612-045</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>seal the deal</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>/siːl ðə diːl/</t>
+        </is>
+      </c>
+      <c r="G1803" t="inlineStr">
+        <is>
+          <t>거래를 최종 확정 짓다</t>
+        </is>
+      </c>
+      <c r="H1803" t="inlineStr">
+        <is>
+          <t>They hope to seal the deal on the maritime border reopened by next month.</t>
+        </is>
+      </c>
+      <c r="I1803" t="inlineStr">
+        <is>
+          <t>The sales team flew out to Chicago to seal the deal with our biggest client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>ENG-20260612-046</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>skirt the rules</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>/skɜːrt ðə ruːlz/</t>
+        </is>
+      </c>
+      <c r="G1804" t="inlineStr">
+        <is>
+          <t>교묘하게 법망을 피하다, 규칙을 우회하다</t>
+        </is>
+      </c>
+      <c r="H1804" t="inlineStr">
+        <is>
+          <t>The tech firm attempted to skirt the rules by moving its headquarters overseas.</t>
+        </is>
+      </c>
+      <c r="I1804" t="inlineStr">
+        <is>
+          <t>They managed to skirt the rules on limits by splitting the transactions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>ENG-20260612-047</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>weigh the options</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>/weɪ ðə ˈɑːpʃənz/</t>
+        </is>
+      </c>
+      <c r="G1805" t="inlineStr">
+        <is>
+          <t>선택지들을 신중히 저울질하다</t>
+        </is>
+      </c>
+      <c r="H1805" t="inlineStr">
+        <is>
+          <t>The board decided to weigh the options carefully before refusing the payout.</t>
+        </is>
+      </c>
+      <c r="I1805" t="inlineStr">
+        <is>
+          <t>We need to weigh our options between organic growth and acquisition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
